--- a/templates/BIRDS_data_template.xlsx
+++ b/templates/BIRDS_data_template.xlsx
@@ -1812,320 +1812,464 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:BX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="9" customWidth="1" min="25" max="25"/>
-    <col width="9" customWidth="1" min="26" max="26"/>
-    <col width="9" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="9" customWidth="1" min="31" max="31"/>
-    <col width="9" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="17" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
     <col width="9" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="16" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="9" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
     <col width="9" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="9" customWidth="1" min="41" max="41"/>
+    <col width="9" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
     <col width="9" customWidth="1" min="42" max="42"/>
-    <col width="9" customWidth="1" min="43" max="43"/>
-    <col width="9" customWidth="1" min="44" max="44"/>
-    <col width="9" customWidth="1" min="45" max="45"/>
-    <col width="9" customWidth="1" min="46" max="46"/>
-    <col width="9" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="22" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="15" customWidth="1" min="51" max="51"/>
-    <col width="22" customWidth="1" min="52" max="52"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="16" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="16" customWidth="1" min="48" max="48"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="50" max="50"/>
+    <col width="9" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="52" max="52"/>
+    <col width="16" customWidth="1" min="53" max="53"/>
+    <col width="13" customWidth="1" min="54" max="54"/>
+    <col width="9" customWidth="1" min="55" max="55"/>
+    <col width="9" customWidth="1" min="56" max="56"/>
+    <col width="13" customWidth="1" min="57" max="57"/>
+    <col width="9" customWidth="1" min="58" max="58"/>
+    <col width="13" customWidth="1" min="59" max="59"/>
+    <col width="16" customWidth="1" min="60" max="60"/>
+    <col width="13" customWidth="1" min="61" max="61"/>
+    <col width="9" customWidth="1" min="62" max="62"/>
+    <col width="9" customWidth="1" min="63" max="63"/>
+    <col width="13" customWidth="1" min="64" max="64"/>
+    <col width="9" customWidth="1" min="65" max="65"/>
+    <col width="9" customWidth="1" min="66" max="66"/>
+    <col width="9" customWidth="1" min="67" max="67"/>
+    <col width="9" customWidth="1" min="68" max="68"/>
+    <col width="9" customWidth="1" min="69" max="69"/>
+    <col width="9" customWidth="1" min="70" max="70"/>
+    <col width="9" customWidth="1" min="71" max="71"/>
+    <col width="14" customWidth="1" min="72" max="72"/>
+    <col width="22" customWidth="1" min="73" max="73"/>
+    <col width="14" customWidth="1" min="74" max="74"/>
+    <col width="15" customWidth="1" min="75" max="75"/>
+    <col width="22" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Sample_Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Sample_Label</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Elevation</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Locality</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Dataset_DOI</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Age_Unit</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Age_Method</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Rock_Type</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>TAS_Composition</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Lithology</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Magmatic_Series</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Tectonic_Setting</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Texture</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Mineral_Assemblage</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="X1" s="5" t="inlineStr">
+        <is>
+          <t>Analytical_Method</t>
+        </is>
+      </c>
+      <c r="Y1" s="5" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="Z1" s="5" t="inlineStr">
+        <is>
+          <t>Analysis_Date</t>
+        </is>
+      </c>
+      <c r="AA1" s="5" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="AB1" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AC1" s="6" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="AD1" s="17" t="inlineStr">
         <is>
           <t>87Sr/86Sr</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="AE1" s="17" t="inlineStr">
         <is>
           <t>87Sr/86Sr_2σ</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="AF1" s="17" t="inlineStr">
         <is>
           <t>87Rb/86Sr</t>
         </is>
       </c>
-      <c r="I1" s="17" t="inlineStr">
+      <c r="AG1" s="17" t="inlineStr">
         <is>
           <t>Sr_iso</t>
         </is>
       </c>
-      <c r="J1" s="17" t="inlineStr">
+      <c r="AH1" s="17" t="inlineStr">
         <is>
           <t>Rb_iso</t>
         </is>
       </c>
-      <c r="K1" s="17" t="inlineStr">
+      <c r="AI1" s="17" t="inlineStr">
         <is>
           <t>εSr_initial</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="AJ1" s="18" t="inlineStr">
         <is>
           <t>143Nd/144Nd</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="AK1" s="18" t="inlineStr">
         <is>
           <t>143Nd/144Nd_2σ</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="AL1" s="18" t="inlineStr">
         <is>
           <t>147Sm/144Nd</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="AM1" s="18" t="inlineStr">
         <is>
           <t>Sm_iso</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="AN1" s="18" t="inlineStr">
         <is>
           <t>Nd_iso</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="inlineStr">
+      <c r="AO1" s="18" t="inlineStr">
         <is>
           <t>εNd_initial</t>
         </is>
       </c>
-      <c r="R1" s="18" t="inlineStr">
+      <c r="AP1" s="18" t="inlineStr">
         <is>
           <t>TDM_Nd</t>
         </is>
       </c>
-      <c r="S1" s="19" t="inlineStr">
+      <c r="AQ1" s="19" t="inlineStr">
         <is>
           <t>206Pb/204Pb</t>
         </is>
       </c>
-      <c r="T1" s="19" t="inlineStr">
+      <c r="AR1" s="19" t="inlineStr">
         <is>
           <t>206Pb/204Pb_2σ</t>
         </is>
       </c>
-      <c r="U1" s="19" t="inlineStr">
+      <c r="AS1" s="19" t="inlineStr">
         <is>
           <t>207Pb/204Pb</t>
         </is>
       </c>
-      <c r="V1" s="19" t="inlineStr">
+      <c r="AT1" s="19" t="inlineStr">
         <is>
           <t>207Pb/204Pb_2σ</t>
         </is>
       </c>
-      <c r="W1" s="19" t="inlineStr">
+      <c r="AU1" s="19" t="inlineStr">
         <is>
           <t>208Pb/204Pb</t>
         </is>
       </c>
-      <c r="X1" s="19" t="inlineStr">
+      <c r="AV1" s="19" t="inlineStr">
         <is>
           <t>208Pb/204Pb_2σ</t>
         </is>
       </c>
-      <c r="Y1" s="19" t="inlineStr">
+      <c r="AW1" s="19" t="inlineStr">
         <is>
           <t>Pb_iso</t>
         </is>
       </c>
-      <c r="Z1" s="19" t="inlineStr">
+      <c r="AX1" s="19" t="inlineStr">
         <is>
           <t>U_iso</t>
         </is>
       </c>
-      <c r="AA1" s="19" t="inlineStr">
+      <c r="AY1" s="19" t="inlineStr">
         <is>
           <t>Th_iso</t>
         </is>
       </c>
-      <c r="AB1" s="20" t="inlineStr">
+      <c r="AZ1" s="20" t="inlineStr">
         <is>
           <t>176Hf/177Hf</t>
         </is>
       </c>
-      <c r="AC1" s="20" t="inlineStr">
+      <c r="BA1" s="20" t="inlineStr">
         <is>
           <t>176Hf/177Hf_2σ</t>
         </is>
       </c>
-      <c r="AD1" s="20" t="inlineStr">
+      <c r="BB1" s="20" t="inlineStr">
         <is>
           <t>176Lu/177Hf</t>
         </is>
       </c>
-      <c r="AE1" s="20" t="inlineStr">
+      <c r="BC1" s="20" t="inlineStr">
         <is>
           <t>Hf_iso</t>
         </is>
       </c>
-      <c r="AF1" s="20" t="inlineStr">
+      <c r="BD1" s="20" t="inlineStr">
         <is>
           <t>Lu_iso</t>
         </is>
       </c>
-      <c r="AG1" s="20" t="inlineStr">
+      <c r="BE1" s="20" t="inlineStr">
         <is>
           <t>εHf_initial</t>
         </is>
       </c>
-      <c r="AH1" s="20" t="inlineStr">
+      <c r="BF1" s="20" t="inlineStr">
         <is>
           <t>TDM_Hf</t>
         </is>
       </c>
-      <c r="AI1" s="21" t="inlineStr">
+      <c r="BG1" s="21" t="inlineStr">
         <is>
           <t>187Os/188Os</t>
         </is>
       </c>
-      <c r="AJ1" s="21" t="inlineStr">
+      <c r="BH1" s="21" t="inlineStr">
         <is>
           <t>187Os/188Os_2σ</t>
         </is>
       </c>
-      <c r="AK1" s="21" t="inlineStr">
+      <c r="BI1" s="21" t="inlineStr">
         <is>
           <t>187Re/188Os</t>
         </is>
       </c>
-      <c r="AL1" s="21" t="inlineStr">
+      <c r="BJ1" s="21" t="inlineStr">
         <is>
           <t>Os_iso</t>
         </is>
       </c>
-      <c r="AM1" s="21" t="inlineStr">
+      <c r="BK1" s="21" t="inlineStr">
         <is>
           <t>Re_iso</t>
         </is>
       </c>
-      <c r="AN1" s="21" t="inlineStr">
+      <c r="BL1" s="21" t="inlineStr">
         <is>
           <t>γOs_initial</t>
         </is>
       </c>
-      <c r="AO1" s="22" t="inlineStr">
+      <c r="BM1" s="22" t="inlineStr">
         <is>
           <t>δ18O</t>
         </is>
       </c>
-      <c r="AP1" s="22" t="inlineStr">
+      <c r="BN1" s="22" t="inlineStr">
         <is>
           <t>δ18O_2σ</t>
         </is>
       </c>
-      <c r="AQ1" s="22" t="inlineStr">
+      <c r="BO1" s="22" t="inlineStr">
         <is>
           <t>δD</t>
         </is>
       </c>
-      <c r="AR1" s="22" t="inlineStr">
+      <c r="BP1" s="22" t="inlineStr">
         <is>
           <t>δD_2σ</t>
         </is>
       </c>
-      <c r="AS1" s="22" t="inlineStr">
+      <c r="BQ1" s="22" t="inlineStr">
         <is>
           <t>δ13C</t>
         </is>
       </c>
-      <c r="AT1" s="22" t="inlineStr">
+      <c r="BR1" s="22" t="inlineStr">
         <is>
           <t>δ13C_2σ</t>
         </is>
       </c>
-      <c r="AU1" s="22" t="inlineStr">
+      <c r="BS1" s="22" t="inlineStr">
         <is>
           <t>δ11B</t>
         </is>
       </c>
-      <c r="AV1" s="23" t="inlineStr">
+      <c r="BT1" s="23" t="inlineStr">
         <is>
           <t>Iso_Method</t>
         </is>
       </c>
-      <c r="AW1" s="23" t="inlineStr">
+      <c r="BU1" s="23" t="inlineStr">
         <is>
           <t>Iso_Laboratory</t>
         </is>
       </c>
-      <c r="AX1" s="23" t="inlineStr">
+      <c r="BV1" s="23" t="inlineStr">
         <is>
           <t>Iso_Date</t>
         </is>
       </c>
-      <c r="AY1" s="23" t="inlineStr">
+      <c r="BW1" s="23" t="inlineStr">
         <is>
           <t>Iso_Analyst</t>
         </is>
       </c>
-      <c r="AZ1" s="23" t="inlineStr">
+      <c r="BX1" s="23" t="inlineStr">
         <is>
           <t>Iso_Notes</t>
         </is>
@@ -2135,139 +2279,175 @@
       <c r="A2" s="9" t="inlineStr"/>
       <c r="B2" s="9" t="inlineStr"/>
       <c r="C2" s="9" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr"/>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr"/>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="11" t="inlineStr"/>
+      <c r="L2" s="11" t="inlineStr"/>
+      <c r="M2" s="12" t="inlineStr"/>
+      <c r="N2" s="12" t="inlineStr"/>
+      <c r="O2" s="12" t="inlineStr"/>
+      <c r="P2" s="12" t="inlineStr"/>
+      <c r="Q2" s="12" t="inlineStr"/>
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr"/>
+      <c r="T2" s="12" t="inlineStr"/>
+      <c r="U2" s="12" t="inlineStr"/>
+      <c r="V2" s="12" t="inlineStr"/>
+      <c r="W2" s="12" t="inlineStr"/>
+      <c r="X2" s="13" t="inlineStr"/>
+      <c r="Y2" s="13" t="inlineStr"/>
+      <c r="Z2" s="13" t="inlineStr"/>
+      <c r="AA2" s="13" t="inlineStr"/>
+      <c r="AB2" s="13" t="inlineStr"/>
+      <c r="AC2" s="14" t="inlineStr">
+        <is>
+          <t>wt%</t>
+        </is>
+      </c>
+      <c r="AD2" s="24" t="inlineStr"/>
+      <c r="AE2" s="24" t="inlineStr"/>
+      <c r="AF2" s="24" t="inlineStr"/>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="AI2" s="24" t="inlineStr"/>
+      <c r="AJ2" s="25" t="inlineStr"/>
+      <c r="AK2" s="25" t="inlineStr"/>
+      <c r="AL2" s="25" t="inlineStr"/>
+      <c r="AM2" s="25" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="AN2" s="25" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="AO2" s="25" t="inlineStr"/>
+      <c r="AP2" s="25" t="inlineStr">
         <is>
           <t>Ma</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr"/>
-      <c r="F2" s="24" t="inlineStr"/>
-      <c r="G2" s="24" t="inlineStr"/>
-      <c r="H2" s="24" t="inlineStr"/>
-      <c r="I2" s="24" t="inlineStr">
+      <c r="AQ2" s="26" t="inlineStr"/>
+      <c r="AR2" s="26" t="inlineStr"/>
+      <c r="AS2" s="26" t="inlineStr"/>
+      <c r="AT2" s="26" t="inlineStr"/>
+      <c r="AU2" s="26" t="inlineStr"/>
+      <c r="AV2" s="26" t="inlineStr"/>
+      <c r="AW2" s="26" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="J2" s="24" t="inlineStr">
+      <c r="AX2" s="26" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="K2" s="24" t="inlineStr"/>
-      <c r="L2" s="25" t="inlineStr"/>
-      <c r="M2" s="25" t="inlineStr"/>
-      <c r="N2" s="25" t="inlineStr"/>
-      <c r="O2" s="25" t="inlineStr">
+      <c r="AY2" s="26" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="P2" s="25" t="inlineStr">
+      <c r="AZ2" s="27" t="inlineStr"/>
+      <c r="BA2" s="27" t="inlineStr"/>
+      <c r="BB2" s="27" t="inlineStr"/>
+      <c r="BC2" s="27" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="Q2" s="25" t="inlineStr"/>
-      <c r="R2" s="25" t="inlineStr">
+      <c r="BD2" s="27" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="BE2" s="27" t="inlineStr"/>
+      <c r="BF2" s="27" t="inlineStr">
         <is>
           <t>Ma</t>
         </is>
       </c>
-      <c r="S2" s="26" t="inlineStr"/>
-      <c r="T2" s="26" t="inlineStr"/>
-      <c r="U2" s="26" t="inlineStr"/>
-      <c r="V2" s="26" t="inlineStr"/>
-      <c r="W2" s="26" t="inlineStr"/>
-      <c r="X2" s="26" t="inlineStr"/>
-      <c r="Y2" s="26" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="Z2" s="26" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AA2" s="26" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AB2" s="27" t="inlineStr"/>
-      <c r="AC2" s="27" t="inlineStr"/>
-      <c r="AD2" s="27" t="inlineStr"/>
-      <c r="AE2" s="27" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AF2" s="27" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AG2" s="27" t="inlineStr"/>
-      <c r="AH2" s="27" t="inlineStr">
-        <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="AI2" s="28" t="inlineStr"/>
-      <c r="AJ2" s="28" t="inlineStr"/>
-      <c r="AK2" s="28" t="inlineStr"/>
-      <c r="AL2" s="28" t="inlineStr">
+      <c r="BG2" s="28" t="inlineStr"/>
+      <c r="BH2" s="28" t="inlineStr"/>
+      <c r="BI2" s="28" t="inlineStr"/>
+      <c r="BJ2" s="28" t="inlineStr">
         <is>
           <t>ppb</t>
         </is>
       </c>
-      <c r="AM2" s="28" t="inlineStr">
+      <c r="BK2" s="28" t="inlineStr">
         <is>
           <t>ppb</t>
         </is>
       </c>
-      <c r="AN2" s="28" t="inlineStr"/>
-      <c r="AO2" s="29" t="inlineStr">
+      <c r="BL2" s="28" t="inlineStr"/>
+      <c r="BM2" s="29" t="inlineStr">
         <is>
           <t>‰ VSMOW</t>
         </is>
       </c>
-      <c r="AP2" s="29" t="inlineStr">
+      <c r="BN2" s="29" t="inlineStr">
         <is>
           <t>‰</t>
         </is>
       </c>
-      <c r="AQ2" s="29" t="inlineStr">
+      <c r="BO2" s="29" t="inlineStr">
         <is>
           <t>‰ VSMOW</t>
         </is>
       </c>
-      <c r="AR2" s="29" t="inlineStr">
+      <c r="BP2" s="29" t="inlineStr">
         <is>
           <t>‰</t>
         </is>
       </c>
-      <c r="AS2" s="29" t="inlineStr">
+      <c r="BQ2" s="29" t="inlineStr">
         <is>
           <t>‰ VPDB</t>
         </is>
       </c>
-      <c r="AT2" s="29" t="inlineStr">
+      <c r="BR2" s="29" t="inlineStr">
         <is>
           <t>‰</t>
         </is>
       </c>
-      <c r="AU2" s="29" t="inlineStr">
+      <c r="BS2" s="29" t="inlineStr">
         <is>
           <t>‰</t>
         </is>
       </c>
-      <c r="AV2" s="30" t="inlineStr"/>
-      <c r="AW2" s="30" t="inlineStr"/>
-      <c r="AX2" s="30" t="inlineStr"/>
-      <c r="AY2" s="30" t="inlineStr"/>
-      <c r="AZ2" s="30" t="inlineStr"/>
+      <c r="BT2" s="30" t="inlineStr"/>
+      <c r="BU2" s="30" t="inlineStr"/>
+      <c r="BV2" s="30" t="inlineStr"/>
+      <c r="BW2" s="30" t="inlineStr"/>
+      <c r="BX2" s="30" t="inlineStr"/>
     </row>
     <row r="3" ht="16" customHeight="1"/>
     <row r="4" ht="16" customHeight="1"/>
@@ -2470,8 +2650,26 @@
     <row r="201" ht="16" customHeight="1"/>
     <row r="202" ht="16" customHeight="1"/>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="AV3:AV1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: TIMS, MC-ICP-MS, Solution MC-ICP-MS, LA-MC-ICP-MS, SIMS, SHRIMP, N-TIMS (Os), Laser fluorination (δ¹⁸O), EA-IRMS (δ¹³C, δD), CRDS, Mixed" type="list">
+  <dataValidations count="7">
+    <dataValidation sqref="N3:N1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ma, ka, Ga, yr" type="list">
+      <formula1>"Ma,ka,Ga,yr"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P3:P1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein" type="list">
+      <formula1>"Volcanic,Plutonic,Sub-volcanic,Pyroclastic,Vein"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q3:Q1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite" type="list">
+      <formula1>"Picro-basalt,Basalt,Basaltic andesite,Andesite,Dacite,Rhyolite,Trachy-basalt,Basaltic trachy-andesite,Trachy-andesite,Trachyte,Trachy-dacite,Tephrite,Phono-tephrite,Tephri-phonolite,Phonolite,Foidite,Gabbro,Diorite,Granodiorite,Granite,Monzogabbro,Monzodiorite,Monzonite,Syenite,Foid-syenite,Foidolite"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S3:S1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic" type="list">
+      <formula1>"Tholeiitic,Calc-alkaline,High-K calc-alkaline,Shoshonitic,Alkaline,Ultra-alkaline,Boninitic"</formula1>
+    </dataValidation>
+    <dataValidation sqref="W3:W1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed" type="list">
+      <formula1>"Fresh,Slightly altered,Moderately altered,Strongly altered,Metamorphosed"</formula1>
+    </dataValidation>
+    <dataValidation sqref="X3:X1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed" type="list">
+      <formula1>"XRF,ICP-OES,ICP-MS,Solution ICP-MS,LA-ICP-MS,EMP / EPMA,INAA,Wet chemistry,Mixed"</formula1>
+    </dataValidation>
+    <dataValidation sqref="BT3:BT1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: TIMS, MC-ICP-MS, Solution MC-ICP-MS, LA-MC-ICP-MS, SIMS, SHRIMP, N-TIMS (Os), Laser fluorination (δ¹⁸O), EA-IRMS (δ¹³C, δD), CRDS, Mixed" type="list">
       <formula1>"TIMS,MC-ICP-MS,Solution MC-ICP-MS,LA-MC-ICP-MS,SIMS,SHRIMP,N-TIMS (Os),Laser fluorination (δ¹⁸O),EA-IRMS (δ¹³C, δD),CRDS,Mixed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3138,10 +3336,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="43.8" customHeight="1">
+    <row r="12" ht="94.19999999999999" customHeight="1">
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>6. The 'Isotopes' sheet is independent of the 'Data' sheet. Use it to record Sr-Nd-Pb-Hf-Os-Re-O-C-H-B isotopic analyses. Rows are joined back to the bulk composition through the 'Sample_Name' column, which MUST match exactly between the two sheets (case-sensitive).</t>
+          <t>6. The 'Isotopes' sheet is independent of the 'Data' sheet. Use it to record Sr-Nd-Pb-Hf-Os-Re-O-C-H-B isotopic analyses. Its first columns — identification, location, source, geology and analysis — are the same, in the same order, as the columns before the major elements in 'Data', so a sample's context can be copied across in one block; then comes SiO2, to read the isotopes against silica. Rows are joined back to the bulk composition through the 'Sample_Name' column, which MUST match exactly between the two sheets (case-sensitive). Where both sheets fill a column, 'Data' is kept.</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6305,24 +6503,24 @@
       </c>
       <c r="C91" s="40" t="inlineStr">
         <is>
-          <t>Sample_Name</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="D91" s="41" t="inlineStr">
         <is>
-          <t>Iso-ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E91" s="38" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>VOL-2024-018</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H91" s="42" t="inlineStr">
         <is>
-          <t>Must exactly match the Sample_Name in the Data sheet — this is how B.I.R.D.S joins the isotopic analysis back to the bulk composition.</t>
+          <t>Sequential row number (1, 2, 3 ...).</t>
         </is>
       </c>
     </row>
@@ -6337,24 +6535,24 @@
       </c>
       <c r="C92" s="40" t="inlineStr">
         <is>
-          <t>Sample_Label</t>
+          <t>Sample_Name</t>
         </is>
       </c>
       <c r="D92" s="41" t="inlineStr">
         <is>
-          <t>Iso-ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E92" s="38" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Mt. Pico flow 18</t>
+          <t>VOL-2024-018</t>
         </is>
       </c>
       <c r="H92" s="42" t="inlineStr">
         <is>
-          <t>Optional friendly label used in plots.  Leave blank to inherit the value from the Data sheet (B.I.R.D.S fills this column automatically at import time).</t>
+          <t>Unique short identifier for the sample (lab code / field number). Avoid spaces.</t>
         </is>
       </c>
     </row>
@@ -6369,24 +6567,24 @@
       </c>
       <c r="C93" s="40" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Sample_Label</t>
         </is>
       </c>
       <c r="D93" s="41" t="inlineStr">
         <is>
-          <t>Iso-ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E93" s="38" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lower flow</t>
+          <t>Mt. Pico flow 18</t>
         </is>
       </c>
       <c r="H93" s="42" t="inlineStr">
         <is>
-          <t>Optional group for colouring / legend.  Like Sample_Label, B.I.R.D.S inherits this from the Data sheet at import time so you only need to set it once.</t>
+          <t>Free-text label used in plots if you don't want to expose the lab code.</t>
         </is>
       </c>
     </row>
@@ -6401,28 +6599,24 @@
       </c>
       <c r="C94" s="40" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="D94" s="41" t="inlineStr">
         <is>
-          <t>Iso-ID</t>
-        </is>
-      </c>
-      <c r="E94" s="38" t="inlineStr">
-        <is>
-          <t>Ma</t>
-        </is>
-      </c>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E94" s="38" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>Lower flow</t>
         </is>
       </c>
       <c r="H94" s="42" t="inlineStr">
         <is>
-          <t>Crystallisation / eruption age used for the initial-ratio correction. Leave empty to plot only present-day ratios.</t>
+          <t>Optional user-defined group used by the legend (e.g. unit, eruption, age cluster).</t>
         </is>
       </c>
     </row>
@@ -6437,24 +6631,28 @@
       </c>
       <c r="C95" s="40" t="inlineStr">
         <is>
-          <t>Age_Method</t>
-        </is>
-      </c>
-      <c r="D95" s="41" t="inlineStr">
-        <is>
-          <t>Iso-ID</t>
-        </is>
-      </c>
-      <c r="E95" s="38" t="inlineStr"/>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="D95" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E95" s="38" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ar-Ar</t>
+          <t>-19.4250</t>
         </is>
       </c>
       <c r="H95" s="42" t="inlineStr">
         <is>
-          <t>Method used to obtain the age (K-Ar, Ar-Ar, U-Pb, stratigraphic …).</t>
+          <t>Decimal degrees (WGS-84). Negative = south.</t>
         </is>
       </c>
     </row>
@@ -6469,24 +6667,28 @@
       </c>
       <c r="C96" s="40" t="inlineStr">
         <is>
-          <t>87Sr/86Sr</t>
-        </is>
-      </c>
-      <c r="D96" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
-        </is>
-      </c>
-      <c r="E96" s="38" t="inlineStr"/>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="D96" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E96" s="38" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0.70428</t>
+          <t>-69.1583</t>
         </is>
       </c>
       <c r="H96" s="42" t="inlineStr">
         <is>
-          <t>Measured ⁸⁷Sr/⁸⁶Sr ratio. Typical values: 0.7022 (DM), 0.7045 (CHUR), 0.708-0.710 (arc/upper crust).</t>
+          <t>Decimal degrees (WGS-84). Negative = west.</t>
         </is>
       </c>
     </row>
@@ -6501,24 +6703,28 @@
       </c>
       <c r="C97" s="40" t="inlineStr">
         <is>
-          <t>87Sr/86Sr_2σ</t>
-        </is>
-      </c>
-      <c r="D97" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
-        </is>
-      </c>
-      <c r="E97" s="38" t="inlineStr"/>
+          <t>Elevation</t>
+        </is>
+      </c>
+      <c r="D97" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E97" s="38" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0.00001</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="H97" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty of ⁸⁷Sr/⁸⁶Sr (absolute, e.g. 0.000010).</t>
+          <t>Sampling elevation above sea level.</t>
         </is>
       </c>
     </row>
@@ -6533,24 +6739,24 @@
       </c>
       <c r="C98" s="40" t="inlineStr">
         <is>
-          <t>87Rb/86Sr</t>
-        </is>
-      </c>
-      <c r="D98" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D98" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
         </is>
       </c>
       <c r="E98" s="38" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="H98" s="42" t="inlineStr">
         <is>
-          <t>Parent ratio used for the initial-Sr correction. If missing, B.I.R.D.S derives it from Rb / Sr concentrations (~2.894 × Rb/Sr).</t>
+          <t>Country where the sample was collected.</t>
         </is>
       </c>
     </row>
@@ -6565,28 +6771,24 @@
       </c>
       <c r="C99" s="40" t="inlineStr">
         <is>
-          <t>Sr_iso</t>
-        </is>
-      </c>
-      <c r="D99" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
-        </is>
-      </c>
-      <c r="E99" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D99" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E99" s="38" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="H99" s="42" t="inlineStr">
         <is>
-          <t>Sr concentration measured on the same aliquot as the isotope ratio (optional; only needed if it differs from the bulk value in the Data sheet).</t>
+          <t>State / province / volcanic field.</t>
         </is>
       </c>
     </row>
@@ -6601,28 +6803,24 @@
       </c>
       <c r="C100" s="40" t="inlineStr">
         <is>
-          <t>Rb_iso</t>
-        </is>
-      </c>
-      <c r="D100" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
-        </is>
-      </c>
-      <c r="E100" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>Locality</t>
+        </is>
+      </c>
+      <c r="D100" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E100" s="38" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Taapaca Volcanic Complex</t>
         </is>
       </c>
       <c r="H100" s="42" t="inlineStr">
         <is>
-          <t>Rb concentration measured on the same aliquot.</t>
+          <t>Specific outcrop or feature.</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6835,24 @@
       </c>
       <c r="C101" s="40" t="inlineStr">
         <is>
-          <t>εSr_initial</t>
-        </is>
-      </c>
-      <c r="D101" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D101" s="44" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="E101" s="38" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Aguirre et al. (2022) Lithos 408</t>
+        </is>
+      </c>
       <c r="H101" s="42" t="inlineStr">
         <is>
-          <t>Computed by B.I.R.D.S — leave empty.</t>
+          <t>Bibliographic reference for the analysis (author year, or DOI).</t>
         </is>
       </c>
     </row>
@@ -6665,24 +6867,24 @@
       </c>
       <c r="C102" s="40" t="inlineStr">
         <is>
-          <t>143Nd/144Nd</t>
-        </is>
-      </c>
-      <c r="D102" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
+          <t>Dataset_DOI</t>
+        </is>
+      </c>
+      <c r="D102" s="44" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="E102" s="38" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>0.51285</t>
+          <t>10.5281/zenodo.1234567</t>
         </is>
       </c>
       <c r="H102" s="42" t="inlineStr">
         <is>
-          <t>Measured ¹⁴³Nd/¹⁴⁴Nd ratio. CHUR = 0.512638 (Bouvier et al. 2008).</t>
+          <t>DOI of the original dataset, if published separately.</t>
         </is>
       </c>
     </row>
@@ -6697,24 +6899,24 @@
       </c>
       <c r="C103" s="40" t="inlineStr">
         <is>
-          <t>143Nd/144Nd_2σ</t>
-        </is>
-      </c>
-      <c r="D103" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="D103" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E103" s="38" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0.000007</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="H103" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Numeric age (matched with AGE_UNIT). Leave empty if unknown.</t>
         </is>
       </c>
     </row>
@@ -6729,24 +6931,28 @@
       </c>
       <c r="C104" s="40" t="inlineStr">
         <is>
-          <t>147Sm/144Nd</t>
-        </is>
-      </c>
-      <c r="D104" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
+          <t>Age_Unit</t>
+        </is>
+      </c>
+      <c r="D104" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E104" s="38" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ma, ka, Ga, yr</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="H104" s="42" t="inlineStr">
         <is>
-          <t>Parent ratio for the initial-Nd correction. If missing, derived from Sm/Nd (~0.6043 × Sm/Nd).</t>
+          <t>Unit of the AGE column. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
@@ -6761,28 +6967,24 @@
       </c>
       <c r="C105" s="40" t="inlineStr">
         <is>
-          <t>Sm_iso</t>
-        </is>
-      </c>
-      <c r="D105" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
-        </is>
-      </c>
-      <c r="E105" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>Age_Method</t>
+        </is>
+      </c>
+      <c r="D105" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
+        </is>
+      </c>
+      <c r="E105" s="38" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>Ar-Ar</t>
         </is>
       </c>
       <c r="H105" s="42" t="inlineStr">
         <is>
-          <t>Sm concentration in the isotope aliquot.</t>
+          <t>Dating method (K-Ar, Ar-Ar, U-Pb, fission track, stratigraphic).</t>
         </is>
       </c>
     </row>
@@ -6797,28 +6999,28 @@
       </c>
       <c r="C106" s="40" t="inlineStr">
         <is>
-          <t>Nd_iso</t>
-        </is>
-      </c>
-      <c r="D106" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
-        </is>
-      </c>
-      <c r="E106" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
+          <t>Rock_Type</t>
+        </is>
+      </c>
+      <c r="D106" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
+        </is>
+      </c>
+      <c r="E106" s="38" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>Volcanic</t>
         </is>
       </c>
       <c r="H106" s="42" t="inlineStr">
         <is>
-          <t>Nd concentration in the isotope aliquot.</t>
+          <t>Volcanic vs. plutonic family — used by B.I.R.D.S to pick the right TAS panel and tectonic catalogue.</t>
         </is>
       </c>
     </row>
@@ -6833,20 +7035,28 @@
       </c>
       <c r="C107" s="40" t="inlineStr">
         <is>
-          <t>εNd_initial</t>
-        </is>
-      </c>
-      <c r="D107" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
+          <t>TAS_Composition</t>
+        </is>
+      </c>
+      <c r="D107" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E107" s="38" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Basaltic andesite</t>
+        </is>
+      </c>
       <c r="H107" s="42" t="inlineStr">
         <is>
-          <t>Computed by B.I.R.D.S.</t>
+          <t>Rock name from the TAS diagram (Le Bas et al. 1986). Leave empty to let B.I.R.D.S compute it from SiO2 / alkalis.</t>
         </is>
       </c>
     </row>
@@ -6861,28 +7071,24 @@
       </c>
       <c r="C108" s="40" t="inlineStr">
         <is>
-          <t>TDM_Nd</t>
-        </is>
-      </c>
-      <c r="D108" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
-        </is>
-      </c>
-      <c r="E108" s="38" t="inlineStr">
-        <is>
-          <t>Ma</t>
-        </is>
-      </c>
+          <t>Lithology</t>
+        </is>
+      </c>
+      <c r="D108" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
+        </is>
+      </c>
+      <c r="E108" s="38" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>Olivine basalt</t>
         </is>
       </c>
       <c r="H108" s="42" t="inlineStr">
         <is>
-          <t>Nd depleted-mantle model age (DePaolo 1981 or Goldstein 1984 — pick your convention).</t>
+          <t>Petrographic name beyond TAS (e.g. olivine basalt, biotite-amphibole granodiorite).</t>
         </is>
       </c>
     </row>
@@ -6897,24 +7103,28 @@
       </c>
       <c r="C109" s="40" t="inlineStr">
         <is>
-          <t>206Pb/204Pb</t>
-        </is>
-      </c>
-      <c r="D109" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
+          <t>Magmatic_Series</t>
+        </is>
+      </c>
+      <c r="D109" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E109" s="38" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>Calc-alkaline</t>
         </is>
       </c>
       <c r="H109" s="42" t="inlineStr">
         <is>
-          <t>Measured ²⁰⁶Pb/²⁰⁴Pb ratio.</t>
+          <t>Magma series. Optional — also derivable from K2O-SiO2 and AFM diagrams.</t>
         </is>
       </c>
     </row>
@@ -6929,24 +7139,24 @@
       </c>
       <c r="C110" s="40" t="inlineStr">
         <is>
-          <t>206Pb/204Pb_2σ</t>
-        </is>
-      </c>
-      <c r="D110" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
+          <t>Tectonic_Setting</t>
+        </is>
+      </c>
+      <c r="D110" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E110" s="38" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Continental arc</t>
         </is>
       </c>
       <c r="H110" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Inferred tectonic environment (MORB, OIB, IAB, CRB, OP, ...).</t>
         </is>
       </c>
     </row>
@@ -6961,24 +7171,24 @@
       </c>
       <c r="C111" s="40" t="inlineStr">
         <is>
-          <t>207Pb/204Pb</t>
-        </is>
-      </c>
-      <c r="D111" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
+          <t>Texture</t>
+        </is>
+      </c>
+      <c r="D111" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E111" s="38" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>Porphyritic</t>
         </is>
       </c>
       <c r="H111" s="42" t="inlineStr">
         <is>
-          <t>Measured ²⁰⁷Pb/²⁰⁴Pb ratio.</t>
+          <t>Porphyritic / aphanitic / glassy / phaneritic / vesicular / etc.</t>
         </is>
       </c>
     </row>
@@ -6993,24 +7203,24 @@
       </c>
       <c r="C112" s="40" t="inlineStr">
         <is>
-          <t>207Pb/204Pb_2σ</t>
-        </is>
-      </c>
-      <c r="D112" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
+          <t>Mineral_Assemblage</t>
+        </is>
+      </c>
+      <c r="D112" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E112" s="38" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Pl + Cpx + Ol ± Opx</t>
         </is>
       </c>
       <c r="H112" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Main minerals (plagioclase, olivine, clinopyroxene, amphibole, biotite, K-feldspar, quartz ...).</t>
         </is>
       </c>
     </row>
@@ -7025,24 +7235,28 @@
       </c>
       <c r="C113" s="40" t="inlineStr">
         <is>
-          <t>208Pb/204Pb</t>
-        </is>
-      </c>
-      <c r="D113" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="D113" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E113" s="38" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="H113" s="42" t="inlineStr">
         <is>
-          <t>Measured ²⁰⁸Pb/²⁰⁴Pb ratio.</t>
+          <t>Visual / petrographic alteration grade.</t>
         </is>
       </c>
     </row>
@@ -7057,24 +7271,28 @@
       </c>
       <c r="C114" s="40" t="inlineStr">
         <is>
-          <t>208Pb/204Pb_2σ</t>
-        </is>
-      </c>
-      <c r="D114" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
+          <t>Analytical_Method</t>
+        </is>
+      </c>
+      <c r="D114" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="E114" s="38" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>XRF + ICP-MS</t>
         </is>
       </c>
       <c r="H114" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Technique used for the bulk analysis.</t>
         </is>
       </c>
     </row>
@@ -7089,28 +7307,24 @@
       </c>
       <c r="C115" s="40" t="inlineStr">
         <is>
-          <t>Pb_iso</t>
-        </is>
-      </c>
-      <c r="D115" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
-        </is>
-      </c>
-      <c r="E115" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="D115" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="E115" s="38" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>ALS Geochemistry (Vancouver)</t>
         </is>
       </c>
       <c r="H115" s="42" t="inlineStr">
         <is>
-          <t>Pb concentration in the isotope aliquot.</t>
+          <t>Lab where the analysis was carried out.</t>
         </is>
       </c>
     </row>
@@ -7125,28 +7339,24 @@
       </c>
       <c r="C116" s="40" t="inlineStr">
         <is>
-          <t>U_iso</t>
-        </is>
-      </c>
-      <c r="D116" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
-        </is>
-      </c>
-      <c r="E116" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>Analysis_Date</t>
+        </is>
+      </c>
+      <c r="D116" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="E116" s="38" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="H116" s="42" t="inlineStr">
         <is>
-          <t>U concentration (for μ = ²³⁸U/²⁰⁴Pb).</t>
+          <t>Year / date of the analysis (YYYY or YYYY-MM-DD).</t>
         </is>
       </c>
     </row>
@@ -7161,28 +7371,24 @@
       </c>
       <c r="C117" s="40" t="inlineStr">
         <is>
-          <t>Th_iso</t>
-        </is>
-      </c>
-      <c r="D117" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
-        </is>
-      </c>
-      <c r="E117" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D117" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="E117" s="38" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>JLF</t>
         </is>
       </c>
       <c r="H117" s="42" t="inlineStr">
         <is>
-          <t>Th concentration (for κ = ²³²Th/²³⁸U).</t>
+          <t>Analyst initials or name (optional).</t>
         </is>
       </c>
     </row>
@@ -7197,24 +7403,20 @@
       </c>
       <c r="C118" s="40" t="inlineStr">
         <is>
-          <t>176Hf/177Hf</t>
-        </is>
-      </c>
-      <c r="D118" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D118" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="E118" s="38" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>0.28298</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" s="42" t="inlineStr">
         <is>
-          <t>Measured ¹⁷⁶Hf/¹⁷⁷Hf ratio. CHUR = 0.282785 (Bouvier et al. 2008).</t>
+          <t>Free-text notes (anomalies, dilutions, repeated analyses, etc.).</t>
         </is>
       </c>
     </row>
@@ -7229,24 +7431,28 @@
       </c>
       <c r="C119" s="40" t="inlineStr">
         <is>
-          <t>176Hf/177Hf_2σ</t>
-        </is>
-      </c>
-      <c r="D119" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
-        </is>
-      </c>
-      <c r="E119" s="38" t="inlineStr"/>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="D119" s="47" t="inlineStr">
+        <is>
+          <t>Majors</t>
+        </is>
+      </c>
+      <c r="E119" s="38" t="inlineStr">
+        <is>
+          <t>wt%</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="H119" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Silica of the sample, for reading the isotope ratios against differentiation on this sheet (e.g. ⁸⁷Sr/⁸⁶Sr vs SiO2 for crustal assimilation). Copy it from the Data sheet, or give the value measured on the isotope aliquot. At import the Data sheet's SiO2 is kept for the bulk analysis.</t>
         </is>
       </c>
     </row>
@@ -7261,24 +7467,24 @@
       </c>
       <c r="C120" s="40" t="inlineStr">
         <is>
-          <t>176Lu/177Hf</t>
-        </is>
-      </c>
-      <c r="D120" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
+          <t>87Sr/86Sr</t>
+        </is>
+      </c>
+      <c r="D120" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
         </is>
       </c>
       <c r="E120" s="38" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.70428</t>
         </is>
       </c>
       <c r="H120" s="42" t="inlineStr">
         <is>
-          <t>Parent ratio for initial-Hf correction.</t>
+          <t>Measured ⁸⁷Sr/⁸⁶Sr ratio. Typical values: 0.7022 (DM), 0.7045 (CHUR), 0.708-0.710 (arc/upper crust).</t>
         </is>
       </c>
     </row>
@@ -7293,28 +7499,24 @@
       </c>
       <c r="C121" s="40" t="inlineStr">
         <is>
-          <t>Hf_iso</t>
-        </is>
-      </c>
-      <c r="D121" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
-        </is>
-      </c>
-      <c r="E121" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>87Sr/86Sr_2σ</t>
+        </is>
+      </c>
+      <c r="D121" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
+        </is>
+      </c>
+      <c r="E121" s="38" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.00001</t>
         </is>
       </c>
       <c r="H121" s="42" t="inlineStr">
         <is>
-          <t>Hf concentration in the isotope aliquot.</t>
+          <t>Analytical 2σ uncertainty of ⁸⁷Sr/⁸⁶Sr (absolute, e.g. 0.000010).</t>
         </is>
       </c>
     </row>
@@ -7329,28 +7531,24 @@
       </c>
       <c r="C122" s="40" t="inlineStr">
         <is>
-          <t>Lu_iso</t>
-        </is>
-      </c>
-      <c r="D122" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
-        </is>
-      </c>
-      <c r="E122" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>87Rb/86Sr</t>
+        </is>
+      </c>
+      <c r="D122" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
+        </is>
+      </c>
+      <c r="E122" s="38" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="H122" s="42" t="inlineStr">
         <is>
-          <t>Lu concentration in the isotope aliquot.</t>
+          <t>Parent ratio used for the initial-Sr correction. If missing, B.I.R.D.S derives it from Rb / Sr concentrations (~2.894 × Rb/Sr).</t>
         </is>
       </c>
     </row>
@@ -7365,20 +7563,28 @@
       </c>
       <c r="C123" s="40" t="inlineStr">
         <is>
-          <t>εHf_initial</t>
-        </is>
-      </c>
-      <c r="D123" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
-        </is>
-      </c>
-      <c r="E123" s="38" t="inlineStr"/>
+          <t>Sr_iso</t>
+        </is>
+      </c>
+      <c r="D123" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
+        </is>
+      </c>
+      <c r="E123" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
       <c r="H123" s="42" t="inlineStr">
         <is>
-          <t>Computed by B.I.R.D.S.</t>
+          <t>Sr concentration measured on the same aliquot as the isotope ratio (optional; only needed if it differs from the bulk value in the Data sheet).</t>
         </is>
       </c>
     </row>
@@ -7393,28 +7599,28 @@
       </c>
       <c r="C124" s="40" t="inlineStr">
         <is>
-          <t>TDM_Hf</t>
-        </is>
-      </c>
-      <c r="D124" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
+          <t>Rb_iso</t>
+        </is>
+      </c>
+      <c r="D124" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
         </is>
       </c>
       <c r="E124" s="38" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>ppm</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H124" s="42" t="inlineStr">
         <is>
-          <t>Hf depleted-mantle model age.</t>
+          <t>Rb concentration measured on the same aliquot.</t>
         </is>
       </c>
     </row>
@@ -7429,24 +7635,20 @@
       </c>
       <c r="C125" s="40" t="inlineStr">
         <is>
-          <t>187Os/188Os</t>
-        </is>
-      </c>
-      <c r="D125" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
+          <t>εSr_initial</t>
+        </is>
+      </c>
+      <c r="D125" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
         </is>
       </c>
       <c r="E125" s="38" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>0.131</t>
-        </is>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" s="42" t="inlineStr">
         <is>
-          <t>Measured ¹⁸⁷Os/¹⁸⁸Os ratio. Primitive Upper Mantle (PUM) ≈ 0.1296.</t>
+          <t>Computed by B.I.R.D.S — leave empty.</t>
         </is>
       </c>
     </row>
@@ -7461,24 +7663,24 @@
       </c>
       <c r="C126" s="40" t="inlineStr">
         <is>
-          <t>187Os/188Os_2σ</t>
-        </is>
-      </c>
-      <c r="D126" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
+          <t>143Nd/144Nd</t>
+        </is>
+      </c>
+      <c r="D126" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
         </is>
       </c>
       <c r="E126" s="38" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.51285</t>
         </is>
       </c>
       <c r="H126" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Measured ¹⁴³Nd/¹⁴⁴Nd ratio. CHUR = 0.512638 (Bouvier et al. 2008).</t>
         </is>
       </c>
     </row>
@@ -7493,24 +7695,24 @@
       </c>
       <c r="C127" s="40" t="inlineStr">
         <is>
-          <t>187Re/188Os</t>
-        </is>
-      </c>
-      <c r="D127" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
+          <t>143Nd/144Nd_2σ</t>
+        </is>
+      </c>
+      <c r="D127" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
         </is>
       </c>
       <c r="E127" s="38" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.000007</t>
         </is>
       </c>
       <c r="H127" s="42" t="inlineStr">
         <is>
-          <t>Parent ratio for the initial-Os correction.</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -7525,28 +7727,24 @@
       </c>
       <c r="C128" s="40" t="inlineStr">
         <is>
-          <t>Os_iso</t>
-        </is>
-      </c>
-      <c r="D128" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
-        </is>
-      </c>
-      <c r="E128" s="38" t="inlineStr">
-        <is>
-          <t>ppb</t>
-        </is>
-      </c>
+          <t>147Sm/144Nd</t>
+        </is>
+      </c>
+      <c r="D128" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
+        </is>
+      </c>
+      <c r="E128" s="38" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="H128" s="42" t="inlineStr">
         <is>
-          <t>Os concentration (parts per billion).</t>
+          <t>Parent ratio for the initial-Nd correction. If missing, derived from Sm/Nd (~0.6043 × Sm/Nd).</t>
         </is>
       </c>
     </row>
@@ -7561,28 +7759,28 @@
       </c>
       <c r="C129" s="40" t="inlineStr">
         <is>
-          <t>Re_iso</t>
-        </is>
-      </c>
-      <c r="D129" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
+          <t>Sm_iso</t>
+        </is>
+      </c>
+      <c r="D129" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
         </is>
       </c>
       <c r="E129" s="38" t="inlineStr">
         <is>
-          <t>ppb</t>
+          <t>ppm</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="H129" s="42" t="inlineStr">
         <is>
-          <t>Re concentration.</t>
+          <t>Sm concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
@@ -7597,20 +7795,28 @@
       </c>
       <c r="C130" s="40" t="inlineStr">
         <is>
-          <t>γOs_initial</t>
-        </is>
-      </c>
-      <c r="D130" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
-        </is>
-      </c>
-      <c r="E130" s="38" t="inlineStr"/>
+          <t>Nd_iso</t>
+        </is>
+      </c>
+      <c r="D130" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
+        </is>
+      </c>
+      <c r="E130" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
       <c r="H130" s="42" t="inlineStr">
         <is>
-          <t>Computed by B.I.R.D.S.</t>
+          <t>Nd concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
@@ -7625,28 +7831,20 @@
       </c>
       <c r="C131" s="40" t="inlineStr">
         <is>
-          <t>δ18O</t>
-        </is>
-      </c>
-      <c r="D131" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
-        </is>
-      </c>
-      <c r="E131" s="38" t="inlineStr">
-        <is>
-          <t>‰ VSMOW</t>
-        </is>
-      </c>
+          <t>εNd_initial</t>
+        </is>
+      </c>
+      <c r="D131" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
+        </is>
+      </c>
+      <c r="E131" s="38" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>+5.8</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" s="42" t="inlineStr">
         <is>
-          <t>Oxygen isotope composition relative to VSMOW. Mantle olivine ≈ +5.2 ‰; crustal sediments commonly &gt;+10 ‰.</t>
+          <t>Computed by B.I.R.D.S.</t>
         </is>
       </c>
     </row>
@@ -7661,28 +7859,28 @@
       </c>
       <c r="C132" s="40" t="inlineStr">
         <is>
-          <t>δ18O_2σ</t>
-        </is>
-      </c>
-      <c r="D132" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
+          <t>TDM_Nd</t>
+        </is>
+      </c>
+      <c r="D132" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
         </is>
       </c>
       <c r="E132" s="38" t="inlineStr">
         <is>
-          <t>‰</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H132" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Nd depleted-mantle model age (DePaolo 1981 or Goldstein 1984 — pick your convention).</t>
         </is>
       </c>
     </row>
@@ -7697,28 +7895,24 @@
       </c>
       <c r="C133" s="40" t="inlineStr">
         <is>
-          <t>δD</t>
-        </is>
-      </c>
-      <c r="D133" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
-        </is>
-      </c>
-      <c r="E133" s="38" t="inlineStr">
-        <is>
-          <t>‰ VSMOW</t>
-        </is>
-      </c>
+          <t>206Pb/204Pb</t>
+        </is>
+      </c>
+      <c r="D133" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E133" s="38" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-65</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="H133" s="42" t="inlineStr">
         <is>
-          <t>Hydrogen isotope composition relative to VSMOW. Useful for hydrous phases (amphibole, biotite, melt inclusions).</t>
+          <t>Measured ²⁰⁶Pb/²⁰⁴Pb ratio.</t>
         </is>
       </c>
     </row>
@@ -7733,23 +7927,19 @@
       </c>
       <c r="C134" s="40" t="inlineStr">
         <is>
-          <t>δD_2σ</t>
-        </is>
-      </c>
-      <c r="D134" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
-        </is>
-      </c>
-      <c r="E134" s="38" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
+          <t>206Pb/204Pb_2σ</t>
+        </is>
+      </c>
+      <c r="D134" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E134" s="38" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H134" s="42" t="inlineStr">
@@ -7769,28 +7959,24 @@
       </c>
       <c r="C135" s="40" t="inlineStr">
         <is>
-          <t>δ13C</t>
-        </is>
-      </c>
-      <c r="D135" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
-        </is>
-      </c>
-      <c r="E135" s="38" t="inlineStr">
-        <is>
-          <t>‰ VPDB</t>
-        </is>
-      </c>
+          <t>207Pb/204Pb</t>
+        </is>
+      </c>
+      <c r="D135" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E135" s="38" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="H135" s="42" t="inlineStr">
         <is>
-          <t>Carbon isotope composition relative to VPDB. Mantle CO₂ ≈ -5 ‰; biogenic carbon strongly negative.</t>
+          <t>Measured ²⁰⁷Pb/²⁰⁴Pb ratio.</t>
         </is>
       </c>
     </row>
@@ -7805,23 +7991,19 @@
       </c>
       <c r="C136" s="40" t="inlineStr">
         <is>
-          <t>δ13C_2σ</t>
-        </is>
-      </c>
-      <c r="D136" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
-        </is>
-      </c>
-      <c r="E136" s="38" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
+          <t>207Pb/204Pb_2σ</t>
+        </is>
+      </c>
+      <c r="D136" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E136" s="38" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H136" s="42" t="inlineStr">
@@ -7841,28 +8023,24 @@
       </c>
       <c r="C137" s="40" t="inlineStr">
         <is>
-          <t>δ11B</t>
-        </is>
-      </c>
-      <c r="D137" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
-        </is>
-      </c>
-      <c r="E137" s="38" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
+          <t>208Pb/204Pb</t>
+        </is>
+      </c>
+      <c r="D137" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E137" s="38" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="H137" s="42" t="inlineStr">
         <is>
-          <t>Boron isotope composition. Slab fluids / sediments show very contrasted signatures.</t>
+          <t>Measured ²⁰⁸Pb/²⁰⁴Pb ratio.</t>
         </is>
       </c>
     </row>
@@ -7877,28 +8055,24 @@
       </c>
       <c r="C138" s="40" t="inlineStr">
         <is>
-          <t>Iso_Method</t>
-        </is>
-      </c>
-      <c r="D138" s="56" t="inlineStr">
-        <is>
-          <t>Iso-Meta</t>
+          <t>208Pb/204Pb_2σ</t>
+        </is>
+      </c>
+      <c r="D138" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
         </is>
       </c>
       <c r="E138" s="38" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>TIMS, MC-ICP-MS, Solution MC-ICP-MS, LA-MC-ICP-MS, SIMS, SHRIMP, N-TIMS (Os), Laser fluorination (δ¹⁸O), EA-IRMS (δ¹³C, δD), CRDS, Mixed</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>MC-ICP-MS</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H138" s="42" t="inlineStr">
         <is>
-          <t>Mass-spectrometry technique used for the isotope ratio(s).</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -7913,24 +8087,28 @@
       </c>
       <c r="C139" s="40" t="inlineStr">
         <is>
-          <t>Iso_Laboratory</t>
-        </is>
-      </c>
-      <c r="D139" s="56" t="inlineStr">
-        <is>
-          <t>Iso-Meta</t>
-        </is>
-      </c>
-      <c r="E139" s="38" t="inlineStr"/>
+          <t>Pb_iso</t>
+        </is>
+      </c>
+      <c r="D139" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E139" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>MIT Radiogenic Isotope Lab</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="H139" s="42" t="inlineStr">
         <is>
-          <t>Lab where the isotope analysis was carried out.</t>
+          <t>Pb concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
@@ -7945,24 +8123,28 @@
       </c>
       <c r="C140" s="40" t="inlineStr">
         <is>
-          <t>Iso_Date</t>
-        </is>
-      </c>
-      <c r="D140" s="56" t="inlineStr">
-        <is>
-          <t>Iso-Meta</t>
-        </is>
-      </c>
-      <c r="E140" s="38" t="inlineStr"/>
+          <t>U_iso</t>
+        </is>
+      </c>
+      <c r="D140" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E140" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="H140" s="42" t="inlineStr">
         <is>
-          <t>Year or full date of the isotope analysis.</t>
+          <t>U concentration (for μ = ²³⁸U/²⁰⁴Pb).</t>
         </is>
       </c>
     </row>
@@ -7977,24 +8159,28 @@
       </c>
       <c r="C141" s="40" t="inlineStr">
         <is>
-          <t>Iso_Analyst</t>
-        </is>
-      </c>
-      <c r="D141" s="56" t="inlineStr">
-        <is>
-          <t>Iso-Meta</t>
-        </is>
-      </c>
-      <c r="E141" s="38" t="inlineStr"/>
+          <t>Th_iso</t>
+        </is>
+      </c>
+      <c r="D141" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E141" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>MLG</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="H141" s="42" t="inlineStr">
         <is>
-          <t>Analyst initials or name.</t>
+          <t>Th concentration (for κ = ²³²Th/²³⁸U).</t>
         </is>
       </c>
     </row>
@@ -8009,20 +8195,24 @@
       </c>
       <c r="C142" s="40" t="inlineStr">
         <is>
-          <t>Iso_Notes</t>
-        </is>
-      </c>
-      <c r="D142" s="56" t="inlineStr">
-        <is>
-          <t>Iso-Meta</t>
+          <t>176Hf/177Hf</t>
+        </is>
+      </c>
+      <c r="D142" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
         </is>
       </c>
       <c r="E142" s="38" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>0.28298</t>
+        </is>
+      </c>
       <c r="H142" s="42" t="inlineStr">
         <is>
-          <t>Free-text notes (column chemistry, spike, repeated measurements, blanks).</t>
+          <t>Measured ¹⁷⁶Hf/¹⁷⁷Hf ratio. CHUR = 0.282785 (Bouvier et al. 2008).</t>
         </is>
       </c>
     </row>
@@ -8032,29 +8222,29 @@
       </c>
       <c r="B143" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C143" s="40" t="inlineStr">
         <is>
-          <t>Sample_Name</t>
-        </is>
-      </c>
-      <c r="D143" s="41" t="inlineStr">
-        <is>
-          <t>Petro-ID</t>
+          <t>176Hf/177Hf_2σ</t>
+        </is>
+      </c>
+      <c r="D143" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
         </is>
       </c>
       <c r="E143" s="38" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>VOL-2024-018</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="H143" s="42" t="inlineStr">
         <is>
-          <t>Must exactly match the Sample_Name in the Data sheet — this is the key B.I.R.D.S uses to join the modal mineralogy back to the bulk composition.</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8064,29 +8254,29 @@
       </c>
       <c r="B144" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C144" s="40" t="inlineStr">
         <is>
-          <t>Sample_Label</t>
-        </is>
-      </c>
-      <c r="D144" s="41" t="inlineStr">
-        <is>
-          <t>Petro-ID</t>
+          <t>176Lu/177Hf</t>
+        </is>
+      </c>
+      <c r="D144" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
         </is>
       </c>
       <c r="E144" s="38" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Mt. Pico flow 18</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="H144" s="42" t="inlineStr">
         <is>
-          <t>Optional friendly label used in plots.  Leave blank to inherit the value from the Data sheet — B.I.R.D.S fills this column automatically at import time.</t>
+          <t>Parent ratio for initial-Hf correction.</t>
         </is>
       </c>
     </row>
@@ -8096,29 +8286,33 @@
       </c>
       <c r="B145" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C145" s="40" t="inlineStr">
         <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="D145" s="41" t="inlineStr">
-        <is>
-          <t>Petro-ID</t>
-        </is>
-      </c>
-      <c r="E145" s="38" t="inlineStr"/>
+          <t>Hf_iso</t>
+        </is>
+      </c>
+      <c r="D145" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
+        </is>
+      </c>
+      <c r="E145" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lower flow</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="H145" s="42" t="inlineStr">
         <is>
-          <t>Optional group used for colouring / legend.  Inherited from the Data sheet at import time if left blank.</t>
+          <t>Hf concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
@@ -8128,33 +8322,33 @@
       </c>
       <c r="B146" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C146" s="40" t="inlineStr">
         <is>
-          <t>Texture</t>
-        </is>
-      </c>
-      <c r="D146" s="41" t="inlineStr">
-        <is>
-          <t>Petro-ID</t>
-        </is>
-      </c>
-      <c r="E146" s="38" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Phaneritic, Aphanitic, Porphyritic, Glassy, Vesicular, Pyroclastic, Cumulate, Cataclastic, Foliated / Gneissic, Mixed</t>
-        </is>
-      </c>
+          <t>Lu_iso</t>
+        </is>
+      </c>
+      <c r="D146" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
+        </is>
+      </c>
+      <c r="E146" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porphyritic</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="H146" s="42" t="inlineStr">
         <is>
-          <t>Overall rock fabric. Pick from the dropdown.</t>
+          <t>Lu concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
@@ -8164,33 +8358,25 @@
       </c>
       <c r="B147" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C147" s="40" t="inlineStr">
         <is>
-          <t>Q_mode</t>
-        </is>
-      </c>
-      <c r="D147" s="57" t="inlineStr">
-        <is>
-          <t>Petro-QAPF</t>
-        </is>
-      </c>
-      <c r="E147" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>εHf_initial</t>
+        </is>
+      </c>
+      <c r="D147" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
+        </is>
+      </c>
+      <c r="E147" s="38" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" s="42" t="inlineStr">
         <is>
-          <t>Modal Quartz (Q apex of the Streckeisen QAPF diagram).</t>
+          <t>Computed by B.I.R.D.S.</t>
         </is>
       </c>
     </row>
@@ -8200,33 +8386,33 @@
       </c>
       <c r="B148" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C148" s="40" t="inlineStr">
         <is>
-          <t>A_mode</t>
-        </is>
-      </c>
-      <c r="D148" s="57" t="inlineStr">
-        <is>
-          <t>Petro-QAPF</t>
+          <t>TDM_Hf</t>
+        </is>
+      </c>
+      <c r="D148" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
         </is>
       </c>
       <c r="E148" s="38" t="inlineStr">
         <is>
-          <t>vol %</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H148" s="42" t="inlineStr">
         <is>
-          <t>Modal Alkali feldspar (K-feldspar + albite component); A apex of QAPF.</t>
+          <t>Hf depleted-mantle model age.</t>
         </is>
       </c>
     </row>
@@ -8236,33 +8422,29 @@
       </c>
       <c r="B149" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C149" s="40" t="inlineStr">
         <is>
-          <t>P_mode</t>
-        </is>
-      </c>
-      <c r="D149" s="57" t="inlineStr">
-        <is>
-          <t>Petro-QAPF</t>
-        </is>
-      </c>
-      <c r="E149" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>187Os/188Os</t>
+        </is>
+      </c>
+      <c r="D149" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
+        </is>
+      </c>
+      <c r="E149" s="38" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="H149" s="42" t="inlineStr">
         <is>
-          <t>Modal Plagioclase (calcic / sodic plagioclase); P apex of QAPF.</t>
+          <t>Measured ¹⁸⁷Os/¹⁸⁸Os ratio. Primitive Upper Mantle (PUM) ≈ 0.1296.</t>
         </is>
       </c>
     </row>
@@ -8272,33 +8454,29 @@
       </c>
       <c r="B150" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C150" s="40" t="inlineStr">
         <is>
-          <t>F_mode</t>
-        </is>
-      </c>
-      <c r="D150" s="57" t="inlineStr">
-        <is>
-          <t>Petro-QAPF</t>
-        </is>
-      </c>
-      <c r="E150" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>187Os/188Os_2σ</t>
+        </is>
+      </c>
+      <c r="D150" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
+        </is>
+      </c>
+      <c r="E150" s="38" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="H150" s="42" t="inlineStr">
         <is>
-          <t>Modal Feldspathoid (nepheline, leucite, sodalite …); F apex of the bottom QAPF triangle. Mutually exclusive with Q (one rock can't have both).</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8308,33 +8486,29 @@
       </c>
       <c r="B151" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C151" s="40" t="inlineStr">
         <is>
-          <t>Ol_mode</t>
-        </is>
-      </c>
-      <c r="D151" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
-        </is>
-      </c>
-      <c r="E151" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>187Re/188Os</t>
+        </is>
+      </c>
+      <c r="D151" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
+        </is>
+      </c>
+      <c r="E151" s="38" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="H151" s="42" t="inlineStr">
         <is>
-          <t>Modal Olivine. Ol apex of the gabbro Pl-Px-Ol ternary and of the ultramafic Ol-Opx-Cpx ternary.</t>
+          <t>Parent ratio for the initial-Os correction.</t>
         </is>
       </c>
     </row>
@@ -8344,33 +8518,33 @@
       </c>
       <c r="B152" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C152" s="40" t="inlineStr">
         <is>
-          <t>Opx_mode</t>
-        </is>
-      </c>
-      <c r="D152" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
+          <t>Os_iso</t>
+        </is>
+      </c>
+      <c r="D152" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
         </is>
       </c>
       <c r="E152" s="38" t="inlineStr">
         <is>
-          <t>vol %</t>
+          <t>ppb</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="H152" s="42" t="inlineStr">
         <is>
-          <t>Modal Orthopyroxene (enstatite to ferrosilite). Opx apex of the ultramafic ternary.</t>
+          <t>Os concentration (parts per billion).</t>
         </is>
       </c>
     </row>
@@ -8380,33 +8554,33 @@
       </c>
       <c r="B153" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C153" s="40" t="inlineStr">
         <is>
-          <t>Cpx_mode</t>
-        </is>
-      </c>
-      <c r="D153" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
+          <t>Re_iso</t>
+        </is>
+      </c>
+      <c r="D153" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
         </is>
       </c>
       <c r="E153" s="38" t="inlineStr">
         <is>
-          <t>vol %</t>
+          <t>ppb</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="H153" s="42" t="inlineStr">
         <is>
-          <t>Modal Clinopyroxene (diopside, augite, pigeonite …). Cpx apex of the ultramafic ternary.</t>
+          <t>Re concentration.</t>
         </is>
       </c>
     </row>
@@ -8416,29 +8590,25 @@
       </c>
       <c r="B154" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C154" s="40" t="inlineStr">
         <is>
-          <t>Px_mode</t>
-        </is>
-      </c>
-      <c r="D154" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
-        </is>
-      </c>
-      <c r="E154" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>γOs_initial</t>
+        </is>
+      </c>
+      <c r="D154" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
+        </is>
+      </c>
+      <c r="E154" s="38" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
       <c r="H154" s="42" t="inlineStr">
         <is>
-          <t>Total pyroxene (Opx + Cpx) used by the gabbro Pl-Px-Ol ternary. Leave empty — B.I.R.D.S sums Opx + Cpx automatically if you fill those.</t>
+          <t>Computed by B.I.R.D.S.</t>
         </is>
       </c>
     </row>
@@ -8448,33 +8618,33 @@
       </c>
       <c r="B155" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C155" s="40" t="inlineStr">
         <is>
-          <t>Amph_mode</t>
-        </is>
-      </c>
-      <c r="D155" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
+          <t>δ18O</t>
+        </is>
+      </c>
+      <c r="D155" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
         </is>
       </c>
       <c r="E155" s="38" t="inlineStr">
         <is>
-          <t>vol %</t>
+          <t>‰ VSMOW</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>+5.8</t>
         </is>
       </c>
       <c r="H155" s="42" t="inlineStr">
         <is>
-          <t>Modal Amphibole (hornblende, actinolite, kaersutite …). Not used by QAPF but reported for completeness.</t>
+          <t>Oxygen isotope composition relative to VSMOW. Mantle olivine ≈ +5.2 ‰; crustal sediments commonly &gt;+10 ‰.</t>
         </is>
       </c>
     </row>
@@ -8484,33 +8654,33 @@
       </c>
       <c r="B156" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C156" s="40" t="inlineStr">
         <is>
-          <t>Bt_mode</t>
-        </is>
-      </c>
-      <c r="D156" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
+          <t>δ18O_2σ</t>
+        </is>
+      </c>
+      <c r="D156" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
         </is>
       </c>
       <c r="E156" s="38" t="inlineStr">
         <is>
-          <t>vol %</t>
+          <t>‰</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H156" s="42" t="inlineStr">
         <is>
-          <t>Modal Biotite.</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8520,33 +8690,33 @@
       </c>
       <c r="B157" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C157" s="40" t="inlineStr">
         <is>
-          <t>Ms_mode</t>
-        </is>
-      </c>
-      <c r="D157" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
+          <t>δD</t>
+        </is>
+      </c>
+      <c r="D157" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
         </is>
       </c>
       <c r="E157" s="38" t="inlineStr">
         <is>
-          <t>vol %</t>
+          <t>‰ VSMOW</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-65</t>
         </is>
       </c>
       <c r="H157" s="42" t="inlineStr">
         <is>
-          <t>Modal Muscovite.</t>
+          <t>Hydrogen isotope composition relative to VSMOW. Useful for hydrous phases (amphibole, biotite, melt inclusions).</t>
         </is>
       </c>
     </row>
@@ -8556,33 +8726,33 @@
       </c>
       <c r="B158" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C158" s="40" t="inlineStr">
         <is>
-          <t>Opaque_mode</t>
-        </is>
-      </c>
-      <c r="D158" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
+          <t>δD_2σ</t>
+        </is>
+      </c>
+      <c r="D158" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
         </is>
       </c>
       <c r="E158" s="38" t="inlineStr">
         <is>
-          <t>vol %</t>
+          <t>‰</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H158" s="42" t="inlineStr">
         <is>
-          <t>Modal Fe-Ti oxides (magnetite, ilmenite, hematite, chromite).</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8592,33 +8762,33 @@
       </c>
       <c r="B159" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C159" s="40" t="inlineStr">
         <is>
-          <t>Apatite_mode</t>
-        </is>
-      </c>
-      <c r="D159" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
+          <t>δ13C</t>
+        </is>
+      </c>
+      <c r="D159" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
         </is>
       </c>
       <c r="E159" s="38" t="inlineStr">
         <is>
-          <t>vol %</t>
+          <t>‰ VPDB</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="H159" s="42" t="inlineStr">
         <is>
-          <t>Modal Apatite.</t>
+          <t>Carbon isotope composition relative to VPDB. Mantle CO₂ ≈ -5 ‰; biogenic carbon strongly negative.</t>
         </is>
       </c>
     </row>
@@ -8628,22 +8798,22 @@
       </c>
       <c r="B160" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C160" s="40" t="inlineStr">
         <is>
-          <t>Zircon_mode</t>
-        </is>
-      </c>
-      <c r="D160" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
+          <t>δ13C_2σ</t>
+        </is>
+      </c>
+      <c r="D160" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
         </is>
       </c>
       <c r="E160" s="38" t="inlineStr">
         <is>
-          <t>vol %</t>
+          <t>‰</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -8654,7 +8824,7 @@
       </c>
       <c r="H160" s="42" t="inlineStr">
         <is>
-          <t>Modal Zircon.</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8664,33 +8834,33 @@
       </c>
       <c r="B161" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C161" s="40" t="inlineStr">
         <is>
-          <t>Titanite_mode</t>
-        </is>
-      </c>
-      <c r="D161" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
+          <t>δ11B</t>
+        </is>
+      </c>
+      <c r="D161" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
         </is>
       </c>
       <c r="E161" s="38" t="inlineStr">
         <is>
-          <t>vol %</t>
+          <t>‰</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>+3.5</t>
         </is>
       </c>
       <c r="H161" s="42" t="inlineStr">
         <is>
-          <t>Modal Titanite / sphene.</t>
+          <t>Boron isotope composition. Slab fluids / sediments show very contrasted signatures.</t>
         </is>
       </c>
     </row>
@@ -8700,33 +8870,33 @@
       </c>
       <c r="B162" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C162" s="40" t="inlineStr">
         <is>
-          <t>Carbonate_mode</t>
-        </is>
-      </c>
-      <c r="D162" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
-        </is>
-      </c>
-      <c r="E162" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr"/>
+          <t>Iso_Method</t>
+        </is>
+      </c>
+      <c r="D162" s="56" t="inlineStr">
+        <is>
+          <t>Iso-Meta</t>
+        </is>
+      </c>
+      <c r="E162" s="38" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>TIMS, MC-ICP-MS, Solution MC-ICP-MS, LA-MC-ICP-MS, SIMS, SHRIMP, N-TIMS (Os), Laser fluorination (δ¹⁸O), EA-IRMS (δ¹³C, δD), CRDS, Mixed</t>
+        </is>
+      </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>MC-ICP-MS</t>
         </is>
       </c>
       <c r="H162" s="42" t="inlineStr">
         <is>
-          <t>Modal Calcite, dolomite, ankerite (esp. in alteration / carbonatites).</t>
+          <t>Mass-spectrometry technique used for the isotope ratio(s).</t>
         </is>
       </c>
     </row>
@@ -8736,33 +8906,29 @@
       </c>
       <c r="B163" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C163" s="40" t="inlineStr">
         <is>
-          <t>Other_acc_mode</t>
-        </is>
-      </c>
-      <c r="D163" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
-        </is>
-      </c>
-      <c r="E163" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Iso_Laboratory</t>
+        </is>
+      </c>
+      <c r="D163" s="56" t="inlineStr">
+        <is>
+          <t>Iso-Meta</t>
+        </is>
+      </c>
+      <c r="E163" s="38" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>MIT Radiogenic Isotope Lab</t>
         </is>
       </c>
       <c r="H163" s="42" t="inlineStr">
         <is>
-          <t>Modal other accessories (epidote, chlorite, sericite, garnet, tourmaline, monazite, …).</t>
+          <t>Lab where the isotope analysis was carried out.</t>
         </is>
       </c>
     </row>
@@ -8772,29 +8938,29 @@
       </c>
       <c r="B164" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C164" s="40" t="inlineStr">
         <is>
-          <t>Mode_Total</t>
-        </is>
-      </c>
-      <c r="D164" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
-        </is>
-      </c>
-      <c r="E164" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Iso_Date</t>
+        </is>
+      </c>
+      <c r="D164" s="56" t="inlineStr">
+        <is>
+          <t>Iso-Meta</t>
+        </is>
+      </c>
+      <c r="E164" s="38" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
       <c r="H164" s="42" t="inlineStr">
         <is>
-          <t>Quality-control sum of every modal column above. Should fall between 99 and 101 vol %.</t>
+          <t>Year or full date of the isotope analysis.</t>
         </is>
       </c>
     </row>
@@ -8804,33 +8970,29 @@
       </c>
       <c r="B165" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C165" s="40" t="inlineStr">
         <is>
-          <t>Crystal_pct</t>
-        </is>
-      </c>
-      <c r="D165" s="55" t="inlineStr">
-        <is>
-          <t>Petro-Tuff</t>
-        </is>
-      </c>
-      <c r="E165" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Iso_Analyst</t>
+        </is>
+      </c>
+      <c r="D165" s="56" t="inlineStr">
+        <is>
+          <t>Iso-Meta</t>
+        </is>
+      </c>
+      <c r="E165" s="38" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>MLG</t>
         </is>
       </c>
       <c r="H165" s="42" t="inlineStr">
         <is>
-          <t>Crystal fragments — Crystal apex of the IUGS tuff ternary (Schmid 1981).</t>
+          <t>Analyst initials or name.</t>
         </is>
       </c>
     </row>
@@ -8840,33 +9002,25 @@
       </c>
       <c r="B166" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C166" s="40" t="inlineStr">
         <is>
-          <t>Vitric_pct</t>
-        </is>
-      </c>
-      <c r="D166" s="55" t="inlineStr">
-        <is>
-          <t>Petro-Tuff</t>
-        </is>
-      </c>
-      <c r="E166" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Iso_Notes</t>
+        </is>
+      </c>
+      <c r="D166" s="56" t="inlineStr">
+        <is>
+          <t>Iso-Meta</t>
+        </is>
+      </c>
+      <c r="E166" s="38" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" s="42" t="inlineStr">
         <is>
-          <t>Glass shards / pumice fragments — Vitric apex.</t>
+          <t>Free-text notes (column chemistry, spike, repeated measurements, blanks).</t>
         </is>
       </c>
     </row>
@@ -8881,28 +9035,24 @@
       </c>
       <c r="C167" s="40" t="inlineStr">
         <is>
-          <t>Lithic_pct</t>
-        </is>
-      </c>
-      <c r="D167" s="55" t="inlineStr">
-        <is>
-          <t>Petro-Tuff</t>
-        </is>
-      </c>
-      <c r="E167" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Sample_Name</t>
+        </is>
+      </c>
+      <c r="D167" s="41" t="inlineStr">
+        <is>
+          <t>Petro-ID</t>
+        </is>
+      </c>
+      <c r="E167" s="38" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>VOL-2024-018</t>
         </is>
       </c>
       <c r="H167" s="42" t="inlineStr">
         <is>
-          <t>Lithic / rock fragments — Lithic apex.</t>
+          <t>Must exactly match the Sample_Name in the Data sheet — this is the key B.I.R.D.S uses to join the modal mineralogy back to the bulk composition.</t>
         </is>
       </c>
     </row>
@@ -8917,28 +9067,24 @@
       </c>
       <c r="C168" s="40" t="inlineStr">
         <is>
-          <t>Pyroclast_size</t>
-        </is>
-      </c>
-      <c r="D168" s="55" t="inlineStr">
-        <is>
-          <t>Petro-Tuff</t>
+          <t>Sample_Label</t>
+        </is>
+      </c>
+      <c r="D168" s="41" t="inlineStr">
+        <is>
+          <t>Petro-ID</t>
         </is>
       </c>
       <c r="E168" s="38" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Ash (&lt; 2 mm), Lapilli (2-64 mm), Block / Bomb (&gt; 64 mm), Mixed</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lapilli (2-64 mm)</t>
+          <t>Mt. Pico flow 18</t>
         </is>
       </c>
       <c r="H168" s="42" t="inlineStr">
         <is>
-          <t>Granulometric class. Pick from the dropdown.</t>
+          <t>Optional friendly label used in plots.  Leave blank to inherit the value from the Data sheet — B.I.R.D.S fills this column automatically at import time.</t>
         </is>
       </c>
     </row>
@@ -8953,28 +9099,24 @@
       </c>
       <c r="C169" s="40" t="inlineStr">
         <is>
-          <t>Grain_size_mm</t>
-        </is>
-      </c>
-      <c r="D169" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
-        </is>
-      </c>
-      <c r="E169" s="38" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="D169" s="41" t="inlineStr">
+        <is>
+          <t>Petro-ID</t>
+        </is>
+      </c>
+      <c r="E169" s="38" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>Lower flow</t>
         </is>
       </c>
       <c r="H169" s="42" t="inlineStr">
         <is>
-          <t>Average grain size (groundmass for porphyritic rocks).</t>
+          <t>Optional group used for colouring / legend.  Inherited from the Data sheet at import time if left blank.</t>
         </is>
       </c>
     </row>
@@ -8989,28 +9131,28 @@
       </c>
       <c r="C170" s="40" t="inlineStr">
         <is>
-          <t>Phenocryst_pct</t>
-        </is>
-      </c>
-      <c r="D170" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
-        </is>
-      </c>
-      <c r="E170" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr"/>
+          <t>Texture</t>
+        </is>
+      </c>
+      <c r="D170" s="41" t="inlineStr">
+        <is>
+          <t>Petro-ID</t>
+        </is>
+      </c>
+      <c r="E170" s="38" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Phaneritic, Aphanitic, Porphyritic, Glassy, Vesicular, Pyroclastic, Cumulate, Cataclastic, Foliated / Gneissic, Mixed</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Porphyritic</t>
         </is>
       </c>
       <c r="H170" s="42" t="inlineStr">
         <is>
-          <t>Total phenocryst content (porphyritic rocks).</t>
+          <t>Overall rock fabric. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
@@ -9025,12 +9167,12 @@
       </c>
       <c r="C171" s="40" t="inlineStr">
         <is>
-          <t>Vesicle_pct</t>
-        </is>
-      </c>
-      <c r="D171" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
+          <t>Q_mode</t>
+        </is>
+      </c>
+      <c r="D171" s="57" t="inlineStr">
+        <is>
+          <t>Petro-QAPF</t>
         </is>
       </c>
       <c r="E171" s="38" t="inlineStr">
@@ -9041,12 +9183,12 @@
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H171" s="42" t="inlineStr">
         <is>
-          <t>Vesicle / vug content.</t>
+          <t>Modal Quartz (Q apex of the Streckeisen QAPF diagram).</t>
         </is>
       </c>
     </row>
@@ -9061,12 +9203,12 @@
       </c>
       <c r="C172" s="40" t="inlineStr">
         <is>
-          <t>Alteration_pct</t>
-        </is>
-      </c>
-      <c r="D172" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
+          <t>A_mode</t>
+        </is>
+      </c>
+      <c r="D172" s="57" t="inlineStr">
+        <is>
+          <t>Petro-QAPF</t>
         </is>
       </c>
       <c r="E172" s="38" t="inlineStr">
@@ -9077,12 +9219,12 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H172" s="42" t="inlineStr">
         <is>
-          <t>Secondary minerals / alteration overprint (sericite, chlorite, clay …).</t>
+          <t>Modal Alkali feldspar (K-feldspar + albite component); A apex of QAPF.</t>
         </is>
       </c>
     </row>
@@ -9097,24 +9239,28 @@
       </c>
       <c r="C173" s="40" t="inlineStr">
         <is>
-          <t>Texture_notes</t>
-        </is>
-      </c>
-      <c r="D173" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
-        </is>
-      </c>
-      <c r="E173" s="38" t="inlineStr"/>
+          <t>P_mode</t>
+        </is>
+      </c>
+      <c r="D173" s="57" t="inlineStr">
+        <is>
+          <t>Petro-QAPF</t>
+        </is>
+      </c>
+      <c r="E173" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Plg zoned; Cpx with sieve texture</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H173" s="42" t="inlineStr">
         <is>
-          <t>Free-text observations (zoning, reaction rims, embayments, cumulate textures, mineral assemblage).</t>
+          <t>Modal Plagioclase (calcic / sodic plagioclase); P apex of QAPF.</t>
         </is>
       </c>
     </row>
@@ -9129,28 +9275,28 @@
       </c>
       <c r="C174" s="40" t="inlineStr">
         <is>
-          <t>Microscope_method</t>
-        </is>
-      </c>
-      <c r="D174" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
-        </is>
-      </c>
-      <c r="E174" s="38" t="inlineStr"/>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Point-count (≥ 300 points), Point-count (100-300 points), Visual estimate, Modal calculation (CIPW), Image analysis (software), SEM-EDS / EBSD, Mixed</t>
-        </is>
-      </c>
+          <t>F_mode</t>
+        </is>
+      </c>
+      <c r="D174" s="57" t="inlineStr">
+        <is>
+          <t>Petro-QAPF</t>
+        </is>
+      </c>
+      <c r="E174" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Point-count (≥ 300 points)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H174" s="42" t="inlineStr">
         <is>
-          <t>How the modal proportions were obtained.</t>
+          <t>Modal Feldspathoid (nepheline, leucite, sodalite …); F apex of the bottom QAPF triangle. Mutually exclusive with Q (one rock can't have both).</t>
         </is>
       </c>
     </row>
@@ -9165,24 +9311,28 @@
       </c>
       <c r="C175" s="40" t="inlineStr">
         <is>
-          <t>Microscope_lab</t>
-        </is>
-      </c>
-      <c r="D175" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
-        </is>
-      </c>
-      <c r="E175" s="38" t="inlineStr"/>
+          <t>Ol_mode</t>
+        </is>
+      </c>
+      <c r="D175" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
+        </is>
+      </c>
+      <c r="E175" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>UNAM — Petrology lab</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H175" s="42" t="inlineStr">
         <is>
-          <t>Lab / university where the thin section was studied.</t>
+          <t>Modal Olivine. Ol apex of the gabbro Pl-Px-Ol ternary and of the ultramafic Ol-Opx-Cpx ternary.</t>
         </is>
       </c>
     </row>
@@ -9197,24 +9347,28 @@
       </c>
       <c r="C176" s="40" t="inlineStr">
         <is>
-          <t>Petrography_date</t>
-        </is>
-      </c>
-      <c r="D176" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
-        </is>
-      </c>
-      <c r="E176" s="38" t="inlineStr"/>
+          <t>Opx_mode</t>
+        </is>
+      </c>
+      <c r="D176" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
+        </is>
+      </c>
+      <c r="E176" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H176" s="42" t="inlineStr">
         <is>
-          <t>Year / date of the petrographic analysis (YYYY or YYYY-MM-DD).</t>
+          <t>Modal Orthopyroxene (enstatite to ferrosilite). Opx apex of the ultramafic ternary.</t>
         </is>
       </c>
     </row>
@@ -9229,24 +9383,28 @@
       </c>
       <c r="C177" s="40" t="inlineStr">
         <is>
-          <t>Petrographer</t>
-        </is>
-      </c>
-      <c r="D177" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
-        </is>
-      </c>
-      <c r="E177" s="38" t="inlineStr"/>
+          <t>Cpx_mode</t>
+        </is>
+      </c>
+      <c r="D177" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
+        </is>
+      </c>
+      <c r="E177" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
-          <t>MDC</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H177" s="42" t="inlineStr">
         <is>
-          <t>Analyst initials or name.</t>
+          <t>Modal Clinopyroxene (diopside, augite, pigeonite …). Cpx apex of the ultramafic ternary.</t>
         </is>
       </c>
     </row>
@@ -9261,18 +9419,858 @@
       </c>
       <c r="C178" s="40" t="inlineStr">
         <is>
-          <t>Petrography_notes</t>
-        </is>
-      </c>
-      <c r="D178" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
-        </is>
-      </c>
-      <c r="E178" s="38" t="inlineStr"/>
+          <t>Px_mode</t>
+        </is>
+      </c>
+      <c r="D178" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
+        </is>
+      </c>
+      <c r="E178" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
       <c r="H178" s="42" t="inlineStr">
+        <is>
+          <t>Total pyroxene (Opx + Cpx) used by the gabbro Pl-Px-Ol ternary. Leave empty — B.I.R.D.S sums Opx + Cpx automatically if you fill those.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="38" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C179" s="40" t="inlineStr">
+        <is>
+          <t>Amph_mode</t>
+        </is>
+      </c>
+      <c r="D179" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
+        </is>
+      </c>
+      <c r="E179" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H179" s="42" t="inlineStr">
+        <is>
+          <t>Modal Amphibole (hornblende, actinolite, kaersutite …). Not used by QAPF but reported for completeness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="38" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C180" s="40" t="inlineStr">
+        <is>
+          <t>Bt_mode</t>
+        </is>
+      </c>
+      <c r="D180" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
+        </is>
+      </c>
+      <c r="E180" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H180" s="42" t="inlineStr">
+        <is>
+          <t>Modal Biotite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="38" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C181" s="40" t="inlineStr">
+        <is>
+          <t>Ms_mode</t>
+        </is>
+      </c>
+      <c r="D181" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
+        </is>
+      </c>
+      <c r="E181" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H181" s="42" t="inlineStr">
+        <is>
+          <t>Modal Muscovite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="38" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C182" s="40" t="inlineStr">
+        <is>
+          <t>Opaque_mode</t>
+        </is>
+      </c>
+      <c r="D182" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
+        </is>
+      </c>
+      <c r="E182" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="H182" s="42" t="inlineStr">
+        <is>
+          <t>Modal Fe-Ti oxides (magnetite, ilmenite, hematite, chromite).</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="38" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C183" s="40" t="inlineStr">
+        <is>
+          <t>Apatite_mode</t>
+        </is>
+      </c>
+      <c r="D183" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
+        </is>
+      </c>
+      <c r="E183" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H183" s="42" t="inlineStr">
+        <is>
+          <t>Modal Apatite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="38" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C184" s="40" t="inlineStr">
+        <is>
+          <t>Zircon_mode</t>
+        </is>
+      </c>
+      <c r="D184" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
+        </is>
+      </c>
+      <c r="E184" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H184" s="42" t="inlineStr">
+        <is>
+          <t>Modal Zircon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="38" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C185" s="40" t="inlineStr">
+        <is>
+          <t>Titanite_mode</t>
+        </is>
+      </c>
+      <c r="D185" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
+        </is>
+      </c>
+      <c r="E185" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="H185" s="42" t="inlineStr">
+        <is>
+          <t>Modal Titanite / sphene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="38" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C186" s="40" t="inlineStr">
+        <is>
+          <t>Carbonate_mode</t>
+        </is>
+      </c>
+      <c r="D186" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
+        </is>
+      </c>
+      <c r="E186" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H186" s="42" t="inlineStr">
+        <is>
+          <t>Modal Calcite, dolomite, ankerite (esp. in alteration / carbonatites).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="38" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C187" s="40" t="inlineStr">
+        <is>
+          <t>Other_acc_mode</t>
+        </is>
+      </c>
+      <c r="D187" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
+        </is>
+      </c>
+      <c r="E187" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H187" s="42" t="inlineStr">
+        <is>
+          <t>Modal other accessories (epidote, chlorite, sericite, garnet, tourmaline, monazite, …).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="38" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C188" s="40" t="inlineStr">
+        <is>
+          <t>Mode_Total</t>
+        </is>
+      </c>
+      <c r="D188" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
+        </is>
+      </c>
+      <c r="E188" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" s="42" t="inlineStr">
+        <is>
+          <t>Quality-control sum of every modal column above. Should fall between 99 and 101 vol %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="38" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C189" s="40" t="inlineStr">
+        <is>
+          <t>Crystal_pct</t>
+        </is>
+      </c>
+      <c r="D189" s="55" t="inlineStr">
+        <is>
+          <t>Petro-Tuff</t>
+        </is>
+      </c>
+      <c r="E189" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H189" s="42" t="inlineStr">
+        <is>
+          <t>Crystal fragments — Crystal apex of the IUGS tuff ternary (Schmid 1981).</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="38" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C190" s="40" t="inlineStr">
+        <is>
+          <t>Vitric_pct</t>
+        </is>
+      </c>
+      <c r="D190" s="55" t="inlineStr">
+        <is>
+          <t>Petro-Tuff</t>
+        </is>
+      </c>
+      <c r="E190" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H190" s="42" t="inlineStr">
+        <is>
+          <t>Glass shards / pumice fragments — Vitric apex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="38" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C191" s="40" t="inlineStr">
+        <is>
+          <t>Lithic_pct</t>
+        </is>
+      </c>
+      <c r="D191" s="55" t="inlineStr">
+        <is>
+          <t>Petro-Tuff</t>
+        </is>
+      </c>
+      <c r="E191" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H191" s="42" t="inlineStr">
+        <is>
+          <t>Lithic / rock fragments — Lithic apex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="38" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C192" s="40" t="inlineStr">
+        <is>
+          <t>Pyroclast_size</t>
+        </is>
+      </c>
+      <c r="D192" s="55" t="inlineStr">
+        <is>
+          <t>Petro-Tuff</t>
+        </is>
+      </c>
+      <c r="E192" s="38" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Ash (&lt; 2 mm), Lapilli (2-64 mm), Block / Bomb (&gt; 64 mm), Mixed</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Lapilli (2-64 mm)</t>
+        </is>
+      </c>
+      <c r="H192" s="42" t="inlineStr">
+        <is>
+          <t>Granulometric class. Pick from the dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="38" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C193" s="40" t="inlineStr">
+        <is>
+          <t>Grain_size_mm</t>
+        </is>
+      </c>
+      <c r="D193" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E193" s="38" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H193" s="42" t="inlineStr">
+        <is>
+          <t>Average grain size (groundmass for porphyritic rocks).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="38" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C194" s="40" t="inlineStr">
+        <is>
+          <t>Phenocryst_pct</t>
+        </is>
+      </c>
+      <c r="D194" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E194" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H194" s="42" t="inlineStr">
+        <is>
+          <t>Total phenocryst content (porphyritic rocks).</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="38" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C195" s="40" t="inlineStr">
+        <is>
+          <t>Vesicle_pct</t>
+        </is>
+      </c>
+      <c r="D195" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E195" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H195" s="42" t="inlineStr">
+        <is>
+          <t>Vesicle / vug content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="38" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C196" s="40" t="inlineStr">
+        <is>
+          <t>Alteration_pct</t>
+        </is>
+      </c>
+      <c r="D196" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E196" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H196" s="42" t="inlineStr">
+        <is>
+          <t>Secondary minerals / alteration overprint (sericite, chlorite, clay …).</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="38" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C197" s="40" t="inlineStr">
+        <is>
+          <t>Texture_notes</t>
+        </is>
+      </c>
+      <c r="D197" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E197" s="38" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Plg zoned; Cpx with sieve texture</t>
+        </is>
+      </c>
+      <c r="H197" s="42" t="inlineStr">
+        <is>
+          <t>Free-text observations (zoning, reaction rims, embayments, cumulate textures, mineral assemblage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="38" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C198" s="40" t="inlineStr">
+        <is>
+          <t>Microscope_method</t>
+        </is>
+      </c>
+      <c r="D198" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E198" s="38" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Point-count (≥ 300 points), Point-count (100-300 points), Visual estimate, Modal calculation (CIPW), Image analysis (software), SEM-EDS / EBSD, Mixed</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Point-count (≥ 300 points)</t>
+        </is>
+      </c>
+      <c r="H198" s="42" t="inlineStr">
+        <is>
+          <t>How the modal proportions were obtained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="38" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C199" s="40" t="inlineStr">
+        <is>
+          <t>Microscope_lab</t>
+        </is>
+      </c>
+      <c r="D199" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E199" s="38" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>UNAM — Petrology lab</t>
+        </is>
+      </c>
+      <c r="H199" s="42" t="inlineStr">
+        <is>
+          <t>Lab / university where the thin section was studied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="38" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C200" s="40" t="inlineStr">
+        <is>
+          <t>Petrography_date</t>
+        </is>
+      </c>
+      <c r="D200" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E200" s="38" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="H200" s="42" t="inlineStr">
+        <is>
+          <t>Year / date of the petrographic analysis (YYYY or YYYY-MM-DD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="38" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C201" s="40" t="inlineStr">
+        <is>
+          <t>Petrographer</t>
+        </is>
+      </c>
+      <c r="D201" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E201" s="38" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>MDC</t>
+        </is>
+      </c>
+      <c r="H201" s="42" t="inlineStr">
+        <is>
+          <t>Analyst initials or name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="38" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C202" s="40" t="inlineStr">
+        <is>
+          <t>Petrography_notes</t>
+        </is>
+      </c>
+      <c r="D202" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E202" s="38" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" s="42" t="inlineStr">
         <is>
           <t>Free-text notes (sample preservation, mounting, staining for K-feldspar, etc.).</t>
         </is>

--- a/templates/BIRDS_data_template.xlsx
+++ b/templates/BIRDS_data_template.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK2"/>
+  <dimension ref="A1:CO2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -705,29 +705,29 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="17" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
     <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="9" customWidth="1" min="31" max="31"/>
-    <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
     <col width="9" customWidth="1" min="33" max="33"/>
     <col width="9" customWidth="1" min="34" max="34"/>
     <col width="9" customWidth="1" min="35" max="35"/>
@@ -785,6 +785,10 @@
     <col width="9" customWidth="1" min="87" max="87"/>
     <col width="9" customWidth="1" min="88" max="88"/>
     <col width="9" customWidth="1" min="89" max="89"/>
+    <col width="9" customWidth="1" min="90" max="90"/>
+    <col width="9" customWidth="1" min="91" max="91"/>
+    <col width="9" customWidth="1" min="92" max="92"/>
+    <col width="9" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -820,415 +824,435 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>Easting</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>UTM_Zone</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Hemisphere</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
           <t>Elevation</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Locality</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Dataset_DOI</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Age_Unit</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Age_Method</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Rock_Type</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>TAS_Composition</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>Lithology</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>Magmatic_Series</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>Tectonic_Setting</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>Texture</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>Mineral_Assemblage</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>Alteration</t>
         </is>
       </c>
-      <c r="X1" s="5" t="inlineStr">
+      <c r="AB1" s="5" t="inlineStr">
         <is>
           <t>Analytical_Method</t>
         </is>
       </c>
-      <c r="Y1" s="5" t="inlineStr">
+      <c r="AC1" s="5" t="inlineStr">
         <is>
           <t>Laboratory</t>
         </is>
       </c>
-      <c r="Z1" s="5" t="inlineStr">
+      <c r="AD1" s="5" t="inlineStr">
         <is>
           <t>Analysis_Date</t>
         </is>
       </c>
-      <c r="AA1" s="5" t="inlineStr">
+      <c r="AE1" s="5" t="inlineStr">
         <is>
           <t>Analyst</t>
         </is>
       </c>
-      <c r="AB1" s="5" t="inlineStr">
+      <c r="AF1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AC1" s="6" t="inlineStr">
+      <c r="AG1" s="6" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="AD1" s="6" t="inlineStr">
+      <c r="AH1" s="6" t="inlineStr">
         <is>
           <t>TiO2</t>
         </is>
       </c>
-      <c r="AE1" s="6" t="inlineStr">
+      <c r="AI1" s="6" t="inlineStr">
         <is>
           <t>Al2O3</t>
         </is>
       </c>
-      <c r="AF1" s="6" t="inlineStr">
+      <c r="AJ1" s="6" t="inlineStr">
         <is>
           <t>Fe2O3</t>
         </is>
       </c>
-      <c r="AG1" s="6" t="inlineStr">
+      <c r="AK1" s="6" t="inlineStr">
         <is>
           <t>FeO</t>
         </is>
       </c>
-      <c r="AH1" s="6" t="inlineStr">
+      <c r="AL1" s="6" t="inlineStr">
         <is>
           <t>FeOt</t>
         </is>
       </c>
-      <c r="AI1" s="6" t="inlineStr">
+      <c r="AM1" s="6" t="inlineStr">
         <is>
           <t>MnO</t>
         </is>
       </c>
-      <c r="AJ1" s="6" t="inlineStr">
+      <c r="AN1" s="6" t="inlineStr">
         <is>
           <t>MgO</t>
         </is>
       </c>
-      <c r="AK1" s="6" t="inlineStr">
+      <c r="AO1" s="6" t="inlineStr">
         <is>
           <t>CaO</t>
         </is>
       </c>
-      <c r="AL1" s="6" t="inlineStr">
+      <c r="AP1" s="6" t="inlineStr">
         <is>
           <t>Na2O</t>
         </is>
       </c>
-      <c r="AM1" s="6" t="inlineStr">
+      <c r="AQ1" s="6" t="inlineStr">
         <is>
           <t>K2O</t>
         </is>
       </c>
-      <c r="AN1" s="6" t="inlineStr">
+      <c r="AR1" s="6" t="inlineStr">
         <is>
           <t>P2O5</t>
         </is>
       </c>
-      <c r="AO1" s="6" t="inlineStr">
+      <c r="AS1" s="6" t="inlineStr">
         <is>
           <t>Cr2O3</t>
         </is>
       </c>
-      <c r="AP1" s="6" t="inlineStr">
+      <c r="AT1" s="6" t="inlineStr">
         <is>
           <t>NiO</t>
         </is>
       </c>
-      <c r="AQ1" s="6" t="inlineStr">
+      <c r="AU1" s="6" t="inlineStr">
         <is>
           <t>LOI</t>
         </is>
       </c>
-      <c r="AR1" s="6" t="inlineStr">
+      <c r="AV1" s="6" t="inlineStr">
         <is>
           <t>H2O+</t>
         </is>
       </c>
-      <c r="AS1" s="6" t="inlineStr">
+      <c r="AW1" s="6" t="inlineStr">
         <is>
           <t>H2O-</t>
         </is>
       </c>
-      <c r="AT1" s="6" t="inlineStr">
+      <c r="AX1" s="6" t="inlineStr">
         <is>
           <t>CO2</t>
         </is>
       </c>
-      <c r="AU1" s="6" t="inlineStr">
+      <c r="AY1" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="AV1" s="7" t="inlineStr">
+      <c r="AZ1" s="7" t="inlineStr">
         <is>
           <t>Li</t>
         </is>
       </c>
-      <c r="AW1" s="7" t="inlineStr">
+      <c r="BA1" s="7" t="inlineStr">
         <is>
           <t>Be</t>
         </is>
       </c>
-      <c r="AX1" s="7" t="inlineStr">
+      <c r="BB1" s="7" t="inlineStr">
         <is>
           <t>Sc</t>
         </is>
       </c>
-      <c r="AY1" s="7" t="inlineStr">
+      <c r="BC1" s="7" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="AZ1" s="7" t="inlineStr">
+      <c r="BD1" s="7" t="inlineStr">
         <is>
           <t>Cr</t>
         </is>
       </c>
-      <c r="BA1" s="7" t="inlineStr">
+      <c r="BE1" s="7" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="BB1" s="7" t="inlineStr">
+      <c r="BF1" s="7" t="inlineStr">
         <is>
           <t>Ni</t>
         </is>
       </c>
-      <c r="BC1" s="7" t="inlineStr">
+      <c r="BG1" s="7" t="inlineStr">
         <is>
           <t>Cu</t>
         </is>
       </c>
-      <c r="BD1" s="7" t="inlineStr">
+      <c r="BH1" s="7" t="inlineStr">
         <is>
           <t>Zn</t>
         </is>
       </c>
-      <c r="BE1" s="7" t="inlineStr">
+      <c r="BI1" s="7" t="inlineStr">
         <is>
           <t>Ga</t>
         </is>
       </c>
-      <c r="BF1" s="7" t="inlineStr">
+      <c r="BJ1" s="7" t="inlineStr">
         <is>
           <t>Rb</t>
         </is>
       </c>
-      <c r="BG1" s="7" t="inlineStr">
+      <c r="BK1" s="7" t="inlineStr">
         <is>
           <t>Sr</t>
         </is>
       </c>
-      <c r="BH1" s="7" t="inlineStr">
+      <c r="BL1" s="7" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BI1" s="7" t="inlineStr">
+      <c r="BM1" s="7" t="inlineStr">
         <is>
           <t>Zr</t>
         </is>
       </c>
-      <c r="BJ1" s="7" t="inlineStr">
+      <c r="BN1" s="7" t="inlineStr">
         <is>
           <t>Nb</t>
         </is>
       </c>
-      <c r="BK1" s="7" t="inlineStr">
+      <c r="BO1" s="7" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="BL1" s="7" t="inlineStr">
+      <c r="BP1" s="7" t="inlineStr">
         <is>
           <t>Sn</t>
         </is>
       </c>
-      <c r="BM1" s="7" t="inlineStr">
+      <c r="BQ1" s="7" t="inlineStr">
         <is>
           <t>Sb</t>
         </is>
       </c>
-      <c r="BN1" s="7" t="inlineStr">
+      <c r="BR1" s="7" t="inlineStr">
         <is>
           <t>Cs</t>
         </is>
       </c>
-      <c r="BO1" s="7" t="inlineStr">
+      <c r="BS1" s="7" t="inlineStr">
         <is>
           <t>Ba</t>
         </is>
       </c>
-      <c r="BP1" s="7" t="inlineStr">
+      <c r="BT1" s="7" t="inlineStr">
         <is>
           <t>Hf</t>
         </is>
       </c>
-      <c r="BQ1" s="7" t="inlineStr">
+      <c r="BU1" s="7" t="inlineStr">
         <is>
           <t>Ta</t>
         </is>
       </c>
-      <c r="BR1" s="7" t="inlineStr">
+      <c r="BV1" s="7" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="BS1" s="7" t="inlineStr">
+      <c r="BW1" s="7" t="inlineStr">
         <is>
           <t>Tl</t>
         </is>
       </c>
-      <c r="BT1" s="7" t="inlineStr">
+      <c r="BX1" s="7" t="inlineStr">
         <is>
           <t>Pb</t>
         </is>
       </c>
-      <c r="BU1" s="7" t="inlineStr">
+      <c r="BY1" s="7" t="inlineStr">
         <is>
           <t>Bi</t>
         </is>
       </c>
-      <c r="BV1" s="7" t="inlineStr">
+      <c r="BZ1" s="7" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="BW1" s="7" t="inlineStr">
+      <c r="CA1" s="7" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="BX1" s="8" t="inlineStr">
+      <c r="CB1" s="8" t="inlineStr">
         <is>
           <t>La</t>
         </is>
       </c>
-      <c r="BY1" s="8" t="inlineStr">
+      <c r="CC1" s="8" t="inlineStr">
         <is>
           <t>Ce</t>
         </is>
       </c>
-      <c r="BZ1" s="8" t="inlineStr">
+      <c r="CD1" s="8" t="inlineStr">
         <is>
           <t>Pr</t>
         </is>
       </c>
-      <c r="CA1" s="8" t="inlineStr">
+      <c r="CE1" s="8" t="inlineStr">
         <is>
           <t>Nd</t>
         </is>
       </c>
-      <c r="CB1" s="8" t="inlineStr">
+      <c r="CF1" s="8" t="inlineStr">
         <is>
           <t>Sm</t>
         </is>
       </c>
-      <c r="CC1" s="8" t="inlineStr">
+      <c r="CG1" s="8" t="inlineStr">
         <is>
           <t>Eu</t>
         </is>
       </c>
-      <c r="CD1" s="8" t="inlineStr">
+      <c r="CH1" s="8" t="inlineStr">
         <is>
           <t>Gd</t>
         </is>
       </c>
-      <c r="CE1" s="8" t="inlineStr">
+      <c r="CI1" s="8" t="inlineStr">
         <is>
           <t>Tb</t>
         </is>
       </c>
-      <c r="CF1" s="8" t="inlineStr">
+      <c r="CJ1" s="8" t="inlineStr">
         <is>
           <t>Dy</t>
         </is>
       </c>
-      <c r="CG1" s="8" t="inlineStr">
+      <c r="CK1" s="8" t="inlineStr">
         <is>
           <t>Ho</t>
         </is>
       </c>
-      <c r="CH1" s="8" t="inlineStr">
+      <c r="CL1" s="8" t="inlineStr">
         <is>
           <t>Er</t>
         </is>
       </c>
-      <c r="CI1" s="8" t="inlineStr">
+      <c r="CM1" s="8" t="inlineStr">
         <is>
           <t>Tm</t>
         </is>
       </c>
-      <c r="CJ1" s="8" t="inlineStr">
+      <c r="CN1" s="8" t="inlineStr">
         <is>
           <t>Yb</t>
         </is>
       </c>
-      <c r="CK1" s="8" t="inlineStr">
+      <c r="CO1" s="8" t="inlineStr">
         <is>
           <t>Lu</t>
         </is>
@@ -1254,15 +1278,23 @@
           <t>m</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr"/>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="I2" s="10" t="inlineStr"/>
       <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="11" t="inlineStr"/>
-      <c r="L2" s="11" t="inlineStr"/>
-      <c r="M2" s="12" t="inlineStr"/>
-      <c r="N2" s="12" t="inlineStr"/>
-      <c r="O2" s="12" t="inlineStr"/>
-      <c r="P2" s="12" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" s="11" t="inlineStr"/>
+      <c r="P2" s="11" t="inlineStr"/>
       <c r="Q2" s="12" t="inlineStr"/>
       <c r="R2" s="12" t="inlineStr"/>
       <c r="S2" s="12" t="inlineStr"/>
@@ -1270,1184 +1302,320 @@
       <c r="U2" s="12" t="inlineStr"/>
       <c r="V2" s="12" t="inlineStr"/>
       <c r="W2" s="12" t="inlineStr"/>
-      <c r="X2" s="13" t="inlineStr"/>
-      <c r="Y2" s="13" t="inlineStr"/>
-      <c r="Z2" s="13" t="inlineStr"/>
-      <c r="AA2" s="13" t="inlineStr"/>
+      <c r="X2" s="12" t="inlineStr"/>
+      <c r="Y2" s="12" t="inlineStr"/>
+      <c r="Z2" s="12" t="inlineStr"/>
+      <c r="AA2" s="12" t="inlineStr"/>
       <c r="AB2" s="13" t="inlineStr"/>
-      <c r="AC2" s="14" t="inlineStr">
+      <c r="AC2" s="13" t="inlineStr"/>
+      <c r="AD2" s="13" t="inlineStr"/>
+      <c r="AE2" s="13" t="inlineStr"/>
+      <c r="AF2" s="13" t="inlineStr"/>
+      <c r="AG2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AD2" s="14" t="inlineStr">
+      <c r="AH2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AE2" s="14" t="inlineStr">
+      <c r="AI2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AF2" s="14" t="inlineStr">
+      <c r="AJ2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AG2" s="14" t="inlineStr">
+      <c r="AK2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AH2" s="14" t="inlineStr">
+      <c r="AL2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AI2" s="14" t="inlineStr">
+      <c r="AM2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AJ2" s="14" t="inlineStr">
+      <c r="AN2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AK2" s="14" t="inlineStr">
+      <c r="AO2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AL2" s="14" t="inlineStr">
+      <c r="AP2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AM2" s="14" t="inlineStr">
+      <c r="AQ2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AN2" s="14" t="inlineStr">
+      <c r="AR2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AO2" s="14" t="inlineStr">
+      <c r="AS2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AP2" s="14" t="inlineStr">
+      <c r="AT2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AQ2" s="14" t="inlineStr">
+      <c r="AU2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AR2" s="14" t="inlineStr">
+      <c r="AV2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AS2" s="14" t="inlineStr">
+      <c r="AW2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AT2" s="14" t="inlineStr">
+      <c r="AX2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AU2" s="14" t="inlineStr">
+      <c r="AY2" s="14" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
-      <c r="AV2" s="15" t="inlineStr">
+      <c r="AZ2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="AW2" s="15" t="inlineStr">
+      <c r="BA2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="AX2" s="15" t="inlineStr">
+      <c r="BB2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="AY2" s="15" t="inlineStr">
+      <c r="BC2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="AZ2" s="15" t="inlineStr">
+      <c r="BD2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BA2" s="15" t="inlineStr">
+      <c r="BE2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BB2" s="15" t="inlineStr">
+      <c r="BF2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BC2" s="15" t="inlineStr">
+      <c r="BG2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BD2" s="15" t="inlineStr">
+      <c r="BH2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BE2" s="15" t="inlineStr">
+      <c r="BI2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BF2" s="15" t="inlineStr">
+      <c r="BJ2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BG2" s="15" t="inlineStr">
+      <c r="BK2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BH2" s="15" t="inlineStr">
+      <c r="BL2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BI2" s="15" t="inlineStr">
+      <c r="BM2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BJ2" s="15" t="inlineStr">
+      <c r="BN2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BK2" s="15" t="inlineStr">
+      <c r="BO2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BL2" s="15" t="inlineStr">
+      <c r="BP2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BM2" s="15" t="inlineStr">
+      <c r="BQ2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BN2" s="15" t="inlineStr">
+      <c r="BR2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BO2" s="15" t="inlineStr">
+      <c r="BS2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BP2" s="15" t="inlineStr">
+      <c r="BT2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BQ2" s="15" t="inlineStr">
+      <c r="BU2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BR2" s="15" t="inlineStr">
+      <c r="BV2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BS2" s="15" t="inlineStr">
+      <c r="BW2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BT2" s="15" t="inlineStr">
+      <c r="BX2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BU2" s="15" t="inlineStr">
+      <c r="BY2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BV2" s="15" t="inlineStr">
+      <c r="BZ2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BW2" s="15" t="inlineStr">
+      <c r="CA2" s="15" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BX2" s="16" t="inlineStr">
+      <c r="CB2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BY2" s="16" t="inlineStr">
+      <c r="CC2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="BZ2" s="16" t="inlineStr">
+      <c r="CD2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="CA2" s="16" t="inlineStr">
+      <c r="CE2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="CB2" s="16" t="inlineStr">
+      <c r="CF2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="CC2" s="16" t="inlineStr">
+      <c r="CG2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="CD2" s="16" t="inlineStr">
+      <c r="CH2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="CE2" s="16" t="inlineStr">
+      <c r="CI2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="CF2" s="16" t="inlineStr">
+      <c r="CJ2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="CG2" s="16" t="inlineStr">
+      <c r="CK2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="CH2" s="16" t="inlineStr">
+      <c r="CL2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="CI2" s="16" t="inlineStr">
+      <c r="CM2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="CJ2" s="16" t="inlineStr">
+      <c r="CN2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-      <c r="CK2" s="16" t="inlineStr">
+      <c r="CO2" s="16" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="16" customHeight="1"/>
-    <row r="4" ht="16" customHeight="1"/>
-    <row r="5" ht="16" customHeight="1"/>
-    <row r="6" ht="16" customHeight="1"/>
-    <row r="7" ht="16" customHeight="1"/>
-    <row r="8" ht="16" customHeight="1"/>
-    <row r="9" ht="16" customHeight="1"/>
-    <row r="10" ht="16" customHeight="1"/>
-    <row r="11" ht="16" customHeight="1"/>
-    <row r="12" ht="16" customHeight="1"/>
-    <row r="13" ht="16" customHeight="1"/>
-    <row r="14" ht="16" customHeight="1"/>
-    <row r="15" ht="16" customHeight="1"/>
-    <row r="16" ht="16" customHeight="1"/>
-    <row r="17" ht="16" customHeight="1"/>
-    <row r="18" ht="16" customHeight="1"/>
-    <row r="19" ht="16" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1"/>
-    <row r="21" ht="16" customHeight="1"/>
-    <row r="22" ht="16" customHeight="1"/>
-    <row r="23" ht="16" customHeight="1"/>
-    <row r="24" ht="16" customHeight="1"/>
-    <row r="25" ht="16" customHeight="1"/>
-    <row r="26" ht="16" customHeight="1"/>
-    <row r="27" ht="16" customHeight="1"/>
-    <row r="28" ht="16" customHeight="1"/>
-    <row r="29" ht="16" customHeight="1"/>
-    <row r="30" ht="16" customHeight="1"/>
-    <row r="31" ht="16" customHeight="1"/>
-    <row r="32" ht="16" customHeight="1"/>
-    <row r="33" ht="16" customHeight="1"/>
-    <row r="34" ht="16" customHeight="1"/>
-    <row r="35" ht="16" customHeight="1"/>
-    <row r="36" ht="16" customHeight="1"/>
-    <row r="37" ht="16" customHeight="1"/>
-    <row r="38" ht="16" customHeight="1"/>
-    <row r="39" ht="16" customHeight="1"/>
-    <row r="40" ht="16" customHeight="1"/>
-    <row r="41" ht="16" customHeight="1"/>
-    <row r="42" ht="16" customHeight="1"/>
-    <row r="43" ht="16" customHeight="1"/>
-    <row r="44" ht="16" customHeight="1"/>
-    <row r="45" ht="16" customHeight="1"/>
-    <row r="46" ht="16" customHeight="1"/>
-    <row r="47" ht="16" customHeight="1"/>
-    <row r="48" ht="16" customHeight="1"/>
-    <row r="49" ht="16" customHeight="1"/>
-    <row r="50" ht="16" customHeight="1"/>
-    <row r="51" ht="16" customHeight="1"/>
-    <row r="52" ht="16" customHeight="1"/>
-    <row r="53" ht="16" customHeight="1"/>
-    <row r="54" ht="16" customHeight="1"/>
-    <row r="55" ht="16" customHeight="1"/>
-    <row r="56" ht="16" customHeight="1"/>
-    <row r="57" ht="16" customHeight="1"/>
-    <row r="58" ht="16" customHeight="1"/>
-    <row r="59" ht="16" customHeight="1"/>
-    <row r="60" ht="16" customHeight="1"/>
-    <row r="61" ht="16" customHeight="1"/>
-    <row r="62" ht="16" customHeight="1"/>
-    <row r="63" ht="16" customHeight="1"/>
-    <row r="64" ht="16" customHeight="1"/>
-    <row r="65" ht="16" customHeight="1"/>
-    <row r="66" ht="16" customHeight="1"/>
-    <row r="67" ht="16" customHeight="1"/>
-    <row r="68" ht="16" customHeight="1"/>
-    <row r="69" ht="16" customHeight="1"/>
-    <row r="70" ht="16" customHeight="1"/>
-    <row r="71" ht="16" customHeight="1"/>
-    <row r="72" ht="16" customHeight="1"/>
-    <row r="73" ht="16" customHeight="1"/>
-    <row r="74" ht="16" customHeight="1"/>
-    <row r="75" ht="16" customHeight="1"/>
-    <row r="76" ht="16" customHeight="1"/>
-    <row r="77" ht="16" customHeight="1"/>
-    <row r="78" ht="16" customHeight="1"/>
-    <row r="79" ht="16" customHeight="1"/>
-    <row r="80" ht="16" customHeight="1"/>
-    <row r="81" ht="16" customHeight="1"/>
-    <row r="82" ht="16" customHeight="1"/>
-    <row r="83" ht="16" customHeight="1"/>
-    <row r="84" ht="16" customHeight="1"/>
-    <row r="85" ht="16" customHeight="1"/>
-    <row r="86" ht="16" customHeight="1"/>
-    <row r="87" ht="16" customHeight="1"/>
-    <row r="88" ht="16" customHeight="1"/>
-    <row r="89" ht="16" customHeight="1"/>
-    <row r="90" ht="16" customHeight="1"/>
-    <row r="91" ht="16" customHeight="1"/>
-    <row r="92" ht="16" customHeight="1"/>
-    <row r="93" ht="16" customHeight="1"/>
-    <row r="94" ht="16" customHeight="1"/>
-    <row r="95" ht="16" customHeight="1"/>
-    <row r="96" ht="16" customHeight="1"/>
-    <row r="97" ht="16" customHeight="1"/>
-    <row r="98" ht="16" customHeight="1"/>
-    <row r="99" ht="16" customHeight="1"/>
-    <row r="100" ht="16" customHeight="1"/>
-    <row r="101" ht="16" customHeight="1"/>
-    <row r="102" ht="16" customHeight="1"/>
-    <row r="103" ht="16" customHeight="1"/>
-    <row r="104" ht="16" customHeight="1"/>
-    <row r="105" ht="16" customHeight="1"/>
-    <row r="106" ht="16" customHeight="1"/>
-    <row r="107" ht="16" customHeight="1"/>
-    <row r="108" ht="16" customHeight="1"/>
-    <row r="109" ht="16" customHeight="1"/>
-    <row r="110" ht="16" customHeight="1"/>
-    <row r="111" ht="16" customHeight="1"/>
-    <row r="112" ht="16" customHeight="1"/>
-    <row r="113" ht="16" customHeight="1"/>
-    <row r="114" ht="16" customHeight="1"/>
-    <row r="115" ht="16" customHeight="1"/>
-    <row r="116" ht="16" customHeight="1"/>
-    <row r="117" ht="16" customHeight="1"/>
-    <row r="118" ht="16" customHeight="1"/>
-    <row r="119" ht="16" customHeight="1"/>
-    <row r="120" ht="16" customHeight="1"/>
-    <row r="121" ht="16" customHeight="1"/>
-    <row r="122" ht="16" customHeight="1"/>
-    <row r="123" ht="16" customHeight="1"/>
-    <row r="124" ht="16" customHeight="1"/>
-    <row r="125" ht="16" customHeight="1"/>
-    <row r="126" ht="16" customHeight="1"/>
-    <row r="127" ht="16" customHeight="1"/>
-    <row r="128" ht="16" customHeight="1"/>
-    <row r="129" ht="16" customHeight="1"/>
-    <row r="130" ht="16" customHeight="1"/>
-    <row r="131" ht="16" customHeight="1"/>
-    <row r="132" ht="16" customHeight="1"/>
-    <row r="133" ht="16" customHeight="1"/>
-    <row r="134" ht="16" customHeight="1"/>
-    <row r="135" ht="16" customHeight="1"/>
-    <row r="136" ht="16" customHeight="1"/>
-    <row r="137" ht="16" customHeight="1"/>
-    <row r="138" ht="16" customHeight="1"/>
-    <row r="139" ht="16" customHeight="1"/>
-    <row r="140" ht="16" customHeight="1"/>
-    <row r="141" ht="16" customHeight="1"/>
-    <row r="142" ht="16" customHeight="1"/>
-    <row r="143" ht="16" customHeight="1"/>
-    <row r="144" ht="16" customHeight="1"/>
-    <row r="145" ht="16" customHeight="1"/>
-    <row r="146" ht="16" customHeight="1"/>
-    <row r="147" ht="16" customHeight="1"/>
-    <row r="148" ht="16" customHeight="1"/>
-    <row r="149" ht="16" customHeight="1"/>
-    <row r="150" ht="16" customHeight="1"/>
-    <row r="151" ht="16" customHeight="1"/>
-    <row r="152" ht="16" customHeight="1"/>
-    <row r="153" ht="16" customHeight="1"/>
-    <row r="154" ht="16" customHeight="1"/>
-    <row r="155" ht="16" customHeight="1"/>
-    <row r="156" ht="16" customHeight="1"/>
-    <row r="157" ht="16" customHeight="1"/>
-    <row r="158" ht="16" customHeight="1"/>
-    <row r="159" ht="16" customHeight="1"/>
-    <row r="160" ht="16" customHeight="1"/>
-    <row r="161" ht="16" customHeight="1"/>
-    <row r="162" ht="16" customHeight="1"/>
-    <row r="163" ht="16" customHeight="1"/>
-    <row r="164" ht="16" customHeight="1"/>
-    <row r="165" ht="16" customHeight="1"/>
-    <row r="166" ht="16" customHeight="1"/>
-    <row r="167" ht="16" customHeight="1"/>
-    <row r="168" ht="16" customHeight="1"/>
-    <row r="169" ht="16" customHeight="1"/>
-    <row r="170" ht="16" customHeight="1"/>
-    <row r="171" ht="16" customHeight="1"/>
-    <row r="172" ht="16" customHeight="1"/>
-    <row r="173" ht="16" customHeight="1"/>
-    <row r="174" ht="16" customHeight="1"/>
-    <row r="175" ht="16" customHeight="1"/>
-    <row r="176" ht="16" customHeight="1"/>
-    <row r="177" ht="16" customHeight="1"/>
-    <row r="178" ht="16" customHeight="1"/>
-    <row r="179" ht="16" customHeight="1"/>
-    <row r="180" ht="16" customHeight="1"/>
-    <row r="181" ht="16" customHeight="1"/>
-    <row r="182" ht="16" customHeight="1"/>
-    <row r="183" ht="16" customHeight="1"/>
-    <row r="184" ht="16" customHeight="1"/>
-    <row r="185" ht="16" customHeight="1"/>
-    <row r="186" ht="16" customHeight="1"/>
-    <row r="187" ht="16" customHeight="1"/>
-    <row r="188" ht="16" customHeight="1"/>
-    <row r="189" ht="16" customHeight="1"/>
-    <row r="190" ht="16" customHeight="1"/>
-    <row r="191" ht="16" customHeight="1"/>
-    <row r="192" ht="16" customHeight="1"/>
-    <row r="193" ht="16" customHeight="1"/>
-    <row r="194" ht="16" customHeight="1"/>
-    <row r="195" ht="16" customHeight="1"/>
-    <row r="196" ht="16" customHeight="1"/>
-    <row r="197" ht="16" customHeight="1"/>
-    <row r="198" ht="16" customHeight="1"/>
-    <row r="199" ht="16" customHeight="1"/>
-    <row r="200" ht="16" customHeight="1"/>
-    <row r="201" ht="16" customHeight="1"/>
-    <row r="202" ht="16" customHeight="1"/>
-  </sheetData>
-  <dataValidations count="6">
-    <dataValidation sqref="N3:N1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ma, ka, Ga, yr" type="list">
-      <formula1>"Ma,ka,Ga,yr"</formula1>
-    </dataValidation>
-    <dataValidation sqref="P3:P1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein" type="list">
-      <formula1>"Volcanic,Plutonic,Sub-volcanic,Pyroclastic,Vein"</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q3:Q1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite" type="list">
-      <formula1>"Picro-basalt,Basalt,Basaltic andesite,Andesite,Dacite,Rhyolite,Trachy-basalt,Basaltic trachy-andesite,Trachy-andesite,Trachyte,Trachy-dacite,Tephrite,Phono-tephrite,Tephri-phonolite,Phonolite,Foidite,Gabbro,Diorite,Granodiorite,Granite,Monzogabbro,Monzodiorite,Monzonite,Syenite,Foid-syenite,Foidolite"</formula1>
-    </dataValidation>
-    <dataValidation sqref="S3:S1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic" type="list">
-      <formula1>"Tholeiitic,Calc-alkaline,High-K calc-alkaline,Shoshonitic,Alkaline,Ultra-alkaline,Boninitic"</formula1>
-    </dataValidation>
-    <dataValidation sqref="W3:W1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed" type="list">
-      <formula1>"Fresh,Slightly altered,Moderately altered,Strongly altered,Metamorphosed"</formula1>
-    </dataValidation>
-    <dataValidation sqref="X3:X1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed" type="list">
-      <formula1>"XRF,ICP-OES,ICP-MS,Solution ICP-MS,LA-ICP-MS,EMP / EPMA,INAA,Wet chemistry,Mixed"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:BX2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="21" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="17" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="9" customWidth="1" min="33" max="33"/>
-    <col width="9" customWidth="1" min="34" max="34"/>
-    <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="16" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="9" customWidth="1" min="39" max="39"/>
-    <col width="9" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="9" customWidth="1" min="42" max="42"/>
-    <col width="13" customWidth="1" min="43" max="43"/>
-    <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="16" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="16" customWidth="1" min="48" max="48"/>
-    <col width="9" customWidth="1" min="49" max="49"/>
-    <col width="9" customWidth="1" min="50" max="50"/>
-    <col width="9" customWidth="1" min="51" max="51"/>
-    <col width="13" customWidth="1" min="52" max="52"/>
-    <col width="16" customWidth="1" min="53" max="53"/>
-    <col width="13" customWidth="1" min="54" max="54"/>
-    <col width="9" customWidth="1" min="55" max="55"/>
-    <col width="9" customWidth="1" min="56" max="56"/>
-    <col width="13" customWidth="1" min="57" max="57"/>
-    <col width="9" customWidth="1" min="58" max="58"/>
-    <col width="13" customWidth="1" min="59" max="59"/>
-    <col width="16" customWidth="1" min="60" max="60"/>
-    <col width="13" customWidth="1" min="61" max="61"/>
-    <col width="9" customWidth="1" min="62" max="62"/>
-    <col width="9" customWidth="1" min="63" max="63"/>
-    <col width="13" customWidth="1" min="64" max="64"/>
-    <col width="9" customWidth="1" min="65" max="65"/>
-    <col width="9" customWidth="1" min="66" max="66"/>
-    <col width="9" customWidth="1" min="67" max="67"/>
-    <col width="9" customWidth="1" min="68" max="68"/>
-    <col width="9" customWidth="1" min="69" max="69"/>
-    <col width="9" customWidth="1" min="70" max="70"/>
-    <col width="9" customWidth="1" min="71" max="71"/>
-    <col width="14" customWidth="1" min="72" max="72"/>
-    <col width="22" customWidth="1" min="73" max="73"/>
-    <col width="14" customWidth="1" min="74" max="74"/>
-    <col width="15" customWidth="1" min="75" max="75"/>
-    <col width="22" customWidth="1" min="76" max="76"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Sample_Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Sample_Label</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Elevation</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Locality</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Dataset_DOI</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>Age_Unit</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>Age_Method</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>Rock_Type</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>TAS_Composition</t>
-        </is>
-      </c>
-      <c r="R1" s="4" t="inlineStr">
-        <is>
-          <t>Lithology</t>
-        </is>
-      </c>
-      <c r="S1" s="4" t="inlineStr">
-        <is>
-          <t>Magmatic_Series</t>
-        </is>
-      </c>
-      <c r="T1" s="4" t="inlineStr">
-        <is>
-          <t>Tectonic_Setting</t>
-        </is>
-      </c>
-      <c r="U1" s="4" t="inlineStr">
-        <is>
-          <t>Texture</t>
-        </is>
-      </c>
-      <c r="V1" s="4" t="inlineStr">
-        <is>
-          <t>Mineral_Assemblage</t>
-        </is>
-      </c>
-      <c r="W1" s="4" t="inlineStr">
-        <is>
-          <t>Alteration</t>
-        </is>
-      </c>
-      <c r="X1" s="5" t="inlineStr">
-        <is>
-          <t>Analytical_Method</t>
-        </is>
-      </c>
-      <c r="Y1" s="5" t="inlineStr">
-        <is>
-          <t>Laboratory</t>
-        </is>
-      </c>
-      <c r="Z1" s="5" t="inlineStr">
-        <is>
-          <t>Analysis_Date</t>
-        </is>
-      </c>
-      <c r="AA1" s="5" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="AB1" s="5" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="AC1" s="6" t="inlineStr">
-        <is>
-          <t>SiO2</t>
-        </is>
-      </c>
-      <c r="AD1" s="17" t="inlineStr">
-        <is>
-          <t>87Sr/86Sr</t>
-        </is>
-      </c>
-      <c r="AE1" s="17" t="inlineStr">
-        <is>
-          <t>87Sr/86Sr_2σ</t>
-        </is>
-      </c>
-      <c r="AF1" s="17" t="inlineStr">
-        <is>
-          <t>87Rb/86Sr</t>
-        </is>
-      </c>
-      <c r="AG1" s="17" t="inlineStr">
-        <is>
-          <t>Sr_iso</t>
-        </is>
-      </c>
-      <c r="AH1" s="17" t="inlineStr">
-        <is>
-          <t>Rb_iso</t>
-        </is>
-      </c>
-      <c r="AI1" s="17" t="inlineStr">
-        <is>
-          <t>εSr_initial</t>
-        </is>
-      </c>
-      <c r="AJ1" s="18" t="inlineStr">
-        <is>
-          <t>143Nd/144Nd</t>
-        </is>
-      </c>
-      <c r="AK1" s="18" t="inlineStr">
-        <is>
-          <t>143Nd/144Nd_2σ</t>
-        </is>
-      </c>
-      <c r="AL1" s="18" t="inlineStr">
-        <is>
-          <t>147Sm/144Nd</t>
-        </is>
-      </c>
-      <c r="AM1" s="18" t="inlineStr">
-        <is>
-          <t>Sm_iso</t>
-        </is>
-      </c>
-      <c r="AN1" s="18" t="inlineStr">
-        <is>
-          <t>Nd_iso</t>
-        </is>
-      </c>
-      <c r="AO1" s="18" t="inlineStr">
-        <is>
-          <t>εNd_initial</t>
-        </is>
-      </c>
-      <c r="AP1" s="18" t="inlineStr">
-        <is>
-          <t>TDM_Nd</t>
-        </is>
-      </c>
-      <c r="AQ1" s="19" t="inlineStr">
-        <is>
-          <t>206Pb/204Pb</t>
-        </is>
-      </c>
-      <c r="AR1" s="19" t="inlineStr">
-        <is>
-          <t>206Pb/204Pb_2σ</t>
-        </is>
-      </c>
-      <c r="AS1" s="19" t="inlineStr">
-        <is>
-          <t>207Pb/204Pb</t>
-        </is>
-      </c>
-      <c r="AT1" s="19" t="inlineStr">
-        <is>
-          <t>207Pb/204Pb_2σ</t>
-        </is>
-      </c>
-      <c r="AU1" s="19" t="inlineStr">
-        <is>
-          <t>208Pb/204Pb</t>
-        </is>
-      </c>
-      <c r="AV1" s="19" t="inlineStr">
-        <is>
-          <t>208Pb/204Pb_2σ</t>
-        </is>
-      </c>
-      <c r="AW1" s="19" t="inlineStr">
-        <is>
-          <t>Pb_iso</t>
-        </is>
-      </c>
-      <c r="AX1" s="19" t="inlineStr">
-        <is>
-          <t>U_iso</t>
-        </is>
-      </c>
-      <c r="AY1" s="19" t="inlineStr">
-        <is>
-          <t>Th_iso</t>
-        </is>
-      </c>
-      <c r="AZ1" s="20" t="inlineStr">
-        <is>
-          <t>176Hf/177Hf</t>
-        </is>
-      </c>
-      <c r="BA1" s="20" t="inlineStr">
-        <is>
-          <t>176Hf/177Hf_2σ</t>
-        </is>
-      </c>
-      <c r="BB1" s="20" t="inlineStr">
-        <is>
-          <t>176Lu/177Hf</t>
-        </is>
-      </c>
-      <c r="BC1" s="20" t="inlineStr">
-        <is>
-          <t>Hf_iso</t>
-        </is>
-      </c>
-      <c r="BD1" s="20" t="inlineStr">
-        <is>
-          <t>Lu_iso</t>
-        </is>
-      </c>
-      <c r="BE1" s="20" t="inlineStr">
-        <is>
-          <t>εHf_initial</t>
-        </is>
-      </c>
-      <c r="BF1" s="20" t="inlineStr">
-        <is>
-          <t>TDM_Hf</t>
-        </is>
-      </c>
-      <c r="BG1" s="21" t="inlineStr">
-        <is>
-          <t>187Os/188Os</t>
-        </is>
-      </c>
-      <c r="BH1" s="21" t="inlineStr">
-        <is>
-          <t>187Os/188Os_2σ</t>
-        </is>
-      </c>
-      <c r="BI1" s="21" t="inlineStr">
-        <is>
-          <t>187Re/188Os</t>
-        </is>
-      </c>
-      <c r="BJ1" s="21" t="inlineStr">
-        <is>
-          <t>Os_iso</t>
-        </is>
-      </c>
-      <c r="BK1" s="21" t="inlineStr">
-        <is>
-          <t>Re_iso</t>
-        </is>
-      </c>
-      <c r="BL1" s="21" t="inlineStr">
-        <is>
-          <t>γOs_initial</t>
-        </is>
-      </c>
-      <c r="BM1" s="22" t="inlineStr">
-        <is>
-          <t>δ18O</t>
-        </is>
-      </c>
-      <c r="BN1" s="22" t="inlineStr">
-        <is>
-          <t>δ18O_2σ</t>
-        </is>
-      </c>
-      <c r="BO1" s="22" t="inlineStr">
-        <is>
-          <t>δD</t>
-        </is>
-      </c>
-      <c r="BP1" s="22" t="inlineStr">
-        <is>
-          <t>δD_2σ</t>
-        </is>
-      </c>
-      <c r="BQ1" s="22" t="inlineStr">
-        <is>
-          <t>δ13C</t>
-        </is>
-      </c>
-      <c r="BR1" s="22" t="inlineStr">
-        <is>
-          <t>δ13C_2σ</t>
-        </is>
-      </c>
-      <c r="BS1" s="22" t="inlineStr">
-        <is>
-          <t>δ11B</t>
-        </is>
-      </c>
-      <c r="BT1" s="23" t="inlineStr">
-        <is>
-          <t>Iso_Method</t>
-        </is>
-      </c>
-      <c r="BU1" s="23" t="inlineStr">
-        <is>
-          <t>Iso_Laboratory</t>
-        </is>
-      </c>
-      <c r="BV1" s="23" t="inlineStr">
-        <is>
-          <t>Iso_Date</t>
-        </is>
-      </c>
-      <c r="BW1" s="23" t="inlineStr">
-        <is>
-          <t>Iso_Analyst</t>
-        </is>
-      </c>
-      <c r="BX1" s="23" t="inlineStr">
-        <is>
-          <t>Iso_Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="9" t="inlineStr"/>
-      <c r="B2" s="9" t="inlineStr"/>
-      <c r="C2" s="9" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr"/>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="11" t="inlineStr"/>
-      <c r="L2" s="11" t="inlineStr"/>
-      <c r="M2" s="12" t="inlineStr"/>
-      <c r="N2" s="12" t="inlineStr"/>
-      <c r="O2" s="12" t="inlineStr"/>
-      <c r="P2" s="12" t="inlineStr"/>
-      <c r="Q2" s="12" t="inlineStr"/>
-      <c r="R2" s="12" t="inlineStr"/>
-      <c r="S2" s="12" t="inlineStr"/>
-      <c r="T2" s="12" t="inlineStr"/>
-      <c r="U2" s="12" t="inlineStr"/>
-      <c r="V2" s="12" t="inlineStr"/>
-      <c r="W2" s="12" t="inlineStr"/>
-      <c r="X2" s="13" t="inlineStr"/>
-      <c r="Y2" s="13" t="inlineStr"/>
-      <c r="Z2" s="13" t="inlineStr"/>
-      <c r="AA2" s="13" t="inlineStr"/>
-      <c r="AB2" s="13" t="inlineStr"/>
-      <c r="AC2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AD2" s="24" t="inlineStr"/>
-      <c r="AE2" s="24" t="inlineStr"/>
-      <c r="AF2" s="24" t="inlineStr"/>
-      <c r="AG2" s="24" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AH2" s="24" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AI2" s="24" t="inlineStr"/>
-      <c r="AJ2" s="25" t="inlineStr"/>
-      <c r="AK2" s="25" t="inlineStr"/>
-      <c r="AL2" s="25" t="inlineStr"/>
-      <c r="AM2" s="25" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AN2" s="25" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AO2" s="25" t="inlineStr"/>
-      <c r="AP2" s="25" t="inlineStr">
-        <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="AQ2" s="26" t="inlineStr"/>
-      <c r="AR2" s="26" t="inlineStr"/>
-      <c r="AS2" s="26" t="inlineStr"/>
-      <c r="AT2" s="26" t="inlineStr"/>
-      <c r="AU2" s="26" t="inlineStr"/>
-      <c r="AV2" s="26" t="inlineStr"/>
-      <c r="AW2" s="26" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AX2" s="26" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AY2" s="26" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AZ2" s="27" t="inlineStr"/>
-      <c r="BA2" s="27" t="inlineStr"/>
-      <c r="BB2" s="27" t="inlineStr"/>
-      <c r="BC2" s="27" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BD2" s="27" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BE2" s="27" t="inlineStr"/>
-      <c r="BF2" s="27" t="inlineStr">
-        <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="BG2" s="28" t="inlineStr"/>
-      <c r="BH2" s="28" t="inlineStr"/>
-      <c r="BI2" s="28" t="inlineStr"/>
-      <c r="BJ2" s="28" t="inlineStr">
-        <is>
-          <t>ppb</t>
-        </is>
-      </c>
-      <c r="BK2" s="28" t="inlineStr">
-        <is>
-          <t>ppb</t>
-        </is>
-      </c>
-      <c r="BL2" s="28" t="inlineStr"/>
-      <c r="BM2" s="29" t="inlineStr">
-        <is>
-          <t>‰ VSMOW</t>
-        </is>
-      </c>
-      <c r="BN2" s="29" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
-      <c r="BO2" s="29" t="inlineStr">
-        <is>
-          <t>‰ VSMOW</t>
-        </is>
-      </c>
-      <c r="BP2" s="29" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
-      <c r="BQ2" s="29" t="inlineStr">
-        <is>
-          <t>‰ VPDB</t>
-        </is>
-      </c>
-      <c r="BR2" s="29" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
-      <c r="BS2" s="29" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
-      <c r="BT2" s="30" t="inlineStr"/>
-      <c r="BU2" s="30" t="inlineStr"/>
-      <c r="BV2" s="30" t="inlineStr"/>
-      <c r="BW2" s="30" t="inlineStr"/>
-      <c r="BX2" s="30" t="inlineStr"/>
     </row>
     <row r="3" ht="16" customHeight="1"/>
     <row r="4" ht="16" customHeight="1"/>
@@ -2651,25 +1819,935 @@
     <row r="202" ht="16" customHeight="1"/>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="N3:N1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ma, ka, Ga, yr" type="list">
+    <dataValidation sqref="J3:J1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: N, S" type="list">
+      <formula1>"N,S"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R3:R1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ma, ka, Ga, yr" type="list">
       <formula1>"Ma,ka,Ga,yr"</formula1>
     </dataValidation>
-    <dataValidation sqref="P3:P1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein" type="list">
+    <dataValidation sqref="T3:T1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein" type="list">
       <formula1>"Volcanic,Plutonic,Sub-volcanic,Pyroclastic,Vein"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q3:Q1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite" type="list">
+    <dataValidation sqref="U3:U1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite" type="list">
       <formula1>"Picro-basalt,Basalt,Basaltic andesite,Andesite,Dacite,Rhyolite,Trachy-basalt,Basaltic trachy-andesite,Trachy-andesite,Trachyte,Trachy-dacite,Tephrite,Phono-tephrite,Tephri-phonolite,Phonolite,Foidite,Gabbro,Diorite,Granodiorite,Granite,Monzogabbro,Monzodiorite,Monzonite,Syenite,Foid-syenite,Foidolite"</formula1>
     </dataValidation>
-    <dataValidation sqref="S3:S1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic" type="list">
+    <dataValidation sqref="W3:W1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic" type="list">
       <formula1>"Tholeiitic,Calc-alkaline,High-K calc-alkaline,Shoshonitic,Alkaline,Ultra-alkaline,Boninitic"</formula1>
     </dataValidation>
-    <dataValidation sqref="W3:W1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed" type="list">
+    <dataValidation sqref="AA3:AA1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed" type="list">
       <formula1>"Fresh,Slightly altered,Moderately altered,Strongly altered,Metamorphosed"</formula1>
     </dataValidation>
-    <dataValidation sqref="X3:X1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed" type="list">
+    <dataValidation sqref="AB3:AB1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed" type="list">
       <formula1>"XRF,ICP-OES,ICP-MS,Solution ICP-MS,LA-ICP-MS,EMP / EPMA,INAA,Wet chemistry,Mixed"</formula1>
     </dataValidation>
-    <dataValidation sqref="BT3:BT1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: TIMS, MC-ICP-MS, Solution MC-ICP-MS, LA-MC-ICP-MS, SIMS, SHRIMP, N-TIMS (Os), Laser fluorination (δ¹⁸O), EA-IRMS (δ¹³C, δD), CRDS, Mixed" type="list">
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CB2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="9" customWidth="1" min="37" max="37"/>
+    <col width="9" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="16" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="9" customWidth="1" min="43" max="43"/>
+    <col width="9" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="9" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="16" customWidth="1" min="48" max="48"/>
+    <col width="13" customWidth="1" min="49" max="49"/>
+    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="51" max="51"/>
+    <col width="16" customWidth="1" min="52" max="52"/>
+    <col width="9" customWidth="1" min="53" max="53"/>
+    <col width="9" customWidth="1" min="54" max="54"/>
+    <col width="9" customWidth="1" min="55" max="55"/>
+    <col width="13" customWidth="1" min="56" max="56"/>
+    <col width="16" customWidth="1" min="57" max="57"/>
+    <col width="13" customWidth="1" min="58" max="58"/>
+    <col width="9" customWidth="1" min="59" max="59"/>
+    <col width="9" customWidth="1" min="60" max="60"/>
+    <col width="13" customWidth="1" min="61" max="61"/>
+    <col width="9" customWidth="1" min="62" max="62"/>
+    <col width="13" customWidth="1" min="63" max="63"/>
+    <col width="16" customWidth="1" min="64" max="64"/>
+    <col width="13" customWidth="1" min="65" max="65"/>
+    <col width="9" customWidth="1" min="66" max="66"/>
+    <col width="9" customWidth="1" min="67" max="67"/>
+    <col width="13" customWidth="1" min="68" max="68"/>
+    <col width="9" customWidth="1" min="69" max="69"/>
+    <col width="9" customWidth="1" min="70" max="70"/>
+    <col width="9" customWidth="1" min="71" max="71"/>
+    <col width="9" customWidth="1" min="72" max="72"/>
+    <col width="9" customWidth="1" min="73" max="73"/>
+    <col width="9" customWidth="1" min="74" max="74"/>
+    <col width="9" customWidth="1" min="75" max="75"/>
+    <col width="14" customWidth="1" min="76" max="76"/>
+    <col width="22" customWidth="1" min="77" max="77"/>
+    <col width="14" customWidth="1" min="78" max="78"/>
+    <col width="15" customWidth="1" min="79" max="79"/>
+    <col width="22" customWidth="1" min="80" max="80"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sample_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sample_Label</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Easting</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>UTM_Zone</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Hemisphere</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Elevation</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Locality</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Dataset_DOI</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Age_Unit</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Age_Method</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Rock_Type</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>TAS_Composition</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Lithology</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Magmatic_Series</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Tectonic_Setting</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>Texture</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>Mineral_Assemblage</t>
+        </is>
+      </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="AB1" s="5" t="inlineStr">
+        <is>
+          <t>Analytical_Method</t>
+        </is>
+      </c>
+      <c r="AC1" s="5" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="AD1" s="5" t="inlineStr">
+        <is>
+          <t>Analysis_Date</t>
+        </is>
+      </c>
+      <c r="AE1" s="5" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="AF1" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AG1" s="6" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="AH1" s="17" t="inlineStr">
+        <is>
+          <t>87Sr/86Sr</t>
+        </is>
+      </c>
+      <c r="AI1" s="17" t="inlineStr">
+        <is>
+          <t>87Sr/86Sr_2σ</t>
+        </is>
+      </c>
+      <c r="AJ1" s="17" t="inlineStr">
+        <is>
+          <t>87Rb/86Sr</t>
+        </is>
+      </c>
+      <c r="AK1" s="17" t="inlineStr">
+        <is>
+          <t>Sr_iso</t>
+        </is>
+      </c>
+      <c r="AL1" s="17" t="inlineStr">
+        <is>
+          <t>Rb_iso</t>
+        </is>
+      </c>
+      <c r="AM1" s="17" t="inlineStr">
+        <is>
+          <t>εSr_initial</t>
+        </is>
+      </c>
+      <c r="AN1" s="18" t="inlineStr">
+        <is>
+          <t>143Nd/144Nd</t>
+        </is>
+      </c>
+      <c r="AO1" s="18" t="inlineStr">
+        <is>
+          <t>143Nd/144Nd_2σ</t>
+        </is>
+      </c>
+      <c r="AP1" s="18" t="inlineStr">
+        <is>
+          <t>147Sm/144Nd</t>
+        </is>
+      </c>
+      <c r="AQ1" s="18" t="inlineStr">
+        <is>
+          <t>Sm_iso</t>
+        </is>
+      </c>
+      <c r="AR1" s="18" t="inlineStr">
+        <is>
+          <t>Nd_iso</t>
+        </is>
+      </c>
+      <c r="AS1" s="18" t="inlineStr">
+        <is>
+          <t>εNd_initial</t>
+        </is>
+      </c>
+      <c r="AT1" s="18" t="inlineStr">
+        <is>
+          <t>TDM_Nd</t>
+        </is>
+      </c>
+      <c r="AU1" s="19" t="inlineStr">
+        <is>
+          <t>206Pb/204Pb</t>
+        </is>
+      </c>
+      <c r="AV1" s="19" t="inlineStr">
+        <is>
+          <t>206Pb/204Pb_2σ</t>
+        </is>
+      </c>
+      <c r="AW1" s="19" t="inlineStr">
+        <is>
+          <t>207Pb/204Pb</t>
+        </is>
+      </c>
+      <c r="AX1" s="19" t="inlineStr">
+        <is>
+          <t>207Pb/204Pb_2σ</t>
+        </is>
+      </c>
+      <c r="AY1" s="19" t="inlineStr">
+        <is>
+          <t>208Pb/204Pb</t>
+        </is>
+      </c>
+      <c r="AZ1" s="19" t="inlineStr">
+        <is>
+          <t>208Pb/204Pb_2σ</t>
+        </is>
+      </c>
+      <c r="BA1" s="19" t="inlineStr">
+        <is>
+          <t>Pb_iso</t>
+        </is>
+      </c>
+      <c r="BB1" s="19" t="inlineStr">
+        <is>
+          <t>U_iso</t>
+        </is>
+      </c>
+      <c r="BC1" s="19" t="inlineStr">
+        <is>
+          <t>Th_iso</t>
+        </is>
+      </c>
+      <c r="BD1" s="20" t="inlineStr">
+        <is>
+          <t>176Hf/177Hf</t>
+        </is>
+      </c>
+      <c r="BE1" s="20" t="inlineStr">
+        <is>
+          <t>176Hf/177Hf_2σ</t>
+        </is>
+      </c>
+      <c r="BF1" s="20" t="inlineStr">
+        <is>
+          <t>176Lu/177Hf</t>
+        </is>
+      </c>
+      <c r="BG1" s="20" t="inlineStr">
+        <is>
+          <t>Hf_iso</t>
+        </is>
+      </c>
+      <c r="BH1" s="20" t="inlineStr">
+        <is>
+          <t>Lu_iso</t>
+        </is>
+      </c>
+      <c r="BI1" s="20" t="inlineStr">
+        <is>
+          <t>εHf_initial</t>
+        </is>
+      </c>
+      <c r="BJ1" s="20" t="inlineStr">
+        <is>
+          <t>TDM_Hf</t>
+        </is>
+      </c>
+      <c r="BK1" s="21" t="inlineStr">
+        <is>
+          <t>187Os/188Os</t>
+        </is>
+      </c>
+      <c r="BL1" s="21" t="inlineStr">
+        <is>
+          <t>187Os/188Os_2σ</t>
+        </is>
+      </c>
+      <c r="BM1" s="21" t="inlineStr">
+        <is>
+          <t>187Re/188Os</t>
+        </is>
+      </c>
+      <c r="BN1" s="21" t="inlineStr">
+        <is>
+          <t>Os_iso</t>
+        </is>
+      </c>
+      <c r="BO1" s="21" t="inlineStr">
+        <is>
+          <t>Re_iso</t>
+        </is>
+      </c>
+      <c r="BP1" s="21" t="inlineStr">
+        <is>
+          <t>γOs_initial</t>
+        </is>
+      </c>
+      <c r="BQ1" s="22" t="inlineStr">
+        <is>
+          <t>δ18O</t>
+        </is>
+      </c>
+      <c r="BR1" s="22" t="inlineStr">
+        <is>
+          <t>δ18O_2σ</t>
+        </is>
+      </c>
+      <c r="BS1" s="22" t="inlineStr">
+        <is>
+          <t>δD</t>
+        </is>
+      </c>
+      <c r="BT1" s="22" t="inlineStr">
+        <is>
+          <t>δD_2σ</t>
+        </is>
+      </c>
+      <c r="BU1" s="22" t="inlineStr">
+        <is>
+          <t>δ13C</t>
+        </is>
+      </c>
+      <c r="BV1" s="22" t="inlineStr">
+        <is>
+          <t>δ13C_2σ</t>
+        </is>
+      </c>
+      <c r="BW1" s="22" t="inlineStr">
+        <is>
+          <t>δ11B</t>
+        </is>
+      </c>
+      <c r="BX1" s="23" t="inlineStr">
+        <is>
+          <t>Iso_Method</t>
+        </is>
+      </c>
+      <c r="BY1" s="23" t="inlineStr">
+        <is>
+          <t>Iso_Laboratory</t>
+        </is>
+      </c>
+      <c r="BZ1" s="23" t="inlineStr">
+        <is>
+          <t>Iso_Date</t>
+        </is>
+      </c>
+      <c r="CA1" s="23" t="inlineStr">
+        <is>
+          <t>Iso_Analyst</t>
+        </is>
+      </c>
+      <c r="CB1" s="23" t="inlineStr">
+        <is>
+          <t>Iso_Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="9" t="inlineStr"/>
+      <c r="B2" s="9" t="inlineStr"/>
+      <c r="C2" s="9" t="inlineStr"/>
+      <c r="D2" s="9" t="inlineStr"/>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" s="11" t="inlineStr"/>
+      <c r="P2" s="11" t="inlineStr"/>
+      <c r="Q2" s="12" t="inlineStr"/>
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr"/>
+      <c r="T2" s="12" t="inlineStr"/>
+      <c r="U2" s="12" t="inlineStr"/>
+      <c r="V2" s="12" t="inlineStr"/>
+      <c r="W2" s="12" t="inlineStr"/>
+      <c r="X2" s="12" t="inlineStr"/>
+      <c r="Y2" s="12" t="inlineStr"/>
+      <c r="Z2" s="12" t="inlineStr"/>
+      <c r="AA2" s="12" t="inlineStr"/>
+      <c r="AB2" s="13" t="inlineStr"/>
+      <c r="AC2" s="13" t="inlineStr"/>
+      <c r="AD2" s="13" t="inlineStr"/>
+      <c r="AE2" s="13" t="inlineStr"/>
+      <c r="AF2" s="13" t="inlineStr"/>
+      <c r="AG2" s="14" t="inlineStr">
+        <is>
+          <t>wt%</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="inlineStr"/>
+      <c r="AI2" s="24" t="inlineStr"/>
+      <c r="AJ2" s="24" t="inlineStr"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="AL2" s="24" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="AM2" s="24" t="inlineStr"/>
+      <c r="AN2" s="25" t="inlineStr"/>
+      <c r="AO2" s="25" t="inlineStr"/>
+      <c r="AP2" s="25" t="inlineStr"/>
+      <c r="AQ2" s="25" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="AR2" s="25" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="AS2" s="25" t="inlineStr"/>
+      <c r="AT2" s="25" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="AU2" s="26" t="inlineStr"/>
+      <c r="AV2" s="26" t="inlineStr"/>
+      <c r="AW2" s="26" t="inlineStr"/>
+      <c r="AX2" s="26" t="inlineStr"/>
+      <c r="AY2" s="26" t="inlineStr"/>
+      <c r="AZ2" s="26" t="inlineStr"/>
+      <c r="BA2" s="26" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="BB2" s="26" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="BC2" s="26" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="BD2" s="27" t="inlineStr"/>
+      <c r="BE2" s="27" t="inlineStr"/>
+      <c r="BF2" s="27" t="inlineStr"/>
+      <c r="BG2" s="27" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="BH2" s="27" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+      <c r="BI2" s="27" t="inlineStr"/>
+      <c r="BJ2" s="27" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="BK2" s="28" t="inlineStr"/>
+      <c r="BL2" s="28" t="inlineStr"/>
+      <c r="BM2" s="28" t="inlineStr"/>
+      <c r="BN2" s="28" t="inlineStr">
+        <is>
+          <t>ppb</t>
+        </is>
+      </c>
+      <c r="BO2" s="28" t="inlineStr">
+        <is>
+          <t>ppb</t>
+        </is>
+      </c>
+      <c r="BP2" s="28" t="inlineStr"/>
+      <c r="BQ2" s="29" t="inlineStr">
+        <is>
+          <t>‰ VSMOW</t>
+        </is>
+      </c>
+      <c r="BR2" s="29" t="inlineStr">
+        <is>
+          <t>‰</t>
+        </is>
+      </c>
+      <c r="BS2" s="29" t="inlineStr">
+        <is>
+          <t>‰ VSMOW</t>
+        </is>
+      </c>
+      <c r="BT2" s="29" t="inlineStr">
+        <is>
+          <t>‰</t>
+        </is>
+      </c>
+      <c r="BU2" s="29" t="inlineStr">
+        <is>
+          <t>‰ VPDB</t>
+        </is>
+      </c>
+      <c r="BV2" s="29" t="inlineStr">
+        <is>
+          <t>‰</t>
+        </is>
+      </c>
+      <c r="BW2" s="29" t="inlineStr">
+        <is>
+          <t>‰</t>
+        </is>
+      </c>
+      <c r="BX2" s="30" t="inlineStr"/>
+      <c r="BY2" s="30" t="inlineStr"/>
+      <c r="BZ2" s="30" t="inlineStr"/>
+      <c r="CA2" s="30" t="inlineStr"/>
+      <c r="CB2" s="30" t="inlineStr"/>
+    </row>
+    <row r="3" ht="16" customHeight="1"/>
+    <row r="4" ht="16" customHeight="1"/>
+    <row r="5" ht="16" customHeight="1"/>
+    <row r="6" ht="16" customHeight="1"/>
+    <row r="7" ht="16" customHeight="1"/>
+    <row r="8" ht="16" customHeight="1"/>
+    <row r="9" ht="16" customHeight="1"/>
+    <row r="10" ht="16" customHeight="1"/>
+    <row r="11" ht="16" customHeight="1"/>
+    <row r="12" ht="16" customHeight="1"/>
+    <row r="13" ht="16" customHeight="1"/>
+    <row r="14" ht="16" customHeight="1"/>
+    <row r="15" ht="16" customHeight="1"/>
+    <row r="16" ht="16" customHeight="1"/>
+    <row r="17" ht="16" customHeight="1"/>
+    <row r="18" ht="16" customHeight="1"/>
+    <row r="19" ht="16" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1"/>
+    <row r="21" ht="16" customHeight="1"/>
+    <row r="22" ht="16" customHeight="1"/>
+    <row r="23" ht="16" customHeight="1"/>
+    <row r="24" ht="16" customHeight="1"/>
+    <row r="25" ht="16" customHeight="1"/>
+    <row r="26" ht="16" customHeight="1"/>
+    <row r="27" ht="16" customHeight="1"/>
+    <row r="28" ht="16" customHeight="1"/>
+    <row r="29" ht="16" customHeight="1"/>
+    <row r="30" ht="16" customHeight="1"/>
+    <row r="31" ht="16" customHeight="1"/>
+    <row r="32" ht="16" customHeight="1"/>
+    <row r="33" ht="16" customHeight="1"/>
+    <row r="34" ht="16" customHeight="1"/>
+    <row r="35" ht="16" customHeight="1"/>
+    <row r="36" ht="16" customHeight="1"/>
+    <row r="37" ht="16" customHeight="1"/>
+    <row r="38" ht="16" customHeight="1"/>
+    <row r="39" ht="16" customHeight="1"/>
+    <row r="40" ht="16" customHeight="1"/>
+    <row r="41" ht="16" customHeight="1"/>
+    <row r="42" ht="16" customHeight="1"/>
+    <row r="43" ht="16" customHeight="1"/>
+    <row r="44" ht="16" customHeight="1"/>
+    <row r="45" ht="16" customHeight="1"/>
+    <row r="46" ht="16" customHeight="1"/>
+    <row r="47" ht="16" customHeight="1"/>
+    <row r="48" ht="16" customHeight="1"/>
+    <row r="49" ht="16" customHeight="1"/>
+    <row r="50" ht="16" customHeight="1"/>
+    <row r="51" ht="16" customHeight="1"/>
+    <row r="52" ht="16" customHeight="1"/>
+    <row r="53" ht="16" customHeight="1"/>
+    <row r="54" ht="16" customHeight="1"/>
+    <row r="55" ht="16" customHeight="1"/>
+    <row r="56" ht="16" customHeight="1"/>
+    <row r="57" ht="16" customHeight="1"/>
+    <row r="58" ht="16" customHeight="1"/>
+    <row r="59" ht="16" customHeight="1"/>
+    <row r="60" ht="16" customHeight="1"/>
+    <row r="61" ht="16" customHeight="1"/>
+    <row r="62" ht="16" customHeight="1"/>
+    <row r="63" ht="16" customHeight="1"/>
+    <row r="64" ht="16" customHeight="1"/>
+    <row r="65" ht="16" customHeight="1"/>
+    <row r="66" ht="16" customHeight="1"/>
+    <row r="67" ht="16" customHeight="1"/>
+    <row r="68" ht="16" customHeight="1"/>
+    <row r="69" ht="16" customHeight="1"/>
+    <row r="70" ht="16" customHeight="1"/>
+    <row r="71" ht="16" customHeight="1"/>
+    <row r="72" ht="16" customHeight="1"/>
+    <row r="73" ht="16" customHeight="1"/>
+    <row r="74" ht="16" customHeight="1"/>
+    <row r="75" ht="16" customHeight="1"/>
+    <row r="76" ht="16" customHeight="1"/>
+    <row r="77" ht="16" customHeight="1"/>
+    <row r="78" ht="16" customHeight="1"/>
+    <row r="79" ht="16" customHeight="1"/>
+    <row r="80" ht="16" customHeight="1"/>
+    <row r="81" ht="16" customHeight="1"/>
+    <row r="82" ht="16" customHeight="1"/>
+    <row r="83" ht="16" customHeight="1"/>
+    <row r="84" ht="16" customHeight="1"/>
+    <row r="85" ht="16" customHeight="1"/>
+    <row r="86" ht="16" customHeight="1"/>
+    <row r="87" ht="16" customHeight="1"/>
+    <row r="88" ht="16" customHeight="1"/>
+    <row r="89" ht="16" customHeight="1"/>
+    <row r="90" ht="16" customHeight="1"/>
+    <row r="91" ht="16" customHeight="1"/>
+    <row r="92" ht="16" customHeight="1"/>
+    <row r="93" ht="16" customHeight="1"/>
+    <row r="94" ht="16" customHeight="1"/>
+    <row r="95" ht="16" customHeight="1"/>
+    <row r="96" ht="16" customHeight="1"/>
+    <row r="97" ht="16" customHeight="1"/>
+    <row r="98" ht="16" customHeight="1"/>
+    <row r="99" ht="16" customHeight="1"/>
+    <row r="100" ht="16" customHeight="1"/>
+    <row r="101" ht="16" customHeight="1"/>
+    <row r="102" ht="16" customHeight="1"/>
+    <row r="103" ht="16" customHeight="1"/>
+    <row r="104" ht="16" customHeight="1"/>
+    <row r="105" ht="16" customHeight="1"/>
+    <row r="106" ht="16" customHeight="1"/>
+    <row r="107" ht="16" customHeight="1"/>
+    <row r="108" ht="16" customHeight="1"/>
+    <row r="109" ht="16" customHeight="1"/>
+    <row r="110" ht="16" customHeight="1"/>
+    <row r="111" ht="16" customHeight="1"/>
+    <row r="112" ht="16" customHeight="1"/>
+    <row r="113" ht="16" customHeight="1"/>
+    <row r="114" ht="16" customHeight="1"/>
+    <row r="115" ht="16" customHeight="1"/>
+    <row r="116" ht="16" customHeight="1"/>
+    <row r="117" ht="16" customHeight="1"/>
+    <row r="118" ht="16" customHeight="1"/>
+    <row r="119" ht="16" customHeight="1"/>
+    <row r="120" ht="16" customHeight="1"/>
+    <row r="121" ht="16" customHeight="1"/>
+    <row r="122" ht="16" customHeight="1"/>
+    <row r="123" ht="16" customHeight="1"/>
+    <row r="124" ht="16" customHeight="1"/>
+    <row r="125" ht="16" customHeight="1"/>
+    <row r="126" ht="16" customHeight="1"/>
+    <row r="127" ht="16" customHeight="1"/>
+    <row r="128" ht="16" customHeight="1"/>
+    <row r="129" ht="16" customHeight="1"/>
+    <row r="130" ht="16" customHeight="1"/>
+    <row r="131" ht="16" customHeight="1"/>
+    <row r="132" ht="16" customHeight="1"/>
+    <row r="133" ht="16" customHeight="1"/>
+    <row r="134" ht="16" customHeight="1"/>
+    <row r="135" ht="16" customHeight="1"/>
+    <row r="136" ht="16" customHeight="1"/>
+    <row r="137" ht="16" customHeight="1"/>
+    <row r="138" ht="16" customHeight="1"/>
+    <row r="139" ht="16" customHeight="1"/>
+    <row r="140" ht="16" customHeight="1"/>
+    <row r="141" ht="16" customHeight="1"/>
+    <row r="142" ht="16" customHeight="1"/>
+    <row r="143" ht="16" customHeight="1"/>
+    <row r="144" ht="16" customHeight="1"/>
+    <row r="145" ht="16" customHeight="1"/>
+    <row r="146" ht="16" customHeight="1"/>
+    <row r="147" ht="16" customHeight="1"/>
+    <row r="148" ht="16" customHeight="1"/>
+    <row r="149" ht="16" customHeight="1"/>
+    <row r="150" ht="16" customHeight="1"/>
+    <row r="151" ht="16" customHeight="1"/>
+    <row r="152" ht="16" customHeight="1"/>
+    <row r="153" ht="16" customHeight="1"/>
+    <row r="154" ht="16" customHeight="1"/>
+    <row r="155" ht="16" customHeight="1"/>
+    <row r="156" ht="16" customHeight="1"/>
+    <row r="157" ht="16" customHeight="1"/>
+    <row r="158" ht="16" customHeight="1"/>
+    <row r="159" ht="16" customHeight="1"/>
+    <row r="160" ht="16" customHeight="1"/>
+    <row r="161" ht="16" customHeight="1"/>
+    <row r="162" ht="16" customHeight="1"/>
+    <row r="163" ht="16" customHeight="1"/>
+    <row r="164" ht="16" customHeight="1"/>
+    <row r="165" ht="16" customHeight="1"/>
+    <row r="166" ht="16" customHeight="1"/>
+    <row r="167" ht="16" customHeight="1"/>
+    <row r="168" ht="16" customHeight="1"/>
+    <row r="169" ht="16" customHeight="1"/>
+    <row r="170" ht="16" customHeight="1"/>
+    <row r="171" ht="16" customHeight="1"/>
+    <row r="172" ht="16" customHeight="1"/>
+    <row r="173" ht="16" customHeight="1"/>
+    <row r="174" ht="16" customHeight="1"/>
+    <row r="175" ht="16" customHeight="1"/>
+    <row r="176" ht="16" customHeight="1"/>
+    <row r="177" ht="16" customHeight="1"/>
+    <row r="178" ht="16" customHeight="1"/>
+    <row r="179" ht="16" customHeight="1"/>
+    <row r="180" ht="16" customHeight="1"/>
+    <row r="181" ht="16" customHeight="1"/>
+    <row r="182" ht="16" customHeight="1"/>
+    <row r="183" ht="16" customHeight="1"/>
+    <row r="184" ht="16" customHeight="1"/>
+    <row r="185" ht="16" customHeight="1"/>
+    <row r="186" ht="16" customHeight="1"/>
+    <row r="187" ht="16" customHeight="1"/>
+    <row r="188" ht="16" customHeight="1"/>
+    <row r="189" ht="16" customHeight="1"/>
+    <row r="190" ht="16" customHeight="1"/>
+    <row r="191" ht="16" customHeight="1"/>
+    <row r="192" ht="16" customHeight="1"/>
+    <row r="193" ht="16" customHeight="1"/>
+    <row r="194" ht="16" customHeight="1"/>
+    <row r="195" ht="16" customHeight="1"/>
+    <row r="196" ht="16" customHeight="1"/>
+    <row r="197" ht="16" customHeight="1"/>
+    <row r="198" ht="16" customHeight="1"/>
+    <row r="199" ht="16" customHeight="1"/>
+    <row r="200" ht="16" customHeight="1"/>
+    <row r="201" ht="16" customHeight="1"/>
+    <row r="202" ht="16" customHeight="1"/>
+  </sheetData>
+  <dataValidations count="8">
+    <dataValidation sqref="J3:J1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: N, S" type="list">
+      <formula1>"N,S"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R3:R1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ma, ka, Ga, yr" type="list">
+      <formula1>"Ma,ka,Ga,yr"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T3:T1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein" type="list">
+      <formula1>"Volcanic,Plutonic,Sub-volcanic,Pyroclastic,Vein"</formula1>
+    </dataValidation>
+    <dataValidation sqref="U3:U1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite" type="list">
+      <formula1>"Picro-basalt,Basalt,Basaltic andesite,Andesite,Dacite,Rhyolite,Trachy-basalt,Basaltic trachy-andesite,Trachy-andesite,Trachyte,Trachy-dacite,Tephrite,Phono-tephrite,Tephri-phonolite,Phonolite,Foidite,Gabbro,Diorite,Granodiorite,Granite,Monzogabbro,Monzodiorite,Monzonite,Syenite,Foid-syenite,Foidolite"</formula1>
+    </dataValidation>
+    <dataValidation sqref="W3:W1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic" type="list">
+      <formula1>"Tholeiitic,Calc-alkaline,High-K calc-alkaline,Shoshonitic,Alkaline,Ultra-alkaline,Boninitic"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AA3:AA1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed" type="list">
+      <formula1>"Fresh,Slightly altered,Moderately altered,Strongly altered,Metamorphosed"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB3:AB1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed" type="list">
+      <formula1>"XRF,ICP-OES,ICP-MS,Solution ICP-MS,LA-ICP-MS,EMP / EPMA,INAA,Wet chemistry,Mixed"</formula1>
+    </dataValidation>
+    <dataValidation sqref="BX3:BX1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: TIMS, MC-ICP-MS, Solution MC-ICP-MS, LA-MC-ICP-MS, SIMS, SHRIMP, N-TIMS (Os), Laser fluorination (δ¹⁸O), EA-IRMS (δ¹³C, δD), CRDS, Mixed" type="list">
       <formula1>"TIMS,MC-ICP-MS,Solution MC-ICP-MS,LA-MC-ICP-MS,SIMS,SHRIMP,N-TIMS (Os),Laser fluorination (δ¹⁸O),EA-IRMS (δ¹³C, δD),CRDS,Mixed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3557,7 +3635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3823,7 +3901,7 @@
       </c>
       <c r="C8" s="40" t="inlineStr">
         <is>
-          <t>Elevation</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="D8" s="43" t="inlineStr">
@@ -3839,12 +3917,12 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>483382</t>
         </is>
       </c>
       <c r="H8" s="42" t="inlineStr">
         <is>
-          <t>Sampling elevation above sea level.</t>
+          <t>UTM easting, if the location is in UTM rather than degrees; the map reads either.</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3937,7 @@
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="D9" s="43" t="inlineStr">
@@ -3867,16 +3945,20 @@
           <t>Location</t>
         </is>
       </c>
-      <c r="E9" s="38" t="inlineStr"/>
+      <c r="E9" s="38" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>7852139</t>
         </is>
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
-          <t>Country where the sample was collected.</t>
+          <t>UTM northing, in metres from the equator (south: from 10 000 km below it).</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3973,7 @@
       </c>
       <c r="C10" s="40" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>UTM_Zone</t>
         </is>
       </c>
       <c r="D10" s="43" t="inlineStr">
@@ -3903,12 +3985,12 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
-          <t>State / province / volcanic field.</t>
+          <t>UTM zone number, 1-60.</t>
         </is>
       </c>
     </row>
@@ -3923,7 +4005,7 @@
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
-          <t>Locality</t>
+          <t>Hemisphere</t>
         </is>
       </c>
       <c r="D11" s="43" t="inlineStr">
@@ -3932,15 +4014,19 @@
         </is>
       </c>
       <c r="E11" s="38" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>N, S</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Taapaca Volcanic Complex</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H11" s="42" t="inlineStr">
         <is>
-          <t>Specific outcrop or feature.</t>
+          <t>N or S: the UTM hemisphere. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
@@ -3955,24 +4041,28 @@
       </c>
       <c r="C12" s="40" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="D12" s="44" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="E12" s="38" t="inlineStr"/>
+          <t>Elevation</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E12" s="38" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Aguirre et al. (2022) Lithos 408</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="H12" s="42" t="inlineStr">
         <is>
-          <t>Bibliographic reference for the analysis (author year, or DOI).</t>
+          <t>Sampling elevation above sea level.</t>
         </is>
       </c>
     </row>
@@ -3987,24 +4077,24 @@
       </c>
       <c r="C13" s="40" t="inlineStr">
         <is>
-          <t>Dataset_DOI</t>
-        </is>
-      </c>
-      <c r="D13" s="44" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
         </is>
       </c>
       <c r="E13" s="38" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10.5281/zenodo.1234567</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="H13" s="42" t="inlineStr">
         <is>
-          <t>DOI of the original dataset, if published separately.</t>
+          <t>Country where the sample was collected.</t>
         </is>
       </c>
     </row>
@@ -4019,24 +4109,24 @@
       </c>
       <c r="C14" s="40" t="inlineStr">
         <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="D14" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
         </is>
       </c>
       <c r="E14" s="38" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="H14" s="42" t="inlineStr">
         <is>
-          <t>Numeric age (matched with AGE_UNIT). Leave empty if unknown.</t>
+          <t>State / province / volcanic field.</t>
         </is>
       </c>
     </row>
@@ -4051,28 +4141,24 @@
       </c>
       <c r="C15" s="40" t="inlineStr">
         <is>
-          <t>Age_Unit</t>
-        </is>
-      </c>
-      <c r="D15" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
+          <t>Locality</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
         </is>
       </c>
       <c r="E15" s="38" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ma, ka, Ga, yr</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Taapaca Volcanic Complex</t>
         </is>
       </c>
       <c r="H15" s="42" t="inlineStr">
         <is>
-          <t>Unit of the AGE column. Pick from the dropdown.</t>
+          <t>Specific outcrop or feature.</t>
         </is>
       </c>
     </row>
@@ -4087,24 +4173,24 @@
       </c>
       <c r="C16" s="40" t="inlineStr">
         <is>
-          <t>Age_Method</t>
-        </is>
-      </c>
-      <c r="D16" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D16" s="44" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="E16" s="38" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ar-Ar</t>
+          <t>Aguirre et al. (2022) Lithos 408</t>
         </is>
       </c>
       <c r="H16" s="42" t="inlineStr">
         <is>
-          <t>Dating method (K-Ar, Ar-Ar, U-Pb, fission track, stratigraphic).</t>
+          <t>Bibliographic reference for the analysis (author year, or DOI).</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4205,24 @@
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
-          <t>Rock_Type</t>
-        </is>
-      </c>
-      <c r="D17" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
+          <t>Dataset_DOI</t>
+        </is>
+      </c>
+      <c r="D17" s="44" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="E17" s="38" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Volcanic</t>
+          <t>10.5281/zenodo.1234567</t>
         </is>
       </c>
       <c r="H17" s="42" t="inlineStr">
         <is>
-          <t>Volcanic vs. plutonic family — used by B.I.R.D.S to pick the right TAS panel and tectonic catalogue.</t>
+          <t>DOI of the original dataset, if published separately.</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4237,7 @@
       </c>
       <c r="C18" s="40" t="inlineStr">
         <is>
-          <t>TAS_Composition</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="D18" s="45" t="inlineStr">
@@ -4164,19 +4246,15 @@
         </is>
       </c>
       <c r="E18" s="38" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Basaltic andesite</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="H18" s="42" t="inlineStr">
         <is>
-          <t>Rock name from the TAS diagram (Le Bas et al. 1986). Leave empty to let B.I.R.D.S compute it from SiO2 / alkalis.</t>
+          <t>Numeric age (matched with AGE_UNIT). Leave empty if unknown.</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4269,7 @@
       </c>
       <c r="C19" s="40" t="inlineStr">
         <is>
-          <t>Lithology</t>
+          <t>Age_Unit</t>
         </is>
       </c>
       <c r="D19" s="45" t="inlineStr">
@@ -4200,15 +4278,19 @@
         </is>
       </c>
       <c r="E19" s="38" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ma, ka, Ga, yr</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Olivine basalt</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="H19" s="42" t="inlineStr">
         <is>
-          <t>Petrographic name beyond TAS (e.g. olivine basalt, biotite-amphibole granodiorite).</t>
+          <t>Unit of the AGE column. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4305,7 @@
       </c>
       <c r="C20" s="40" t="inlineStr">
         <is>
-          <t>Magmatic_Series</t>
+          <t>Age_Method</t>
         </is>
       </c>
       <c r="D20" s="45" t="inlineStr">
@@ -4232,19 +4314,15 @@
         </is>
       </c>
       <c r="E20" s="38" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calc-alkaline</t>
+          <t>Ar-Ar</t>
         </is>
       </c>
       <c r="H20" s="42" t="inlineStr">
         <is>
-          <t>Magma series. Optional — also derivable from K2O-SiO2 and AFM diagrams.</t>
+          <t>Dating method (K-Ar, Ar-Ar, U-Pb, fission track, stratigraphic).</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4337,7 @@
       </c>
       <c r="C21" s="40" t="inlineStr">
         <is>
-          <t>Tectonic_Setting</t>
+          <t>Rock_Type</t>
         </is>
       </c>
       <c r="D21" s="45" t="inlineStr">
@@ -4268,15 +4346,19 @@
         </is>
       </c>
       <c r="E21" s="38" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Continental arc</t>
+          <t>Volcanic</t>
         </is>
       </c>
       <c r="H21" s="42" t="inlineStr">
         <is>
-          <t>Inferred tectonic environment (MORB, OIB, IAB, CRB, OP, ...).</t>
+          <t>Volcanic vs. plutonic family — used by B.I.R.D.S to pick the right TAS panel and tectonic catalogue.</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4373,7 @@
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
-          <t>Texture</t>
+          <t>TAS_Composition</t>
         </is>
       </c>
       <c r="D22" s="45" t="inlineStr">
@@ -4300,15 +4382,19 @@
         </is>
       </c>
       <c r="E22" s="38" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porphyritic</t>
+          <t>Basaltic andesite</t>
         </is>
       </c>
       <c r="H22" s="42" t="inlineStr">
         <is>
-          <t>Porphyritic / aphanitic / glassy / phaneritic / vesicular / etc.</t>
+          <t>Rock name from the TAS diagram (Le Bas et al. 1986). Leave empty to let B.I.R.D.S compute it from SiO2 / alkalis.</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4409,7 @@
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
-          <t>Mineral_Assemblage</t>
+          <t>Lithology</t>
         </is>
       </c>
       <c r="D23" s="45" t="inlineStr">
@@ -4335,12 +4421,12 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pl + Cpx + Ol ± Opx</t>
+          <t>Olivine basalt</t>
         </is>
       </c>
       <c r="H23" s="42" t="inlineStr">
         <is>
-          <t>Main minerals (plagioclase, olivine, clinopyroxene, amphibole, biotite, K-feldspar, quartz ...).</t>
+          <t>Petrographic name beyond TAS (e.g. olivine basalt, biotite-amphibole granodiorite).</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4441,7 @@
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>Magmatic_Series</t>
         </is>
       </c>
       <c r="D24" s="45" t="inlineStr">
@@ -4366,17 +4452,17 @@
       <c r="E24" s="38" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed</t>
+          <t>Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Calc-alkaline</t>
         </is>
       </c>
       <c r="H24" s="42" t="inlineStr">
         <is>
-          <t>Visual / petrographic alteration grade.</t>
+          <t>Magma series. Optional — also derivable from K2O-SiO2 and AFM diagrams.</t>
         </is>
       </c>
     </row>
@@ -4391,28 +4477,24 @@
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
-          <t>Analytical_Method</t>
-        </is>
-      </c>
-      <c r="D25" s="46" t="inlineStr">
-        <is>
-          <t>Analysis</t>
+          <t>Tectonic_Setting</t>
+        </is>
+      </c>
+      <c r="D25" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E25" s="38" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>XRF + ICP-MS</t>
+          <t>Continental arc</t>
         </is>
       </c>
       <c r="H25" s="42" t="inlineStr">
         <is>
-          <t>Technique used for the bulk analysis.</t>
+          <t>Inferred tectonic environment (MORB, OIB, IAB, CRB, OP, ...).</t>
         </is>
       </c>
     </row>
@@ -4427,24 +4509,24 @@
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
-          <t>Laboratory</t>
-        </is>
-      </c>
-      <c r="D26" s="46" t="inlineStr">
-        <is>
-          <t>Analysis</t>
+          <t>Texture</t>
+        </is>
+      </c>
+      <c r="D26" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E26" s="38" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ALS Geochemistry (Vancouver)</t>
+          <t>Porphyritic</t>
         </is>
       </c>
       <c r="H26" s="42" t="inlineStr">
         <is>
-          <t>Lab where the analysis was carried out.</t>
+          <t>Porphyritic / aphanitic / glassy / phaneritic / vesicular / etc.</t>
         </is>
       </c>
     </row>
@@ -4459,24 +4541,24 @@
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
-          <t>Analysis_Date</t>
-        </is>
-      </c>
-      <c r="D27" s="46" t="inlineStr">
-        <is>
-          <t>Analysis</t>
+          <t>Mineral_Assemblage</t>
+        </is>
+      </c>
+      <c r="D27" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E27" s="38" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>Pl + Cpx + Ol ± Opx</t>
         </is>
       </c>
       <c r="H27" s="42" t="inlineStr">
         <is>
-          <t>Year / date of the analysis (YYYY or YYYY-MM-DD).</t>
+          <t>Main minerals (plagioclase, olivine, clinopyroxene, amphibole, biotite, K-feldspar, quartz ...).</t>
         </is>
       </c>
     </row>
@@ -4491,24 +4573,28 @@
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D28" s="46" t="inlineStr">
-        <is>
-          <t>Analysis</t>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="D28" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E28" s="38" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>JLF</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="H28" s="42" t="inlineStr">
         <is>
-          <t>Analyst initials or name (optional).</t>
+          <t>Visual / petrographic alteration grade.</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4609,7 @@
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Analytical_Method</t>
         </is>
       </c>
       <c r="D29" s="46" t="inlineStr">
@@ -4532,11 +4618,19 @@
         </is>
       </c>
       <c r="E29" s="38" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>XRF + ICP-MS</t>
+        </is>
+      </c>
       <c r="H29" s="42" t="inlineStr">
         <is>
-          <t>Free-text notes (anomalies, dilutions, repeated analyses, etc.).</t>
+          <t>Technique used for the bulk analysis.</t>
         </is>
       </c>
     </row>
@@ -4551,24 +4645,24 @@
       </c>
       <c r="C30" s="40" t="inlineStr">
         <is>
-          <t>SiO2</t>
-        </is>
-      </c>
-      <c r="D30" s="47" t="inlineStr">
-        <is>
-          <t>Majors</t>
-        </is>
-      </c>
-      <c r="E30" s="38" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="D30" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="E30" s="38" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ALS Geochemistry (Vancouver)</t>
+        </is>
+      </c>
       <c r="H30" s="42" t="inlineStr">
         <is>
-          <t>silicon dioxide</t>
+          <t>Lab where the analysis was carried out.</t>
         </is>
       </c>
     </row>
@@ -4583,24 +4677,24 @@
       </c>
       <c r="C31" s="40" t="inlineStr">
         <is>
-          <t>TiO2</t>
-        </is>
-      </c>
-      <c r="D31" s="47" t="inlineStr">
-        <is>
-          <t>Majors</t>
-        </is>
-      </c>
-      <c r="E31" s="38" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
+          <t>Analysis_Date</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="E31" s="38" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
       <c r="H31" s="42" t="inlineStr">
         <is>
-          <t>titanium dioxide</t>
+          <t>Year / date of the analysis (YYYY or YYYY-MM-DD).</t>
         </is>
       </c>
     </row>
@@ -4615,24 +4709,24 @@
       </c>
       <c r="C32" s="40" t="inlineStr">
         <is>
-          <t>Al2O3</t>
-        </is>
-      </c>
-      <c r="D32" s="47" t="inlineStr">
-        <is>
-          <t>Majors</t>
-        </is>
-      </c>
-      <c r="E32" s="38" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D32" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="E32" s="38" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>JLF</t>
+        </is>
+      </c>
       <c r="H32" s="42" t="inlineStr">
         <is>
-          <t>aluminium oxide</t>
+          <t>Analyst initials or name (optional).</t>
         </is>
       </c>
     </row>
@@ -4647,24 +4741,20 @@
       </c>
       <c r="C33" s="40" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
-        </is>
-      </c>
-      <c r="D33" s="47" t="inlineStr">
-        <is>
-          <t>Majors</t>
-        </is>
-      </c>
-      <c r="E33" s="38" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="E33" s="38" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" s="42" t="inlineStr">
         <is>
-          <t>ferric iron</t>
+          <t>Free-text notes (anomalies, dilutions, repeated analyses, etc.).</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4769,7 @@
       </c>
       <c r="C34" s="40" t="inlineStr">
         <is>
-          <t>FeO</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D34" s="47" t="inlineStr">
@@ -4696,7 +4786,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" s="42" t="inlineStr">
         <is>
-          <t>ferrous iron</t>
+          <t>silicon dioxide</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4801,7 @@
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
-          <t>FeOt</t>
+          <t>TiO2</t>
         </is>
       </c>
       <c r="D35" s="47" t="inlineStr">
@@ -4728,7 +4818,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" s="42" t="inlineStr">
         <is>
-          <t>total iron as FeO (used by Verma DFs)</t>
+          <t>titanium dioxide</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4833,7 @@
       </c>
       <c r="C36" s="40" t="inlineStr">
         <is>
-          <t>MnO</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D36" s="47" t="inlineStr">
@@ -4760,7 +4850,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" s="42" t="inlineStr">
         <is>
-          <t>manganese oxide</t>
+          <t>aluminium oxide</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4865,7 @@
       </c>
       <c r="C37" s="40" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D37" s="47" t="inlineStr">
@@ -4792,7 +4882,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" s="42" t="inlineStr">
         <is>
-          <t>magnesium oxide</t>
+          <t>ferric iron</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4897,7 @@
       </c>
       <c r="C38" s="40" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>FeO</t>
         </is>
       </c>
       <c r="D38" s="47" t="inlineStr">
@@ -4824,7 +4914,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" s="42" t="inlineStr">
         <is>
-          <t>calcium oxide</t>
+          <t>ferrous iron</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4929,7 @@
       </c>
       <c r="C39" s="40" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>FeOt</t>
         </is>
       </c>
       <c r="D39" s="47" t="inlineStr">
@@ -4856,7 +4946,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" s="42" t="inlineStr">
         <is>
-          <t>sodium oxide</t>
+          <t>total iron as FeO (used by Verma DFs)</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4961,7 @@
       </c>
       <c r="C40" s="40" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>MnO</t>
         </is>
       </c>
       <c r="D40" s="47" t="inlineStr">
@@ -4888,7 +4978,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" s="42" t="inlineStr">
         <is>
-          <t>potassium oxide</t>
+          <t>manganese oxide</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4993,7 @@
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
-          <t>P2O5</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D41" s="47" t="inlineStr">
@@ -4920,7 +5010,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" s="42" t="inlineStr">
         <is>
-          <t>phosphorus pentoxide</t>
+          <t>magnesium oxide</t>
         </is>
       </c>
     </row>
@@ -4935,7 +5025,7 @@
       </c>
       <c r="C42" s="40" t="inlineStr">
         <is>
-          <t>Cr2O3</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D42" s="47" t="inlineStr">
@@ -4952,7 +5042,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" s="42" t="inlineStr">
         <is>
-          <t>chromium oxide</t>
+          <t>calcium oxide</t>
         </is>
       </c>
     </row>
@@ -4967,7 +5057,7 @@
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
-          <t>NiO</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D43" s="47" t="inlineStr">
@@ -4984,7 +5074,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" s="42" t="inlineStr">
         <is>
-          <t>nickel oxide</t>
+          <t>sodium oxide</t>
         </is>
       </c>
     </row>
@@ -4999,7 +5089,7 @@
       </c>
       <c r="C44" s="40" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D44" s="47" t="inlineStr">
@@ -5016,7 +5106,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" s="42" t="inlineStr">
         <is>
-          <t>loss on ignition (heating at 1000 °C)</t>
+          <t>potassium oxide</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5121,7 @@
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
-          <t>H2O+</t>
+          <t>P2O5</t>
         </is>
       </c>
       <c r="D45" s="47" t="inlineStr">
@@ -5048,7 +5138,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" s="42" t="inlineStr">
         <is>
-          <t>structural water (above 110 °C)</t>
+          <t>phosphorus pentoxide</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5153,7 @@
       </c>
       <c r="C46" s="40" t="inlineStr">
         <is>
-          <t>H2O-</t>
+          <t>Cr2O3</t>
         </is>
       </c>
       <c r="D46" s="47" t="inlineStr">
@@ -5080,7 +5170,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="42" t="inlineStr">
         <is>
-          <t>absorbed water (below 110 °C)</t>
+          <t>chromium oxide</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5185,7 @@
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
-          <t>CO2</t>
+          <t>NiO</t>
         </is>
       </c>
       <c r="D47" s="47" t="inlineStr">
@@ -5112,7 +5202,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" s="42" t="inlineStr">
         <is>
-          <t>carbon dioxide</t>
+          <t>nickel oxide</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5217,7 @@
       </c>
       <c r="C48" s="40" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D48" s="47" t="inlineStr">
@@ -5144,7 +5234,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="42" t="inlineStr">
         <is>
-          <t>sum of oxides (quality-control, target 99-101 wt%)</t>
+          <t>loss on ignition (heating at 1000 °C)</t>
         </is>
       </c>
     </row>
@@ -5159,24 +5249,24 @@
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
-          <t>Li</t>
-        </is>
-      </c>
-      <c r="D49" s="48" t="inlineStr">
-        <is>
-          <t>Traces</t>
+          <t>H2O+</t>
+        </is>
+      </c>
+      <c r="D49" s="47" t="inlineStr">
+        <is>
+          <t>Majors</t>
         </is>
       </c>
       <c r="E49" s="38" t="inlineStr">
         <is>
-          <t>ppm</t>
+          <t>wt%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="42" t="inlineStr">
         <is>
-          <t>Trace element Li concentration.</t>
+          <t>structural water (above 110 °C)</t>
         </is>
       </c>
     </row>
@@ -5191,24 +5281,24 @@
       </c>
       <c r="C50" s="40" t="inlineStr">
         <is>
-          <t>Be</t>
-        </is>
-      </c>
-      <c r="D50" s="48" t="inlineStr">
-        <is>
-          <t>Traces</t>
+          <t>H2O-</t>
+        </is>
+      </c>
+      <c r="D50" s="47" t="inlineStr">
+        <is>
+          <t>Majors</t>
         </is>
       </c>
       <c r="E50" s="38" t="inlineStr">
         <is>
-          <t>ppm</t>
+          <t>wt%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" s="42" t="inlineStr">
         <is>
-          <t>Trace element Be concentration.</t>
+          <t>absorbed water (below 110 °C)</t>
         </is>
       </c>
     </row>
@@ -5223,24 +5313,24 @@
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
-          <t>Sc</t>
-        </is>
-      </c>
-      <c r="D51" s="48" t="inlineStr">
-        <is>
-          <t>Traces</t>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="D51" s="47" t="inlineStr">
+        <is>
+          <t>Majors</t>
         </is>
       </c>
       <c r="E51" s="38" t="inlineStr">
         <is>
-          <t>ppm</t>
+          <t>wt%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" s="42" t="inlineStr">
         <is>
-          <t>Trace element Sc concentration.</t>
+          <t>carbon dioxide</t>
         </is>
       </c>
     </row>
@@ -5255,24 +5345,24 @@
       </c>
       <c r="C52" s="40" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D52" s="48" t="inlineStr">
-        <is>
-          <t>Traces</t>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D52" s="47" t="inlineStr">
+        <is>
+          <t>Majors</t>
         </is>
       </c>
       <c r="E52" s="38" t="inlineStr">
         <is>
-          <t>ppm</t>
+          <t>wt%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" s="42" t="inlineStr">
         <is>
-          <t>Trace element V concentration.</t>
+          <t>sum of oxides (quality-control, target 99-101 wt%)</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5377,7 @@
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
-          <t>Cr</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="D53" s="48" t="inlineStr">
@@ -5304,7 +5394,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" s="42" t="inlineStr">
         <is>
-          <t>Trace element Cr concentration.</t>
+          <t>Trace element Li concentration.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5409,7 @@
       </c>
       <c r="C54" s="40" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Be</t>
         </is>
       </c>
       <c r="D54" s="48" t="inlineStr">
@@ -5336,7 +5426,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="42" t="inlineStr">
         <is>
-          <t>Trace element Co concentration.</t>
+          <t>Trace element Be concentration.</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5441,7 @@
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Sc</t>
         </is>
       </c>
       <c r="D55" s="48" t="inlineStr">
@@ -5368,7 +5458,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" s="42" t="inlineStr">
         <is>
-          <t>Trace element Ni concentration.</t>
+          <t>Trace element Sc concentration.</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5473,7 @@
       </c>
       <c r="C56" s="40" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D56" s="48" t="inlineStr">
@@ -5400,7 +5490,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="42" t="inlineStr">
         <is>
-          <t>Trace element Cu concentration.</t>
+          <t>Trace element V concentration.</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5505,7 @@
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Cr</t>
         </is>
       </c>
       <c r="D57" s="48" t="inlineStr">
@@ -5432,7 +5522,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="42" t="inlineStr">
         <is>
-          <t>Trace element Zn concentration.</t>
+          <t>Trace element Cr concentration.</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5537,7 @@
       </c>
       <c r="C58" s="40" t="inlineStr">
         <is>
-          <t>Ga</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D58" s="48" t="inlineStr">
@@ -5464,7 +5554,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" s="42" t="inlineStr">
         <is>
-          <t>Trace element Ga concentration.</t>
+          <t>Trace element Co concentration.</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5569,7 @@
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
-          <t>Rb</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="D59" s="48" t="inlineStr">
@@ -5496,7 +5586,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" s="42" t="inlineStr">
         <is>
-          <t>Trace element Rb concentration.</t>
+          <t>Trace element Ni concentration.</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5601,7 @@
       </c>
       <c r="C60" s="40" t="inlineStr">
         <is>
-          <t>Sr</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="D60" s="48" t="inlineStr">
@@ -5528,7 +5618,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" s="42" t="inlineStr">
         <is>
-          <t>Trace element Sr concentration.</t>
+          <t>Trace element Cu concentration.</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5633,7 @@
       </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="D61" s="48" t="inlineStr">
@@ -5560,7 +5650,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" s="42" t="inlineStr">
         <is>
-          <t>Trace element Y concentration.</t>
+          <t>Trace element Zn concentration.</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5665,7 @@
       </c>
       <c r="C62" s="40" t="inlineStr">
         <is>
-          <t>Zr</t>
+          <t>Ga</t>
         </is>
       </c>
       <c r="D62" s="48" t="inlineStr">
@@ -5592,7 +5682,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="42" t="inlineStr">
         <is>
-          <t>Trace element Zr concentration.</t>
+          <t>Trace element Ga concentration.</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5697,7 @@
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Rb</t>
         </is>
       </c>
       <c r="D63" s="48" t="inlineStr">
@@ -5624,7 +5714,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="42" t="inlineStr">
         <is>
-          <t>Trace element Nb concentration.</t>
+          <t>Trace element Rb concentration.</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5729,7 @@
       </c>
       <c r="C64" s="40" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Sr</t>
         </is>
       </c>
       <c r="D64" s="48" t="inlineStr">
@@ -5656,7 +5746,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="42" t="inlineStr">
         <is>
-          <t>Trace element Mo concentration.</t>
+          <t>Trace element Sr concentration.</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5761,7 @@
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
-          <t>Sn</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D65" s="48" t="inlineStr">
@@ -5688,7 +5778,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="42" t="inlineStr">
         <is>
-          <t>Trace element Sn concentration.</t>
+          <t>Trace element Y concentration.</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5793,7 @@
       </c>
       <c r="C66" s="40" t="inlineStr">
         <is>
-          <t>Sb</t>
+          <t>Zr</t>
         </is>
       </c>
       <c r="D66" s="48" t="inlineStr">
@@ -5720,7 +5810,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="42" t="inlineStr">
         <is>
-          <t>Trace element Sb concentration.</t>
+          <t>Trace element Zr concentration.</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5825,7 @@
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
-          <t>Cs</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="D67" s="48" t="inlineStr">
@@ -5752,7 +5842,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="42" t="inlineStr">
         <is>
-          <t>Trace element Cs concentration.</t>
+          <t>Trace element Nb concentration.</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5857,7 @@
       </c>
       <c r="C68" s="40" t="inlineStr">
         <is>
-          <t>Ba</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D68" s="48" t="inlineStr">
@@ -5784,7 +5874,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="42" t="inlineStr">
         <is>
-          <t>Trace element Ba concentration.</t>
+          <t>Trace element Mo concentration.</t>
         </is>
       </c>
     </row>
@@ -5799,7 +5889,7 @@
       </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
-          <t>Hf</t>
+          <t>Sn</t>
         </is>
       </c>
       <c r="D69" s="48" t="inlineStr">
@@ -5816,7 +5906,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="42" t="inlineStr">
         <is>
-          <t>Trace element Hf concentration.</t>
+          <t>Trace element Sn concentration.</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5921,7 @@
       </c>
       <c r="C70" s="40" t="inlineStr">
         <is>
-          <t>Ta</t>
+          <t>Sb</t>
         </is>
       </c>
       <c r="D70" s="48" t="inlineStr">
@@ -5848,7 +5938,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" s="42" t="inlineStr">
         <is>
-          <t>Trace element Ta concentration.</t>
+          <t>Trace element Sb concentration.</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5953,7 @@
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Cs</t>
         </is>
       </c>
       <c r="D71" s="48" t="inlineStr">
@@ -5880,7 +5970,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="42" t="inlineStr">
         <is>
-          <t>Trace element W concentration.</t>
+          <t>Trace element Cs concentration.</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5985,7 @@
       </c>
       <c r="C72" s="40" t="inlineStr">
         <is>
-          <t>Tl</t>
+          <t>Ba</t>
         </is>
       </c>
       <c r="D72" s="48" t="inlineStr">
@@ -5912,7 +6002,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="42" t="inlineStr">
         <is>
-          <t>Trace element Tl concentration.</t>
+          <t>Trace element Ba concentration.</t>
         </is>
       </c>
     </row>
@@ -5927,7 +6017,7 @@
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>Hf</t>
         </is>
       </c>
       <c r="D73" s="48" t="inlineStr">
@@ -5944,7 +6034,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="42" t="inlineStr">
         <is>
-          <t>Trace element Pb concentration.</t>
+          <t>Trace element Hf concentration.</t>
         </is>
       </c>
     </row>
@@ -5959,7 +6049,7 @@
       </c>
       <c r="C74" s="40" t="inlineStr">
         <is>
-          <t>Bi</t>
+          <t>Ta</t>
         </is>
       </c>
       <c r="D74" s="48" t="inlineStr">
@@ -5976,7 +6066,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="42" t="inlineStr">
         <is>
-          <t>Trace element Bi concentration.</t>
+          <t>Trace element Ta concentration.</t>
         </is>
       </c>
     </row>
@@ -5991,7 +6081,7 @@
       </c>
       <c r="C75" s="40" t="inlineStr">
         <is>
-          <t>Th</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D75" s="48" t="inlineStr">
@@ -6008,7 +6098,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" s="42" t="inlineStr">
         <is>
-          <t>Trace element Th concentration.</t>
+          <t>Trace element W concentration.</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6113,7 @@
       </c>
       <c r="C76" s="40" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Tl</t>
         </is>
       </c>
       <c r="D76" s="48" t="inlineStr">
@@ -6040,7 +6130,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" s="42" t="inlineStr">
         <is>
-          <t>Trace element U concentration.</t>
+          <t>Trace element Tl concentration.</t>
         </is>
       </c>
     </row>
@@ -6055,12 +6145,12 @@
       </c>
       <c r="C77" s="40" t="inlineStr">
         <is>
-          <t>La</t>
-        </is>
-      </c>
-      <c r="D77" s="49" t="inlineStr">
-        <is>
-          <t>REE</t>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="D77" s="48" t="inlineStr">
+        <is>
+          <t>Traces</t>
         </is>
       </c>
       <c r="E77" s="38" t="inlineStr">
@@ -6072,7 +6162,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element La concentration.</t>
+          <t>Trace element Pb concentration.</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6177,12 @@
       </c>
       <c r="C78" s="40" t="inlineStr">
         <is>
-          <t>Ce</t>
-        </is>
-      </c>
-      <c r="D78" s="49" t="inlineStr">
-        <is>
-          <t>REE</t>
+          <t>Bi</t>
+        </is>
+      </c>
+      <c r="D78" s="48" t="inlineStr">
+        <is>
+          <t>Traces</t>
         </is>
       </c>
       <c r="E78" s="38" t="inlineStr">
@@ -6104,7 +6194,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Ce concentration.</t>
+          <t>Trace element Bi concentration.</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6209,12 @@
       </c>
       <c r="C79" s="40" t="inlineStr">
         <is>
-          <t>Pr</t>
-        </is>
-      </c>
-      <c r="D79" s="49" t="inlineStr">
-        <is>
-          <t>REE</t>
+          <t>Th</t>
+        </is>
+      </c>
+      <c r="D79" s="48" t="inlineStr">
+        <is>
+          <t>Traces</t>
         </is>
       </c>
       <c r="E79" s="38" t="inlineStr">
@@ -6136,7 +6226,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Pr concentration.</t>
+          <t>Trace element Th concentration.</t>
         </is>
       </c>
     </row>
@@ -6151,12 +6241,12 @@
       </c>
       <c r="C80" s="40" t="inlineStr">
         <is>
-          <t>Nd</t>
-        </is>
-      </c>
-      <c r="D80" s="49" t="inlineStr">
-        <is>
-          <t>REE</t>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D80" s="48" t="inlineStr">
+        <is>
+          <t>Traces</t>
         </is>
       </c>
       <c r="E80" s="38" t="inlineStr">
@@ -6168,7 +6258,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Nd concentration.</t>
+          <t>Trace element U concentration.</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6273,7 @@
       </c>
       <c r="C81" s="40" t="inlineStr">
         <is>
-          <t>Sm</t>
+          <t>La</t>
         </is>
       </c>
       <c r="D81" s="49" t="inlineStr">
@@ -6200,7 +6290,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Sm concentration.</t>
+          <t>Rare-earth element La concentration.</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6305,7 @@
       </c>
       <c r="C82" s="40" t="inlineStr">
         <is>
-          <t>Eu</t>
+          <t>Ce</t>
         </is>
       </c>
       <c r="D82" s="49" t="inlineStr">
@@ -6232,7 +6322,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Eu concentration.</t>
+          <t>Rare-earth element Ce concentration.</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6337,7 @@
       </c>
       <c r="C83" s="40" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="D83" s="49" t="inlineStr">
@@ -6264,7 +6354,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Gd concentration.</t>
+          <t>Rare-earth element Pr concentration.</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6369,7 @@
       </c>
       <c r="C84" s="40" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="D84" s="49" t="inlineStr">
@@ -6296,7 +6386,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Tb concentration.</t>
+          <t>Rare-earth element Nd concentration.</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6401,7 @@
       </c>
       <c r="C85" s="40" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Sm</t>
         </is>
       </c>
       <c r="D85" s="49" t="inlineStr">
@@ -6328,7 +6418,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Dy concentration.</t>
+          <t>Rare-earth element Sm concentration.</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6433,7 @@
       </c>
       <c r="C86" s="40" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Eu</t>
         </is>
       </c>
       <c r="D86" s="49" t="inlineStr">
@@ -6360,7 +6450,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Ho concentration.</t>
+          <t>Rare-earth element Eu concentration.</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6465,7 @@
       </c>
       <c r="C87" s="40" t="inlineStr">
         <is>
-          <t>Er</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="D87" s="49" t="inlineStr">
@@ -6392,7 +6482,7 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Er concentration.</t>
+          <t>Rare-earth element Gd concentration.</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6497,7 @@
       </c>
       <c r="C88" s="40" t="inlineStr">
         <is>
-          <t>Tm</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="D88" s="49" t="inlineStr">
@@ -6424,7 +6514,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Tm concentration.</t>
+          <t>Rare-earth element Tb concentration.</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6529,7 @@
       </c>
       <c r="C89" s="40" t="inlineStr">
         <is>
-          <t>Yb</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="D89" s="49" t="inlineStr">
@@ -6456,7 +6546,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Yb concentration.</t>
+          <t>Rare-earth element Dy concentration.</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6561,7 @@
       </c>
       <c r="C90" s="40" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="D90" s="49" t="inlineStr">
@@ -6488,7 +6578,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" s="42" t="inlineStr">
         <is>
-          <t>Rare-earth element Lu concentration.</t>
+          <t>Rare-earth element Ho concentration.</t>
         </is>
       </c>
     </row>
@@ -6498,29 +6588,29 @@
       </c>
       <c r="B91" s="39" t="inlineStr">
         <is>
-          <t>Isotopes</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C91" s="40" t="inlineStr">
         <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="D91" s="41" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E91" s="38" t="inlineStr"/>
+          <t>Er</t>
+        </is>
+      </c>
+      <c r="D91" s="49" t="inlineStr">
+        <is>
+          <t>REE</t>
+        </is>
+      </c>
+      <c r="E91" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" s="42" t="inlineStr">
         <is>
-          <t>Sequential row number (1, 2, 3 ...).</t>
+          <t>Rare-earth element Er concentration.</t>
         </is>
       </c>
     </row>
@@ -6530,29 +6620,29 @@
       </c>
       <c r="B92" s="39" t="inlineStr">
         <is>
-          <t>Isotopes</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C92" s="40" t="inlineStr">
         <is>
-          <t>Sample_Name</t>
-        </is>
-      </c>
-      <c r="D92" s="41" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E92" s="38" t="inlineStr"/>
+          <t>Tm</t>
+        </is>
+      </c>
+      <c r="D92" s="49" t="inlineStr">
+        <is>
+          <t>REE</t>
+        </is>
+      </c>
+      <c r="E92" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>VOL-2024-018</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" s="42" t="inlineStr">
         <is>
-          <t>Unique short identifier for the sample (lab code / field number). Avoid spaces.</t>
+          <t>Rare-earth element Tm concentration.</t>
         </is>
       </c>
     </row>
@@ -6562,29 +6652,29 @@
       </c>
       <c r="B93" s="39" t="inlineStr">
         <is>
-          <t>Isotopes</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C93" s="40" t="inlineStr">
         <is>
-          <t>Sample_Label</t>
-        </is>
-      </c>
-      <c r="D93" s="41" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E93" s="38" t="inlineStr"/>
+          <t>Yb</t>
+        </is>
+      </c>
+      <c r="D93" s="49" t="inlineStr">
+        <is>
+          <t>REE</t>
+        </is>
+      </c>
+      <c r="E93" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Mt. Pico flow 18</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" s="42" t="inlineStr">
         <is>
-          <t>Free-text label used in plots if you don't want to expose the lab code.</t>
+          <t>Rare-earth element Yb concentration.</t>
         </is>
       </c>
     </row>
@@ -6594,29 +6684,29 @@
       </c>
       <c r="B94" s="39" t="inlineStr">
         <is>
-          <t>Isotopes</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C94" s="40" t="inlineStr">
         <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="D94" s="41" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E94" s="38" t="inlineStr"/>
+          <t>Lu</t>
+        </is>
+      </c>
+      <c r="D94" s="49" t="inlineStr">
+        <is>
+          <t>REE</t>
+        </is>
+      </c>
+      <c r="E94" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Lower flow</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" s="42" t="inlineStr">
         <is>
-          <t>Optional user-defined group used by the legend (e.g. unit, eruption, age cluster).</t>
+          <t>Rare-earth element Lu concentration.</t>
         </is>
       </c>
     </row>
@@ -6631,28 +6721,24 @@
       </c>
       <c r="C95" s="40" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="D95" s="43" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E95" s="38" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D95" s="41" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E95" s="38" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-19.4250</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H95" s="42" t="inlineStr">
         <is>
-          <t>Decimal degrees (WGS-84). Negative = south.</t>
+          <t>Sequential row number (1, 2, 3 ...).</t>
         </is>
       </c>
     </row>
@@ -6667,28 +6753,24 @@
       </c>
       <c r="C96" s="40" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="D96" s="43" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E96" s="38" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
+          <t>Sample_Name</t>
+        </is>
+      </c>
+      <c r="D96" s="41" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E96" s="38" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-69.1583</t>
+          <t>VOL-2024-018</t>
         </is>
       </c>
       <c r="H96" s="42" t="inlineStr">
         <is>
-          <t>Decimal degrees (WGS-84). Negative = west.</t>
+          <t>Unique short identifier for the sample (lab code / field number). Avoid spaces.</t>
         </is>
       </c>
     </row>
@@ -6703,28 +6785,24 @@
       </c>
       <c r="C97" s="40" t="inlineStr">
         <is>
-          <t>Elevation</t>
-        </is>
-      </c>
-      <c r="D97" s="43" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E97" s="38" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>Sample_Label</t>
+        </is>
+      </c>
+      <c r="D97" s="41" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E97" s="38" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>Mt. Pico flow 18</t>
         </is>
       </c>
       <c r="H97" s="42" t="inlineStr">
         <is>
-          <t>Sampling elevation above sea level.</t>
+          <t>Free-text label used in plots if you don't want to expose the lab code.</t>
         </is>
       </c>
     </row>
@@ -6739,24 +6817,24 @@
       </c>
       <c r="C98" s="40" t="inlineStr">
         <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="D98" s="43" t="inlineStr">
-        <is>
-          <t>Location</t>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="D98" s="41" t="inlineStr">
+        <is>
+          <t>ID</t>
         </is>
       </c>
       <c r="E98" s="38" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Lower flow</t>
         </is>
       </c>
       <c r="H98" s="42" t="inlineStr">
         <is>
-          <t>Country where the sample was collected.</t>
+          <t>Optional user-defined group used by the legend (e.g. unit, eruption, age cluster).</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6849,7 @@
       </c>
       <c r="C99" s="40" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="D99" s="43" t="inlineStr">
@@ -6779,16 +6857,20 @@
           <t>Location</t>
         </is>
       </c>
-      <c r="E99" s="38" t="inlineStr"/>
+      <c r="E99" s="38" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>-19.4250</t>
         </is>
       </c>
       <c r="H99" s="42" t="inlineStr">
         <is>
-          <t>State / province / volcanic field.</t>
+          <t>Decimal degrees (WGS-84). Negative = south.</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6885,7 @@
       </c>
       <c r="C100" s="40" t="inlineStr">
         <is>
-          <t>Locality</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="D100" s="43" t="inlineStr">
@@ -6811,16 +6893,20 @@
           <t>Location</t>
         </is>
       </c>
-      <c r="E100" s="38" t="inlineStr"/>
+      <c r="E100" s="38" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Taapaca Volcanic Complex</t>
+          <t>-69.1583</t>
         </is>
       </c>
       <c r="H100" s="42" t="inlineStr">
         <is>
-          <t>Specific outcrop or feature.</t>
+          <t>Decimal degrees (WGS-84). Negative = west.</t>
         </is>
       </c>
     </row>
@@ -6835,24 +6921,28 @@
       </c>
       <c r="C101" s="40" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="D101" s="44" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="E101" s="38" t="inlineStr"/>
+          <t>Easting</t>
+        </is>
+      </c>
+      <c r="D101" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E101" s="38" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Aguirre et al. (2022) Lithos 408</t>
+          <t>483382</t>
         </is>
       </c>
       <c r="H101" s="42" t="inlineStr">
         <is>
-          <t>Bibliographic reference for the analysis (author year, or DOI).</t>
+          <t>UTM easting, if the location is in UTM rather than degrees; the map reads either.</t>
         </is>
       </c>
     </row>
@@ -6867,24 +6957,28 @@
       </c>
       <c r="C102" s="40" t="inlineStr">
         <is>
-          <t>Dataset_DOI</t>
-        </is>
-      </c>
-      <c r="D102" s="44" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="E102" s="38" t="inlineStr"/>
+          <t>Northing</t>
+        </is>
+      </c>
+      <c r="D102" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E102" s="38" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>10.5281/zenodo.1234567</t>
+          <t>7852139</t>
         </is>
       </c>
       <c r="H102" s="42" t="inlineStr">
         <is>
-          <t>DOI of the original dataset, if published separately.</t>
+          <t>UTM northing, in metres from the equator (south: from 10 000 km below it).</t>
         </is>
       </c>
     </row>
@@ -6899,24 +6993,24 @@
       </c>
       <c r="C103" s="40" t="inlineStr">
         <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="D103" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
+          <t>UTM_Zone</t>
+        </is>
+      </c>
+      <c r="D103" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
         </is>
       </c>
       <c r="E103" s="38" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H103" s="42" t="inlineStr">
         <is>
-          <t>Numeric age (matched with AGE_UNIT). Leave empty if unknown.</t>
+          <t>UTM zone number, 1-60.</t>
         </is>
       </c>
     </row>
@@ -6931,28 +7025,28 @@
       </c>
       <c r="C104" s="40" t="inlineStr">
         <is>
-          <t>Age_Unit</t>
-        </is>
-      </c>
-      <c r="D104" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
+          <t>Hemisphere</t>
+        </is>
+      </c>
+      <c r="D104" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
         </is>
       </c>
       <c r="E104" s="38" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ma, ka, Ga, yr</t>
+          <t>N, S</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H104" s="42" t="inlineStr">
         <is>
-          <t>Unit of the AGE column. Pick from the dropdown.</t>
+          <t>N or S: the UTM hemisphere. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
@@ -6967,24 +7061,28 @@
       </c>
       <c r="C105" s="40" t="inlineStr">
         <is>
-          <t>Age_Method</t>
-        </is>
-      </c>
-      <c r="D105" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
-        </is>
-      </c>
-      <c r="E105" s="38" t="inlineStr"/>
+          <t>Elevation</t>
+        </is>
+      </c>
+      <c r="D105" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E105" s="38" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ar-Ar</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="H105" s="42" t="inlineStr">
         <is>
-          <t>Dating method (K-Ar, Ar-Ar, U-Pb, fission track, stratigraphic).</t>
+          <t>Sampling elevation above sea level.</t>
         </is>
       </c>
     </row>
@@ -6999,28 +7097,24 @@
       </c>
       <c r="C106" s="40" t="inlineStr">
         <is>
-          <t>Rock_Type</t>
-        </is>
-      </c>
-      <c r="D106" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D106" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
         </is>
       </c>
       <c r="E106" s="38" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Volcanic</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="H106" s="42" t="inlineStr">
         <is>
-          <t>Volcanic vs. plutonic family — used by B.I.R.D.S to pick the right TAS panel and tectonic catalogue.</t>
+          <t>Country where the sample was collected.</t>
         </is>
       </c>
     </row>
@@ -7035,28 +7129,24 @@
       </c>
       <c r="C107" s="40" t="inlineStr">
         <is>
-          <t>TAS_Composition</t>
-        </is>
-      </c>
-      <c r="D107" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D107" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
         </is>
       </c>
       <c r="E107" s="38" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Basaltic andesite</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="H107" s="42" t="inlineStr">
         <is>
-          <t>Rock name from the TAS diagram (Le Bas et al. 1986). Leave empty to let B.I.R.D.S compute it from SiO2 / alkalis.</t>
+          <t>State / province / volcanic field.</t>
         </is>
       </c>
     </row>
@@ -7071,24 +7161,24 @@
       </c>
       <c r="C108" s="40" t="inlineStr">
         <is>
-          <t>Lithology</t>
-        </is>
-      </c>
-      <c r="D108" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
+          <t>Locality</t>
+        </is>
+      </c>
+      <c r="D108" s="43" t="inlineStr">
+        <is>
+          <t>Location</t>
         </is>
       </c>
       <c r="E108" s="38" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Olivine basalt</t>
+          <t>Taapaca Volcanic Complex</t>
         </is>
       </c>
       <c r="H108" s="42" t="inlineStr">
         <is>
-          <t>Petrographic name beyond TAS (e.g. olivine basalt, biotite-amphibole granodiorite).</t>
+          <t>Specific outcrop or feature.</t>
         </is>
       </c>
     </row>
@@ -7103,28 +7193,24 @@
       </c>
       <c r="C109" s="40" t="inlineStr">
         <is>
-          <t>Magmatic_Series</t>
-        </is>
-      </c>
-      <c r="D109" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D109" s="44" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="E109" s="38" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Calc-alkaline</t>
+          <t>Aguirre et al. (2022) Lithos 408</t>
         </is>
       </c>
       <c r="H109" s="42" t="inlineStr">
         <is>
-          <t>Magma series. Optional — also derivable from K2O-SiO2 and AFM diagrams.</t>
+          <t>Bibliographic reference for the analysis (author year, or DOI).</t>
         </is>
       </c>
     </row>
@@ -7139,24 +7225,24 @@
       </c>
       <c r="C110" s="40" t="inlineStr">
         <is>
-          <t>Tectonic_Setting</t>
-        </is>
-      </c>
-      <c r="D110" s="45" t="inlineStr">
-        <is>
-          <t>Geology</t>
+          <t>Dataset_DOI</t>
+        </is>
+      </c>
+      <c r="D110" s="44" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="E110" s="38" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Continental arc</t>
+          <t>10.5281/zenodo.1234567</t>
         </is>
       </c>
       <c r="H110" s="42" t="inlineStr">
         <is>
-          <t>Inferred tectonic environment (MORB, OIB, IAB, CRB, OP, ...).</t>
+          <t>DOI of the original dataset, if published separately.</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7257,7 @@
       </c>
       <c r="C111" s="40" t="inlineStr">
         <is>
-          <t>Texture</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="D111" s="45" t="inlineStr">
@@ -7183,12 +7269,12 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porphyritic</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="H111" s="42" t="inlineStr">
         <is>
-          <t>Porphyritic / aphanitic / glassy / phaneritic / vesicular / etc.</t>
+          <t>Numeric age (matched with AGE_UNIT). Leave empty if unknown.</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7289,7 @@
       </c>
       <c r="C112" s="40" t="inlineStr">
         <is>
-          <t>Mineral_Assemblage</t>
+          <t>Age_Unit</t>
         </is>
       </c>
       <c r="D112" s="45" t="inlineStr">
@@ -7212,15 +7298,19 @@
         </is>
       </c>
       <c r="E112" s="38" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Ma, ka, Ga, yr</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pl + Cpx + Ol ± Opx</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="H112" s="42" t="inlineStr">
         <is>
-          <t>Main minerals (plagioclase, olivine, clinopyroxene, amphibole, biotite, K-feldspar, quartz ...).</t>
+          <t>Unit of the AGE column. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7325,7 @@
       </c>
       <c r="C113" s="40" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>Age_Method</t>
         </is>
       </c>
       <c r="D113" s="45" t="inlineStr">
@@ -7244,19 +7334,15 @@
         </is>
       </c>
       <c r="E113" s="38" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Ar-Ar</t>
         </is>
       </c>
       <c r="H113" s="42" t="inlineStr">
         <is>
-          <t>Visual / petrographic alteration grade.</t>
+          <t>Dating method (K-Ar, Ar-Ar, U-Pb, fission track, stratigraphic).</t>
         </is>
       </c>
     </row>
@@ -7271,28 +7357,28 @@
       </c>
       <c r="C114" s="40" t="inlineStr">
         <is>
-          <t>Analytical_Method</t>
-        </is>
-      </c>
-      <c r="D114" s="46" t="inlineStr">
-        <is>
-          <t>Analysis</t>
+          <t>Rock_Type</t>
+        </is>
+      </c>
+      <c r="D114" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E114" s="38" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed</t>
+          <t>Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>XRF + ICP-MS</t>
+          <t>Volcanic</t>
         </is>
       </c>
       <c r="H114" s="42" t="inlineStr">
         <is>
-          <t>Technique used for the bulk analysis.</t>
+          <t>Volcanic vs. plutonic family — used by B.I.R.D.S to pick the right TAS panel and tectonic catalogue.</t>
         </is>
       </c>
     </row>
@@ -7307,24 +7393,28 @@
       </c>
       <c r="C115" s="40" t="inlineStr">
         <is>
-          <t>Laboratory</t>
-        </is>
-      </c>
-      <c r="D115" s="46" t="inlineStr">
-        <is>
-          <t>Analysis</t>
+          <t>TAS_Composition</t>
+        </is>
+      </c>
+      <c r="D115" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E115" s="38" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ALS Geochemistry (Vancouver)</t>
+          <t>Basaltic andesite</t>
         </is>
       </c>
       <c r="H115" s="42" t="inlineStr">
         <is>
-          <t>Lab where the analysis was carried out.</t>
+          <t>Rock name from the TAS diagram (Le Bas et al. 1986). Leave empty to let B.I.R.D.S compute it from SiO2 / alkalis.</t>
         </is>
       </c>
     </row>
@@ -7339,24 +7429,24 @@
       </c>
       <c r="C116" s="40" t="inlineStr">
         <is>
-          <t>Analysis_Date</t>
-        </is>
-      </c>
-      <c r="D116" s="46" t="inlineStr">
-        <is>
-          <t>Analysis</t>
+          <t>Lithology</t>
+        </is>
+      </c>
+      <c r="D116" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E116" s="38" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>Olivine basalt</t>
         </is>
       </c>
       <c r="H116" s="42" t="inlineStr">
         <is>
-          <t>Year / date of the analysis (YYYY or YYYY-MM-DD).</t>
+          <t>Petrographic name beyond TAS (e.g. olivine basalt, biotite-amphibole granodiorite).</t>
         </is>
       </c>
     </row>
@@ -7371,24 +7461,28 @@
       </c>
       <c r="C117" s="40" t="inlineStr">
         <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D117" s="46" t="inlineStr">
-        <is>
-          <t>Analysis</t>
+          <t>Magmatic_Series</t>
+        </is>
+      </c>
+      <c r="D117" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E117" s="38" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>JLF</t>
+          <t>Calc-alkaline</t>
         </is>
       </c>
       <c r="H117" s="42" t="inlineStr">
         <is>
-          <t>Analyst initials or name (optional).</t>
+          <t>Magma series. Optional — also derivable from K2O-SiO2 and AFM diagrams.</t>
         </is>
       </c>
     </row>
@@ -7403,20 +7497,24 @@
       </c>
       <c r="C118" s="40" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D118" s="46" t="inlineStr">
-        <is>
-          <t>Analysis</t>
+          <t>Tectonic_Setting</t>
+        </is>
+      </c>
+      <c r="D118" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E118" s="38" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Continental arc</t>
+        </is>
+      </c>
       <c r="H118" s="42" t="inlineStr">
         <is>
-          <t>Free-text notes (anomalies, dilutions, repeated analyses, etc.).</t>
+          <t>Inferred tectonic environment (MORB, OIB, IAB, CRB, OP, ...).</t>
         </is>
       </c>
     </row>
@@ -7431,28 +7529,24 @@
       </c>
       <c r="C119" s="40" t="inlineStr">
         <is>
-          <t>SiO2</t>
-        </is>
-      </c>
-      <c r="D119" s="47" t="inlineStr">
-        <is>
-          <t>Majors</t>
-        </is>
-      </c>
-      <c r="E119" s="38" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
+          <t>Texture</t>
+        </is>
+      </c>
+      <c r="D119" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
+        </is>
+      </c>
+      <c r="E119" s="38" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>Porphyritic</t>
         </is>
       </c>
       <c r="H119" s="42" t="inlineStr">
         <is>
-          <t>Silica of the sample, for reading the isotope ratios against differentiation on this sheet (e.g. ⁸⁷Sr/⁸⁶Sr vs SiO2 for crustal assimilation). Copy it from the Data sheet, or give the value measured on the isotope aliquot. At import the Data sheet's SiO2 is kept for the bulk analysis.</t>
+          <t>Porphyritic / aphanitic / glassy / phaneritic / vesicular / etc.</t>
         </is>
       </c>
     </row>
@@ -7467,24 +7561,24 @@
       </c>
       <c r="C120" s="40" t="inlineStr">
         <is>
-          <t>87Sr/86Sr</t>
-        </is>
-      </c>
-      <c r="D120" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
+          <t>Mineral_Assemblage</t>
+        </is>
+      </c>
+      <c r="D120" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E120" s="38" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>0.70428</t>
+          <t>Pl + Cpx + Ol ± Opx</t>
         </is>
       </c>
       <c r="H120" s="42" t="inlineStr">
         <is>
-          <t>Measured ⁸⁷Sr/⁸⁶Sr ratio. Typical values: 0.7022 (DM), 0.7045 (CHUR), 0.708-0.710 (arc/upper crust).</t>
+          <t>Main minerals (plagioclase, olivine, clinopyroxene, amphibole, biotite, K-feldspar, quartz ...).</t>
         </is>
       </c>
     </row>
@@ -7499,24 +7593,28 @@
       </c>
       <c r="C121" s="40" t="inlineStr">
         <is>
-          <t>87Sr/86Sr_2σ</t>
-        </is>
-      </c>
-      <c r="D121" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="D121" s="45" t="inlineStr">
+        <is>
+          <t>Geology</t>
         </is>
       </c>
       <c r="E121" s="38" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0.00001</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="H121" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty of ⁸⁷Sr/⁸⁶Sr (absolute, e.g. 0.000010).</t>
+          <t>Visual / petrographic alteration grade.</t>
         </is>
       </c>
     </row>
@@ -7531,24 +7629,28 @@
       </c>
       <c r="C122" s="40" t="inlineStr">
         <is>
-          <t>87Rb/86Sr</t>
-        </is>
-      </c>
-      <c r="D122" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
+          <t>Analytical_Method</t>
+        </is>
+      </c>
+      <c r="D122" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="E122" s="38" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>XRF + ICP-MS</t>
         </is>
       </c>
       <c r="H122" s="42" t="inlineStr">
         <is>
-          <t>Parent ratio used for the initial-Sr correction. If missing, B.I.R.D.S derives it from Rb / Sr concentrations (~2.894 × Rb/Sr).</t>
+          <t>Technique used for the bulk analysis.</t>
         </is>
       </c>
     </row>
@@ -7563,28 +7665,24 @@
       </c>
       <c r="C123" s="40" t="inlineStr">
         <is>
-          <t>Sr_iso</t>
-        </is>
-      </c>
-      <c r="D123" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
-        </is>
-      </c>
-      <c r="E123" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="D123" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="E123" s="38" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>ALS Geochemistry (Vancouver)</t>
         </is>
       </c>
       <c r="H123" s="42" t="inlineStr">
         <is>
-          <t>Sr concentration measured on the same aliquot as the isotope ratio (optional; only needed if it differs from the bulk value in the Data sheet).</t>
+          <t>Lab where the analysis was carried out.</t>
         </is>
       </c>
     </row>
@@ -7599,28 +7697,24 @@
       </c>
       <c r="C124" s="40" t="inlineStr">
         <is>
-          <t>Rb_iso</t>
-        </is>
-      </c>
-      <c r="D124" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
-        </is>
-      </c>
-      <c r="E124" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>Analysis_Date</t>
+        </is>
+      </c>
+      <c r="D124" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="E124" s="38" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="H124" s="42" t="inlineStr">
         <is>
-          <t>Rb concentration measured on the same aliquot.</t>
+          <t>Year / date of the analysis (YYYY or YYYY-MM-DD).</t>
         </is>
       </c>
     </row>
@@ -7635,20 +7729,24 @@
       </c>
       <c r="C125" s="40" t="inlineStr">
         <is>
-          <t>εSr_initial</t>
-        </is>
-      </c>
-      <c r="D125" s="50" t="inlineStr">
-        <is>
-          <t>Iso-Sr</t>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D125" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="E125" s="38" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>JLF</t>
+        </is>
+      </c>
       <c r="H125" s="42" t="inlineStr">
         <is>
-          <t>Computed by B.I.R.D.S — leave empty.</t>
+          <t>Analyst initials or name (optional).</t>
         </is>
       </c>
     </row>
@@ -7663,24 +7761,20 @@
       </c>
       <c r="C126" s="40" t="inlineStr">
         <is>
-          <t>143Nd/144Nd</t>
-        </is>
-      </c>
-      <c r="D126" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D126" s="46" t="inlineStr">
+        <is>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="E126" s="38" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>0.51285</t>
-        </is>
-      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" s="42" t="inlineStr">
         <is>
-          <t>Measured ¹⁴³Nd/¹⁴⁴Nd ratio. CHUR = 0.512638 (Bouvier et al. 2008).</t>
+          <t>Free-text notes (anomalies, dilutions, repeated analyses, etc.).</t>
         </is>
       </c>
     </row>
@@ -7695,24 +7789,28 @@
       </c>
       <c r="C127" s="40" t="inlineStr">
         <is>
-          <t>143Nd/144Nd_2σ</t>
-        </is>
-      </c>
-      <c r="D127" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
-        </is>
-      </c>
-      <c r="E127" s="38" t="inlineStr"/>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="D127" s="47" t="inlineStr">
+        <is>
+          <t>Majors</t>
+        </is>
+      </c>
+      <c r="E127" s="38" t="inlineStr">
+        <is>
+          <t>wt%</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>0.000007</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="H127" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Silica of the sample, for reading the isotope ratios against differentiation on this sheet (e.g. ⁸⁷Sr/⁸⁶Sr vs SiO2 for crustal assimilation). Copy it from the Data sheet, or give the value measured on the isotope aliquot. At import the Data sheet's SiO2 is kept for the bulk analysis.</t>
         </is>
       </c>
     </row>
@@ -7727,24 +7825,24 @@
       </c>
       <c r="C128" s="40" t="inlineStr">
         <is>
-          <t>147Sm/144Nd</t>
-        </is>
-      </c>
-      <c r="D128" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
+          <t>87Sr/86Sr</t>
+        </is>
+      </c>
+      <c r="D128" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
         </is>
       </c>
       <c r="E128" s="38" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.70428</t>
         </is>
       </c>
       <c r="H128" s="42" t="inlineStr">
         <is>
-          <t>Parent ratio for the initial-Nd correction. If missing, derived from Sm/Nd (~0.6043 × Sm/Nd).</t>
+          <t>Measured ⁸⁷Sr/⁸⁶Sr ratio. Typical values: 0.7022 (DM), 0.7045 (CHUR), 0.708-0.710 (arc/upper crust).</t>
         </is>
       </c>
     </row>
@@ -7759,28 +7857,24 @@
       </c>
       <c r="C129" s="40" t="inlineStr">
         <is>
-          <t>Sm_iso</t>
-        </is>
-      </c>
-      <c r="D129" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
-        </is>
-      </c>
-      <c r="E129" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>87Sr/86Sr_2σ</t>
+        </is>
+      </c>
+      <c r="D129" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
+        </is>
+      </c>
+      <c r="E129" s="38" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>0.00001</t>
         </is>
       </c>
       <c r="H129" s="42" t="inlineStr">
         <is>
-          <t>Sm concentration in the isotope aliquot.</t>
+          <t>Analytical 2σ uncertainty of ⁸⁷Sr/⁸⁶Sr (absolute, e.g. 0.000010).</t>
         </is>
       </c>
     </row>
@@ -7795,28 +7889,24 @@
       </c>
       <c r="C130" s="40" t="inlineStr">
         <is>
-          <t>Nd_iso</t>
-        </is>
-      </c>
-      <c r="D130" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
-        </is>
-      </c>
-      <c r="E130" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>87Rb/86Sr</t>
+        </is>
+      </c>
+      <c r="D130" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
+        </is>
+      </c>
+      <c r="E130" s="38" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="H130" s="42" t="inlineStr">
         <is>
-          <t>Nd concentration in the isotope aliquot.</t>
+          <t>Parent ratio used for the initial-Sr correction. If missing, B.I.R.D.S derives it from Rb / Sr concentrations (~2.894 × Rb/Sr).</t>
         </is>
       </c>
     </row>
@@ -7831,20 +7921,28 @@
       </c>
       <c r="C131" s="40" t="inlineStr">
         <is>
-          <t>εNd_initial</t>
-        </is>
-      </c>
-      <c r="D131" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
-        </is>
-      </c>
-      <c r="E131" s="38" t="inlineStr"/>
+          <t>Sr_iso</t>
+        </is>
+      </c>
+      <c r="D131" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
+        </is>
+      </c>
+      <c r="E131" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
       <c r="H131" s="42" t="inlineStr">
         <is>
-          <t>Computed by B.I.R.D.S.</t>
+          <t>Sr concentration measured on the same aliquot as the isotope ratio (optional; only needed if it differs from the bulk value in the Data sheet).</t>
         </is>
       </c>
     </row>
@@ -7859,28 +7957,28 @@
       </c>
       <c r="C132" s="40" t="inlineStr">
         <is>
-          <t>TDM_Nd</t>
-        </is>
-      </c>
-      <c r="D132" s="51" t="inlineStr">
-        <is>
-          <t>Iso-Nd</t>
+          <t>Rb_iso</t>
+        </is>
+      </c>
+      <c r="D132" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
         </is>
       </c>
       <c r="E132" s="38" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>ppm</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H132" s="42" t="inlineStr">
         <is>
-          <t>Nd depleted-mantle model age (DePaolo 1981 or Goldstein 1984 — pick your convention).</t>
+          <t>Rb concentration measured on the same aliquot.</t>
         </is>
       </c>
     </row>
@@ -7895,24 +7993,20 @@
       </c>
       <c r="C133" s="40" t="inlineStr">
         <is>
-          <t>206Pb/204Pb</t>
-        </is>
-      </c>
-      <c r="D133" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
+          <t>εSr_initial</t>
+        </is>
+      </c>
+      <c r="D133" s="50" t="inlineStr">
+        <is>
+          <t>Iso-Sr</t>
         </is>
       </c>
       <c r="E133" s="38" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>18.65</t>
-        </is>
-      </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" s="42" t="inlineStr">
         <is>
-          <t>Measured ²⁰⁶Pb/²⁰⁴Pb ratio.</t>
+          <t>Computed by B.I.R.D.S — leave empty.</t>
         </is>
       </c>
     </row>
@@ -7927,24 +8021,24 @@
       </c>
       <c r="C134" s="40" t="inlineStr">
         <is>
-          <t>206Pb/204Pb_2σ</t>
-        </is>
-      </c>
-      <c r="D134" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
+          <t>143Nd/144Nd</t>
+        </is>
+      </c>
+      <c r="D134" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
         </is>
       </c>
       <c r="E134" s="38" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.51285</t>
         </is>
       </c>
       <c r="H134" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Measured ¹⁴³Nd/¹⁴⁴Nd ratio. CHUR = 0.512638 (Bouvier et al. 2008).</t>
         </is>
       </c>
     </row>
@@ -7959,24 +8053,24 @@
       </c>
       <c r="C135" s="40" t="inlineStr">
         <is>
-          <t>207Pb/204Pb</t>
-        </is>
-      </c>
-      <c r="D135" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
+          <t>143Nd/144Nd_2σ</t>
+        </is>
+      </c>
+      <c r="D135" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
         </is>
       </c>
       <c r="E135" s="38" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>0.000007</t>
         </is>
       </c>
       <c r="H135" s="42" t="inlineStr">
         <is>
-          <t>Measured ²⁰⁷Pb/²⁰⁴Pb ratio.</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -7991,24 +8085,24 @@
       </c>
       <c r="C136" s="40" t="inlineStr">
         <is>
-          <t>207Pb/204Pb_2σ</t>
-        </is>
-      </c>
-      <c r="D136" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
+          <t>147Sm/144Nd</t>
+        </is>
+      </c>
+      <c r="D136" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
         </is>
       </c>
       <c r="E136" s="38" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="H136" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Parent ratio for the initial-Nd correction. If missing, derived from Sm/Nd (~0.6043 × Sm/Nd).</t>
         </is>
       </c>
     </row>
@@ -8023,24 +8117,28 @@
       </c>
       <c r="C137" s="40" t="inlineStr">
         <is>
-          <t>208Pb/204Pb</t>
-        </is>
-      </c>
-      <c r="D137" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
-        </is>
-      </c>
-      <c r="E137" s="38" t="inlineStr"/>
+          <t>Sm_iso</t>
+        </is>
+      </c>
+      <c r="D137" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
+        </is>
+      </c>
+      <c r="E137" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="H137" s="42" t="inlineStr">
         <is>
-          <t>Measured ²⁰⁸Pb/²⁰⁴Pb ratio.</t>
+          <t>Sm concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
@@ -8055,24 +8153,28 @@
       </c>
       <c r="C138" s="40" t="inlineStr">
         <is>
-          <t>208Pb/204Pb_2σ</t>
-        </is>
-      </c>
-      <c r="D138" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
-        </is>
-      </c>
-      <c r="E138" s="38" t="inlineStr"/>
+          <t>Nd_iso</t>
+        </is>
+      </c>
+      <c r="D138" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
+        </is>
+      </c>
+      <c r="E138" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="H138" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Nd concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
@@ -8087,28 +8189,20 @@
       </c>
       <c r="C139" s="40" t="inlineStr">
         <is>
-          <t>Pb_iso</t>
-        </is>
-      </c>
-      <c r="D139" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
-        </is>
-      </c>
-      <c r="E139" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>εNd_initial</t>
+        </is>
+      </c>
+      <c r="D139" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
+        </is>
+      </c>
+      <c r="E139" s="38" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" s="42" t="inlineStr">
         <is>
-          <t>Pb concentration in the isotope aliquot.</t>
+          <t>Computed by B.I.R.D.S.</t>
         </is>
       </c>
     </row>
@@ -8123,28 +8217,28 @@
       </c>
       <c r="C140" s="40" t="inlineStr">
         <is>
-          <t>U_iso</t>
-        </is>
-      </c>
-      <c r="D140" s="52" t="inlineStr">
-        <is>
-          <t>Iso-Pb</t>
+          <t>TDM_Nd</t>
+        </is>
+      </c>
+      <c r="D140" s="51" t="inlineStr">
+        <is>
+          <t>Iso-Nd</t>
         </is>
       </c>
       <c r="E140" s="38" t="inlineStr">
         <is>
-          <t>ppm</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H140" s="42" t="inlineStr">
         <is>
-          <t>U concentration (for μ = ²³⁸U/²⁰⁴Pb).</t>
+          <t>Nd depleted-mantle model age (DePaolo 1981 or Goldstein 1984 — pick your convention).</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8253,7 @@
       </c>
       <c r="C141" s="40" t="inlineStr">
         <is>
-          <t>Th_iso</t>
+          <t>206Pb/204Pb</t>
         </is>
       </c>
       <c r="D141" s="52" t="inlineStr">
@@ -8167,20 +8261,16 @@
           <t>Iso-Pb</t>
         </is>
       </c>
-      <c r="E141" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+      <c r="E141" s="38" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="H141" s="42" t="inlineStr">
         <is>
-          <t>Th concentration (for κ = ²³²Th/²³⁸U).</t>
+          <t>Measured ²⁰⁶Pb/²⁰⁴Pb ratio.</t>
         </is>
       </c>
     </row>
@@ -8195,24 +8285,24 @@
       </c>
       <c r="C142" s="40" t="inlineStr">
         <is>
-          <t>176Hf/177Hf</t>
-        </is>
-      </c>
-      <c r="D142" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
+          <t>206Pb/204Pb_2σ</t>
+        </is>
+      </c>
+      <c r="D142" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
         </is>
       </c>
       <c r="E142" s="38" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>0.28298</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H142" s="42" t="inlineStr">
         <is>
-          <t>Measured ¹⁷⁶Hf/¹⁷⁷Hf ratio. CHUR = 0.282785 (Bouvier et al. 2008).</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8227,24 +8317,24 @@
       </c>
       <c r="C143" s="40" t="inlineStr">
         <is>
-          <t>176Hf/177Hf_2σ</t>
-        </is>
-      </c>
-      <c r="D143" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
+          <t>207Pb/204Pb</t>
+        </is>
+      </c>
+      <c r="D143" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
         </is>
       </c>
       <c r="E143" s="38" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="H143" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Measured ²⁰⁷Pb/²⁰⁴Pb ratio.</t>
         </is>
       </c>
     </row>
@@ -8259,24 +8349,24 @@
       </c>
       <c r="C144" s="40" t="inlineStr">
         <is>
-          <t>176Lu/177Hf</t>
-        </is>
-      </c>
-      <c r="D144" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
+          <t>207Pb/204Pb_2σ</t>
+        </is>
+      </c>
+      <c r="D144" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
         </is>
       </c>
       <c r="E144" s="38" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H144" s="42" t="inlineStr">
         <is>
-          <t>Parent ratio for initial-Hf correction.</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8291,28 +8381,24 @@
       </c>
       <c r="C145" s="40" t="inlineStr">
         <is>
-          <t>Hf_iso</t>
-        </is>
-      </c>
-      <c r="D145" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
-        </is>
-      </c>
-      <c r="E145" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>208Pb/204Pb</t>
+        </is>
+      </c>
+      <c r="D145" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E145" s="38" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="H145" s="42" t="inlineStr">
         <is>
-          <t>Hf concentration in the isotope aliquot.</t>
+          <t>Measured ²⁰⁸Pb/²⁰⁴Pb ratio.</t>
         </is>
       </c>
     </row>
@@ -8327,28 +8413,24 @@
       </c>
       <c r="C146" s="40" t="inlineStr">
         <is>
-          <t>Lu_iso</t>
-        </is>
-      </c>
-      <c r="D146" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
-        </is>
-      </c>
-      <c r="E146" s="38" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
+          <t>208Pb/204Pb_2σ</t>
+        </is>
+      </c>
+      <c r="D146" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E146" s="38" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H146" s="42" t="inlineStr">
         <is>
-          <t>Lu concentration in the isotope aliquot.</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8363,20 +8445,28 @@
       </c>
       <c r="C147" s="40" t="inlineStr">
         <is>
-          <t>εHf_initial</t>
-        </is>
-      </c>
-      <c r="D147" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
-        </is>
-      </c>
-      <c r="E147" s="38" t="inlineStr"/>
+          <t>Pb_iso</t>
+        </is>
+      </c>
+      <c r="D147" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E147" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
       <c r="H147" s="42" t="inlineStr">
         <is>
-          <t>Computed by B.I.R.D.S.</t>
+          <t>Pb concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
@@ -8391,28 +8481,28 @@
       </c>
       <c r="C148" s="40" t="inlineStr">
         <is>
-          <t>TDM_Hf</t>
-        </is>
-      </c>
-      <c r="D148" s="53" t="inlineStr">
-        <is>
-          <t>Iso-Hf</t>
+          <t>U_iso</t>
+        </is>
+      </c>
+      <c r="D148" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
         </is>
       </c>
       <c r="E148" s="38" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>ppm</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="H148" s="42" t="inlineStr">
         <is>
-          <t>Hf depleted-mantle model age.</t>
+          <t>U concentration (for μ = ²³⁸U/²⁰⁴Pb).</t>
         </is>
       </c>
     </row>
@@ -8427,24 +8517,28 @@
       </c>
       <c r="C149" s="40" t="inlineStr">
         <is>
-          <t>187Os/188Os</t>
-        </is>
-      </c>
-      <c r="D149" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
-        </is>
-      </c>
-      <c r="E149" s="38" t="inlineStr"/>
+          <t>Th_iso</t>
+        </is>
+      </c>
+      <c r="D149" s="52" t="inlineStr">
+        <is>
+          <t>Iso-Pb</t>
+        </is>
+      </c>
+      <c r="E149" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="H149" s="42" t="inlineStr">
         <is>
-          <t>Measured ¹⁸⁷Os/¹⁸⁸Os ratio. Primitive Upper Mantle (PUM) ≈ 0.1296.</t>
+          <t>Th concentration (for κ = ²³²Th/²³⁸U).</t>
         </is>
       </c>
     </row>
@@ -8459,24 +8553,24 @@
       </c>
       <c r="C150" s="40" t="inlineStr">
         <is>
-          <t>187Os/188Os_2σ</t>
-        </is>
-      </c>
-      <c r="D150" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
+          <t>176Hf/177Hf</t>
+        </is>
+      </c>
+      <c r="D150" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
         </is>
       </c>
       <c r="E150" s="38" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.28298</t>
         </is>
       </c>
       <c r="H150" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Measured ¹⁷⁶Hf/¹⁷⁷Hf ratio. CHUR = 0.282785 (Bouvier et al. 2008).</t>
         </is>
       </c>
     </row>
@@ -8491,24 +8585,24 @@
       </c>
       <c r="C151" s="40" t="inlineStr">
         <is>
-          <t>187Re/188Os</t>
-        </is>
-      </c>
-      <c r="D151" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
+          <t>176Hf/177Hf_2σ</t>
+        </is>
+      </c>
+      <c r="D151" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
         </is>
       </c>
       <c r="E151" s="38" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="H151" s="42" t="inlineStr">
         <is>
-          <t>Parent ratio for the initial-Os correction.</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8523,28 +8617,24 @@
       </c>
       <c r="C152" s="40" t="inlineStr">
         <is>
-          <t>Os_iso</t>
-        </is>
-      </c>
-      <c r="D152" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
-        </is>
-      </c>
-      <c r="E152" s="38" t="inlineStr">
-        <is>
-          <t>ppb</t>
-        </is>
-      </c>
+          <t>176Lu/177Hf</t>
+        </is>
+      </c>
+      <c r="D152" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
+        </is>
+      </c>
+      <c r="E152" s="38" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="H152" s="42" t="inlineStr">
         <is>
-          <t>Os concentration (parts per billion).</t>
+          <t>Parent ratio for initial-Hf correction.</t>
         </is>
       </c>
     </row>
@@ -8559,28 +8649,28 @@
       </c>
       <c r="C153" s="40" t="inlineStr">
         <is>
-          <t>Re_iso</t>
-        </is>
-      </c>
-      <c r="D153" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
+          <t>Hf_iso</t>
+        </is>
+      </c>
+      <c r="D153" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
         </is>
       </c>
       <c r="E153" s="38" t="inlineStr">
         <is>
-          <t>ppb</t>
+          <t>ppm</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="H153" s="42" t="inlineStr">
         <is>
-          <t>Re concentration.</t>
+          <t>Hf concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
@@ -8595,20 +8685,28 @@
       </c>
       <c r="C154" s="40" t="inlineStr">
         <is>
-          <t>γOs_initial</t>
-        </is>
-      </c>
-      <c r="D154" s="54" t="inlineStr">
-        <is>
-          <t>Iso-Os</t>
-        </is>
-      </c>
-      <c r="E154" s="38" t="inlineStr"/>
+          <t>Lu_iso</t>
+        </is>
+      </c>
+      <c r="D154" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
+        </is>
+      </c>
+      <c r="E154" s="38" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
       <c r="H154" s="42" t="inlineStr">
         <is>
-          <t>Computed by B.I.R.D.S.</t>
+          <t>Lu concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
@@ -8623,28 +8721,20 @@
       </c>
       <c r="C155" s="40" t="inlineStr">
         <is>
-          <t>δ18O</t>
-        </is>
-      </c>
-      <c r="D155" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
-        </is>
-      </c>
-      <c r="E155" s="38" t="inlineStr">
-        <is>
-          <t>‰ VSMOW</t>
-        </is>
-      </c>
+          <t>εHf_initial</t>
+        </is>
+      </c>
+      <c r="D155" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
+        </is>
+      </c>
+      <c r="E155" s="38" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>+5.8</t>
-        </is>
-      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" s="42" t="inlineStr">
         <is>
-          <t>Oxygen isotope composition relative to VSMOW. Mantle olivine ≈ +5.2 ‰; crustal sediments commonly &gt;+10 ‰.</t>
+          <t>Computed by B.I.R.D.S.</t>
         </is>
       </c>
     </row>
@@ -8659,28 +8749,28 @@
       </c>
       <c r="C156" s="40" t="inlineStr">
         <is>
-          <t>δ18O_2σ</t>
-        </is>
-      </c>
-      <c r="D156" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
+          <t>TDM_Hf</t>
+        </is>
+      </c>
+      <c r="D156" s="53" t="inlineStr">
+        <is>
+          <t>Iso-Hf</t>
         </is>
       </c>
       <c r="E156" s="38" t="inlineStr">
         <is>
-          <t>‰</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H156" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Hf depleted-mantle model age.</t>
         </is>
       </c>
     </row>
@@ -8695,28 +8785,24 @@
       </c>
       <c r="C157" s="40" t="inlineStr">
         <is>
-          <t>δD</t>
-        </is>
-      </c>
-      <c r="D157" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
-        </is>
-      </c>
-      <c r="E157" s="38" t="inlineStr">
-        <is>
-          <t>‰ VSMOW</t>
-        </is>
-      </c>
+          <t>187Os/188Os</t>
+        </is>
+      </c>
+      <c r="D157" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
+        </is>
+      </c>
+      <c r="E157" s="38" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>-65</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="H157" s="42" t="inlineStr">
         <is>
-          <t>Hydrogen isotope composition relative to VSMOW. Useful for hydrous phases (amphibole, biotite, melt inclusions).</t>
+          <t>Measured ¹⁸⁷Os/¹⁸⁸Os ratio. Primitive Upper Mantle (PUM) ≈ 0.1296.</t>
         </is>
       </c>
     </row>
@@ -8731,23 +8817,19 @@
       </c>
       <c r="C158" s="40" t="inlineStr">
         <is>
-          <t>δD_2σ</t>
-        </is>
-      </c>
-      <c r="D158" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
-        </is>
-      </c>
-      <c r="E158" s="38" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
+          <t>187Os/188Os_2σ</t>
+        </is>
+      </c>
+      <c r="D158" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
+        </is>
+      </c>
+      <c r="E158" s="38" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="H158" s="42" t="inlineStr">
@@ -8767,28 +8849,24 @@
       </c>
       <c r="C159" s="40" t="inlineStr">
         <is>
-          <t>δ13C</t>
-        </is>
-      </c>
-      <c r="D159" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
-        </is>
-      </c>
-      <c r="E159" s="38" t="inlineStr">
-        <is>
-          <t>‰ VPDB</t>
-        </is>
-      </c>
+          <t>187Re/188Os</t>
+        </is>
+      </c>
+      <c r="D159" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
+        </is>
+      </c>
+      <c r="E159" s="38" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="H159" s="42" t="inlineStr">
         <is>
-          <t>Carbon isotope composition relative to VPDB. Mantle CO₂ ≈ -5 ‰; biogenic carbon strongly negative.</t>
+          <t>Parent ratio for the initial-Os correction.</t>
         </is>
       </c>
     </row>
@@ -8803,28 +8881,28 @@
       </c>
       <c r="C160" s="40" t="inlineStr">
         <is>
-          <t>δ13C_2σ</t>
-        </is>
-      </c>
-      <c r="D160" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
+          <t>Os_iso</t>
+        </is>
+      </c>
+      <c r="D160" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
         </is>
       </c>
       <c r="E160" s="38" t="inlineStr">
         <is>
-          <t>‰</t>
+          <t>ppb</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="H160" s="42" t="inlineStr">
         <is>
-          <t>Analytical 2σ uncertainty.</t>
+          <t>Os concentration (parts per billion).</t>
         </is>
       </c>
     </row>
@@ -8839,28 +8917,28 @@
       </c>
       <c r="C161" s="40" t="inlineStr">
         <is>
-          <t>δ11B</t>
-        </is>
-      </c>
-      <c r="D161" s="55" t="inlineStr">
-        <is>
-          <t>Iso-Stable</t>
+          <t>Re_iso</t>
+        </is>
+      </c>
+      <c r="D161" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
         </is>
       </c>
       <c r="E161" s="38" t="inlineStr">
         <is>
-          <t>‰</t>
+          <t>ppb</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="H161" s="42" t="inlineStr">
         <is>
-          <t>Boron isotope composition. Slab fluids / sediments show very contrasted signatures.</t>
+          <t>Re concentration.</t>
         </is>
       </c>
     </row>
@@ -8875,28 +8953,20 @@
       </c>
       <c r="C162" s="40" t="inlineStr">
         <is>
-          <t>Iso_Method</t>
-        </is>
-      </c>
-      <c r="D162" s="56" t="inlineStr">
-        <is>
-          <t>Iso-Meta</t>
+          <t>γOs_initial</t>
+        </is>
+      </c>
+      <c r="D162" s="54" t="inlineStr">
+        <is>
+          <t>Iso-Os</t>
         </is>
       </c>
       <c r="E162" s="38" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>TIMS, MC-ICP-MS, Solution MC-ICP-MS, LA-MC-ICP-MS, SIMS, SHRIMP, N-TIMS (Os), Laser fluorination (δ¹⁸O), EA-IRMS (δ¹³C, δD), CRDS, Mixed</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>MC-ICP-MS</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
       <c r="H162" s="42" t="inlineStr">
         <is>
-          <t>Mass-spectrometry technique used for the isotope ratio(s).</t>
+          <t>Computed by B.I.R.D.S.</t>
         </is>
       </c>
     </row>
@@ -8911,24 +8981,28 @@
       </c>
       <c r="C163" s="40" t="inlineStr">
         <is>
-          <t>Iso_Laboratory</t>
-        </is>
-      </c>
-      <c r="D163" s="56" t="inlineStr">
-        <is>
-          <t>Iso-Meta</t>
-        </is>
-      </c>
-      <c r="E163" s="38" t="inlineStr"/>
+          <t>δ18O</t>
+        </is>
+      </c>
+      <c r="D163" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
+        </is>
+      </c>
+      <c r="E163" s="38" t="inlineStr">
+        <is>
+          <t>‰ VSMOW</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>MIT Radiogenic Isotope Lab</t>
+          <t>+5.8</t>
         </is>
       </c>
       <c r="H163" s="42" t="inlineStr">
         <is>
-          <t>Lab where the isotope analysis was carried out.</t>
+          <t>Oxygen isotope composition relative to VSMOW. Mantle olivine ≈ +5.2 ‰; crustal sediments commonly &gt;+10 ‰.</t>
         </is>
       </c>
     </row>
@@ -8943,24 +9017,28 @@
       </c>
       <c r="C164" s="40" t="inlineStr">
         <is>
-          <t>Iso_Date</t>
-        </is>
-      </c>
-      <c r="D164" s="56" t="inlineStr">
-        <is>
-          <t>Iso-Meta</t>
-        </is>
-      </c>
-      <c r="E164" s="38" t="inlineStr"/>
+          <t>δ18O_2σ</t>
+        </is>
+      </c>
+      <c r="D164" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
+        </is>
+      </c>
+      <c r="E164" s="38" t="inlineStr">
+        <is>
+          <t>‰</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H164" s="42" t="inlineStr">
         <is>
-          <t>Year or full date of the isotope analysis.</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8975,24 +9053,28 @@
       </c>
       <c r="C165" s="40" t="inlineStr">
         <is>
-          <t>Iso_Analyst</t>
-        </is>
-      </c>
-      <c r="D165" s="56" t="inlineStr">
-        <is>
-          <t>Iso-Meta</t>
-        </is>
-      </c>
-      <c r="E165" s="38" t="inlineStr"/>
+          <t>δD</t>
+        </is>
+      </c>
+      <c r="D165" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
+        </is>
+      </c>
+      <c r="E165" s="38" t="inlineStr">
+        <is>
+          <t>‰ VSMOW</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>MLG</t>
+          <t>-65</t>
         </is>
       </c>
       <c r="H165" s="42" t="inlineStr">
         <is>
-          <t>Analyst initials or name.</t>
+          <t>Hydrogen isotope composition relative to VSMOW. Useful for hydrous phases (amphibole, biotite, melt inclusions).</t>
         </is>
       </c>
     </row>
@@ -9007,20 +9089,28 @@
       </c>
       <c r="C166" s="40" t="inlineStr">
         <is>
-          <t>Iso_Notes</t>
-        </is>
-      </c>
-      <c r="D166" s="56" t="inlineStr">
-        <is>
-          <t>Iso-Meta</t>
-        </is>
-      </c>
-      <c r="E166" s="38" t="inlineStr"/>
+          <t>δD_2σ</t>
+        </is>
+      </c>
+      <c r="D166" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
+        </is>
+      </c>
+      <c r="E166" s="38" t="inlineStr">
+        <is>
+          <t>‰</t>
+        </is>
+      </c>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H166" s="42" t="inlineStr">
         <is>
-          <t>Free-text notes (column chemistry, spike, repeated measurements, blanks).</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -9030,29 +9120,33 @@
       </c>
       <c r="B167" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C167" s="40" t="inlineStr">
         <is>
-          <t>Sample_Name</t>
-        </is>
-      </c>
-      <c r="D167" s="41" t="inlineStr">
-        <is>
-          <t>Petro-ID</t>
-        </is>
-      </c>
-      <c r="E167" s="38" t="inlineStr"/>
+          <t>δ13C</t>
+        </is>
+      </c>
+      <c r="D167" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
+        </is>
+      </c>
+      <c r="E167" s="38" t="inlineStr">
+        <is>
+          <t>‰ VPDB</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>VOL-2024-018</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="H167" s="42" t="inlineStr">
         <is>
-          <t>Must exactly match the Sample_Name in the Data sheet — this is the key B.I.R.D.S uses to join the modal mineralogy back to the bulk composition.</t>
+          <t>Carbon isotope composition relative to VPDB. Mantle CO₂ ≈ -5 ‰; biogenic carbon strongly negative.</t>
         </is>
       </c>
     </row>
@@ -9062,29 +9156,33 @@
       </c>
       <c r="B168" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C168" s="40" t="inlineStr">
         <is>
-          <t>Sample_Label</t>
-        </is>
-      </c>
-      <c r="D168" s="41" t="inlineStr">
-        <is>
-          <t>Petro-ID</t>
-        </is>
-      </c>
-      <c r="E168" s="38" t="inlineStr"/>
+          <t>δ13C_2σ</t>
+        </is>
+      </c>
+      <c r="D168" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
+        </is>
+      </c>
+      <c r="E168" s="38" t="inlineStr">
+        <is>
+          <t>‰</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Mt. Pico flow 18</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H168" s="42" t="inlineStr">
         <is>
-          <t>Optional friendly label used in plots.  Leave blank to inherit the value from the Data sheet — B.I.R.D.S fills this column automatically at import time.</t>
+          <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
@@ -9094,29 +9192,33 @@
       </c>
       <c r="B169" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C169" s="40" t="inlineStr">
         <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="D169" s="41" t="inlineStr">
-        <is>
-          <t>Petro-ID</t>
-        </is>
-      </c>
-      <c r="E169" s="38" t="inlineStr"/>
+          <t>δ11B</t>
+        </is>
+      </c>
+      <c r="D169" s="55" t="inlineStr">
+        <is>
+          <t>Iso-Stable</t>
+        </is>
+      </c>
+      <c r="E169" s="38" t="inlineStr">
+        <is>
+          <t>‰</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lower flow</t>
+          <t>+3.5</t>
         </is>
       </c>
       <c r="H169" s="42" t="inlineStr">
         <is>
-          <t>Optional group used for colouring / legend.  Inherited from the Data sheet at import time if left blank.</t>
+          <t>Boron isotope composition. Slab fluids / sediments show very contrasted signatures.</t>
         </is>
       </c>
     </row>
@@ -9126,33 +9228,33 @@
       </c>
       <c r="B170" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C170" s="40" t="inlineStr">
         <is>
-          <t>Texture</t>
-        </is>
-      </c>
-      <c r="D170" s="41" t="inlineStr">
-        <is>
-          <t>Petro-ID</t>
+          <t>Iso_Method</t>
+        </is>
+      </c>
+      <c r="D170" s="56" t="inlineStr">
+        <is>
+          <t>Iso-Meta</t>
         </is>
       </c>
       <c r="E170" s="38" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Phaneritic, Aphanitic, Porphyritic, Glassy, Vesicular, Pyroclastic, Cumulate, Cataclastic, Foliated / Gneissic, Mixed</t>
+          <t>TIMS, MC-ICP-MS, Solution MC-ICP-MS, LA-MC-ICP-MS, SIMS, SHRIMP, N-TIMS (Os), Laser fluorination (δ¹⁸O), EA-IRMS (δ¹³C, δD), CRDS, Mixed</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porphyritic</t>
+          <t>MC-ICP-MS</t>
         </is>
       </c>
       <c r="H170" s="42" t="inlineStr">
         <is>
-          <t>Overall rock fabric. Pick from the dropdown.</t>
+          <t>Mass-spectrometry technique used for the isotope ratio(s).</t>
         </is>
       </c>
     </row>
@@ -9162,33 +9264,29 @@
       </c>
       <c r="B171" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C171" s="40" t="inlineStr">
         <is>
-          <t>Q_mode</t>
-        </is>
-      </c>
-      <c r="D171" s="57" t="inlineStr">
-        <is>
-          <t>Petro-QAPF</t>
-        </is>
-      </c>
-      <c r="E171" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Iso_Laboratory</t>
+        </is>
+      </c>
+      <c r="D171" s="56" t="inlineStr">
+        <is>
+          <t>Iso-Meta</t>
+        </is>
+      </c>
+      <c r="E171" s="38" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>MIT Radiogenic Isotope Lab</t>
         </is>
       </c>
       <c r="H171" s="42" t="inlineStr">
         <is>
-          <t>Modal Quartz (Q apex of the Streckeisen QAPF diagram).</t>
+          <t>Lab where the isotope analysis was carried out.</t>
         </is>
       </c>
     </row>
@@ -9198,33 +9296,29 @@
       </c>
       <c r="B172" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C172" s="40" t="inlineStr">
         <is>
-          <t>A_mode</t>
-        </is>
-      </c>
-      <c r="D172" s="57" t="inlineStr">
-        <is>
-          <t>Petro-QAPF</t>
-        </is>
-      </c>
-      <c r="E172" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Iso_Date</t>
+        </is>
+      </c>
+      <c r="D172" s="56" t="inlineStr">
+        <is>
+          <t>Iso-Meta</t>
+        </is>
+      </c>
+      <c r="E172" s="38" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="H172" s="42" t="inlineStr">
         <is>
-          <t>Modal Alkali feldspar (K-feldspar + albite component); A apex of QAPF.</t>
+          <t>Year or full date of the isotope analysis.</t>
         </is>
       </c>
     </row>
@@ -9234,33 +9328,29 @@
       </c>
       <c r="B173" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C173" s="40" t="inlineStr">
         <is>
-          <t>P_mode</t>
-        </is>
-      </c>
-      <c r="D173" s="57" t="inlineStr">
-        <is>
-          <t>Petro-QAPF</t>
-        </is>
-      </c>
-      <c r="E173" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Iso_Analyst</t>
+        </is>
+      </c>
+      <c r="D173" s="56" t="inlineStr">
+        <is>
+          <t>Iso-Meta</t>
+        </is>
+      </c>
+      <c r="E173" s="38" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>MLG</t>
         </is>
       </c>
       <c r="H173" s="42" t="inlineStr">
         <is>
-          <t>Modal Plagioclase (calcic / sodic plagioclase); P apex of QAPF.</t>
+          <t>Analyst initials or name.</t>
         </is>
       </c>
     </row>
@@ -9270,33 +9360,25 @@
       </c>
       <c r="B174" s="39" t="inlineStr">
         <is>
-          <t>Petrography</t>
+          <t>Isotopes</t>
         </is>
       </c>
       <c r="C174" s="40" t="inlineStr">
         <is>
-          <t>F_mode</t>
-        </is>
-      </c>
-      <c r="D174" s="57" t="inlineStr">
-        <is>
-          <t>Petro-QAPF</t>
-        </is>
-      </c>
-      <c r="E174" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Iso_Notes</t>
+        </is>
+      </c>
+      <c r="D174" s="56" t="inlineStr">
+        <is>
+          <t>Iso-Meta</t>
+        </is>
+      </c>
+      <c r="E174" s="38" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" s="42" t="inlineStr">
         <is>
-          <t>Modal Feldspathoid (nepheline, leucite, sodalite …); F apex of the bottom QAPF triangle. Mutually exclusive with Q (one rock can't have both).</t>
+          <t>Free-text notes (column chemistry, spike, repeated measurements, blanks).</t>
         </is>
       </c>
     </row>
@@ -9311,28 +9393,24 @@
       </c>
       <c r="C175" s="40" t="inlineStr">
         <is>
-          <t>Ol_mode</t>
-        </is>
-      </c>
-      <c r="D175" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
-        </is>
-      </c>
-      <c r="E175" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Sample_Name</t>
+        </is>
+      </c>
+      <c r="D175" s="41" t="inlineStr">
+        <is>
+          <t>Petro-ID</t>
+        </is>
+      </c>
+      <c r="E175" s="38" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>VOL-2024-018</t>
         </is>
       </c>
       <c r="H175" s="42" t="inlineStr">
         <is>
-          <t>Modal Olivine. Ol apex of the gabbro Pl-Px-Ol ternary and of the ultramafic Ol-Opx-Cpx ternary.</t>
+          <t>Must exactly match the Sample_Name in the Data sheet — this is the key B.I.R.D.S uses to join the modal mineralogy back to the bulk composition.</t>
         </is>
       </c>
     </row>
@@ -9347,28 +9425,24 @@
       </c>
       <c r="C176" s="40" t="inlineStr">
         <is>
-          <t>Opx_mode</t>
-        </is>
-      </c>
-      <c r="D176" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
-        </is>
-      </c>
-      <c r="E176" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Sample_Label</t>
+        </is>
+      </c>
+      <c r="D176" s="41" t="inlineStr">
+        <is>
+          <t>Petro-ID</t>
+        </is>
+      </c>
+      <c r="E176" s="38" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Mt. Pico flow 18</t>
         </is>
       </c>
       <c r="H176" s="42" t="inlineStr">
         <is>
-          <t>Modal Orthopyroxene (enstatite to ferrosilite). Opx apex of the ultramafic ternary.</t>
+          <t>Optional friendly label used in plots.  Leave blank to inherit the value from the Data sheet — B.I.R.D.S fills this column automatically at import time.</t>
         </is>
       </c>
     </row>
@@ -9383,28 +9457,24 @@
       </c>
       <c r="C177" s="40" t="inlineStr">
         <is>
-          <t>Cpx_mode</t>
-        </is>
-      </c>
-      <c r="D177" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
-        </is>
-      </c>
-      <c r="E177" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="D177" s="41" t="inlineStr">
+        <is>
+          <t>Petro-ID</t>
+        </is>
+      </c>
+      <c r="E177" s="38" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Lower flow</t>
         </is>
       </c>
       <c r="H177" s="42" t="inlineStr">
         <is>
-          <t>Modal Clinopyroxene (diopside, augite, pigeonite …). Cpx apex of the ultramafic ternary.</t>
+          <t>Optional group used for colouring / legend.  Inherited from the Data sheet at import time if left blank.</t>
         </is>
       </c>
     </row>
@@ -9419,24 +9489,28 @@
       </c>
       <c r="C178" s="40" t="inlineStr">
         <is>
-          <t>Px_mode</t>
-        </is>
-      </c>
-      <c r="D178" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
-        </is>
-      </c>
-      <c r="E178" s="38" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
+          <t>Texture</t>
+        </is>
+      </c>
+      <c r="D178" s="41" t="inlineStr">
+        <is>
+          <t>Petro-ID</t>
+        </is>
+      </c>
+      <c r="E178" s="38" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Phaneritic, Aphanitic, Porphyritic, Glassy, Vesicular, Pyroclastic, Cumulate, Cataclastic, Foliated / Gneissic, Mixed</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Porphyritic</t>
+        </is>
+      </c>
       <c r="H178" s="42" t="inlineStr">
         <is>
-          <t>Total pyroxene (Opx + Cpx) used by the gabbro Pl-Px-Ol ternary. Leave empty — B.I.R.D.S sums Opx + Cpx automatically if you fill those.</t>
+          <t>Overall rock fabric. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
@@ -9451,12 +9525,12 @@
       </c>
       <c r="C179" s="40" t="inlineStr">
         <is>
-          <t>Amph_mode</t>
-        </is>
-      </c>
-      <c r="D179" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
+          <t>Q_mode</t>
+        </is>
+      </c>
+      <c r="D179" s="57" t="inlineStr">
+        <is>
+          <t>Petro-QAPF</t>
         </is>
       </c>
       <c r="E179" s="38" t="inlineStr">
@@ -9467,12 +9541,12 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H179" s="42" t="inlineStr">
         <is>
-          <t>Modal Amphibole (hornblende, actinolite, kaersutite …). Not used by QAPF but reported for completeness.</t>
+          <t>Modal Quartz (Q apex of the Streckeisen QAPF diagram).</t>
         </is>
       </c>
     </row>
@@ -9487,12 +9561,12 @@
       </c>
       <c r="C180" s="40" t="inlineStr">
         <is>
-          <t>Bt_mode</t>
-        </is>
-      </c>
-      <c r="D180" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
+          <t>A_mode</t>
+        </is>
+      </c>
+      <c r="D180" s="57" t="inlineStr">
+        <is>
+          <t>Petro-QAPF</t>
         </is>
       </c>
       <c r="E180" s="38" t="inlineStr">
@@ -9503,12 +9577,12 @@
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H180" s="42" t="inlineStr">
         <is>
-          <t>Modal Biotite.</t>
+          <t>Modal Alkali feldspar (K-feldspar + albite component); A apex of QAPF.</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9597,12 @@
       </c>
       <c r="C181" s="40" t="inlineStr">
         <is>
-          <t>Ms_mode</t>
-        </is>
-      </c>
-      <c r="D181" s="53" t="inlineStr">
-        <is>
-          <t>Petro-Mafic</t>
+          <t>P_mode</t>
+        </is>
+      </c>
+      <c r="D181" s="57" t="inlineStr">
+        <is>
+          <t>Petro-QAPF</t>
         </is>
       </c>
       <c r="E181" s="38" t="inlineStr">
@@ -9539,12 +9613,12 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H181" s="42" t="inlineStr">
         <is>
-          <t>Modal Muscovite.</t>
+          <t>Modal Plagioclase (calcic / sodic plagioclase); P apex of QAPF.</t>
         </is>
       </c>
     </row>
@@ -9559,12 +9633,12 @@
       </c>
       <c r="C182" s="40" t="inlineStr">
         <is>
-          <t>Opaque_mode</t>
-        </is>
-      </c>
-      <c r="D182" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
+          <t>F_mode</t>
+        </is>
+      </c>
+      <c r="D182" s="57" t="inlineStr">
+        <is>
+          <t>Petro-QAPF</t>
         </is>
       </c>
       <c r="E182" s="38" t="inlineStr">
@@ -9575,12 +9649,12 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H182" s="42" t="inlineStr">
         <is>
-          <t>Modal Fe-Ti oxides (magnetite, ilmenite, hematite, chromite).</t>
+          <t>Modal Feldspathoid (nepheline, leucite, sodalite …); F apex of the bottom QAPF triangle. Mutually exclusive with Q (one rock can't have both).</t>
         </is>
       </c>
     </row>
@@ -9595,12 +9669,12 @@
       </c>
       <c r="C183" s="40" t="inlineStr">
         <is>
-          <t>Apatite_mode</t>
-        </is>
-      </c>
-      <c r="D183" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
+          <t>Ol_mode</t>
+        </is>
+      </c>
+      <c r="D183" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
         </is>
       </c>
       <c r="E183" s="38" t="inlineStr">
@@ -9611,12 +9685,12 @@
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H183" s="42" t="inlineStr">
         <is>
-          <t>Modal Apatite.</t>
+          <t>Modal Olivine. Ol apex of the gabbro Pl-Px-Ol ternary and of the ultramafic Ol-Opx-Cpx ternary.</t>
         </is>
       </c>
     </row>
@@ -9631,12 +9705,12 @@
       </c>
       <c r="C184" s="40" t="inlineStr">
         <is>
-          <t>Zircon_mode</t>
-        </is>
-      </c>
-      <c r="D184" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
+          <t>Opx_mode</t>
+        </is>
+      </c>
+      <c r="D184" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
         </is>
       </c>
       <c r="E184" s="38" t="inlineStr">
@@ -9647,12 +9721,12 @@
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H184" s="42" t="inlineStr">
         <is>
-          <t>Modal Zircon.</t>
+          <t>Modal Orthopyroxene (enstatite to ferrosilite). Opx apex of the ultramafic ternary.</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9741,12 @@
       </c>
       <c r="C185" s="40" t="inlineStr">
         <is>
-          <t>Titanite_mode</t>
-        </is>
-      </c>
-      <c r="D185" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
+          <t>Cpx_mode</t>
+        </is>
+      </c>
+      <c r="D185" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
         </is>
       </c>
       <c r="E185" s="38" t="inlineStr">
@@ -9683,12 +9757,12 @@
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H185" s="42" t="inlineStr">
         <is>
-          <t>Modal Titanite / sphene.</t>
+          <t>Modal Clinopyroxene (diopside, augite, pigeonite …). Cpx apex of the ultramafic ternary.</t>
         </is>
       </c>
     </row>
@@ -9703,12 +9777,12 @@
       </c>
       <c r="C186" s="40" t="inlineStr">
         <is>
-          <t>Carbonate_mode</t>
-        </is>
-      </c>
-      <c r="D186" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
+          <t>Px_mode</t>
+        </is>
+      </c>
+      <c r="D186" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
         </is>
       </c>
       <c r="E186" s="38" t="inlineStr">
@@ -9717,14 +9791,10 @@
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" s="42" t="inlineStr">
         <is>
-          <t>Modal Calcite, dolomite, ankerite (esp. in alteration / carbonatites).</t>
+          <t>Total pyroxene (Opx + Cpx) used by the gabbro Pl-Px-Ol ternary. Leave empty — B.I.R.D.S sums Opx + Cpx automatically if you fill those.</t>
         </is>
       </c>
     </row>
@@ -9739,12 +9809,12 @@
       </c>
       <c r="C187" s="40" t="inlineStr">
         <is>
-          <t>Other_acc_mode</t>
-        </is>
-      </c>
-      <c r="D187" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
+          <t>Amph_mode</t>
+        </is>
+      </c>
+      <c r="D187" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
         </is>
       </c>
       <c r="E187" s="38" t="inlineStr">
@@ -9755,12 +9825,12 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H187" s="42" t="inlineStr">
         <is>
-          <t>Modal other accessories (epidote, chlorite, sericite, garnet, tourmaline, monazite, …).</t>
+          <t>Modal Amphibole (hornblende, actinolite, kaersutite …). Not used by QAPF but reported for completeness.</t>
         </is>
       </c>
     </row>
@@ -9775,12 +9845,12 @@
       </c>
       <c r="C188" s="40" t="inlineStr">
         <is>
-          <t>Mode_Total</t>
-        </is>
-      </c>
-      <c r="D188" s="54" t="inlineStr">
-        <is>
-          <t>Petro-Acc</t>
+          <t>Bt_mode</t>
+        </is>
+      </c>
+      <c r="D188" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
         </is>
       </c>
       <c r="E188" s="38" t="inlineStr">
@@ -9789,10 +9859,14 @@
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="H188" s="42" t="inlineStr">
         <is>
-          <t>Quality-control sum of every modal column above. Should fall between 99 and 101 vol %.</t>
+          <t>Modal Biotite.</t>
         </is>
       </c>
     </row>
@@ -9807,12 +9881,12 @@
       </c>
       <c r="C189" s="40" t="inlineStr">
         <is>
-          <t>Crystal_pct</t>
-        </is>
-      </c>
-      <c r="D189" s="55" t="inlineStr">
-        <is>
-          <t>Petro-Tuff</t>
+          <t>Ms_mode</t>
+        </is>
+      </c>
+      <c r="D189" s="53" t="inlineStr">
+        <is>
+          <t>Petro-Mafic</t>
         </is>
       </c>
       <c r="E189" s="38" t="inlineStr">
@@ -9823,12 +9897,12 @@
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H189" s="42" t="inlineStr">
         <is>
-          <t>Crystal fragments — Crystal apex of the IUGS tuff ternary (Schmid 1981).</t>
+          <t>Modal Muscovite.</t>
         </is>
       </c>
     </row>
@@ -9843,12 +9917,12 @@
       </c>
       <c r="C190" s="40" t="inlineStr">
         <is>
-          <t>Vitric_pct</t>
-        </is>
-      </c>
-      <c r="D190" s="55" t="inlineStr">
-        <is>
-          <t>Petro-Tuff</t>
+          <t>Opaque_mode</t>
+        </is>
+      </c>
+      <c r="D190" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
         </is>
       </c>
       <c r="E190" s="38" t="inlineStr">
@@ -9859,12 +9933,12 @@
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H190" s="42" t="inlineStr">
         <is>
-          <t>Glass shards / pumice fragments — Vitric apex.</t>
+          <t>Modal Fe-Ti oxides (magnetite, ilmenite, hematite, chromite).</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9953,12 @@
       </c>
       <c r="C191" s="40" t="inlineStr">
         <is>
-          <t>Lithic_pct</t>
-        </is>
-      </c>
-      <c r="D191" s="55" t="inlineStr">
-        <is>
-          <t>Petro-Tuff</t>
+          <t>Apatite_mode</t>
+        </is>
+      </c>
+      <c r="D191" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
         </is>
       </c>
       <c r="E191" s="38" t="inlineStr">
@@ -9895,12 +9969,12 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H191" s="42" t="inlineStr">
         <is>
-          <t>Lithic / rock fragments — Lithic apex.</t>
+          <t>Modal Apatite.</t>
         </is>
       </c>
     </row>
@@ -9915,28 +9989,28 @@
       </c>
       <c r="C192" s="40" t="inlineStr">
         <is>
-          <t>Pyroclast_size</t>
-        </is>
-      </c>
-      <c r="D192" s="55" t="inlineStr">
-        <is>
-          <t>Petro-Tuff</t>
-        </is>
-      </c>
-      <c r="E192" s="38" t="inlineStr"/>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Ash (&lt; 2 mm), Lapilli (2-64 mm), Block / Bomb (&gt; 64 mm), Mixed</t>
-        </is>
-      </c>
+          <t>Zircon_mode</t>
+        </is>
+      </c>
+      <c r="D192" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
+        </is>
+      </c>
+      <c r="E192" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Lapilli (2-64 mm)</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H192" s="42" t="inlineStr">
         <is>
-          <t>Granulometric class. Pick from the dropdown.</t>
+          <t>Modal Zircon.</t>
         </is>
       </c>
     </row>
@@ -9951,28 +10025,28 @@
       </c>
       <c r="C193" s="40" t="inlineStr">
         <is>
-          <t>Grain_size_mm</t>
-        </is>
-      </c>
-      <c r="D193" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
+          <t>Titanite_mode</t>
+        </is>
+      </c>
+      <c r="D193" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
         </is>
       </c>
       <c r="E193" s="38" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>vol %</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H193" s="42" t="inlineStr">
         <is>
-          <t>Average grain size (groundmass for porphyritic rocks).</t>
+          <t>Modal Titanite / sphene.</t>
         </is>
       </c>
     </row>
@@ -9987,12 +10061,12 @@
       </c>
       <c r="C194" s="40" t="inlineStr">
         <is>
-          <t>Phenocryst_pct</t>
-        </is>
-      </c>
-      <c r="D194" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
+          <t>Carbonate_mode</t>
+        </is>
+      </c>
+      <c r="D194" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
         </is>
       </c>
       <c r="E194" s="38" t="inlineStr">
@@ -10003,12 +10077,12 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H194" s="42" t="inlineStr">
         <is>
-          <t>Total phenocryst content (porphyritic rocks).</t>
+          <t>Modal Calcite, dolomite, ankerite (esp. in alteration / carbonatites).</t>
         </is>
       </c>
     </row>
@@ -10023,12 +10097,12 @@
       </c>
       <c r="C195" s="40" t="inlineStr">
         <is>
-          <t>Vesicle_pct</t>
-        </is>
-      </c>
-      <c r="D195" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
+          <t>Other_acc_mode</t>
+        </is>
+      </c>
+      <c r="D195" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
         </is>
       </c>
       <c r="E195" s="38" t="inlineStr">
@@ -10039,12 +10113,12 @@
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H195" s="42" t="inlineStr">
         <is>
-          <t>Vesicle / vug content.</t>
+          <t>Modal other accessories (epidote, chlorite, sericite, garnet, tourmaline, monazite, …).</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10133,12 @@
       </c>
       <c r="C196" s="40" t="inlineStr">
         <is>
-          <t>Alteration_pct</t>
-        </is>
-      </c>
-      <c r="D196" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
+          <t>Mode_Total</t>
+        </is>
+      </c>
+      <c r="D196" s="54" t="inlineStr">
+        <is>
+          <t>Petro-Acc</t>
         </is>
       </c>
       <c r="E196" s="38" t="inlineStr">
@@ -10073,14 +10147,10 @@
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" s="42" t="inlineStr">
         <is>
-          <t>Secondary minerals / alteration overprint (sericite, chlorite, clay …).</t>
+          <t>Quality-control sum of every modal column above. Should fall between 99 and 101 vol %.</t>
         </is>
       </c>
     </row>
@@ -10095,24 +10165,28 @@
       </c>
       <c r="C197" s="40" t="inlineStr">
         <is>
-          <t>Texture_notes</t>
-        </is>
-      </c>
-      <c r="D197" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
-        </is>
-      </c>
-      <c r="E197" s="38" t="inlineStr"/>
+          <t>Crystal_pct</t>
+        </is>
+      </c>
+      <c r="D197" s="55" t="inlineStr">
+        <is>
+          <t>Petro-Tuff</t>
+        </is>
+      </c>
+      <c r="E197" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Plg zoned; Cpx with sieve texture</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H197" s="42" t="inlineStr">
         <is>
-          <t>Free-text observations (zoning, reaction rims, embayments, cumulate textures, mineral assemblage).</t>
+          <t>Crystal fragments — Crystal apex of the IUGS tuff ternary (Schmid 1981).</t>
         </is>
       </c>
     </row>
@@ -10127,28 +10201,28 @@
       </c>
       <c r="C198" s="40" t="inlineStr">
         <is>
-          <t>Microscope_method</t>
-        </is>
-      </c>
-      <c r="D198" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
-        </is>
-      </c>
-      <c r="E198" s="38" t="inlineStr"/>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Point-count (≥ 300 points), Point-count (100-300 points), Visual estimate, Modal calculation (CIPW), Image analysis (software), SEM-EDS / EBSD, Mixed</t>
-        </is>
-      </c>
+          <t>Vitric_pct</t>
+        </is>
+      </c>
+      <c r="D198" s="55" t="inlineStr">
+        <is>
+          <t>Petro-Tuff</t>
+        </is>
+      </c>
+      <c r="E198" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Point-count (≥ 300 points)</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H198" s="42" t="inlineStr">
         <is>
-          <t>How the modal proportions were obtained.</t>
+          <t>Glass shards / pumice fragments — Vitric apex.</t>
         </is>
       </c>
     </row>
@@ -10163,24 +10237,28 @@
       </c>
       <c r="C199" s="40" t="inlineStr">
         <is>
-          <t>Microscope_lab</t>
-        </is>
-      </c>
-      <c r="D199" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
-        </is>
-      </c>
-      <c r="E199" s="38" t="inlineStr"/>
+          <t>Lithic_pct</t>
+        </is>
+      </c>
+      <c r="D199" s="55" t="inlineStr">
+        <is>
+          <t>Petro-Tuff</t>
+        </is>
+      </c>
+      <c r="E199" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>UNAM — Petrology lab</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H199" s="42" t="inlineStr">
         <is>
-          <t>Lab / university where the thin section was studied.</t>
+          <t>Lithic / rock fragments — Lithic apex.</t>
         </is>
       </c>
     </row>
@@ -10195,24 +10273,28 @@
       </c>
       <c r="C200" s="40" t="inlineStr">
         <is>
-          <t>Petrography_date</t>
-        </is>
-      </c>
-      <c r="D200" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
+          <t>Pyroclast_size</t>
+        </is>
+      </c>
+      <c r="D200" s="55" t="inlineStr">
+        <is>
+          <t>Petro-Tuff</t>
         </is>
       </c>
       <c r="E200" s="38" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Ash (&lt; 2 mm), Lapilli (2-64 mm), Block / Bomb (&gt; 64 mm), Mixed</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>Lapilli (2-64 mm)</t>
         </is>
       </c>
       <c r="H200" s="42" t="inlineStr">
         <is>
-          <t>Year / date of the petrographic analysis (YYYY or YYYY-MM-DD).</t>
+          <t>Granulometric class. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
@@ -10227,24 +10309,28 @@
       </c>
       <c r="C201" s="40" t="inlineStr">
         <is>
-          <t>Petrographer</t>
-        </is>
-      </c>
-      <c r="D201" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
-        </is>
-      </c>
-      <c r="E201" s="38" t="inlineStr"/>
+          <t>Grain_size_mm</t>
+        </is>
+      </c>
+      <c r="D201" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E201" s="38" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>MDC</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H201" s="42" t="inlineStr">
         <is>
-          <t>Analyst initials or name.</t>
+          <t>Average grain size (groundmass for porphyritic rocks).</t>
         </is>
       </c>
     </row>
@@ -10259,18 +10345,290 @@
       </c>
       <c r="C202" s="40" t="inlineStr">
         <is>
+          <t>Phenocryst_pct</t>
+        </is>
+      </c>
+      <c r="D202" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E202" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H202" s="42" t="inlineStr">
+        <is>
+          <t>Total phenocryst content (porphyritic rocks).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="38" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C203" s="40" t="inlineStr">
+        <is>
+          <t>Vesicle_pct</t>
+        </is>
+      </c>
+      <c r="D203" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E203" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H203" s="42" t="inlineStr">
+        <is>
+          <t>Vesicle / vug content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="38" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C204" s="40" t="inlineStr">
+        <is>
+          <t>Alteration_pct</t>
+        </is>
+      </c>
+      <c r="D204" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E204" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H204" s="42" t="inlineStr">
+        <is>
+          <t>Secondary minerals / alteration overprint (sericite, chlorite, clay …).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="38" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C205" s="40" t="inlineStr">
+        <is>
+          <t>Texture_notes</t>
+        </is>
+      </c>
+      <c r="D205" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E205" s="38" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Plg zoned; Cpx with sieve texture</t>
+        </is>
+      </c>
+      <c r="H205" s="42" t="inlineStr">
+        <is>
+          <t>Free-text observations (zoning, reaction rims, embayments, cumulate textures, mineral assemblage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="38" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C206" s="40" t="inlineStr">
+        <is>
+          <t>Microscope_method</t>
+        </is>
+      </c>
+      <c r="D206" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E206" s="38" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Point-count (≥ 300 points), Point-count (100-300 points), Visual estimate, Modal calculation (CIPW), Image analysis (software), SEM-EDS / EBSD, Mixed</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Point-count (≥ 300 points)</t>
+        </is>
+      </c>
+      <c r="H206" s="42" t="inlineStr">
+        <is>
+          <t>How the modal proportions were obtained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="38" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C207" s="40" t="inlineStr">
+        <is>
+          <t>Microscope_lab</t>
+        </is>
+      </c>
+      <c r="D207" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E207" s="38" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>UNAM — Petrology lab</t>
+        </is>
+      </c>
+      <c r="H207" s="42" t="inlineStr">
+        <is>
+          <t>Lab / university where the thin section was studied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="38" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C208" s="40" t="inlineStr">
+        <is>
+          <t>Petrography_date</t>
+        </is>
+      </c>
+      <c r="D208" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E208" s="38" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="H208" s="42" t="inlineStr">
+        <is>
+          <t>Year / date of the petrographic analysis (YYYY or YYYY-MM-DD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="38" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C209" s="40" t="inlineStr">
+        <is>
+          <t>Petrographer</t>
+        </is>
+      </c>
+      <c r="D209" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E209" s="38" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>MDC</t>
+        </is>
+      </c>
+      <c r="H209" s="42" t="inlineStr">
+        <is>
+          <t>Analyst initials or name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="38" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C210" s="40" t="inlineStr">
+        <is>
           <t>Petrography_notes</t>
         </is>
       </c>
-      <c r="D202" s="56" t="inlineStr">
+      <c r="D210" s="56" t="inlineStr">
         <is>
           <t>Petro-Meta</t>
         </is>
       </c>
-      <c r="E202" s="38" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" s="42" t="inlineStr">
+      <c r="E210" s="38" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" s="42" t="inlineStr">
         <is>
           <t>Free-text notes (sample preservation, mounting, staining for K-feldspar, etc.).</t>
         </is>

--- a/templates/BIRDS_data_template.xlsx
+++ b/templates/BIRDS_data_template.xlsx
@@ -2761,7 +2761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AM2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2790,16 +2790,19 @@
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="16" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
-    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
-    <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="19" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="19" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="18" customWidth="1" min="37" max="37"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2933,52 +2936,67 @@
           <t>Pyroclast_size</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AA1" s="22" t="inlineStr">
+        <is>
+          <t>Blocks_bombs_pct</t>
+        </is>
+      </c>
+      <c r="AB1" s="22" t="inlineStr">
+        <is>
+          <t>Lapilli_pct</t>
+        </is>
+      </c>
+      <c r="AC1" s="22" t="inlineStr">
+        <is>
+          <t>Ash_pct</t>
+        </is>
+      </c>
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>Grain_size_mm</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AE1" s="4" t="inlineStr">
         <is>
           <t>Phenocryst_pct</t>
         </is>
       </c>
-      <c r="AC1" s="4" t="inlineStr">
+      <c r="AF1" s="4" t="inlineStr">
         <is>
           <t>Vesicle_pct</t>
         </is>
       </c>
-      <c r="AD1" s="4" t="inlineStr">
+      <c r="AG1" s="4" t="inlineStr">
         <is>
           <t>Alteration_pct</t>
         </is>
       </c>
-      <c r="AE1" s="4" t="inlineStr">
+      <c r="AH1" s="4" t="inlineStr">
         <is>
           <t>Texture_notes</t>
         </is>
       </c>
-      <c r="AF1" s="23" t="inlineStr">
+      <c r="AI1" s="23" t="inlineStr">
         <is>
           <t>Microscope_method</t>
         </is>
       </c>
-      <c r="AG1" s="23" t="inlineStr">
+      <c r="AJ1" s="23" t="inlineStr">
         <is>
           <t>Microscope_lab</t>
         </is>
       </c>
-      <c r="AH1" s="23" t="inlineStr">
+      <c r="AK1" s="23" t="inlineStr">
         <is>
           <t>Petrography_date</t>
         </is>
       </c>
-      <c r="AI1" s="23" t="inlineStr">
+      <c r="AL1" s="23" t="inlineStr">
         <is>
           <t>Petrographer</t>
         </is>
       </c>
-      <c r="AJ1" s="23" t="inlineStr">
+      <c r="AM1" s="23" t="inlineStr">
         <is>
           <t>Petrography_notes</t>
         </is>
@@ -3095,32 +3113,47 @@
         </is>
       </c>
       <c r="Z2" s="29" t="inlineStr"/>
-      <c r="AA2" s="12" t="inlineStr">
+      <c r="AA2" s="29" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="AB2" s="29" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="AC2" s="29" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="AD2" s="12" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="AB2" s="12" t="inlineStr">
+      <c r="AE2" s="12" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
       </c>
-      <c r="AC2" s="12" t="inlineStr">
+      <c r="AF2" s="12" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
       </c>
-      <c r="AD2" s="12" t="inlineStr">
+      <c r="AG2" s="12" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
       </c>
-      <c r="AE2" s="12" t="inlineStr"/>
-      <c r="AF2" s="30" t="inlineStr"/>
-      <c r="AG2" s="30" t="inlineStr"/>
-      <c r="AH2" s="30" t="inlineStr"/>
+      <c r="AH2" s="12" t="inlineStr"/>
       <c r="AI2" s="30" t="inlineStr"/>
       <c r="AJ2" s="30" t="inlineStr"/>
+      <c r="AK2" s="30" t="inlineStr"/>
+      <c r="AL2" s="30" t="inlineStr"/>
+      <c r="AM2" s="30" t="inlineStr"/>
     </row>
     <row r="3" ht="16" customHeight="1"/>
     <row r="4" ht="16" customHeight="1"/>
@@ -3330,7 +3363,7 @@
     <dataValidation sqref="Z3:Z1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ash (&lt; 2 mm), Lapilli (2-64 mm), Block / Bomb (&gt; 64 mm), Mixed" type="list">
       <formula1>"Ash (&lt; 2 mm),Lapilli (2-64 mm),Block / Bomb (&gt; 64 mm),Mixed"</formula1>
     </dataValidation>
-    <dataValidation sqref="AF3:AF1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Point-count (≥ 300 points), Point-count (100-300 points), Visual estimate, Modal calculation (CIPW), Image analysis (software), SEM-EDS / EBSD, Mixed" type="list">
+    <dataValidation sqref="AI3:AI1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Point-count (≥ 300 points), Point-count (100-300 points), Visual estimate, Modal calculation (CIPW), Image analysis (software), SEM-EDS / EBSD, Mixed" type="list">
       <formula1>"Point-count (≥ 300 points),Point-count (100-300 points),Visual estimate,Modal calculation (CIPW),Image analysis (software),SEM-EDS / EBSD,Mixed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3344,7 +3377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B45"/>
+  <dimension ref="B1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3442,10 +3475,10 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="43.8" customHeight="1">
+    <row r="17" ht="56.4" customHeight="1">
       <c r="B17" s="36" t="inlineStr">
         <is>
-          <t>9. The 'Petrography' sheet captures modal mineralogy from thin sections: Q-A-P-F (Streckeisen QAPF), Ol-Opx-Cpx (ultramafic rocks), Pl-Px-Ol (gabbroic rocks) and Crystal-Vitric-Lithic (pyroclastic tuffs). Rows are joined to the bulk dataset by 'Sample_Name'.</t>
+          <t>9. The 'Petrography' sheet captures modal mineralogy from thin sections: Q-A-P-F (Streckeisen QAPF), Ol-Opx-Cpx (ultramafic rocks), Pl-Px-Ol (gabbroic rocks), Crystal-Vitric-Lithic (tuffs) and Blocks-Lapilli-Ash (pyroclastic rocks by fragment size). Rows are joined to the bulk dataset by 'Sample_Name'.</t>
         </is>
       </c>
     </row>
@@ -3578,47 +3611,54 @@
     <row r="38" ht="18.6" customHeight="1">
       <c r="B38" s="37" t="inlineStr">
         <is>
-          <t>• Petrography — Pyroclastic tuffs → Crystal_pct, Vitric_pct, Lithic_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18.6" customHeight="1">
-      <c r="B40" s="35" t="inlineStr">
+          <t>• Petrography — Pyroclastic tuffs (Schmid 1981) → Crystal_pct, Vitric_pct, Lithic_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="31.2" customHeight="1">
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>• Petrography — Pyroclastic rocks by fragment size (Fisher 1966) → Blocks_bombs_pct, Lapilli_pct, Ash_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18.6" customHeight="1">
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>Tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="31.2" customHeight="1">
-      <c r="B41" s="36" t="inlineStr">
-        <is>
-          <t>• Keep 'No.' as a sequential integer so it can be used as a sample ID when 'Sample_Name' is missing.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="31.2" customHeight="1">
       <c r="B42" s="36" t="inlineStr">
         <is>
+          <t>• Keep 'No.' as a sequential integer so it can be used as a sample ID when 'Sample_Name' is missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="31.2" customHeight="1">
+      <c r="B43" s="36" t="inlineStr">
+        <is>
           <t>• If you only have FeO + Fe2O3 (and not FeOt), B.I.R.D.S will compute FeOt = FeO + 0.8998 × Fe2O3 automatically.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="43.8" customHeight="1">
-      <c r="B43" s="36" t="inlineStr">
+    <row r="44" ht="43.8" customHeight="1">
+      <c r="B44" s="36" t="inlineStr">
         <is>
           <t>• 'TAS_Composition' can be left empty — the TAS diagram will compute it from your SiO2 and alkalis. Filling it in is useful only if you want to colour samples by lithology in other diagrams.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18.6" customHeight="1">
-      <c r="B44" s="36" t="inlineStr">
+    <row r="45" ht="18.6" customHeight="1">
+      <c r="B45" s="36" t="inlineStr">
         <is>
           <t>• Latitude / Longitude in decimal degrees, WGS-84. Negative values are south / west.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="31.2" customHeight="1">
-      <c r="B45" s="36" t="inlineStr">
+    <row r="46" ht="31.2" customHeight="1">
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t>• Always keep a backup of your original lab report. This template is meant for plotting, not for archiving primary data.</t>
         </is>
@@ -3635,7 +3675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10309,28 +10349,28 @@
       </c>
       <c r="C201" s="40" t="inlineStr">
         <is>
-          <t>Grain_size_mm</t>
-        </is>
-      </c>
-      <c r="D201" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
+          <t>Blocks_bombs_pct</t>
+        </is>
+      </c>
+      <c r="D201" s="55" t="inlineStr">
+        <is>
+          <t>Petro-Tuff</t>
         </is>
       </c>
       <c r="E201" s="38" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>vol %</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H201" s="42" t="inlineStr">
         <is>
-          <t>Average grain size (groundmass for porphyritic rocks).</t>
+          <t>Blocks and bombs, fragments over 64 mm — top apex of Fisher's (1966) fragment-size ternary.</t>
         </is>
       </c>
     </row>
@@ -10345,12 +10385,12 @@
       </c>
       <c r="C202" s="40" t="inlineStr">
         <is>
-          <t>Phenocryst_pct</t>
-        </is>
-      </c>
-      <c r="D202" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
+          <t>Lapilli_pct</t>
+        </is>
+      </c>
+      <c r="D202" s="55" t="inlineStr">
+        <is>
+          <t>Petro-Tuff</t>
         </is>
       </c>
       <c r="E202" s="38" t="inlineStr">
@@ -10361,12 +10401,12 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H202" s="42" t="inlineStr">
         <is>
-          <t>Total phenocryst content (porphyritic rocks).</t>
+          <t>Lapilli, fragments of 2-64 mm — left apex.</t>
         </is>
       </c>
     </row>
@@ -10381,12 +10421,12 @@
       </c>
       <c r="C203" s="40" t="inlineStr">
         <is>
-          <t>Vesicle_pct</t>
-        </is>
-      </c>
-      <c r="D203" s="45" t="inlineStr">
-        <is>
-          <t>Petro-Texture</t>
+          <t>Ash_pct</t>
+        </is>
+      </c>
+      <c r="D203" s="55" t="inlineStr">
+        <is>
+          <t>Petro-Tuff</t>
         </is>
       </c>
       <c r="E203" s="38" t="inlineStr">
@@ -10397,12 +10437,12 @@
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H203" s="42" t="inlineStr">
         <is>
-          <t>Vesicle / vug content.</t>
+          <t>Ash, fragments under 2 mm — right apex.</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10457,7 @@
       </c>
       <c r="C204" s="40" t="inlineStr">
         <is>
-          <t>Alteration_pct</t>
+          <t>Grain_size_mm</t>
         </is>
       </c>
       <c r="D204" s="45" t="inlineStr">
@@ -10427,18 +10467,18 @@
       </c>
       <c r="E204" s="38" t="inlineStr">
         <is>
-          <t>vol %</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H204" s="42" t="inlineStr">
         <is>
-          <t>Secondary minerals / alteration overprint (sericite, chlorite, clay …).</t>
+          <t>Average grain size (groundmass for porphyritic rocks).</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10493,7 @@
       </c>
       <c r="C205" s="40" t="inlineStr">
         <is>
-          <t>Texture_notes</t>
+          <t>Phenocryst_pct</t>
         </is>
       </c>
       <c r="D205" s="45" t="inlineStr">
@@ -10461,16 +10501,20 @@
           <t>Petro-Texture</t>
         </is>
       </c>
-      <c r="E205" s="38" t="inlineStr"/>
+      <c r="E205" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Plg zoned; Cpx with sieve texture</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H205" s="42" t="inlineStr">
         <is>
-          <t>Free-text observations (zoning, reaction rims, embayments, cumulate textures, mineral assemblage).</t>
+          <t>Total phenocryst content (porphyritic rocks).</t>
         </is>
       </c>
     </row>
@@ -10485,28 +10529,28 @@
       </c>
       <c r="C206" s="40" t="inlineStr">
         <is>
-          <t>Microscope_method</t>
-        </is>
-      </c>
-      <c r="D206" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
-        </is>
-      </c>
-      <c r="E206" s="38" t="inlineStr"/>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>Point-count (≥ 300 points), Point-count (100-300 points), Visual estimate, Modal calculation (CIPW), Image analysis (software), SEM-EDS / EBSD, Mixed</t>
-        </is>
-      </c>
+          <t>Vesicle_pct</t>
+        </is>
+      </c>
+      <c r="D206" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E206" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Point-count (≥ 300 points)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H206" s="42" t="inlineStr">
         <is>
-          <t>How the modal proportions were obtained.</t>
+          <t>Vesicle / vug content.</t>
         </is>
       </c>
     </row>
@@ -10521,24 +10565,28 @@
       </c>
       <c r="C207" s="40" t="inlineStr">
         <is>
-          <t>Microscope_lab</t>
-        </is>
-      </c>
-      <c r="D207" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
-        </is>
-      </c>
-      <c r="E207" s="38" t="inlineStr"/>
+          <t>Alteration_pct</t>
+        </is>
+      </c>
+      <c r="D207" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
+        </is>
+      </c>
+      <c r="E207" s="38" t="inlineStr">
+        <is>
+          <t>vol %</t>
+        </is>
+      </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>UNAM — Petrology lab</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H207" s="42" t="inlineStr">
         <is>
-          <t>Lab / university where the thin section was studied.</t>
+          <t>Secondary minerals / alteration overprint (sericite, chlorite, clay …).</t>
         </is>
       </c>
     </row>
@@ -10553,24 +10601,24 @@
       </c>
       <c r="C208" s="40" t="inlineStr">
         <is>
-          <t>Petrography_date</t>
-        </is>
-      </c>
-      <c r="D208" s="56" t="inlineStr">
-        <is>
-          <t>Petro-Meta</t>
+          <t>Texture_notes</t>
+        </is>
+      </c>
+      <c r="D208" s="45" t="inlineStr">
+        <is>
+          <t>Petro-Texture</t>
         </is>
       </c>
       <c r="E208" s="38" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>Plg zoned; Cpx with sieve texture</t>
         </is>
       </c>
       <c r="H208" s="42" t="inlineStr">
         <is>
-          <t>Year / date of the petrographic analysis (YYYY or YYYY-MM-DD).</t>
+          <t>Free-text observations (zoning, reaction rims, embayments, cumulate textures, mineral assemblage).</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10633,7 @@
       </c>
       <c r="C209" s="40" t="inlineStr">
         <is>
-          <t>Petrographer</t>
+          <t>Microscope_method</t>
         </is>
       </c>
       <c r="D209" s="56" t="inlineStr">
@@ -10594,15 +10642,19 @@
         </is>
       </c>
       <c r="E209" s="38" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Point-count (≥ 300 points), Point-count (100-300 points), Visual estimate, Modal calculation (CIPW), Image analysis (software), SEM-EDS / EBSD, Mixed</t>
+        </is>
+      </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>MDC</t>
+          <t>Point-count (≥ 300 points)</t>
         </is>
       </c>
       <c r="H209" s="42" t="inlineStr">
         <is>
-          <t>Analyst initials or name.</t>
+          <t>How the modal proportions were obtained.</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10669,7 @@
       </c>
       <c r="C210" s="40" t="inlineStr">
         <is>
-          <t>Petrography_notes</t>
+          <t>Microscope_lab</t>
         </is>
       </c>
       <c r="D210" s="56" t="inlineStr">
@@ -10627,8 +10679,104 @@
       </c>
       <c r="E210" s="38" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>UNAM — Petrology lab</t>
+        </is>
+      </c>
       <c r="H210" s="42" t="inlineStr">
+        <is>
+          <t>Lab / university where the thin section was studied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="38" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C211" s="40" t="inlineStr">
+        <is>
+          <t>Petrography_date</t>
+        </is>
+      </c>
+      <c r="D211" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E211" s="38" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="H211" s="42" t="inlineStr">
+        <is>
+          <t>Year / date of the petrographic analysis (YYYY or YYYY-MM-DD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="38" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C212" s="40" t="inlineStr">
+        <is>
+          <t>Petrographer</t>
+        </is>
+      </c>
+      <c r="D212" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E212" s="38" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>MDC</t>
+        </is>
+      </c>
+      <c r="H212" s="42" t="inlineStr">
+        <is>
+          <t>Analyst initials or name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="38" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="39" t="inlineStr">
+        <is>
+          <t>Petrography</t>
+        </is>
+      </c>
+      <c r="C213" s="40" t="inlineStr">
+        <is>
+          <t>Petrography_notes</t>
+        </is>
+      </c>
+      <c r="D213" s="56" t="inlineStr">
+        <is>
+          <t>Petro-Meta</t>
+        </is>
+      </c>
+      <c r="E213" s="38" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" s="42" t="inlineStr">
         <is>
           <t>Free-text notes (sample preservation, mounting, staining for K-feldspar, etc.).</t>
         </is>

--- a/templates/BIRDS_data_template.xlsx
+++ b/templates/BIRDS_data_template.xlsx
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H134" s="42" t="inlineStr">
         <is>
-          <t>Measured ¹⁴³Nd/¹⁴⁴Nd ratio. CHUR = 0.512638 (Bouvier et al. 2008).</t>
+          <t>Measured ¹⁴³Nd/¹⁴⁴Nd ratio. CHUR = 0.512638 (Jacobsen &amp; Wasserburg 1980; Bouvier et al. 2008 give 0.512630).</t>
         </is>
       </c>
     </row>

--- a/templates/BIRDS_data_template.xlsx
+++ b/templates/BIRDS_data_template.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,12 +34,6 @@
       <b val="1"/>
       <color rgb="001C2237"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="005B6478"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -189,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -215,30 +209,6 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -260,32 +230,11 @@
     <xf numFmtId="0" fontId="1" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -299,16 +248,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -693,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO2"/>
+  <dimension ref="A1:CO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1258,365 +1204,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="9" t="inlineStr"/>
-      <c r="B2" s="9" t="inlineStr"/>
-      <c r="C2" s="9" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr"/>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="L2" s="10" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
-      <c r="O2" s="11" t="inlineStr"/>
-      <c r="P2" s="11" t="inlineStr"/>
-      <c r="Q2" s="12" t="inlineStr"/>
-      <c r="R2" s="12" t="inlineStr"/>
-      <c r="S2" s="12" t="inlineStr"/>
-      <c r="T2" s="12" t="inlineStr"/>
-      <c r="U2" s="12" t="inlineStr"/>
-      <c r="V2" s="12" t="inlineStr"/>
-      <c r="W2" s="12" t="inlineStr"/>
-      <c r="X2" s="12" t="inlineStr"/>
-      <c r="Y2" s="12" t="inlineStr"/>
-      <c r="Z2" s="12" t="inlineStr"/>
-      <c r="AA2" s="12" t="inlineStr"/>
-      <c r="AB2" s="13" t="inlineStr"/>
-      <c r="AC2" s="13" t="inlineStr"/>
-      <c r="AD2" s="13" t="inlineStr"/>
-      <c r="AE2" s="13" t="inlineStr"/>
-      <c r="AF2" s="13" t="inlineStr"/>
-      <c r="AG2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AH2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AI2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AJ2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AK2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AL2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AM2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AN2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AO2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AP2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AQ2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AR2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AS2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AT2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AU2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AV2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AW2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AX2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AY2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AZ2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BA2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BB2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BC2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BD2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BE2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BF2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BG2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BH2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BI2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BJ2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BK2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BL2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BM2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BN2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BO2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BP2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BQ2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BR2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BS2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BT2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BU2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BV2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BW2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BX2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BY2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BZ2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CA2" s="15" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CB2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CC2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CD2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CE2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CF2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CG2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CH2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CI2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CJ2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CK2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CL2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CM2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CN2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="CO2" s="16" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-    </row>
+    <row r="2" ht="16" customHeight="1"/>
     <row r="3" ht="16" customHeight="1"/>
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="16" customHeight="1"/>
@@ -1816,28 +1404,27 @@
     <row r="199" ht="16" customHeight="1"/>
     <row r="200" ht="16" customHeight="1"/>
     <row r="201" ht="16" customHeight="1"/>
-    <row r="202" ht="16" customHeight="1"/>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="J3:J1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: N, S" type="list">
+    <dataValidation sqref="J2:J1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: N, S" type="list">
       <formula1>"N,S"</formula1>
     </dataValidation>
-    <dataValidation sqref="R3:R1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ma, ka, Ga, yr" type="list">
+    <dataValidation sqref="R2:R1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ma, ka, Ga, yr" type="list">
       <formula1>"Ma,ka,Ga,yr"</formula1>
     </dataValidation>
-    <dataValidation sqref="T3:T1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein" type="list">
+    <dataValidation sqref="T2:T1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein" type="list">
       <formula1>"Volcanic,Plutonic,Sub-volcanic,Pyroclastic,Vein"</formula1>
     </dataValidation>
-    <dataValidation sqref="U3:U1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite" type="list">
+    <dataValidation sqref="U2:U1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite" type="list">
       <formula1>"Picro-basalt,Basalt,Basaltic andesite,Andesite,Dacite,Rhyolite,Trachy-basalt,Basaltic trachy-andesite,Trachy-andesite,Trachyte,Trachy-dacite,Tephrite,Phono-tephrite,Tephri-phonolite,Phonolite,Foidite,Gabbro,Diorite,Granodiorite,Granite,Monzogabbro,Monzodiorite,Monzonite,Syenite,Foid-syenite,Foidolite"</formula1>
     </dataValidation>
-    <dataValidation sqref="W3:W1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic" type="list">
+    <dataValidation sqref="W2:W1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic" type="list">
       <formula1>"Tholeiitic,Calc-alkaline,High-K calc-alkaline,Shoshonitic,Alkaline,Ultra-alkaline,Boninitic"</formula1>
     </dataValidation>
-    <dataValidation sqref="AA3:AA1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed" type="list">
+    <dataValidation sqref="AA2:AA1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed" type="list">
       <formula1>"Fresh,Slightly altered,Moderately altered,Strongly altered,Metamorphosed"</formula1>
     </dataValidation>
-    <dataValidation sqref="AB3:AB1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed" type="list">
+    <dataValidation sqref="AB2:AB1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed" type="list">
       <formula1>"XRF,ICP-OES,ICP-MS,Solution ICP-MS,LA-ICP-MS,EMP / EPMA,INAA,Wet chemistry,Mixed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1851,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2102,428 +1689,243 @@
           <t>SiO2</t>
         </is>
       </c>
-      <c r="AH1" s="17" t="inlineStr">
+      <c r="AH1" s="9" t="inlineStr">
         <is>
           <t>87Sr/86Sr</t>
         </is>
       </c>
-      <c r="AI1" s="17" t="inlineStr">
+      <c r="AI1" s="9" t="inlineStr">
         <is>
           <t>87Sr/86Sr_2σ</t>
         </is>
       </c>
-      <c r="AJ1" s="17" t="inlineStr">
+      <c r="AJ1" s="9" t="inlineStr">
         <is>
           <t>87Rb/86Sr</t>
         </is>
       </c>
-      <c r="AK1" s="17" t="inlineStr">
+      <c r="AK1" s="9" t="inlineStr">
         <is>
           <t>Sr_iso</t>
         </is>
       </c>
-      <c r="AL1" s="17" t="inlineStr">
+      <c r="AL1" s="9" t="inlineStr">
         <is>
           <t>Rb_iso</t>
         </is>
       </c>
-      <c r="AM1" s="17" t="inlineStr">
+      <c r="AM1" s="9" t="inlineStr">
         <is>
           <t>εSr_initial</t>
         </is>
       </c>
-      <c r="AN1" s="18" t="inlineStr">
+      <c r="AN1" s="10" t="inlineStr">
         <is>
           <t>143Nd/144Nd</t>
         </is>
       </c>
-      <c r="AO1" s="18" t="inlineStr">
+      <c r="AO1" s="10" t="inlineStr">
         <is>
           <t>143Nd/144Nd_2σ</t>
         </is>
       </c>
-      <c r="AP1" s="18" t="inlineStr">
+      <c r="AP1" s="10" t="inlineStr">
         <is>
           <t>147Sm/144Nd</t>
         </is>
       </c>
-      <c r="AQ1" s="18" t="inlineStr">
+      <c r="AQ1" s="10" t="inlineStr">
         <is>
           <t>Sm_iso</t>
         </is>
       </c>
-      <c r="AR1" s="18" t="inlineStr">
+      <c r="AR1" s="10" t="inlineStr">
         <is>
           <t>Nd_iso</t>
         </is>
       </c>
-      <c r="AS1" s="18" t="inlineStr">
+      <c r="AS1" s="10" t="inlineStr">
         <is>
           <t>εNd_initial</t>
         </is>
       </c>
-      <c r="AT1" s="18" t="inlineStr">
+      <c r="AT1" s="10" t="inlineStr">
         <is>
           <t>TDM_Nd</t>
         </is>
       </c>
-      <c r="AU1" s="19" t="inlineStr">
+      <c r="AU1" s="11" t="inlineStr">
         <is>
           <t>206Pb/204Pb</t>
         </is>
       </c>
-      <c r="AV1" s="19" t="inlineStr">
+      <c r="AV1" s="11" t="inlineStr">
         <is>
           <t>206Pb/204Pb_2σ</t>
         </is>
       </c>
-      <c r="AW1" s="19" t="inlineStr">
+      <c r="AW1" s="11" t="inlineStr">
         <is>
           <t>207Pb/204Pb</t>
         </is>
       </c>
-      <c r="AX1" s="19" t="inlineStr">
+      <c r="AX1" s="11" t="inlineStr">
         <is>
           <t>207Pb/204Pb_2σ</t>
         </is>
       </c>
-      <c r="AY1" s="19" t="inlineStr">
+      <c r="AY1" s="11" t="inlineStr">
         <is>
           <t>208Pb/204Pb</t>
         </is>
       </c>
-      <c r="AZ1" s="19" t="inlineStr">
+      <c r="AZ1" s="11" t="inlineStr">
         <is>
           <t>208Pb/204Pb_2σ</t>
         </is>
       </c>
-      <c r="BA1" s="19" t="inlineStr">
+      <c r="BA1" s="11" t="inlineStr">
         <is>
           <t>Pb_iso</t>
         </is>
       </c>
-      <c r="BB1" s="19" t="inlineStr">
+      <c r="BB1" s="11" t="inlineStr">
         <is>
           <t>U_iso</t>
         </is>
       </c>
-      <c r="BC1" s="19" t="inlineStr">
+      <c r="BC1" s="11" t="inlineStr">
         <is>
           <t>Th_iso</t>
         </is>
       </c>
-      <c r="BD1" s="20" t="inlineStr">
+      <c r="BD1" s="12" t="inlineStr">
         <is>
           <t>176Hf/177Hf</t>
         </is>
       </c>
-      <c r="BE1" s="20" t="inlineStr">
+      <c r="BE1" s="12" t="inlineStr">
         <is>
           <t>176Hf/177Hf_2σ</t>
         </is>
       </c>
-      <c r="BF1" s="20" t="inlineStr">
+      <c r="BF1" s="12" t="inlineStr">
         <is>
           <t>176Lu/177Hf</t>
         </is>
       </c>
-      <c r="BG1" s="20" t="inlineStr">
+      <c r="BG1" s="12" t="inlineStr">
         <is>
           <t>Hf_iso</t>
         </is>
       </c>
-      <c r="BH1" s="20" t="inlineStr">
+      <c r="BH1" s="12" t="inlineStr">
         <is>
           <t>Lu_iso</t>
         </is>
       </c>
-      <c r="BI1" s="20" t="inlineStr">
+      <c r="BI1" s="12" t="inlineStr">
         <is>
           <t>εHf_initial</t>
         </is>
       </c>
-      <c r="BJ1" s="20" t="inlineStr">
+      <c r="BJ1" s="12" t="inlineStr">
         <is>
           <t>TDM_Hf</t>
         </is>
       </c>
-      <c r="BK1" s="21" t="inlineStr">
+      <c r="BK1" s="13" t="inlineStr">
         <is>
           <t>187Os/188Os</t>
         </is>
       </c>
-      <c r="BL1" s="21" t="inlineStr">
+      <c r="BL1" s="13" t="inlineStr">
         <is>
           <t>187Os/188Os_2σ</t>
         </is>
       </c>
-      <c r="BM1" s="21" t="inlineStr">
+      <c r="BM1" s="13" t="inlineStr">
         <is>
           <t>187Re/188Os</t>
         </is>
       </c>
-      <c r="BN1" s="21" t="inlineStr">
+      <c r="BN1" s="13" t="inlineStr">
         <is>
           <t>Os_iso</t>
         </is>
       </c>
-      <c r="BO1" s="21" t="inlineStr">
+      <c r="BO1" s="13" t="inlineStr">
         <is>
           <t>Re_iso</t>
         </is>
       </c>
-      <c r="BP1" s="21" t="inlineStr">
+      <c r="BP1" s="13" t="inlineStr">
         <is>
           <t>γOs_initial</t>
         </is>
       </c>
-      <c r="BQ1" s="22" t="inlineStr">
+      <c r="BQ1" s="14" t="inlineStr">
         <is>
           <t>δ18O</t>
         </is>
       </c>
-      <c r="BR1" s="22" t="inlineStr">
+      <c r="BR1" s="14" t="inlineStr">
         <is>
           <t>δ18O_2σ</t>
         </is>
       </c>
-      <c r="BS1" s="22" t="inlineStr">
+      <c r="BS1" s="14" t="inlineStr">
         <is>
           <t>δD</t>
         </is>
       </c>
-      <c r="BT1" s="22" t="inlineStr">
+      <c r="BT1" s="14" t="inlineStr">
         <is>
           <t>δD_2σ</t>
         </is>
       </c>
-      <c r="BU1" s="22" t="inlineStr">
+      <c r="BU1" s="14" t="inlineStr">
         <is>
           <t>δ13C</t>
         </is>
       </c>
-      <c r="BV1" s="22" t="inlineStr">
+      <c r="BV1" s="14" t="inlineStr">
         <is>
           <t>δ13C_2σ</t>
         </is>
       </c>
-      <c r="BW1" s="22" t="inlineStr">
+      <c r="BW1" s="14" t="inlineStr">
         <is>
           <t>δ11B</t>
         </is>
       </c>
-      <c r="BX1" s="23" t="inlineStr">
+      <c r="BX1" s="15" t="inlineStr">
         <is>
           <t>Iso_Method</t>
         </is>
       </c>
-      <c r="BY1" s="23" t="inlineStr">
+      <c r="BY1" s="15" t="inlineStr">
         <is>
           <t>Iso_Laboratory</t>
         </is>
       </c>
-      <c r="BZ1" s="23" t="inlineStr">
+      <c r="BZ1" s="15" t="inlineStr">
         <is>
           <t>Iso_Date</t>
         </is>
       </c>
-      <c r="CA1" s="23" t="inlineStr">
+      <c r="CA1" s="15" t="inlineStr">
         <is>
           <t>Iso_Analyst</t>
         </is>
       </c>
-      <c r="CB1" s="23" t="inlineStr">
+      <c r="CB1" s="15" t="inlineStr">
         <is>
           <t>Iso_Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="9" t="inlineStr"/>
-      <c r="B2" s="9" t="inlineStr"/>
-      <c r="C2" s="9" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr"/>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="L2" s="10" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
-      <c r="O2" s="11" t="inlineStr"/>
-      <c r="P2" s="11" t="inlineStr"/>
-      <c r="Q2" s="12" t="inlineStr"/>
-      <c r="R2" s="12" t="inlineStr"/>
-      <c r="S2" s="12" t="inlineStr"/>
-      <c r="T2" s="12" t="inlineStr"/>
-      <c r="U2" s="12" t="inlineStr"/>
-      <c r="V2" s="12" t="inlineStr"/>
-      <c r="W2" s="12" t="inlineStr"/>
-      <c r="X2" s="12" t="inlineStr"/>
-      <c r="Y2" s="12" t="inlineStr"/>
-      <c r="Z2" s="12" t="inlineStr"/>
-      <c r="AA2" s="12" t="inlineStr"/>
-      <c r="AB2" s="13" t="inlineStr"/>
-      <c r="AC2" s="13" t="inlineStr"/>
-      <c r="AD2" s="13" t="inlineStr"/>
-      <c r="AE2" s="13" t="inlineStr"/>
-      <c r="AF2" s="13" t="inlineStr"/>
-      <c r="AG2" s="14" t="inlineStr">
-        <is>
-          <t>wt%</t>
-        </is>
-      </c>
-      <c r="AH2" s="24" t="inlineStr"/>
-      <c r="AI2" s="24" t="inlineStr"/>
-      <c r="AJ2" s="24" t="inlineStr"/>
-      <c r="AK2" s="24" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AL2" s="24" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AM2" s="24" t="inlineStr"/>
-      <c r="AN2" s="25" t="inlineStr"/>
-      <c r="AO2" s="25" t="inlineStr"/>
-      <c r="AP2" s="25" t="inlineStr"/>
-      <c r="AQ2" s="25" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AR2" s="25" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="AS2" s="25" t="inlineStr"/>
-      <c r="AT2" s="25" t="inlineStr">
-        <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="AU2" s="26" t="inlineStr"/>
-      <c r="AV2" s="26" t="inlineStr"/>
-      <c r="AW2" s="26" t="inlineStr"/>
-      <c r="AX2" s="26" t="inlineStr"/>
-      <c r="AY2" s="26" t="inlineStr"/>
-      <c r="AZ2" s="26" t="inlineStr"/>
-      <c r="BA2" s="26" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BB2" s="26" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BC2" s="26" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BD2" s="27" t="inlineStr"/>
-      <c r="BE2" s="27" t="inlineStr"/>
-      <c r="BF2" s="27" t="inlineStr"/>
-      <c r="BG2" s="27" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BH2" s="27" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-      <c r="BI2" s="27" t="inlineStr"/>
-      <c r="BJ2" s="27" t="inlineStr">
-        <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="BK2" s="28" t="inlineStr"/>
-      <c r="BL2" s="28" t="inlineStr"/>
-      <c r="BM2" s="28" t="inlineStr"/>
-      <c r="BN2" s="28" t="inlineStr">
-        <is>
-          <t>ppb</t>
-        </is>
-      </c>
-      <c r="BO2" s="28" t="inlineStr">
-        <is>
-          <t>ppb</t>
-        </is>
-      </c>
-      <c r="BP2" s="28" t="inlineStr"/>
-      <c r="BQ2" s="29" t="inlineStr">
-        <is>
-          <t>‰ VSMOW</t>
-        </is>
-      </c>
-      <c r="BR2" s="29" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
-      <c r="BS2" s="29" t="inlineStr">
-        <is>
-          <t>‰ VSMOW</t>
-        </is>
-      </c>
-      <c r="BT2" s="29" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
-      <c r="BU2" s="29" t="inlineStr">
-        <is>
-          <t>‰ VPDB</t>
-        </is>
-      </c>
-      <c r="BV2" s="29" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
-      <c r="BW2" s="29" t="inlineStr">
-        <is>
-          <t>‰</t>
-        </is>
-      </c>
-      <c r="BX2" s="30" t="inlineStr"/>
-      <c r="BY2" s="30" t="inlineStr"/>
-      <c r="BZ2" s="30" t="inlineStr"/>
-      <c r="CA2" s="30" t="inlineStr"/>
-      <c r="CB2" s="30" t="inlineStr"/>
-    </row>
+    <row r="2" ht="16" customHeight="1"/>
     <row r="3" ht="16" customHeight="1"/>
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="16" customHeight="1"/>
@@ -2723,31 +2125,30 @@
     <row r="199" ht="16" customHeight="1"/>
     <row r="200" ht="16" customHeight="1"/>
     <row r="201" ht="16" customHeight="1"/>
-    <row r="202" ht="16" customHeight="1"/>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation sqref="J3:J1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: N, S" type="list">
+    <dataValidation sqref="J2:J1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: N, S" type="list">
       <formula1>"N,S"</formula1>
     </dataValidation>
-    <dataValidation sqref="R3:R1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ma, ka, Ga, yr" type="list">
+    <dataValidation sqref="R2:R1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ma, ka, Ga, yr" type="list">
       <formula1>"Ma,ka,Ga,yr"</formula1>
     </dataValidation>
-    <dataValidation sqref="T3:T1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein" type="list">
+    <dataValidation sqref="T2:T1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein" type="list">
       <formula1>"Volcanic,Plutonic,Sub-volcanic,Pyroclastic,Vein"</formula1>
     </dataValidation>
-    <dataValidation sqref="U3:U1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite" type="list">
+    <dataValidation sqref="U2:U1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite" type="list">
       <formula1>"Picro-basalt,Basalt,Basaltic andesite,Andesite,Dacite,Rhyolite,Trachy-basalt,Basaltic trachy-andesite,Trachy-andesite,Trachyte,Trachy-dacite,Tephrite,Phono-tephrite,Tephri-phonolite,Phonolite,Foidite,Gabbro,Diorite,Granodiorite,Granite,Monzogabbro,Monzodiorite,Monzonite,Syenite,Foid-syenite,Foidolite"</formula1>
     </dataValidation>
-    <dataValidation sqref="W3:W1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic" type="list">
+    <dataValidation sqref="W2:W1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic" type="list">
       <formula1>"Tholeiitic,Calc-alkaline,High-K calc-alkaline,Shoshonitic,Alkaline,Ultra-alkaline,Boninitic"</formula1>
     </dataValidation>
-    <dataValidation sqref="AA3:AA1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed" type="list">
+    <dataValidation sqref="AA2:AA1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed" type="list">
       <formula1>"Fresh,Slightly altered,Moderately altered,Strongly altered,Metamorphosed"</formula1>
     </dataValidation>
-    <dataValidation sqref="AB3:AB1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed" type="list">
+    <dataValidation sqref="AB2:AB1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed" type="list">
       <formula1>"XRF,ICP-OES,ICP-MS,Solution ICP-MS,LA-ICP-MS,EMP / EPMA,INAA,Wet chemistry,Mixed"</formula1>
     </dataValidation>
-    <dataValidation sqref="BX3:BX1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: TIMS, MC-ICP-MS, Solution MC-ICP-MS, LA-MC-ICP-MS, SIMS, SHRIMP, N-TIMS (Os), Laser fluorination (δ¹⁸O), EA-IRMS (δ¹³C, δD), CRDS, Mixed" type="list">
+    <dataValidation sqref="BX2:BX1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: TIMS, MC-ICP-MS, Solution MC-ICP-MS, LA-MC-ICP-MS, SIMS, SHRIMP, N-TIMS (Os), Laser fluorination (δ¹⁸O), EA-IRMS (δ¹³C, δD), CRDS, Mixed" type="list">
       <formula1>"TIMS,MC-ICP-MS,Solution MC-ICP-MS,LA-MC-ICP-MS,SIMS,SHRIMP,N-TIMS (Os),Laser fluorination (δ¹⁸O),EA-IRMS (δ¹³C, δD),CRDS,Mixed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2761,7 +2162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2826,127 +2227,127 @@
           <t>Texture</t>
         </is>
       </c>
-      <c r="E1" s="31" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Q_mode</t>
         </is>
       </c>
-      <c r="F1" s="31" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>A_mode</t>
         </is>
       </c>
-      <c r="G1" s="31" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>P_mode</t>
         </is>
       </c>
-      <c r="H1" s="31" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>F_mode</t>
         </is>
       </c>
-      <c r="I1" s="20" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>Ol_mode</t>
         </is>
       </c>
-      <c r="J1" s="20" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>Opx_mode</t>
         </is>
       </c>
-      <c r="K1" s="20" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>Cpx_mode</t>
         </is>
       </c>
-      <c r="L1" s="20" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>Px_mode</t>
         </is>
       </c>
-      <c r="M1" s="20" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>Amph_mode</t>
         </is>
       </c>
-      <c r="N1" s="20" t="inlineStr">
+      <c r="N1" s="12" t="inlineStr">
         <is>
           <t>Bt_mode</t>
         </is>
       </c>
-      <c r="O1" s="20" t="inlineStr">
+      <c r="O1" s="12" t="inlineStr">
         <is>
           <t>Ms_mode</t>
         </is>
       </c>
-      <c r="P1" s="21" t="inlineStr">
+      <c r="P1" s="13" t="inlineStr">
         <is>
           <t>Opaque_mode</t>
         </is>
       </c>
-      <c r="Q1" s="21" t="inlineStr">
+      <c r="Q1" s="13" t="inlineStr">
         <is>
           <t>Apatite_mode</t>
         </is>
       </c>
-      <c r="R1" s="21" t="inlineStr">
+      <c r="R1" s="13" t="inlineStr">
         <is>
           <t>Zircon_mode</t>
         </is>
       </c>
-      <c r="S1" s="21" t="inlineStr">
+      <c r="S1" s="13" t="inlineStr">
         <is>
           <t>Titanite_mode</t>
         </is>
       </c>
-      <c r="T1" s="21" t="inlineStr">
+      <c r="T1" s="13" t="inlineStr">
         <is>
           <t>Carbonate_mode</t>
         </is>
       </c>
-      <c r="U1" s="21" t="inlineStr">
+      <c r="U1" s="13" t="inlineStr">
         <is>
           <t>Other_acc_mode</t>
         </is>
       </c>
-      <c r="V1" s="21" t="inlineStr">
+      <c r="V1" s="13" t="inlineStr">
         <is>
           <t>Mode_Total</t>
         </is>
       </c>
-      <c r="W1" s="22" t="inlineStr">
+      <c r="W1" s="14" t="inlineStr">
         <is>
           <t>Crystal_pct</t>
         </is>
       </c>
-      <c r="X1" s="22" t="inlineStr">
+      <c r="X1" s="14" t="inlineStr">
         <is>
           <t>Vitric_pct</t>
         </is>
       </c>
-      <c r="Y1" s="22" t="inlineStr">
+      <c r="Y1" s="14" t="inlineStr">
         <is>
           <t>Lithic_pct</t>
         </is>
       </c>
-      <c r="Z1" s="22" t="inlineStr">
+      <c r="Z1" s="14" t="inlineStr">
         <is>
           <t>Pyroclast_size</t>
         </is>
       </c>
-      <c r="AA1" s="22" t="inlineStr">
+      <c r="AA1" s="14" t="inlineStr">
         <is>
           <t>Blocks_bombs_pct</t>
         </is>
       </c>
-      <c r="AB1" s="22" t="inlineStr">
+      <c r="AB1" s="14" t="inlineStr">
         <is>
           <t>Lapilli_pct</t>
         </is>
       </c>
-      <c r="AC1" s="22" t="inlineStr">
+      <c r="AC1" s="14" t="inlineStr">
         <is>
           <t>Ash_pct</t>
         </is>
@@ -2976,185 +2377,33 @@
           <t>Texture_notes</t>
         </is>
       </c>
-      <c r="AI1" s="23" t="inlineStr">
+      <c r="AI1" s="15" t="inlineStr">
         <is>
           <t>Microscope_method</t>
         </is>
       </c>
-      <c r="AJ1" s="23" t="inlineStr">
+      <c r="AJ1" s="15" t="inlineStr">
         <is>
           <t>Microscope_lab</t>
         </is>
       </c>
-      <c r="AK1" s="23" t="inlineStr">
+      <c r="AK1" s="15" t="inlineStr">
         <is>
           <t>Petrography_date</t>
         </is>
       </c>
-      <c r="AL1" s="23" t="inlineStr">
+      <c r="AL1" s="15" t="inlineStr">
         <is>
           <t>Petrographer</t>
         </is>
       </c>
-      <c r="AM1" s="23" t="inlineStr">
+      <c r="AM1" s="15" t="inlineStr">
         <is>
           <t>Petrography_notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="9" t="inlineStr"/>
-      <c r="B2" s="9" t="inlineStr"/>
-      <c r="C2" s="9" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr"/>
-      <c r="E2" s="32" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="F2" s="32" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="G2" s="32" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="H2" s="32" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="I2" s="27" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="J2" s="27" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="K2" s="27" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="L2" s="27" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="M2" s="27" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="N2" s="27" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="O2" s="27" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="P2" s="28" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="Q2" s="28" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="R2" s="28" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="S2" s="28" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="T2" s="28" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="U2" s="28" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="V2" s="28" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="W2" s="29" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="X2" s="29" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="Y2" s="29" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="Z2" s="29" t="inlineStr"/>
-      <c r="AA2" s="29" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="AB2" s="29" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="AC2" s="29" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="AD2" s="12" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="AE2" s="12" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="AF2" s="12" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="AG2" s="12" t="inlineStr">
-        <is>
-          <t>vol %</t>
-        </is>
-      </c>
-      <c r="AH2" s="12" t="inlineStr"/>
-      <c r="AI2" s="30" t="inlineStr"/>
-      <c r="AJ2" s="30" t="inlineStr"/>
-      <c r="AK2" s="30" t="inlineStr"/>
-      <c r="AL2" s="30" t="inlineStr"/>
-      <c r="AM2" s="30" t="inlineStr"/>
-    </row>
+    <row r="2" ht="16" customHeight="1"/>
     <row r="3" ht="16" customHeight="1"/>
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="16" customHeight="1"/>
@@ -3354,16 +2603,15 @@
     <row r="199" ht="16" customHeight="1"/>
     <row r="200" ht="16" customHeight="1"/>
     <row r="201" ht="16" customHeight="1"/>
-    <row r="202" ht="16" customHeight="1"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="D3:D1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Phaneritic, Aphanitic, Porphyritic, Glassy, Vesicular, Pyroclastic, Cumulate, Cataclastic, Foliated / Gneissic, Mixed" type="list">
+    <dataValidation sqref="D2:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Phaneritic, Aphanitic, Porphyritic, Glassy, Vesicular, Pyroclastic, Cumulate, Cataclastic, Foliated / Gneissic, Mixed" type="list">
       <formula1>"Phaneritic,Aphanitic,Porphyritic,Glassy,Vesicular,Pyroclastic,Cumulate,Cataclastic,Foliated / Gneissic,Mixed"</formula1>
     </dataValidation>
-    <dataValidation sqref="Z3:Z1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ash (&lt; 2 mm), Lapilli (2-64 mm), Block / Bomb (&gt; 64 mm), Mixed" type="list">
+    <dataValidation sqref="Z2:Z1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Ash (&lt; 2 mm), Lapilli (2-64 mm), Block / Bomb (&gt; 64 mm), Mixed" type="list">
       <formula1>"Ash (&lt; 2 mm),Lapilli (2-64 mm),Block / Bomb (&gt; 64 mm),Mixed"</formula1>
     </dataValidation>
-    <dataValidation sqref="AI3:AI1002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Point-count (≥ 300 points), Point-count (100-300 points), Visual estimate, Modal calculation (CIPW), Image analysis (software), SEM-EDS / EBSD, Mixed" type="list">
+    <dataValidation sqref="AI2:AI1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: Point-count (≥ 300 points), Point-count (100-300 points), Visual estimate, Modal calculation (CIPW), Image analysis (software), SEM-EDS / EBSD, Mixed" type="list">
       <formula1>"Point-count (≥ 300 points),Point-count (100-300 points),Visual estimate,Modal calculation (CIPW),Image analysis (software),SEM-EDS / EBSD,Mixed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3385,280 +2633,280 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.6" customHeight="1">
-      <c r="B1" s="33" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>B.I.R.D.S — Data-entry template</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.6" customHeight="1">
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Broad Igneous Rocks — Diagrams &amp; Statistics</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18.6" customHeight="1">
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>How to use this workbook</t>
         </is>
       </c>
     </row>
     <row r="5" ht="43.8" customHeight="1">
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>1. Go to the 'Data' sheet — every row is one sample. The first two rows are the header (column name + unit) and are frozen so they stay visible while you scroll. Do not change the header text — B.I.R.D.S relies on the exact names listed in the 'Reference' sheet.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="31.2" customHeight="1">
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>2. Fill in only the columns you have data for. Empty cells are treated as missing values; they will not break the plots and they will not be counted in the statistics.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="43.8" customHeight="1">
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>3. Decimal separator: use a dot (1.234). If your laboratory report uses a comma (1,234), B.I.R.D.S' robust importer will convert it automatically — but exporting from Excel with the dot decimal is the safest path.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="43.8" customHeight="1">
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>4. The columns highlighted with dropdown arrows in the 'Data' sheet (Rock_Type, Magmatic_Series, Alteration, Analytical_Method, Age_Unit, TAS_Composition) are validated — only the values in the list are accepted. This keeps the legend and group filters tidy.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="31.2" customHeight="1">
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>5. Once you have at least one sample and SiO2 + Na2O + K2O filled in, you can save the file as .xlsx or .csv and open it from B.I.R.D.S → Data → Import.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18.6" customHeight="1">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Isotopes sheet (optional)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="94.19999999999999" customHeight="1">
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>6. The 'Isotopes' sheet is independent of the 'Data' sheet. Use it to record Sr-Nd-Pb-Hf-Os-Re-O-C-H-B isotopic analyses. Its first columns — identification, location, source, geology and analysis — are the same, in the same order, as the columns before the major elements in 'Data', so a sample's context can be copied across in one block; then comes SiO2, to read the isotopes against silica. Rows are joined back to the bulk composition through the 'Sample_Name' column, which MUST match exactly between the two sheets (case-sensitive). Where both sheets fill a column, 'Data' is kept.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56.4" customHeight="1">
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>7. Common workflow:  (a) fill in the bulk analysis in 'Data', (b) for the subset of samples with isotopic data, paste the ratios in 'Isotopes' next to the matching 'Sample_Name'. B.I.R.D.S' Isotopes view (menu Isotopes → Sr-Nd, Pb-Pb…) automatically picks up these columns.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="43.8" customHeight="1">
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>8. CSV users: the companion file 'BIRDS_isotopes_template.csv' carries the same isotope columns in a flat file. Keep it side-by-side with the main CSV and join them by 'Sample_Name' when needed.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18.6" customHeight="1">
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Petrography sheet (optional)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56.4" customHeight="1">
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>9. The 'Petrography' sheet captures modal mineralogy from thin sections: Q-A-P-F (Streckeisen QAPF), Ol-Opx-Cpx (ultramafic rocks), Pl-Px-Ol (gabbroic rocks), Crystal-Vitric-Lithic (tuffs) and Blocks-Lapilli-Ash (pyroclastic rocks by fragment size). Rows are joined to the bulk dataset by 'Sample_Name'.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="43.8" customHeight="1">
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>10. The Petrography view (menu Petrography → QAPF, Gabbro, Ultramafic, Tuff …) reads these modal % columns and plots the IUGS classification ternaries. Modal values are in volume %; the Mode_Total column is a QC sum that should fall between 99 and 101.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="31.2" customHeight="1">
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>11. CSV users: a companion file 'BIRDS_petrography_template.csv' is generated next to the bulk and isotope CSVs.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18.6" customHeight="1">
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>What goes into each column?</t>
         </is>
       </c>
     </row>
     <row r="22" ht="43.8" customHeight="1">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>See the 'Reference' sheet for the full glossary — every column has its unit, allowed values and a short description there. The 'Sheet' column tells you whether the entry belongs to Data or Isotopes.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18.6" customHeight="1">
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Minimum data B.I.R.D.S needs by module</t>
         </is>
       </c>
     </row>
     <row r="25" ht="31.2" customHeight="1">
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>• Classification (TAS, K2O-SiO2, AFM, ...) → SiO2, Na2O, K2O (+FeOt, MgO, Al2O3 for AFM / Jensen)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18.6" customHeight="1">
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>• Bivariate diagrams (Harker, custom x-y) → Whatever pair of columns you want to compare</t>
         </is>
       </c>
     </row>
     <row r="27" ht="31.2" customHeight="1">
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>• Spider diagrams (REE / multi-element) → At least the elements asked by the chosen normaliser (e.g. La-Lu for chondrite-normalised REE)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18.6" customHeight="1">
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>• Tectonic — Pearce 2008 → Th, Nb, Yb (+Ti for Ti/Yb-Nb/Yb)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="31.2" customHeight="1">
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>• Tectonic — Verma &amp; Verma 2013 (majors) → SiO2, TiO2, Al2O3, FeOt, MnO, MgO, CaO, Na2O, K2O, P2O5</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18.6" customHeight="1">
-      <c r="B30" s="37" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>• Tectonic — Verma &amp; Agrawal 2011 (traces) → La, Sm, Nb, Th, Zr, Y, Hf, Ti and Yb</t>
         </is>
       </c>
     </row>
     <row r="31" ht="31.2" customHeight="1">
-      <c r="B31" s="37" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>• Statistics &amp; Anomalies → Any numeric column. REE columns enable Eu/Eu*, Ce/Ce*, Pr/Pr*, Gd/Gd*, Y/Y*, Y/Ho automatically.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="31.2" customHeight="1">
-      <c r="B32" s="37" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>• Isotopes — Sr-Nd plot (with εNd/εSr and initials) → 87Sr/86Sr, 143Nd/144Nd (+87Rb/86Sr, 147Sm/144Nd and Age to compute initial ratios)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18.6" customHeight="1">
-      <c r="B33" s="37" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>• Isotopes — Pb-Pb diagrams → 206Pb/204Pb, 207Pb/204Pb and 208Pb/204Pb</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18.6" customHeight="1">
-      <c r="B34" s="37" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>• Map (sample locations) → Latitude and Longitude (decimal degrees, WGS-84)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="31.2" customHeight="1">
-      <c r="B35" s="37" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>• Petrography — Streckeisen QAPF (plutonic &amp; volcanic) → Q_mode, A_mode, P_mode, F_mode (modal %)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18.6" customHeight="1">
-      <c r="B36" s="37" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>• Petrography — Gabbroic rocks (Pl-Px-Ol) → Pl_mode, Px_mode (or Opx+Cpx), Ol_mode</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18.6" customHeight="1">
-      <c r="B37" s="37" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>• Petrography — Ultramafic rocks (Ol-Opx-Cpx) → Ol_mode, Opx_mode, Cpx_mode</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18.6" customHeight="1">
-      <c r="B38" s="37" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>• Petrography — Pyroclastic tuffs (Schmid 1981) → Crystal_pct, Vitric_pct, Lithic_pct</t>
         </is>
       </c>
     </row>
     <row r="39" ht="31.2" customHeight="1">
-      <c r="B39" s="37" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>• Petrography — Pyroclastic rocks by fragment size (Fisher 1966) → Blocks_bombs_pct, Lapilli_pct, Ash_pct</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18.6" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>Tips</t>
         </is>
       </c>
     </row>
     <row r="42" ht="31.2" customHeight="1">
-      <c r="B42" s="36" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>• Keep 'No.' as a sequential integer so it can be used as a sample ID when 'Sample_Name' is missing.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="31.2" customHeight="1">
-      <c r="B43" s="36" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>• If you only have FeO + Fe2O3 (and not FeOt), B.I.R.D.S will compute FeOt = FeO + 0.8998 × Fe2O3 automatically.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="43.8" customHeight="1">
-      <c r="B44" s="36" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>• 'TAS_Composition' can be left empty — the TAS diagram will compute it from your SiO2 and alkalis. Filling it in is useful only if you want to colour samples by lithology in other diagrams.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18.6" customHeight="1">
-      <c r="B45" s="36" t="inlineStr">
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>• Latitude / Longitude in decimal degrees, WGS-84. Negative values are south / west.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="31.2" customHeight="1">
-      <c r="B46" s="36" t="inlineStr">
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>• Always keep a backup of your original lab report. This template is meant for plotting, not for archiving primary data.</t>
         </is>
@@ -3689,195 +2937,195 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Allowed values</t>
         </is>
       </c>
-      <c r="G1" s="23" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="H1" s="23" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="n">
+      <c r="A2" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="39" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C2" s="40" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="D2" s="41" t="inlineStr">
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="E2" s="38" t="inlineStr"/>
+      <c r="E2" s="22" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H2" s="42" t="inlineStr">
+      <c r="H2" s="26" t="inlineStr">
         <is>
           <t>Sequential row number (1, 2, 3 ...).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="38" t="n">
+      <c r="A3" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C3" s="40" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Sample_Name</t>
         </is>
       </c>
-      <c r="D3" s="41" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="E3" s="38" t="inlineStr"/>
+      <c r="E3" s="22" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>VOL-2024-018</t>
         </is>
       </c>
-      <c r="H3" s="42" t="inlineStr">
+      <c r="H3" s="26" t="inlineStr">
         <is>
           <t>Unique short identifier for the sample (lab code / field number). Avoid spaces.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="n">
+      <c r="A4" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Sample_Label</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr"/>
+      <c r="E4" s="22" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Mt. Pico flow 18</t>
         </is>
       </c>
-      <c r="H4" s="42" t="inlineStr">
+      <c r="H4" s="26" t="inlineStr">
         <is>
           <t>Free-text label used in plots if you don't want to expose the lab code.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="n">
+      <c r="A5" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="E5" s="38" t="inlineStr"/>
+      <c r="E5" s="22" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Lower flow</t>
         </is>
       </c>
-      <c r="H5" s="42" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Optional user-defined group used by the legend (e.g. unit, eruption, age cluster).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E6" s="38" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>°</t>
         </is>
@@ -3888,32 +3136,32 @@
           <t>-19.4250</t>
         </is>
       </c>
-      <c r="H6" s="42" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>Decimal degrees (WGS-84). Negative = south.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E7" s="38" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>°</t>
         </is>
@@ -3924,32 +3172,32 @@
           <t>-69.1583</t>
         </is>
       </c>
-      <c r="H7" s="42" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
         <is>
           <t>Decimal degrees (WGS-84). Negative = west.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Easting</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -3960,32 +3208,32 @@
           <t>483382</t>
         </is>
       </c>
-      <c r="H8" s="42" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
         <is>
           <t>UTM easting, if the location is in UTM rather than degrees; the map reads either.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="39" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>Northing</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E9" s="38" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -3996,64 +3244,64 @@
           <t>7852139</t>
         </is>
       </c>
-      <c r="H9" s="42" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
         <is>
           <t>UTM northing, in metres from the equator (south: from 10 000 km below it).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C10" s="40" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>UTM_Zone</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E10" s="38" t="inlineStr"/>
+      <c r="E10" s="22" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H10" s="42" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
         <is>
           <t>UTM zone number, 1-60.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C11" s="40" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Hemisphere</t>
         </is>
       </c>
-      <c r="D11" s="43" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E11" s="38" t="inlineStr"/>
+      <c r="E11" s="22" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>N, S</t>
@@ -4064,32 +3312,32 @@
           <t>S</t>
         </is>
       </c>
-      <c r="H11" s="42" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
         <is>
           <t>N or S: the UTM hemisphere. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>Elevation</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E12" s="38" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -4100,224 +3348,224 @@
           <t>4250</t>
         </is>
       </c>
-      <c r="H12" s="42" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
         <is>
           <t>Sampling elevation above sea level.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="n">
+      <c r="A13" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D13" s="43" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E13" s="38" t="inlineStr"/>
+      <c r="E13" s="22" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Chile</t>
         </is>
       </c>
-      <c r="H13" s="42" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
         <is>
           <t>Country where the sample was collected.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="n">
+      <c r="A14" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C14" s="40" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D14" s="43" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E14" s="38" t="inlineStr"/>
+      <c r="E14" s="22" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Arica y Parinacota</t>
         </is>
       </c>
-      <c r="H14" s="42" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr">
         <is>
           <t>State / province / volcanic field.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="n">
+      <c r="A15" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>Locality</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E15" s="38" t="inlineStr"/>
+      <c r="E15" s="22" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Taapaca Volcanic Complex</t>
         </is>
       </c>
-      <c r="H15" s="42" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
         <is>
           <t>Specific outcrop or feature.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="n">
+      <c r="A16" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C16" s="40" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="D16" s="44" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E16" s="38" t="inlineStr"/>
+      <c r="E16" s="22" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Aguirre et al. (2022) Lithos 408</t>
         </is>
       </c>
-      <c r="H16" s="42" t="inlineStr">
+      <c r="H16" s="26" t="inlineStr">
         <is>
           <t>Bibliographic reference for the analysis (author year, or DOI).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="n">
+      <c r="A17" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>Dataset_DOI</t>
         </is>
       </c>
-      <c r="D17" s="44" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E17" s="38" t="inlineStr"/>
+      <c r="E17" s="22" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>10.5281/zenodo.1234567</t>
         </is>
       </c>
-      <c r="H17" s="42" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
         <is>
           <t>DOI of the original dataset, if published separately.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="n">
+      <c r="A18" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C18" s="40" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="D18" s="45" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E18" s="38" t="inlineStr"/>
+      <c r="E18" s="22" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="H18" s="42" t="inlineStr">
+      <c r="H18" s="26" t="inlineStr">
         <is>
           <t>Numeric age (matched with AGE_UNIT). Leave empty if unknown.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="n">
+      <c r="A19" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Age_Unit</t>
         </is>
       </c>
-      <c r="D19" s="45" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E19" s="38" t="inlineStr"/>
+      <c r="E19" s="22" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Ma, ka, Ga, yr</t>
@@ -4328,64 +3576,64 @@
           <t>Ma</t>
         </is>
       </c>
-      <c r="H19" s="42" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>Unit of the AGE column. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="n">
+      <c r="A20" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="39" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C20" s="40" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>Age_Method</t>
         </is>
       </c>
-      <c r="D20" s="45" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E20" s="38" t="inlineStr"/>
+      <c r="E20" s="22" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Ar-Ar</t>
         </is>
       </c>
-      <c r="H20" s="42" t="inlineStr">
+      <c r="H20" s="26" t="inlineStr">
         <is>
           <t>Dating method (K-Ar, Ar-Ar, U-Pb, fission track, stratigraphic).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="n">
+      <c r="A21" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C21" s="40" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>Rock_Type</t>
         </is>
       </c>
-      <c r="D21" s="45" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E21" s="38" t="inlineStr"/>
+      <c r="E21" s="22" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein</t>
@@ -4396,32 +3644,32 @@
           <t>Volcanic</t>
         </is>
       </c>
-      <c r="H21" s="42" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
         <is>
           <t>Volcanic vs. plutonic family — used by B.I.R.D.S to pick the right TAS panel and tectonic catalogue.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="n">
+      <c r="A22" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="39" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C22" s="40" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>TAS_Composition</t>
         </is>
       </c>
-      <c r="D22" s="45" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E22" s="38" t="inlineStr"/>
+      <c r="E22" s="22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite</t>
@@ -4432,64 +3680,64 @@
           <t>Basaltic andesite</t>
         </is>
       </c>
-      <c r="H22" s="42" t="inlineStr">
+      <c r="H22" s="26" t="inlineStr">
         <is>
           <t>Rock name from the TAS diagram (Le Bas et al. 1986). Leave empty to let B.I.R.D.S compute it from SiO2 / alkalis.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="n">
+      <c r="A23" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="39" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C23" s="40" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>Lithology</t>
         </is>
       </c>
-      <c r="D23" s="45" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E23" s="38" t="inlineStr"/>
+      <c r="E23" s="22" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Olivine basalt</t>
         </is>
       </c>
-      <c r="H23" s="42" t="inlineStr">
+      <c r="H23" s="26" t="inlineStr">
         <is>
           <t>Petrographic name beyond TAS (e.g. olivine basalt, biotite-amphibole granodiorite).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="n">
+      <c r="A24" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C24" s="40" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>Magmatic_Series</t>
         </is>
       </c>
-      <c r="D24" s="45" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E24" s="38" t="inlineStr"/>
+      <c r="E24" s="22" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic</t>
@@ -4500,128 +3748,128 @@
           <t>Calc-alkaline</t>
         </is>
       </c>
-      <c r="H24" s="42" t="inlineStr">
+      <c r="H24" s="26" t="inlineStr">
         <is>
           <t>Magma series. Optional — also derivable from K2O-SiO2 and AFM diagrams.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="n">
+      <c r="A25" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="39" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>Tectonic_Setting</t>
         </is>
       </c>
-      <c r="D25" s="45" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E25" s="38" t="inlineStr"/>
+      <c r="E25" s="22" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>Continental arc</t>
         </is>
       </c>
-      <c r="H25" s="42" t="inlineStr">
+      <c r="H25" s="26" t="inlineStr">
         <is>
           <t>Inferred tectonic environment (MORB, OIB, IAB, CRB, OP, ...).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="38" t="n">
+      <c r="A26" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="39" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C26" s="40" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>Texture</t>
         </is>
       </c>
-      <c r="D26" s="45" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E26" s="38" t="inlineStr"/>
+      <c r="E26" s="22" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Porphyritic</t>
         </is>
       </c>
-      <c r="H26" s="42" t="inlineStr">
+      <c r="H26" s="26" t="inlineStr">
         <is>
           <t>Porphyritic / aphanitic / glassy / phaneritic / vesicular / etc.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="n">
+      <c r="A27" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="39" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C27" s="40" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>Mineral_Assemblage</t>
         </is>
       </c>
-      <c r="D27" s="45" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E27" s="38" t="inlineStr"/>
+      <c r="E27" s="22" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Pl + Cpx + Ol ± Opx</t>
         </is>
       </c>
-      <c r="H27" s="42" t="inlineStr">
+      <c r="H27" s="26" t="inlineStr">
         <is>
           <t>Main minerals (plagioclase, olivine, clinopyroxene, amphibole, biotite, K-feldspar, quartz ...).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="n">
+      <c r="A28" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="39" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C28" s="40" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>Alteration</t>
         </is>
       </c>
-      <c r="D28" s="45" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E28" s="38" t="inlineStr"/>
+      <c r="E28" s="22" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed</t>
@@ -4632,32 +3880,32 @@
           <t>Fresh</t>
         </is>
       </c>
-      <c r="H28" s="42" t="inlineStr">
+      <c r="H28" s="26" t="inlineStr">
         <is>
           <t>Visual / petrographic alteration grade.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="n">
+      <c r="A29" s="22" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="39" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C29" s="40" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>Analytical_Method</t>
         </is>
       </c>
-      <c r="D29" s="46" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="E29" s="38" t="inlineStr"/>
+      <c r="E29" s="22" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed</t>
@@ -4668,2236 +3916,2236 @@
           <t>XRF + ICP-MS</t>
         </is>
       </c>
-      <c r="H29" s="42" t="inlineStr">
+      <c r="H29" s="26" t="inlineStr">
         <is>
           <t>Technique used for the bulk analysis.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="n">
+      <c r="A30" s="22" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="39" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C30" s="40" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>Laboratory</t>
         </is>
       </c>
-      <c r="D30" s="46" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="E30" s="38" t="inlineStr"/>
+      <c r="E30" s="22" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>ALS Geochemistry (Vancouver)</t>
         </is>
       </c>
-      <c r="H30" s="42" t="inlineStr">
+      <c r="H30" s="26" t="inlineStr">
         <is>
           <t>Lab where the analysis was carried out.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="n">
+      <c r="A31" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="39" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C31" s="40" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>Analysis_Date</t>
         </is>
       </c>
-      <c r="D31" s="46" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="E31" s="38" t="inlineStr"/>
+      <c r="E31" s="22" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>2023-04</t>
         </is>
       </c>
-      <c r="H31" s="42" t="inlineStr">
+      <c r="H31" s="26" t="inlineStr">
         <is>
           <t>Year / date of the analysis (YYYY or YYYY-MM-DD).</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="n">
+      <c r="A32" s="22" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="39" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C32" s="40" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>Analyst</t>
         </is>
       </c>
-      <c r="D32" s="46" t="inlineStr">
+      <c r="D32" s="30" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="E32" s="38" t="inlineStr"/>
+      <c r="E32" s="22" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>JLF</t>
         </is>
       </c>
-      <c r="H32" s="42" t="inlineStr">
+      <c r="H32" s="26" t="inlineStr">
         <is>
           <t>Analyst initials or name (optional).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="n">
+      <c r="A33" s="22" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="39" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C33" s="40" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D33" s="46" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="E33" s="38" t="inlineStr"/>
+      <c r="E33" s="22" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" s="42" t="inlineStr">
+      <c r="H33" s="26" t="inlineStr">
         <is>
           <t>Free-text notes (anomalies, dilutions, repeated analyses, etc.).</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="38" t="n">
+      <c r="A34" s="22" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="39" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C34" s="40" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="D34" s="47" t="inlineStr">
+      <c r="D34" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E34" s="38" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" s="42" t="inlineStr">
+      <c r="H34" s="26" t="inlineStr">
         <is>
           <t>silicon dioxide</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="38" t="n">
+      <c r="A35" s="22" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="39" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C35" s="40" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>TiO2</t>
         </is>
       </c>
-      <c r="D35" s="47" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E35" s="38" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" s="42" t="inlineStr">
+      <c r="H35" s="26" t="inlineStr">
         <is>
           <t>titanium dioxide</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="38" t="n">
+      <c r="A36" s="22" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="39" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C36" s="40" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>Al2O3</t>
         </is>
       </c>
-      <c r="D36" s="47" t="inlineStr">
+      <c r="D36" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E36" s="38" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" s="42" t="inlineStr">
+      <c r="H36" s="26" t="inlineStr">
         <is>
           <t>aluminium oxide</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="38" t="n">
+      <c r="A37" s="22" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="39" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C37" s="40" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>Fe2O3</t>
         </is>
       </c>
-      <c r="D37" s="47" t="inlineStr">
+      <c r="D37" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E37" s="38" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" s="42" t="inlineStr">
+      <c r="H37" s="26" t="inlineStr">
         <is>
           <t>ferric iron</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="38" t="n">
+      <c r="A38" s="22" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="39" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C38" s="40" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>FeO</t>
         </is>
       </c>
-      <c r="D38" s="47" t="inlineStr">
+      <c r="D38" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E38" s="38" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" s="42" t="inlineStr">
+      <c r="H38" s="26" t="inlineStr">
         <is>
           <t>ferrous iron</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="38" t="n">
+      <c r="A39" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="39" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C39" s="40" t="inlineStr">
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>FeOt</t>
         </is>
       </c>
-      <c r="D39" s="47" t="inlineStr">
+      <c r="D39" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E39" s="38" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" s="42" t="inlineStr">
+      <c r="H39" s="26" t="inlineStr">
         <is>
           <t>total iron as FeO (used by Verma DFs)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="38" t="n">
+      <c r="A40" s="22" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="39" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C40" s="40" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>MnO</t>
         </is>
       </c>
-      <c r="D40" s="47" t="inlineStr">
+      <c r="D40" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E40" s="38" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" s="42" t="inlineStr">
+      <c r="H40" s="26" t="inlineStr">
         <is>
           <t>manganese oxide</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="38" t="n">
+      <c r="A41" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="39" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C41" s="40" t="inlineStr">
+      <c r="C41" s="24" t="inlineStr">
         <is>
           <t>MgO</t>
         </is>
       </c>
-      <c r="D41" s="47" t="inlineStr">
+      <c r="D41" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E41" s="38" t="inlineStr">
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" s="42" t="inlineStr">
+      <c r="H41" s="26" t="inlineStr">
         <is>
           <t>magnesium oxide</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="38" t="n">
+      <c r="A42" s="22" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="39" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C42" s="40" t="inlineStr">
+      <c r="C42" s="24" t="inlineStr">
         <is>
           <t>CaO</t>
         </is>
       </c>
-      <c r="D42" s="47" t="inlineStr">
+      <c r="D42" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E42" s="38" t="inlineStr">
+      <c r="E42" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" s="42" t="inlineStr">
+      <c r="H42" s="26" t="inlineStr">
         <is>
           <t>calcium oxide</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="38" t="n">
+      <c r="A43" s="22" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="39" t="inlineStr">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C43" s="40" t="inlineStr">
+      <c r="C43" s="24" t="inlineStr">
         <is>
           <t>Na2O</t>
         </is>
       </c>
-      <c r="D43" s="47" t="inlineStr">
+      <c r="D43" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E43" s="38" t="inlineStr">
+      <c r="E43" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" s="42" t="inlineStr">
+      <c r="H43" s="26" t="inlineStr">
         <is>
           <t>sodium oxide</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="38" t="n">
+      <c r="A44" s="22" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="39" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C44" s="40" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>K2O</t>
         </is>
       </c>
-      <c r="D44" s="47" t="inlineStr">
+      <c r="D44" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E44" s="38" t="inlineStr">
+      <c r="E44" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" s="42" t="inlineStr">
+      <c r="H44" s="26" t="inlineStr">
         <is>
           <t>potassium oxide</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="38" t="n">
+      <c r="A45" s="22" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="39" t="inlineStr">
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C45" s="40" t="inlineStr">
+      <c r="C45" s="24" t="inlineStr">
         <is>
           <t>P2O5</t>
         </is>
       </c>
-      <c r="D45" s="47" t="inlineStr">
+      <c r="D45" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E45" s="38" t="inlineStr">
+      <c r="E45" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" s="42" t="inlineStr">
+      <c r="H45" s="26" t="inlineStr">
         <is>
           <t>phosphorus pentoxide</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="38" t="n">
+      <c r="A46" s="22" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="39" t="inlineStr">
+      <c r="B46" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C46" s="40" t="inlineStr">
+      <c r="C46" s="24" t="inlineStr">
         <is>
           <t>Cr2O3</t>
         </is>
       </c>
-      <c r="D46" s="47" t="inlineStr">
+      <c r="D46" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E46" s="38" t="inlineStr">
+      <c r="E46" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" s="42" t="inlineStr">
+      <c r="H46" s="26" t="inlineStr">
         <is>
           <t>chromium oxide</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="38" t="n">
+      <c r="A47" s="22" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="39" t="inlineStr">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C47" s="40" t="inlineStr">
+      <c r="C47" s="24" t="inlineStr">
         <is>
           <t>NiO</t>
         </is>
       </c>
-      <c r="D47" s="47" t="inlineStr">
+      <c r="D47" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E47" s="38" t="inlineStr">
+      <c r="E47" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" s="42" t="inlineStr">
+      <c r="H47" s="26" t="inlineStr">
         <is>
           <t>nickel oxide</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="38" t="n">
+      <c r="A48" s="22" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="39" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C48" s="40" t="inlineStr">
+      <c r="C48" s="24" t="inlineStr">
         <is>
           <t>LOI</t>
         </is>
       </c>
-      <c r="D48" s="47" t="inlineStr">
+      <c r="D48" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E48" s="38" t="inlineStr">
+      <c r="E48" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" s="42" t="inlineStr">
+      <c r="H48" s="26" t="inlineStr">
         <is>
           <t>loss on ignition (heating at 1000 °C)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="38" t="n">
+      <c r="A49" s="22" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="39" t="inlineStr">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C49" s="40" t="inlineStr">
+      <c r="C49" s="24" t="inlineStr">
         <is>
           <t>H2O+</t>
         </is>
       </c>
-      <c r="D49" s="47" t="inlineStr">
+      <c r="D49" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E49" s="38" t="inlineStr">
+      <c r="E49" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" s="42" t="inlineStr">
+      <c r="H49" s="26" t="inlineStr">
         <is>
           <t>structural water (above 110 °C)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="38" t="n">
+      <c r="A50" s="22" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="39" t="inlineStr">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C50" s="40" t="inlineStr">
+      <c r="C50" s="24" t="inlineStr">
         <is>
           <t>H2O-</t>
         </is>
       </c>
-      <c r="D50" s="47" t="inlineStr">
+      <c r="D50" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E50" s="38" t="inlineStr">
+      <c r="E50" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" s="42" t="inlineStr">
+      <c r="H50" s="26" t="inlineStr">
         <is>
           <t>absorbed water (below 110 °C)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="38" t="n">
+      <c r="A51" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="39" t="inlineStr">
+      <c r="B51" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C51" s="40" t="inlineStr">
+      <c r="C51" s="24" t="inlineStr">
         <is>
           <t>CO2</t>
         </is>
       </c>
-      <c r="D51" s="47" t="inlineStr">
+      <c r="D51" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E51" s="38" t="inlineStr">
+      <c r="E51" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" s="42" t="inlineStr">
+      <c r="H51" s="26" t="inlineStr">
         <is>
           <t>carbon dioxide</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="38" t="n">
+      <c r="A52" s="22" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="39" t="inlineStr">
+      <c r="B52" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C52" s="40" t="inlineStr">
+      <c r="C52" s="24" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D52" s="47" t="inlineStr">
+      <c r="D52" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E52" s="38" t="inlineStr">
+      <c r="E52" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" s="42" t="inlineStr">
+      <c r="H52" s="26" t="inlineStr">
         <is>
           <t>sum of oxides (quality-control, target 99-101 wt%)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="38" t="n">
+      <c r="A53" s="22" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="39" t="inlineStr">
+      <c r="B53" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C53" s="40" t="inlineStr">
+      <c r="C53" s="24" t="inlineStr">
         <is>
           <t>Li</t>
         </is>
       </c>
-      <c r="D53" s="48" t="inlineStr">
+      <c r="D53" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E53" s="38" t="inlineStr">
+      <c r="E53" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" s="42" t="inlineStr">
+      <c r="H53" s="26" t="inlineStr">
         <is>
           <t>Trace element Li concentration.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="38" t="n">
+      <c r="A54" s="22" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="39" t="inlineStr">
+      <c r="B54" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C54" s="40" t="inlineStr">
+      <c r="C54" s="24" t="inlineStr">
         <is>
           <t>Be</t>
         </is>
       </c>
-      <c r="D54" s="48" t="inlineStr">
+      <c r="D54" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E54" s="38" t="inlineStr">
+      <c r="E54" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" s="42" t="inlineStr">
+      <c r="H54" s="26" t="inlineStr">
         <is>
           <t>Trace element Be concentration.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="38" t="n">
+      <c r="A55" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="39" t="inlineStr">
+      <c r="B55" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C55" s="40" t="inlineStr">
+      <c r="C55" s="24" t="inlineStr">
         <is>
           <t>Sc</t>
         </is>
       </c>
-      <c r="D55" s="48" t="inlineStr">
+      <c r="D55" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E55" s="38" t="inlineStr">
+      <c r="E55" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" s="42" t="inlineStr">
+      <c r="H55" s="26" t="inlineStr">
         <is>
           <t>Trace element Sc concentration.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="38" t="n">
+      <c r="A56" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="39" t="inlineStr">
+      <c r="B56" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C56" s="40" t="inlineStr">
+      <c r="C56" s="24" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D56" s="48" t="inlineStr">
+      <c r="D56" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E56" s="38" t="inlineStr">
+      <c r="E56" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" s="42" t="inlineStr">
+      <c r="H56" s="26" t="inlineStr">
         <is>
           <t>Trace element V concentration.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="38" t="n">
+      <c r="A57" s="22" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="39" t="inlineStr">
+      <c r="B57" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C57" s="40" t="inlineStr">
+      <c r="C57" s="24" t="inlineStr">
         <is>
           <t>Cr</t>
         </is>
       </c>
-      <c r="D57" s="48" t="inlineStr">
+      <c r="D57" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E57" s="38" t="inlineStr">
+      <c r="E57" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" s="42" t="inlineStr">
+      <c r="H57" s="26" t="inlineStr">
         <is>
           <t>Trace element Cr concentration.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="38" t="n">
+      <c r="A58" s="22" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="39" t="inlineStr">
+      <c r="B58" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C58" s="40" t="inlineStr">
+      <c r="C58" s="24" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D58" s="48" t="inlineStr">
+      <c r="D58" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E58" s="38" t="inlineStr">
+      <c r="E58" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" s="42" t="inlineStr">
+      <c r="H58" s="26" t="inlineStr">
         <is>
           <t>Trace element Co concentration.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="38" t="n">
+      <c r="A59" s="22" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="39" t="inlineStr">
+      <c r="B59" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C59" s="40" t="inlineStr">
+      <c r="C59" s="24" t="inlineStr">
         <is>
           <t>Ni</t>
         </is>
       </c>
-      <c r="D59" s="48" t="inlineStr">
+      <c r="D59" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E59" s="38" t="inlineStr">
+      <c r="E59" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" s="42" t="inlineStr">
+      <c r="H59" s="26" t="inlineStr">
         <is>
           <t>Trace element Ni concentration.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="38" t="n">
+      <c r="A60" s="22" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="39" t="inlineStr">
+      <c r="B60" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C60" s="40" t="inlineStr">
+      <c r="C60" s="24" t="inlineStr">
         <is>
           <t>Cu</t>
         </is>
       </c>
-      <c r="D60" s="48" t="inlineStr">
+      <c r="D60" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E60" s="38" t="inlineStr">
+      <c r="E60" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" s="42" t="inlineStr">
+      <c r="H60" s="26" t="inlineStr">
         <is>
           <t>Trace element Cu concentration.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="38" t="n">
+      <c r="A61" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="39" t="inlineStr">
+      <c r="B61" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C61" s="40" t="inlineStr">
+      <c r="C61" s="24" t="inlineStr">
         <is>
           <t>Zn</t>
         </is>
       </c>
-      <c r="D61" s="48" t="inlineStr">
+      <c r="D61" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E61" s="38" t="inlineStr">
+      <c r="E61" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" s="42" t="inlineStr">
+      <c r="H61" s="26" t="inlineStr">
         <is>
           <t>Trace element Zn concentration.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="38" t="n">
+      <c r="A62" s="22" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="39" t="inlineStr">
+      <c r="B62" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C62" s="40" t="inlineStr">
+      <c r="C62" s="24" t="inlineStr">
         <is>
           <t>Ga</t>
         </is>
       </c>
-      <c r="D62" s="48" t="inlineStr">
+      <c r="D62" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E62" s="38" t="inlineStr">
+      <c r="E62" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" s="42" t="inlineStr">
+      <c r="H62" s="26" t="inlineStr">
         <is>
           <t>Trace element Ga concentration.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="38" t="n">
+      <c r="A63" s="22" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="39" t="inlineStr">
+      <c r="B63" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C63" s="40" t="inlineStr">
+      <c r="C63" s="24" t="inlineStr">
         <is>
           <t>Rb</t>
         </is>
       </c>
-      <c r="D63" s="48" t="inlineStr">
+      <c r="D63" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E63" s="38" t="inlineStr">
+      <c r="E63" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" s="42" t="inlineStr">
+      <c r="H63" s="26" t="inlineStr">
         <is>
           <t>Trace element Rb concentration.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="38" t="n">
+      <c r="A64" s="22" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="39" t="inlineStr">
+      <c r="B64" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C64" s="40" t="inlineStr">
+      <c r="C64" s="24" t="inlineStr">
         <is>
           <t>Sr</t>
         </is>
       </c>
-      <c r="D64" s="48" t="inlineStr">
+      <c r="D64" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E64" s="38" t="inlineStr">
+      <c r="E64" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" s="42" t="inlineStr">
+      <c r="H64" s="26" t="inlineStr">
         <is>
           <t>Trace element Sr concentration.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="38" t="n">
+      <c r="A65" s="22" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="39" t="inlineStr">
+      <c r="B65" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C65" s="40" t="inlineStr">
+      <c r="C65" s="24" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="D65" s="48" t="inlineStr">
+      <c r="D65" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E65" s="38" t="inlineStr">
+      <c r="E65" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" s="42" t="inlineStr">
+      <c r="H65" s="26" t="inlineStr">
         <is>
           <t>Trace element Y concentration.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="38" t="n">
+      <c r="A66" s="22" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="39" t="inlineStr">
+      <c r="B66" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C66" s="40" t="inlineStr">
+      <c r="C66" s="24" t="inlineStr">
         <is>
           <t>Zr</t>
         </is>
       </c>
-      <c r="D66" s="48" t="inlineStr">
+      <c r="D66" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E66" s="38" t="inlineStr">
+      <c r="E66" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" s="42" t="inlineStr">
+      <c r="H66" s="26" t="inlineStr">
         <is>
           <t>Trace element Zr concentration.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="38" t="n">
+      <c r="A67" s="22" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="39" t="inlineStr">
+      <c r="B67" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C67" s="40" t="inlineStr">
+      <c r="C67" s="24" t="inlineStr">
         <is>
           <t>Nb</t>
         </is>
       </c>
-      <c r="D67" s="48" t="inlineStr">
+      <c r="D67" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E67" s="38" t="inlineStr">
+      <c r="E67" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" s="42" t="inlineStr">
+      <c r="H67" s="26" t="inlineStr">
         <is>
           <t>Trace element Nb concentration.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="38" t="n">
+      <c r="A68" s="22" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="39" t="inlineStr">
+      <c r="B68" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C68" s="40" t="inlineStr">
+      <c r="C68" s="24" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D68" s="48" t="inlineStr">
+      <c r="D68" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E68" s="38" t="inlineStr">
+      <c r="E68" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" s="42" t="inlineStr">
+      <c r="H68" s="26" t="inlineStr">
         <is>
           <t>Trace element Mo concentration.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="38" t="n">
+      <c r="A69" s="22" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="39" t="inlineStr">
+      <c r="B69" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C69" s="40" t="inlineStr">
+      <c r="C69" s="24" t="inlineStr">
         <is>
           <t>Sn</t>
         </is>
       </c>
-      <c r="D69" s="48" t="inlineStr">
+      <c r="D69" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E69" s="38" t="inlineStr">
+      <c r="E69" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" s="42" t="inlineStr">
+      <c r="H69" s="26" t="inlineStr">
         <is>
           <t>Trace element Sn concentration.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="38" t="n">
+      <c r="A70" s="22" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="39" t="inlineStr">
+      <c r="B70" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C70" s="40" t="inlineStr">
+      <c r="C70" s="24" t="inlineStr">
         <is>
           <t>Sb</t>
         </is>
       </c>
-      <c r="D70" s="48" t="inlineStr">
+      <c r="D70" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E70" s="38" t="inlineStr">
+      <c r="E70" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" s="42" t="inlineStr">
+      <c r="H70" s="26" t="inlineStr">
         <is>
           <t>Trace element Sb concentration.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="38" t="n">
+      <c r="A71" s="22" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="39" t="inlineStr">
+      <c r="B71" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C71" s="40" t="inlineStr">
+      <c r="C71" s="24" t="inlineStr">
         <is>
           <t>Cs</t>
         </is>
       </c>
-      <c r="D71" s="48" t="inlineStr">
+      <c r="D71" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E71" s="38" t="inlineStr">
+      <c r="E71" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" s="42" t="inlineStr">
+      <c r="H71" s="26" t="inlineStr">
         <is>
           <t>Trace element Cs concentration.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="38" t="n">
+      <c r="A72" s="22" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="39" t="inlineStr">
+      <c r="B72" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C72" s="40" t="inlineStr">
+      <c r="C72" s="24" t="inlineStr">
         <is>
           <t>Ba</t>
         </is>
       </c>
-      <c r="D72" s="48" t="inlineStr">
+      <c r="D72" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E72" s="38" t="inlineStr">
+      <c r="E72" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" s="42" t="inlineStr">
+      <c r="H72" s="26" t="inlineStr">
         <is>
           <t>Trace element Ba concentration.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="38" t="n">
+      <c r="A73" s="22" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="39" t="inlineStr">
+      <c r="B73" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C73" s="40" t="inlineStr">
+      <c r="C73" s="24" t="inlineStr">
         <is>
           <t>Hf</t>
         </is>
       </c>
-      <c r="D73" s="48" t="inlineStr">
+      <c r="D73" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E73" s="38" t="inlineStr">
+      <c r="E73" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" s="42" t="inlineStr">
+      <c r="H73" s="26" t="inlineStr">
         <is>
           <t>Trace element Hf concentration.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="38" t="n">
+      <c r="A74" s="22" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="39" t="inlineStr">
+      <c r="B74" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C74" s="40" t="inlineStr">
+      <c r="C74" s="24" t="inlineStr">
         <is>
           <t>Ta</t>
         </is>
       </c>
-      <c r="D74" s="48" t="inlineStr">
+      <c r="D74" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E74" s="38" t="inlineStr">
+      <c r="E74" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" s="42" t="inlineStr">
+      <c r="H74" s="26" t="inlineStr">
         <is>
           <t>Trace element Ta concentration.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="38" t="n">
+      <c r="A75" s="22" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="39" t="inlineStr">
+      <c r="B75" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C75" s="40" t="inlineStr">
+      <c r="C75" s="24" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D75" s="48" t="inlineStr">
+      <c r="D75" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E75" s="38" t="inlineStr">
+      <c r="E75" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" s="42" t="inlineStr">
+      <c r="H75" s="26" t="inlineStr">
         <is>
           <t>Trace element W concentration.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="38" t="n">
+      <c r="A76" s="22" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="39" t="inlineStr">
+      <c r="B76" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C76" s="40" t="inlineStr">
+      <c r="C76" s="24" t="inlineStr">
         <is>
           <t>Tl</t>
         </is>
       </c>
-      <c r="D76" s="48" t="inlineStr">
+      <c r="D76" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E76" s="38" t="inlineStr">
+      <c r="E76" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" s="42" t="inlineStr">
+      <c r="H76" s="26" t="inlineStr">
         <is>
           <t>Trace element Tl concentration.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="38" t="n">
+      <c r="A77" s="22" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="39" t="inlineStr">
+      <c r="B77" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C77" s="40" t="inlineStr">
+      <c r="C77" s="24" t="inlineStr">
         <is>
           <t>Pb</t>
         </is>
       </c>
-      <c r="D77" s="48" t="inlineStr">
+      <c r="D77" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E77" s="38" t="inlineStr">
+      <c r="E77" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" s="42" t="inlineStr">
+      <c r="H77" s="26" t="inlineStr">
         <is>
           <t>Trace element Pb concentration.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="38" t="n">
+      <c r="A78" s="22" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="39" t="inlineStr">
+      <c r="B78" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C78" s="40" t="inlineStr">
+      <c r="C78" s="24" t="inlineStr">
         <is>
           <t>Bi</t>
         </is>
       </c>
-      <c r="D78" s="48" t="inlineStr">
+      <c r="D78" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E78" s="38" t="inlineStr">
+      <c r="E78" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" s="42" t="inlineStr">
+      <c r="H78" s="26" t="inlineStr">
         <is>
           <t>Trace element Bi concentration.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="38" t="n">
+      <c r="A79" s="22" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="39" t="inlineStr">
+      <c r="B79" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C79" s="40" t="inlineStr">
+      <c r="C79" s="24" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="D79" s="48" t="inlineStr">
+      <c r="D79" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E79" s="38" t="inlineStr">
+      <c r="E79" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" s="42" t="inlineStr">
+      <c r="H79" s="26" t="inlineStr">
         <is>
           <t>Trace element Th concentration.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="38" t="n">
+      <c r="A80" s="22" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="39" t="inlineStr">
+      <c r="B80" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C80" s="40" t="inlineStr">
+      <c r="C80" s="24" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D80" s="48" t="inlineStr">
+      <c r="D80" s="32" t="inlineStr">
         <is>
           <t>Traces</t>
         </is>
       </c>
-      <c r="E80" s="38" t="inlineStr">
+      <c r="E80" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" s="42" t="inlineStr">
+      <c r="H80" s="26" t="inlineStr">
         <is>
           <t>Trace element U concentration.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="38" t="n">
+      <c r="A81" s="22" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="39" t="inlineStr">
+      <c r="B81" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C81" s="40" t="inlineStr">
+      <c r="C81" s="24" t="inlineStr">
         <is>
           <t>La</t>
         </is>
       </c>
-      <c r="D81" s="49" t="inlineStr">
+      <c r="D81" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E81" s="38" t="inlineStr">
+      <c r="E81" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" s="42" t="inlineStr">
+      <c r="H81" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element La concentration.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="38" t="n">
+      <c r="A82" s="22" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="39" t="inlineStr">
+      <c r="B82" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C82" s="40" t="inlineStr">
+      <c r="C82" s="24" t="inlineStr">
         <is>
           <t>Ce</t>
         </is>
       </c>
-      <c r="D82" s="49" t="inlineStr">
+      <c r="D82" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E82" s="38" t="inlineStr">
+      <c r="E82" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" s="42" t="inlineStr">
+      <c r="H82" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Ce concentration.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="38" t="n">
+      <c r="A83" s="22" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="39" t="inlineStr">
+      <c r="B83" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C83" s="40" t="inlineStr">
+      <c r="C83" s="24" t="inlineStr">
         <is>
           <t>Pr</t>
         </is>
       </c>
-      <c r="D83" s="49" t="inlineStr">
+      <c r="D83" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E83" s="38" t="inlineStr">
+      <c r="E83" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" s="42" t="inlineStr">
+      <c r="H83" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Pr concentration.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="38" t="n">
+      <c r="A84" s="22" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="39" t="inlineStr">
+      <c r="B84" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C84" s="40" t="inlineStr">
+      <c r="C84" s="24" t="inlineStr">
         <is>
           <t>Nd</t>
         </is>
       </c>
-      <c r="D84" s="49" t="inlineStr">
+      <c r="D84" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E84" s="38" t="inlineStr">
+      <c r="E84" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" s="42" t="inlineStr">
+      <c r="H84" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Nd concentration.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="38" t="n">
+      <c r="A85" s="22" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="39" t="inlineStr">
+      <c r="B85" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C85" s="40" t="inlineStr">
+      <c r="C85" s="24" t="inlineStr">
         <is>
           <t>Sm</t>
         </is>
       </c>
-      <c r="D85" s="49" t="inlineStr">
+      <c r="D85" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E85" s="38" t="inlineStr">
+      <c r="E85" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" s="42" t="inlineStr">
+      <c r="H85" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Sm concentration.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="38" t="n">
+      <c r="A86" s="22" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="39" t="inlineStr">
+      <c r="B86" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C86" s="40" t="inlineStr">
+      <c r="C86" s="24" t="inlineStr">
         <is>
           <t>Eu</t>
         </is>
       </c>
-      <c r="D86" s="49" t="inlineStr">
+      <c r="D86" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E86" s="38" t="inlineStr">
+      <c r="E86" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" s="42" t="inlineStr">
+      <c r="H86" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Eu concentration.</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="38" t="n">
+      <c r="A87" s="22" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="39" t="inlineStr">
+      <c r="B87" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C87" s="40" t="inlineStr">
+      <c r="C87" s="24" t="inlineStr">
         <is>
           <t>Gd</t>
         </is>
       </c>
-      <c r="D87" s="49" t="inlineStr">
+      <c r="D87" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E87" s="38" t="inlineStr">
+      <c r="E87" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" s="42" t="inlineStr">
+      <c r="H87" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Gd concentration.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="38" t="n">
+      <c r="A88" s="22" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="39" t="inlineStr">
+      <c r="B88" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C88" s="40" t="inlineStr">
+      <c r="C88" s="24" t="inlineStr">
         <is>
           <t>Tb</t>
         </is>
       </c>
-      <c r="D88" s="49" t="inlineStr">
+      <c r="D88" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E88" s="38" t="inlineStr">
+      <c r="E88" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" s="42" t="inlineStr">
+      <c r="H88" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Tb concentration.</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="38" t="n">
+      <c r="A89" s="22" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="39" t="inlineStr">
+      <c r="B89" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C89" s="40" t="inlineStr">
+      <c r="C89" s="24" t="inlineStr">
         <is>
           <t>Dy</t>
         </is>
       </c>
-      <c r="D89" s="49" t="inlineStr">
+      <c r="D89" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E89" s="38" t="inlineStr">
+      <c r="E89" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" s="42" t="inlineStr">
+      <c r="H89" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Dy concentration.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="38" t="n">
+      <c r="A90" s="22" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="39" t="inlineStr">
+      <c r="B90" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C90" s="40" t="inlineStr">
+      <c r="C90" s="24" t="inlineStr">
         <is>
           <t>Ho</t>
         </is>
       </c>
-      <c r="D90" s="49" t="inlineStr">
+      <c r="D90" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E90" s="38" t="inlineStr">
+      <c r="E90" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" s="42" t="inlineStr">
+      <c r="H90" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Ho concentration.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="38" t="n">
+      <c r="A91" s="22" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="39" t="inlineStr">
+      <c r="B91" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C91" s="40" t="inlineStr">
+      <c r="C91" s="24" t="inlineStr">
         <is>
           <t>Er</t>
         </is>
       </c>
-      <c r="D91" s="49" t="inlineStr">
+      <c r="D91" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E91" s="38" t="inlineStr">
+      <c r="E91" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" s="42" t="inlineStr">
+      <c r="H91" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Er concentration.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="38" t="n">
+      <c r="A92" s="22" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="39" t="inlineStr">
+      <c r="B92" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C92" s="40" t="inlineStr">
+      <c r="C92" s="24" t="inlineStr">
         <is>
           <t>Tm</t>
         </is>
       </c>
-      <c r="D92" s="49" t="inlineStr">
+      <c r="D92" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E92" s="38" t="inlineStr">
+      <c r="E92" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" s="42" t="inlineStr">
+      <c r="H92" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Tm concentration.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="38" t="n">
+      <c r="A93" s="22" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="39" t="inlineStr">
+      <c r="B93" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C93" s="40" t="inlineStr">
+      <c r="C93" s="24" t="inlineStr">
         <is>
           <t>Yb</t>
         </is>
       </c>
-      <c r="D93" s="49" t="inlineStr">
+      <c r="D93" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E93" s="38" t="inlineStr">
+      <c r="E93" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" s="42" t="inlineStr">
+      <c r="H93" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Yb concentration.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="38" t="n">
+      <c r="A94" s="22" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="39" t="inlineStr">
+      <c r="B94" s="23" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C94" s="40" t="inlineStr">
+      <c r="C94" s="24" t="inlineStr">
         <is>
           <t>Lu</t>
         </is>
       </c>
-      <c r="D94" s="49" t="inlineStr">
+      <c r="D94" s="33" t="inlineStr">
         <is>
           <t>REE</t>
         </is>
       </c>
-      <c r="E94" s="38" t="inlineStr">
+      <c r="E94" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" s="42" t="inlineStr">
+      <c r="H94" s="26" t="inlineStr">
         <is>
           <t>Rare-earth element Lu concentration.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="38" t="n">
+      <c r="A95" s="22" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="39" t="inlineStr">
+      <c r="B95" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C95" s="40" t="inlineStr">
+      <c r="C95" s="24" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="D95" s="41" t="inlineStr">
+      <c r="D95" s="25" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="E95" s="38" t="inlineStr"/>
+      <c r="E95" s="22" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H95" s="42" t="inlineStr">
+      <c r="H95" s="26" t="inlineStr">
         <is>
           <t>Sequential row number (1, 2, 3 ...).</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="38" t="n">
+      <c r="A96" s="22" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="39" t="inlineStr">
+      <c r="B96" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C96" s="40" t="inlineStr">
+      <c r="C96" s="24" t="inlineStr">
         <is>
           <t>Sample_Name</t>
         </is>
       </c>
-      <c r="D96" s="41" t="inlineStr">
+      <c r="D96" s="25" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="E96" s="38" t="inlineStr"/>
+      <c r="E96" s="22" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>VOL-2024-018</t>
         </is>
       </c>
-      <c r="H96" s="42" t="inlineStr">
+      <c r="H96" s="26" t="inlineStr">
         <is>
           <t>Unique short identifier for the sample (lab code / field number). Avoid spaces.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="38" t="n">
+      <c r="A97" s="22" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="39" t="inlineStr">
+      <c r="B97" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C97" s="40" t="inlineStr">
+      <c r="C97" s="24" t="inlineStr">
         <is>
           <t>Sample_Label</t>
         </is>
       </c>
-      <c r="D97" s="41" t="inlineStr">
+      <c r="D97" s="25" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="E97" s="38" t="inlineStr"/>
+      <c r="E97" s="22" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>Mt. Pico flow 18</t>
         </is>
       </c>
-      <c r="H97" s="42" t="inlineStr">
+      <c r="H97" s="26" t="inlineStr">
         <is>
           <t>Free-text label used in plots if you don't want to expose the lab code.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="38" t="n">
+      <c r="A98" s="22" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="39" t="inlineStr">
+      <c r="B98" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C98" s="40" t="inlineStr">
+      <c r="C98" s="24" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="D98" s="41" t="inlineStr">
+      <c r="D98" s="25" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="E98" s="38" t="inlineStr"/>
+      <c r="E98" s="22" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>Lower flow</t>
         </is>
       </c>
-      <c r="H98" s="42" t="inlineStr">
+      <c r="H98" s="26" t="inlineStr">
         <is>
           <t>Optional user-defined group used by the legend (e.g. unit, eruption, age cluster).</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="38" t="n">
+      <c r="A99" s="22" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="39" t="inlineStr">
+      <c r="B99" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C99" s="40" t="inlineStr">
+      <c r="C99" s="24" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="D99" s="43" t="inlineStr">
+      <c r="D99" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E99" s="38" t="inlineStr">
+      <c r="E99" s="22" t="inlineStr">
         <is>
           <t>°</t>
         </is>
@@ -6908,32 +6156,32 @@
           <t>-19.4250</t>
         </is>
       </c>
-      <c r="H99" s="42" t="inlineStr">
+      <c r="H99" s="26" t="inlineStr">
         <is>
           <t>Decimal degrees (WGS-84). Negative = south.</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="38" t="n">
+      <c r="A100" s="22" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="39" t="inlineStr">
+      <c r="B100" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C100" s="40" t="inlineStr">
+      <c r="C100" s="24" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="D100" s="43" t="inlineStr">
+      <c r="D100" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E100" s="38" t="inlineStr">
+      <c r="E100" s="22" t="inlineStr">
         <is>
           <t>°</t>
         </is>
@@ -6944,32 +6192,32 @@
           <t>-69.1583</t>
         </is>
       </c>
-      <c r="H100" s="42" t="inlineStr">
+      <c r="H100" s="26" t="inlineStr">
         <is>
           <t>Decimal degrees (WGS-84). Negative = west.</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="38" t="n">
+      <c r="A101" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="39" t="inlineStr">
+      <c r="B101" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C101" s="40" t="inlineStr">
+      <c r="C101" s="24" t="inlineStr">
         <is>
           <t>Easting</t>
         </is>
       </c>
-      <c r="D101" s="43" t="inlineStr">
+      <c r="D101" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E101" s="38" t="inlineStr">
+      <c r="E101" s="22" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -6980,32 +6228,32 @@
           <t>483382</t>
         </is>
       </c>
-      <c r="H101" s="42" t="inlineStr">
+      <c r="H101" s="26" t="inlineStr">
         <is>
           <t>UTM easting, if the location is in UTM rather than degrees; the map reads either.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="38" t="n">
+      <c r="A102" s="22" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="39" t="inlineStr">
+      <c r="B102" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C102" s="40" t="inlineStr">
+      <c r="C102" s="24" t="inlineStr">
         <is>
           <t>Northing</t>
         </is>
       </c>
-      <c r="D102" s="43" t="inlineStr">
+      <c r="D102" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E102" s="38" t="inlineStr">
+      <c r="E102" s="22" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -7016,64 +6264,64 @@
           <t>7852139</t>
         </is>
       </c>
-      <c r="H102" s="42" t="inlineStr">
+      <c r="H102" s="26" t="inlineStr">
         <is>
           <t>UTM northing, in metres from the equator (south: from 10 000 km below it).</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="38" t="n">
+      <c r="A103" s="22" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="39" t="inlineStr">
+      <c r="B103" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C103" s="40" t="inlineStr">
+      <c r="C103" s="24" t="inlineStr">
         <is>
           <t>UTM_Zone</t>
         </is>
       </c>
-      <c r="D103" s="43" t="inlineStr">
+      <c r="D103" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E103" s="38" t="inlineStr"/>
+      <c r="E103" s="22" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H103" s="42" t="inlineStr">
+      <c r="H103" s="26" t="inlineStr">
         <is>
           <t>UTM zone number, 1-60.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="38" t="n">
+      <c r="A104" s="22" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="39" t="inlineStr">
+      <c r="B104" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C104" s="40" t="inlineStr">
+      <c r="C104" s="24" t="inlineStr">
         <is>
           <t>Hemisphere</t>
         </is>
       </c>
-      <c r="D104" s="43" t="inlineStr">
+      <c r="D104" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E104" s="38" t="inlineStr"/>
+      <c r="E104" s="22" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>N, S</t>
@@ -7084,32 +6332,32 @@
           <t>S</t>
         </is>
       </c>
-      <c r="H104" s="42" t="inlineStr">
+      <c r="H104" s="26" t="inlineStr">
         <is>
           <t>N or S: the UTM hemisphere. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="38" t="n">
+      <c r="A105" s="22" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="39" t="inlineStr">
+      <c r="B105" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C105" s="40" t="inlineStr">
+      <c r="C105" s="24" t="inlineStr">
         <is>
           <t>Elevation</t>
         </is>
       </c>
-      <c r="D105" s="43" t="inlineStr">
+      <c r="D105" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E105" s="38" t="inlineStr">
+      <c r="E105" s="22" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -7120,224 +6368,224 @@
           <t>4250</t>
         </is>
       </c>
-      <c r="H105" s="42" t="inlineStr">
+      <c r="H105" s="26" t="inlineStr">
         <is>
           <t>Sampling elevation above sea level.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="38" t="n">
+      <c r="A106" s="22" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="39" t="inlineStr">
+      <c r="B106" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C106" s="40" t="inlineStr">
+      <c r="C106" s="24" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D106" s="43" t="inlineStr">
+      <c r="D106" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E106" s="38" t="inlineStr"/>
+      <c r="E106" s="22" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>Chile</t>
         </is>
       </c>
-      <c r="H106" s="42" t="inlineStr">
+      <c r="H106" s="26" t="inlineStr">
         <is>
           <t>Country where the sample was collected.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="38" t="n">
+      <c r="A107" s="22" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="39" t="inlineStr">
+      <c r="B107" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C107" s="40" t="inlineStr">
+      <c r="C107" s="24" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D107" s="43" t="inlineStr">
+      <c r="D107" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E107" s="38" t="inlineStr"/>
+      <c r="E107" s="22" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>Arica y Parinacota</t>
         </is>
       </c>
-      <c r="H107" s="42" t="inlineStr">
+      <c r="H107" s="26" t="inlineStr">
         <is>
           <t>State / province / volcanic field.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="38" t="n">
+      <c r="A108" s="22" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="39" t="inlineStr">
+      <c r="B108" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C108" s="40" t="inlineStr">
+      <c r="C108" s="24" t="inlineStr">
         <is>
           <t>Locality</t>
         </is>
       </c>
-      <c r="D108" s="43" t="inlineStr">
+      <c r="D108" s="27" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E108" s="38" t="inlineStr"/>
+      <c r="E108" s="22" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>Taapaca Volcanic Complex</t>
         </is>
       </c>
-      <c r="H108" s="42" t="inlineStr">
+      <c r="H108" s="26" t="inlineStr">
         <is>
           <t>Specific outcrop or feature.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="38" t="n">
+      <c r="A109" s="22" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="39" t="inlineStr">
+      <c r="B109" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C109" s="40" t="inlineStr">
+      <c r="C109" s="24" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="D109" s="44" t="inlineStr">
+      <c r="D109" s="28" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E109" s="38" t="inlineStr"/>
+      <c r="E109" s="22" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>Aguirre et al. (2022) Lithos 408</t>
         </is>
       </c>
-      <c r="H109" s="42" t="inlineStr">
+      <c r="H109" s="26" t="inlineStr">
         <is>
           <t>Bibliographic reference for the analysis (author year, or DOI).</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="38" t="n">
+      <c r="A110" s="22" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="39" t="inlineStr">
+      <c r="B110" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C110" s="40" t="inlineStr">
+      <c r="C110" s="24" t="inlineStr">
         <is>
           <t>Dataset_DOI</t>
         </is>
       </c>
-      <c r="D110" s="44" t="inlineStr">
+      <c r="D110" s="28" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E110" s="38" t="inlineStr"/>
+      <c r="E110" s="22" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>10.5281/zenodo.1234567</t>
         </is>
       </c>
-      <c r="H110" s="42" t="inlineStr">
+      <c r="H110" s="26" t="inlineStr">
         <is>
           <t>DOI of the original dataset, if published separately.</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="38" t="n">
+      <c r="A111" s="22" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="39" t="inlineStr">
+      <c r="B111" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C111" s="40" t="inlineStr">
+      <c r="C111" s="24" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="D111" s="45" t="inlineStr">
+      <c r="D111" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E111" s="38" t="inlineStr"/>
+      <c r="E111" s="22" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="H111" s="42" t="inlineStr">
+      <c r="H111" s="26" t="inlineStr">
         <is>
           <t>Numeric age (matched with AGE_UNIT). Leave empty if unknown.</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="38" t="n">
+      <c r="A112" s="22" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="39" t="inlineStr">
+      <c r="B112" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C112" s="40" t="inlineStr">
+      <c r="C112" s="24" t="inlineStr">
         <is>
           <t>Age_Unit</t>
         </is>
       </c>
-      <c r="D112" s="45" t="inlineStr">
+      <c r="D112" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E112" s="38" t="inlineStr"/>
+      <c r="E112" s="22" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>Ma, ka, Ga, yr</t>
@@ -7348,64 +6596,64 @@
           <t>Ma</t>
         </is>
       </c>
-      <c r="H112" s="42" t="inlineStr">
+      <c r="H112" s="26" t="inlineStr">
         <is>
           <t>Unit of the AGE column. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="38" t="n">
+      <c r="A113" s="22" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="39" t="inlineStr">
+      <c r="B113" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C113" s="40" t="inlineStr">
+      <c r="C113" s="24" t="inlineStr">
         <is>
           <t>Age_Method</t>
         </is>
       </c>
-      <c r="D113" s="45" t="inlineStr">
+      <c r="D113" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E113" s="38" t="inlineStr"/>
+      <c r="E113" s="22" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>Ar-Ar</t>
         </is>
       </c>
-      <c r="H113" s="42" t="inlineStr">
+      <c r="H113" s="26" t="inlineStr">
         <is>
           <t>Dating method (K-Ar, Ar-Ar, U-Pb, fission track, stratigraphic).</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="38" t="n">
+      <c r="A114" s="22" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="39" t="inlineStr">
+      <c r="B114" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C114" s="40" t="inlineStr">
+      <c r="C114" s="24" t="inlineStr">
         <is>
           <t>Rock_Type</t>
         </is>
       </c>
-      <c r="D114" s="45" t="inlineStr">
+      <c r="D114" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E114" s="38" t="inlineStr"/>
+      <c r="E114" s="22" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>Volcanic, Plutonic, Sub-volcanic, Pyroclastic, Vein</t>
@@ -7416,32 +6664,32 @@
           <t>Volcanic</t>
         </is>
       </c>
-      <c r="H114" s="42" t="inlineStr">
+      <c r="H114" s="26" t="inlineStr">
         <is>
           <t>Volcanic vs. plutonic family — used by B.I.R.D.S to pick the right TAS panel and tectonic catalogue.</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="38" t="n">
+      <c r="A115" s="22" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="39" t="inlineStr">
+      <c r="B115" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C115" s="40" t="inlineStr">
+      <c r="C115" s="24" t="inlineStr">
         <is>
           <t>TAS_Composition</t>
         </is>
       </c>
-      <c r="D115" s="45" t="inlineStr">
+      <c r="D115" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E115" s="38" t="inlineStr"/>
+      <c r="E115" s="22" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>Picro-basalt, Basalt, Basaltic andesite, Andesite, Dacite, Rhyolite, Trachy-basalt, Basaltic trachy-andesite, Trachy-andesite, Trachyte, Trachy-dacite, Tephrite, Phono-tephrite, Tephri-phonolite, Phonolite, Foidite, Gabbro, Diorite, Granodiorite, Granite, Monzogabbro, Monzodiorite, Monzonite, Syenite, Foid-syenite, Foidolite</t>
@@ -7452,64 +6700,64 @@
           <t>Basaltic andesite</t>
         </is>
       </c>
-      <c r="H115" s="42" t="inlineStr">
+      <c r="H115" s="26" t="inlineStr">
         <is>
           <t>Rock name from the TAS diagram (Le Bas et al. 1986). Leave empty to let B.I.R.D.S compute it from SiO2 / alkalis.</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="38" t="n">
+      <c r="A116" s="22" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="39" t="inlineStr">
+      <c r="B116" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C116" s="40" t="inlineStr">
+      <c r="C116" s="24" t="inlineStr">
         <is>
           <t>Lithology</t>
         </is>
       </c>
-      <c r="D116" s="45" t="inlineStr">
+      <c r="D116" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E116" s="38" t="inlineStr"/>
+      <c r="E116" s="22" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>Olivine basalt</t>
         </is>
       </c>
-      <c r="H116" s="42" t="inlineStr">
+      <c r="H116" s="26" t="inlineStr">
         <is>
           <t>Petrographic name beyond TAS (e.g. olivine basalt, biotite-amphibole granodiorite).</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="38" t="n">
+      <c r="A117" s="22" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="39" t="inlineStr">
+      <c r="B117" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C117" s="40" t="inlineStr">
+      <c r="C117" s="24" t="inlineStr">
         <is>
           <t>Magmatic_Series</t>
         </is>
       </c>
-      <c r="D117" s="45" t="inlineStr">
+      <c r="D117" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E117" s="38" t="inlineStr"/>
+      <c r="E117" s="22" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>Tholeiitic, Calc-alkaline, High-K calc-alkaline, Shoshonitic, Alkaline, Ultra-alkaline, Boninitic</t>
@@ -7520,128 +6768,128 @@
           <t>Calc-alkaline</t>
         </is>
       </c>
-      <c r="H117" s="42" t="inlineStr">
+      <c r="H117" s="26" t="inlineStr">
         <is>
           <t>Magma series. Optional — also derivable from K2O-SiO2 and AFM diagrams.</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="38" t="n">
+      <c r="A118" s="22" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="39" t="inlineStr">
+      <c r="B118" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C118" s="40" t="inlineStr">
+      <c r="C118" s="24" t="inlineStr">
         <is>
           <t>Tectonic_Setting</t>
         </is>
       </c>
-      <c r="D118" s="45" t="inlineStr">
+      <c r="D118" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E118" s="38" t="inlineStr"/>
+      <c r="E118" s="22" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>Continental arc</t>
         </is>
       </c>
-      <c r="H118" s="42" t="inlineStr">
+      <c r="H118" s="26" t="inlineStr">
         <is>
           <t>Inferred tectonic environment (MORB, OIB, IAB, CRB, OP, ...).</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="38" t="n">
+      <c r="A119" s="22" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="39" t="inlineStr">
+      <c r="B119" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C119" s="40" t="inlineStr">
+      <c r="C119" s="24" t="inlineStr">
         <is>
           <t>Texture</t>
         </is>
       </c>
-      <c r="D119" s="45" t="inlineStr">
+      <c r="D119" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E119" s="38" t="inlineStr"/>
+      <c r="E119" s="22" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>Porphyritic</t>
         </is>
       </c>
-      <c r="H119" s="42" t="inlineStr">
+      <c r="H119" s="26" t="inlineStr">
         <is>
           <t>Porphyritic / aphanitic / glassy / phaneritic / vesicular / etc.</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="38" t="n">
+      <c r="A120" s="22" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="39" t="inlineStr">
+      <c r="B120" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C120" s="40" t="inlineStr">
+      <c r="C120" s="24" t="inlineStr">
         <is>
           <t>Mineral_Assemblage</t>
         </is>
       </c>
-      <c r="D120" s="45" t="inlineStr">
+      <c r="D120" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E120" s="38" t="inlineStr"/>
+      <c r="E120" s="22" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>Pl + Cpx + Ol ± Opx</t>
         </is>
       </c>
-      <c r="H120" s="42" t="inlineStr">
+      <c r="H120" s="26" t="inlineStr">
         <is>
           <t>Main minerals (plagioclase, olivine, clinopyroxene, amphibole, biotite, K-feldspar, quartz ...).</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="38" t="n">
+      <c r="A121" s="22" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="39" t="inlineStr">
+      <c r="B121" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C121" s="40" t="inlineStr">
+      <c r="C121" s="24" t="inlineStr">
         <is>
           <t>Alteration</t>
         </is>
       </c>
-      <c r="D121" s="45" t="inlineStr">
+      <c r="D121" s="29" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="E121" s="38" t="inlineStr"/>
+      <c r="E121" s="22" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>Fresh, Slightly altered, Moderately altered, Strongly altered, Metamorphosed</t>
@@ -7652,32 +6900,32 @@
           <t>Fresh</t>
         </is>
       </c>
-      <c r="H121" s="42" t="inlineStr">
+      <c r="H121" s="26" t="inlineStr">
         <is>
           <t>Visual / petrographic alteration grade.</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="38" t="n">
+      <c r="A122" s="22" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="39" t="inlineStr">
+      <c r="B122" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C122" s="40" t="inlineStr">
+      <c r="C122" s="24" t="inlineStr">
         <is>
           <t>Analytical_Method</t>
         </is>
       </c>
-      <c r="D122" s="46" t="inlineStr">
+      <c r="D122" s="30" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="E122" s="38" t="inlineStr"/>
+      <c r="E122" s="22" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>XRF, ICP-OES, ICP-MS, Solution ICP-MS, LA-ICP-MS, EMP / EPMA, INAA, Wet chemistry, Mixed</t>
@@ -7688,156 +6936,156 @@
           <t>XRF + ICP-MS</t>
         </is>
       </c>
-      <c r="H122" s="42" t="inlineStr">
+      <c r="H122" s="26" t="inlineStr">
         <is>
           <t>Technique used for the bulk analysis.</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="38" t="n">
+      <c r="A123" s="22" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="39" t="inlineStr">
+      <c r="B123" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C123" s="40" t="inlineStr">
+      <c r="C123" s="24" t="inlineStr">
         <is>
           <t>Laboratory</t>
         </is>
       </c>
-      <c r="D123" s="46" t="inlineStr">
+      <c r="D123" s="30" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="E123" s="38" t="inlineStr"/>
+      <c r="E123" s="22" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>ALS Geochemistry (Vancouver)</t>
         </is>
       </c>
-      <c r="H123" s="42" t="inlineStr">
+      <c r="H123" s="26" t="inlineStr">
         <is>
           <t>Lab where the analysis was carried out.</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="38" t="n">
+      <c r="A124" s="22" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="39" t="inlineStr">
+      <c r="B124" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C124" s="40" t="inlineStr">
+      <c r="C124" s="24" t="inlineStr">
         <is>
           <t>Analysis_Date</t>
         </is>
       </c>
-      <c r="D124" s="46" t="inlineStr">
+      <c r="D124" s="30" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="E124" s="38" t="inlineStr"/>
+      <c r="E124" s="22" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>2023-04</t>
         </is>
       </c>
-      <c r="H124" s="42" t="inlineStr">
+      <c r="H124" s="26" t="inlineStr">
         <is>
           <t>Year / date of the analysis (YYYY or YYYY-MM-DD).</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="38" t="n">
+      <c r="A125" s="22" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="39" t="inlineStr">
+      <c r="B125" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C125" s="40" t="inlineStr">
+      <c r="C125" s="24" t="inlineStr">
         <is>
           <t>Analyst</t>
         </is>
       </c>
-      <c r="D125" s="46" t="inlineStr">
+      <c r="D125" s="30" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="E125" s="38" t="inlineStr"/>
+      <c r="E125" s="22" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>JLF</t>
         </is>
       </c>
-      <c r="H125" s="42" t="inlineStr">
+      <c r="H125" s="26" t="inlineStr">
         <is>
           <t>Analyst initials or name (optional).</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="38" t="n">
+      <c r="A126" s="22" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="39" t="inlineStr">
+      <c r="B126" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C126" s="40" t="inlineStr">
+      <c r="C126" s="24" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D126" s="46" t="inlineStr">
+      <c r="D126" s="30" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="E126" s="38" t="inlineStr"/>
+      <c r="E126" s="22" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
-      <c r="H126" s="42" t="inlineStr">
+      <c r="H126" s="26" t="inlineStr">
         <is>
           <t>Free-text notes (anomalies, dilutions, repeated analyses, etc.).</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="38" t="n">
+      <c r="A127" s="22" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="39" t="inlineStr">
+      <c r="B127" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C127" s="40" t="inlineStr">
+      <c r="C127" s="24" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="D127" s="47" t="inlineStr">
+      <c r="D127" s="31" t="inlineStr">
         <is>
           <t>Majors</t>
         </is>
       </c>
-      <c r="E127" s="38" t="inlineStr">
+      <c r="E127" s="22" t="inlineStr">
         <is>
           <t>wt%</t>
         </is>
@@ -7848,128 +7096,128 @@
           <t>52.4</t>
         </is>
       </c>
-      <c r="H127" s="42" t="inlineStr">
+      <c r="H127" s="26" t="inlineStr">
         <is>
           <t>Silica of the sample, for reading the isotope ratios against differentiation on this sheet (e.g. ⁸⁷Sr/⁸⁶Sr vs SiO2 for crustal assimilation). Copy it from the Data sheet, or give the value measured on the isotope aliquot. At import the Data sheet's SiO2 is kept for the bulk analysis.</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="38" t="n">
+      <c r="A128" s="22" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="39" t="inlineStr">
+      <c r="B128" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C128" s="40" t="inlineStr">
+      <c r="C128" s="24" t="inlineStr">
         <is>
           <t>87Sr/86Sr</t>
         </is>
       </c>
-      <c r="D128" s="50" t="inlineStr">
+      <c r="D128" s="34" t="inlineStr">
         <is>
           <t>Iso-Sr</t>
         </is>
       </c>
-      <c r="E128" s="38" t="inlineStr"/>
+      <c r="E128" s="22" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>0.70428</t>
         </is>
       </c>
-      <c r="H128" s="42" t="inlineStr">
+      <c r="H128" s="26" t="inlineStr">
         <is>
           <t>Measured ⁸⁷Sr/⁸⁶Sr ratio. Typical values: 0.7022 (DM), 0.7045 (CHUR), 0.708-0.710 (arc/upper crust).</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="38" t="n">
+      <c r="A129" s="22" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="39" t="inlineStr">
+      <c r="B129" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C129" s="40" t="inlineStr">
+      <c r="C129" s="24" t="inlineStr">
         <is>
           <t>87Sr/86Sr_2σ</t>
         </is>
       </c>
-      <c r="D129" s="50" t="inlineStr">
+      <c r="D129" s="34" t="inlineStr">
         <is>
           <t>Iso-Sr</t>
         </is>
       </c>
-      <c r="E129" s="38" t="inlineStr"/>
+      <c r="E129" s="22" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>0.00001</t>
         </is>
       </c>
-      <c r="H129" s="42" t="inlineStr">
+      <c r="H129" s="26" t="inlineStr">
         <is>
           <t>Analytical 2σ uncertainty of ⁸⁷Sr/⁸⁶Sr (absolute, e.g. 0.000010).</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="38" t="n">
+      <c r="A130" s="22" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="39" t="inlineStr">
+      <c r="B130" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C130" s="40" t="inlineStr">
+      <c r="C130" s="24" t="inlineStr">
         <is>
           <t>87Rb/86Sr</t>
         </is>
       </c>
-      <c r="D130" s="50" t="inlineStr">
+      <c r="D130" s="34" t="inlineStr">
         <is>
           <t>Iso-Sr</t>
         </is>
       </c>
-      <c r="E130" s="38" t="inlineStr"/>
+      <c r="E130" s="22" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>0.045</t>
         </is>
       </c>
-      <c r="H130" s="42" t="inlineStr">
+      <c r="H130" s="26" t="inlineStr">
         <is>
           <t>Parent ratio used for the initial-Sr correction. If missing, B.I.R.D.S derives it from Rb / Sr concentrations (~2.894 × Rb/Sr).</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="38" t="n">
+      <c r="A131" s="22" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="39" t="inlineStr">
+      <c r="B131" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C131" s="40" t="inlineStr">
+      <c r="C131" s="24" t="inlineStr">
         <is>
           <t>Sr_iso</t>
         </is>
       </c>
-      <c r="D131" s="50" t="inlineStr">
+      <c r="D131" s="34" t="inlineStr">
         <is>
           <t>Iso-Sr</t>
         </is>
       </c>
-      <c r="E131" s="38" t="inlineStr">
+      <c r="E131" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
@@ -7980,32 +7228,32 @@
           <t>385</t>
         </is>
       </c>
-      <c r="H131" s="42" t="inlineStr">
+      <c r="H131" s="26" t="inlineStr">
         <is>
           <t>Sr concentration measured on the same aliquot as the isotope ratio (optional; only needed if it differs from the bulk value in the Data sheet).</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="38" t="n">
+      <c r="A132" s="22" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="39" t="inlineStr">
+      <c r="B132" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C132" s="40" t="inlineStr">
+      <c r="C132" s="24" t="inlineStr">
         <is>
           <t>Rb_iso</t>
         </is>
       </c>
-      <c r="D132" s="50" t="inlineStr">
+      <c r="D132" s="34" t="inlineStr">
         <is>
           <t>Iso-Sr</t>
         </is>
       </c>
-      <c r="E132" s="38" t="inlineStr">
+      <c r="E132" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
@@ -8016,156 +7264,156 @@
           <t>11</t>
         </is>
       </c>
-      <c r="H132" s="42" t="inlineStr">
+      <c r="H132" s="26" t="inlineStr">
         <is>
           <t>Rb concentration measured on the same aliquot.</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="38" t="n">
+      <c r="A133" s="22" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="39" t="inlineStr">
+      <c r="B133" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C133" s="40" t="inlineStr">
+      <c r="C133" s="24" t="inlineStr">
         <is>
           <t>εSr_initial</t>
         </is>
       </c>
-      <c r="D133" s="50" t="inlineStr">
+      <c r="D133" s="34" t="inlineStr">
         <is>
           <t>Iso-Sr</t>
         </is>
       </c>
-      <c r="E133" s="38" t="inlineStr"/>
+      <c r="E133" s="22" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
-      <c r="H133" s="42" t="inlineStr">
+      <c r="H133" s="26" t="inlineStr">
         <is>
           <t>Computed by B.I.R.D.S — leave empty.</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="38" t="n">
+      <c r="A134" s="22" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="39" t="inlineStr">
+      <c r="B134" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C134" s="40" t="inlineStr">
+      <c r="C134" s="24" t="inlineStr">
         <is>
           <t>143Nd/144Nd</t>
         </is>
       </c>
-      <c r="D134" s="51" t="inlineStr">
+      <c r="D134" s="35" t="inlineStr">
         <is>
           <t>Iso-Nd</t>
         </is>
       </c>
-      <c r="E134" s="38" t="inlineStr"/>
+      <c r="E134" s="22" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>0.51285</t>
         </is>
       </c>
-      <c r="H134" s="42" t="inlineStr">
+      <c r="H134" s="26" t="inlineStr">
         <is>
           <t>Measured ¹⁴³Nd/¹⁴⁴Nd ratio. CHUR = 0.512638 (Jacobsen &amp; Wasserburg 1980; Bouvier et al. 2008 give 0.512630).</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="38" t="n">
+      <c r="A135" s="22" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="39" t="inlineStr">
+      <c r="B135" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C135" s="40" t="inlineStr">
+      <c r="C135" s="24" t="inlineStr">
         <is>
           <t>143Nd/144Nd_2σ</t>
         </is>
       </c>
-      <c r="D135" s="51" t="inlineStr">
+      <c r="D135" s="35" t="inlineStr">
         <is>
           <t>Iso-Nd</t>
         </is>
       </c>
-      <c r="E135" s="38" t="inlineStr"/>
+      <c r="E135" s="22" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>0.000007</t>
         </is>
       </c>
-      <c r="H135" s="42" t="inlineStr">
+      <c r="H135" s="26" t="inlineStr">
         <is>
           <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="38" t="n">
+      <c r="A136" s="22" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="39" t="inlineStr">
+      <c r="B136" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C136" s="40" t="inlineStr">
+      <c r="C136" s="24" t="inlineStr">
         <is>
           <t>147Sm/144Nd</t>
         </is>
       </c>
-      <c r="D136" s="51" t="inlineStr">
+      <c r="D136" s="35" t="inlineStr">
         <is>
           <t>Iso-Nd</t>
         </is>
       </c>
-      <c r="E136" s="38" t="inlineStr"/>
+      <c r="E136" s="22" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="H136" s="42" t="inlineStr">
+      <c r="H136" s="26" t="inlineStr">
         <is>
           <t>Parent ratio for the initial-Nd correction. If missing, derived from Sm/Nd (~0.6043 × Sm/Nd).</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="38" t="n">
+      <c r="A137" s="22" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="39" t="inlineStr">
+      <c r="B137" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C137" s="40" t="inlineStr">
+      <c r="C137" s="24" t="inlineStr">
         <is>
           <t>Sm_iso</t>
         </is>
       </c>
-      <c r="D137" s="51" t="inlineStr">
+      <c r="D137" s="35" t="inlineStr">
         <is>
           <t>Iso-Nd</t>
         </is>
       </c>
-      <c r="E137" s="38" t="inlineStr">
+      <c r="E137" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
@@ -8176,32 +7424,32 @@
           <t>4.85</t>
         </is>
       </c>
-      <c r="H137" s="42" t="inlineStr">
+      <c r="H137" s="26" t="inlineStr">
         <is>
           <t>Sm concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="38" t="n">
+      <c r="A138" s="22" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="39" t="inlineStr">
+      <c r="B138" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C138" s="40" t="inlineStr">
+      <c r="C138" s="24" t="inlineStr">
         <is>
           <t>Nd_iso</t>
         </is>
       </c>
-      <c r="D138" s="51" t="inlineStr">
+      <c r="D138" s="35" t="inlineStr">
         <is>
           <t>Iso-Nd</t>
         </is>
       </c>
-      <c r="E138" s="38" t="inlineStr">
+      <c r="E138" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
@@ -8212,60 +7460,60 @@
           <t>20.1</t>
         </is>
       </c>
-      <c r="H138" s="42" t="inlineStr">
+      <c r="H138" s="26" t="inlineStr">
         <is>
           <t>Nd concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="38" t="n">
+      <c r="A139" s="22" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="39" t="inlineStr">
+      <c r="B139" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C139" s="40" t="inlineStr">
+      <c r="C139" s="24" t="inlineStr">
         <is>
           <t>εNd_initial</t>
         </is>
       </c>
-      <c r="D139" s="51" t="inlineStr">
+      <c r="D139" s="35" t="inlineStr">
         <is>
           <t>Iso-Nd</t>
         </is>
       </c>
-      <c r="E139" s="38" t="inlineStr"/>
+      <c r="E139" s="22" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" s="42" t="inlineStr">
+      <c r="H139" s="26" t="inlineStr">
         <is>
           <t>Computed by B.I.R.D.S.</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="38" t="n">
+      <c r="A140" s="22" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="39" t="inlineStr">
+      <c r="B140" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C140" s="40" t="inlineStr">
+      <c r="C140" s="24" t="inlineStr">
         <is>
           <t>TDM_Nd</t>
         </is>
       </c>
-      <c r="D140" s="51" t="inlineStr">
+      <c r="D140" s="35" t="inlineStr">
         <is>
           <t>Iso-Nd</t>
         </is>
       </c>
-      <c r="E140" s="38" t="inlineStr">
+      <c r="E140" s="22" t="inlineStr">
         <is>
           <t>Ma</t>
         </is>
@@ -8276,224 +7524,224 @@
           <t>1250</t>
         </is>
       </c>
-      <c r="H140" s="42" t="inlineStr">
+      <c r="H140" s="26" t="inlineStr">
         <is>
           <t>Nd depleted-mantle model age (DePaolo 1981 or Goldstein 1984 — pick your convention).</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="38" t="n">
+      <c r="A141" s="22" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="39" t="inlineStr">
+      <c r="B141" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C141" s="40" t="inlineStr">
+      <c r="C141" s="24" t="inlineStr">
         <is>
           <t>206Pb/204Pb</t>
         </is>
       </c>
-      <c r="D141" s="52" t="inlineStr">
+      <c r="D141" s="36" t="inlineStr">
         <is>
           <t>Iso-Pb</t>
         </is>
       </c>
-      <c r="E141" s="38" t="inlineStr"/>
+      <c r="E141" s="22" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>18.65</t>
         </is>
       </c>
-      <c r="H141" s="42" t="inlineStr">
+      <c r="H141" s="26" t="inlineStr">
         <is>
           <t>Measured ²⁰⁶Pb/²⁰⁴Pb ratio.</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="38" t="n">
+      <c r="A142" s="22" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="39" t="inlineStr">
+      <c r="B142" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C142" s="40" t="inlineStr">
+      <c r="C142" s="24" t="inlineStr">
         <is>
           <t>206Pb/204Pb_2σ</t>
         </is>
       </c>
-      <c r="D142" s="52" t="inlineStr">
+      <c r="D142" s="36" t="inlineStr">
         <is>
           <t>Iso-Pb</t>
         </is>
       </c>
-      <c r="E142" s="38" t="inlineStr"/>
+      <c r="E142" s="22" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="H142" s="42" t="inlineStr">
+      <c r="H142" s="26" t="inlineStr">
         <is>
           <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="38" t="n">
+      <c r="A143" s="22" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="39" t="inlineStr">
+      <c r="B143" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C143" s="40" t="inlineStr">
+      <c r="C143" s="24" t="inlineStr">
         <is>
           <t>207Pb/204Pb</t>
         </is>
       </c>
-      <c r="D143" s="52" t="inlineStr">
+      <c r="D143" s="36" t="inlineStr">
         <is>
           <t>Iso-Pb</t>
         </is>
       </c>
-      <c r="E143" s="38" t="inlineStr"/>
+      <c r="E143" s="22" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>15.55</t>
         </is>
       </c>
-      <c r="H143" s="42" t="inlineStr">
+      <c r="H143" s="26" t="inlineStr">
         <is>
           <t>Measured ²⁰⁷Pb/²⁰⁴Pb ratio.</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="38" t="n">
+      <c r="A144" s="22" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="39" t="inlineStr">
+      <c r="B144" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C144" s="40" t="inlineStr">
+      <c r="C144" s="24" t="inlineStr">
         <is>
           <t>207Pb/204Pb_2σ</t>
         </is>
       </c>
-      <c r="D144" s="52" t="inlineStr">
+      <c r="D144" s="36" t="inlineStr">
         <is>
           <t>Iso-Pb</t>
         </is>
       </c>
-      <c r="E144" s="38" t="inlineStr"/>
+      <c r="E144" s="22" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="H144" s="42" t="inlineStr">
+      <c r="H144" s="26" t="inlineStr">
         <is>
           <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="38" t="n">
+      <c r="A145" s="22" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="39" t="inlineStr">
+      <c r="B145" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C145" s="40" t="inlineStr">
+      <c r="C145" s="24" t="inlineStr">
         <is>
           <t>208Pb/204Pb</t>
         </is>
       </c>
-      <c r="D145" s="52" t="inlineStr">
+      <c r="D145" s="36" t="inlineStr">
         <is>
           <t>Iso-Pb</t>
         </is>
       </c>
-      <c r="E145" s="38" t="inlineStr"/>
+      <c r="E145" s="22" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>38.45</t>
         </is>
       </c>
-      <c r="H145" s="42" t="inlineStr">
+      <c r="H145" s="26" t="inlineStr">
         <is>
           <t>Measured ²⁰⁸Pb/²⁰⁴Pb ratio.</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="38" t="n">
+      <c r="A146" s="22" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="39" t="inlineStr">
+      <c r="B146" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C146" s="40" t="inlineStr">
+      <c r="C146" s="24" t="inlineStr">
         <is>
           <t>208Pb/204Pb_2σ</t>
         </is>
       </c>
-      <c r="D146" s="52" t="inlineStr">
+      <c r="D146" s="36" t="inlineStr">
         <is>
           <t>Iso-Pb</t>
         </is>
       </c>
-      <c r="E146" s="38" t="inlineStr"/>
+      <c r="E146" s="22" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="H146" s="42" t="inlineStr">
+      <c r="H146" s="26" t="inlineStr">
         <is>
           <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="38" t="n">
+      <c r="A147" s="22" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="39" t="inlineStr">
+      <c r="B147" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C147" s="40" t="inlineStr">
+      <c r="C147" s="24" t="inlineStr">
         <is>
           <t>Pb_iso</t>
         </is>
       </c>
-      <c r="D147" s="52" t="inlineStr">
+      <c r="D147" s="36" t="inlineStr">
         <is>
           <t>Iso-Pb</t>
         </is>
       </c>
-      <c r="E147" s="38" t="inlineStr">
+      <c r="E147" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
@@ -8504,32 +7752,32 @@
           <t>6.2</t>
         </is>
       </c>
-      <c r="H147" s="42" t="inlineStr">
+      <c r="H147" s="26" t="inlineStr">
         <is>
           <t>Pb concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="38" t="n">
+      <c r="A148" s="22" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="39" t="inlineStr">
+      <c r="B148" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C148" s="40" t="inlineStr">
+      <c r="C148" s="24" t="inlineStr">
         <is>
           <t>U_iso</t>
         </is>
       </c>
-      <c r="D148" s="52" t="inlineStr">
+      <c r="D148" s="36" t="inlineStr">
         <is>
           <t>Iso-Pb</t>
         </is>
       </c>
-      <c r="E148" s="38" t="inlineStr">
+      <c r="E148" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
@@ -8540,32 +7788,32 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="H148" s="42" t="inlineStr">
+      <c r="H148" s="26" t="inlineStr">
         <is>
           <t>U concentration (for μ = ²³⁸U/²⁰⁴Pb).</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="38" t="n">
+      <c r="A149" s="22" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="39" t="inlineStr">
+      <c r="B149" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C149" s="40" t="inlineStr">
+      <c r="C149" s="24" t="inlineStr">
         <is>
           <t>Th_iso</t>
         </is>
       </c>
-      <c r="D149" s="52" t="inlineStr">
+      <c r="D149" s="36" t="inlineStr">
         <is>
           <t>Iso-Pb</t>
         </is>
       </c>
-      <c r="E149" s="38" t="inlineStr">
+      <c r="E149" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
@@ -8576,128 +7824,128 @@
           <t>3.6</t>
         </is>
       </c>
-      <c r="H149" s="42" t="inlineStr">
+      <c r="H149" s="26" t="inlineStr">
         <is>
           <t>Th concentration (for κ = ²³²Th/²³⁸U).</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="38" t="n">
+      <c r="A150" s="22" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="39" t="inlineStr">
+      <c r="B150" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C150" s="40" t="inlineStr">
+      <c r="C150" s="24" t="inlineStr">
         <is>
           <t>176Hf/177Hf</t>
         </is>
       </c>
-      <c r="D150" s="53" t="inlineStr">
+      <c r="D150" s="37" t="inlineStr">
         <is>
           <t>Iso-Hf</t>
         </is>
       </c>
-      <c r="E150" s="38" t="inlineStr"/>
+      <c r="E150" s="22" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
           <t>0.28298</t>
         </is>
       </c>
-      <c r="H150" s="42" t="inlineStr">
+      <c r="H150" s="26" t="inlineStr">
         <is>
           <t>Measured ¹⁷⁶Hf/¹⁷⁷Hf ratio. CHUR = 0.282785 (Bouvier et al. 2008).</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="38" t="n">
+      <c r="A151" s="22" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="39" t="inlineStr">
+      <c r="B151" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C151" s="40" t="inlineStr">
+      <c r="C151" s="24" t="inlineStr">
         <is>
           <t>176Hf/177Hf_2σ</t>
         </is>
       </c>
-      <c r="D151" s="53" t="inlineStr">
+      <c r="D151" s="37" t="inlineStr">
         <is>
           <t>Iso-Hf</t>
         </is>
       </c>
-      <c r="E151" s="38" t="inlineStr"/>
+      <c r="E151" s="22" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>0.000005</t>
         </is>
       </c>
-      <c r="H151" s="42" t="inlineStr">
+      <c r="H151" s="26" t="inlineStr">
         <is>
           <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="38" t="n">
+      <c r="A152" s="22" t="n">
         <v>151</v>
       </c>
-      <c r="B152" s="39" t="inlineStr">
+      <c r="B152" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C152" s="40" t="inlineStr">
+      <c r="C152" s="24" t="inlineStr">
         <is>
           <t>176Lu/177Hf</t>
         </is>
       </c>
-      <c r="D152" s="53" t="inlineStr">
+      <c r="D152" s="37" t="inlineStr">
         <is>
           <t>Iso-Hf</t>
         </is>
       </c>
-      <c r="E152" s="38" t="inlineStr"/>
+      <c r="E152" s="22" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>0.018</t>
         </is>
       </c>
-      <c r="H152" s="42" t="inlineStr">
+      <c r="H152" s="26" t="inlineStr">
         <is>
           <t>Parent ratio for initial-Hf correction.</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="38" t="n">
+      <c r="A153" s="22" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="39" t="inlineStr">
+      <c r="B153" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C153" s="40" t="inlineStr">
+      <c r="C153" s="24" t="inlineStr">
         <is>
           <t>Hf_iso</t>
         </is>
       </c>
-      <c r="D153" s="53" t="inlineStr">
+      <c r="D153" s="37" t="inlineStr">
         <is>
           <t>Iso-Hf</t>
         </is>
       </c>
-      <c r="E153" s="38" t="inlineStr">
+      <c r="E153" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
@@ -8708,32 +7956,32 @@
           <t>3.85</t>
         </is>
       </c>
-      <c r="H153" s="42" t="inlineStr">
+      <c r="H153" s="26" t="inlineStr">
         <is>
           <t>Hf concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="38" t="n">
+      <c r="A154" s="22" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="39" t="inlineStr">
+      <c r="B154" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C154" s="40" t="inlineStr">
+      <c r="C154" s="24" t="inlineStr">
         <is>
           <t>Lu_iso</t>
         </is>
       </c>
-      <c r="D154" s="53" t="inlineStr">
+      <c r="D154" s="37" t="inlineStr">
         <is>
           <t>Iso-Hf</t>
         </is>
       </c>
-      <c r="E154" s="38" t="inlineStr">
+      <c r="E154" s="22" t="inlineStr">
         <is>
           <t>ppm</t>
         </is>
@@ -8744,60 +7992,60 @@
           <t>0.42</t>
         </is>
       </c>
-      <c r="H154" s="42" t="inlineStr">
+      <c r="H154" s="26" t="inlineStr">
         <is>
           <t>Lu concentration in the isotope aliquot.</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="38" t="n">
+      <c r="A155" s="22" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="39" t="inlineStr">
+      <c r="B155" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C155" s="40" t="inlineStr">
+      <c r="C155" s="24" t="inlineStr">
         <is>
           <t>εHf_initial</t>
         </is>
       </c>
-      <c r="D155" s="53" t="inlineStr">
+      <c r="D155" s="37" t="inlineStr">
         <is>
           <t>Iso-Hf</t>
         </is>
       </c>
-      <c r="E155" s="38" t="inlineStr"/>
+      <c r="E155" s="22" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
-      <c r="H155" s="42" t="inlineStr">
+      <c r="H155" s="26" t="inlineStr">
         <is>
           <t>Computed by B.I.R.D.S.</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="38" t="n">
+      <c r="A156" s="22" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="39" t="inlineStr">
+      <c r="B156" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C156" s="40" t="inlineStr">
+      <c r="C156" s="24" t="inlineStr">
         <is>
           <t>TDM_Hf</t>
         </is>
       </c>
-      <c r="D156" s="53" t="inlineStr">
+      <c r="D156" s="37" t="inlineStr">
         <is>
           <t>Iso-Hf</t>
         </is>
       </c>
-      <c r="E156" s="38" t="inlineStr">
+      <c r="E156" s="22" t="inlineStr">
         <is>
           <t>Ma</t>
         </is>
@@ -8808,128 +8056,128 @@
           <t>1100</t>
         </is>
       </c>
-      <c r="H156" s="42" t="inlineStr">
+      <c r="H156" s="26" t="inlineStr">
         <is>
           <t>Hf depleted-mantle model age.</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="38" t="n">
+      <c r="A157" s="22" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="39" t="inlineStr">
+      <c r="B157" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C157" s="40" t="inlineStr">
+      <c r="C157" s="24" t="inlineStr">
         <is>
           <t>187Os/188Os</t>
         </is>
       </c>
-      <c r="D157" s="54" t="inlineStr">
+      <c r="D157" s="38" t="inlineStr">
         <is>
           <t>Iso-Os</t>
         </is>
       </c>
-      <c r="E157" s="38" t="inlineStr"/>
+      <c r="E157" s="22" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
           <t>0.131</t>
         </is>
       </c>
-      <c r="H157" s="42" t="inlineStr">
+      <c r="H157" s="26" t="inlineStr">
         <is>
           <t>Measured ¹⁸⁷Os/¹⁸⁸Os ratio. Primitive Upper Mantle (PUM) ≈ 0.1296.</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="38" t="n">
+      <c r="A158" s="22" t="n">
         <v>157</v>
       </c>
-      <c r="B158" s="39" t="inlineStr">
+      <c r="B158" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C158" s="40" t="inlineStr">
+      <c r="C158" s="24" t="inlineStr">
         <is>
           <t>187Os/188Os_2σ</t>
         </is>
       </c>
-      <c r="D158" s="54" t="inlineStr">
+      <c r="D158" s="38" t="inlineStr">
         <is>
           <t>Iso-Os</t>
         </is>
       </c>
-      <c r="E158" s="38" t="inlineStr"/>
+      <c r="E158" s="22" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>0.001</t>
         </is>
       </c>
-      <c r="H158" s="42" t="inlineStr">
+      <c r="H158" s="26" t="inlineStr">
         <is>
           <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="38" t="n">
+      <c r="A159" s="22" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="39" t="inlineStr">
+      <c r="B159" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C159" s="40" t="inlineStr">
+      <c r="C159" s="24" t="inlineStr">
         <is>
           <t>187Re/188Os</t>
         </is>
       </c>
-      <c r="D159" s="54" t="inlineStr">
+      <c r="D159" s="38" t="inlineStr">
         <is>
           <t>Iso-Os</t>
         </is>
       </c>
-      <c r="E159" s="38" t="inlineStr"/>
+      <c r="E159" s="22" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="H159" s="42" t="inlineStr">
+      <c r="H159" s="26" t="inlineStr">
         <is>
           <t>Parent ratio for the initial-Os correction.</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="38" t="n">
+      <c r="A160" s="22" t="n">
         <v>159</v>
       </c>
-      <c r="B160" s="39" t="inlineStr">
+      <c r="B160" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C160" s="40" t="inlineStr">
+      <c r="C160" s="24" t="inlineStr">
         <is>
           <t>Os_iso</t>
         </is>
       </c>
-      <c r="D160" s="54" t="inlineStr">
+      <c r="D160" s="38" t="inlineStr">
         <is>
           <t>Iso-Os</t>
         </is>
       </c>
-      <c r="E160" s="38" t="inlineStr">
+      <c r="E160" s="22" t="inlineStr">
         <is>
           <t>ppb</t>
         </is>
@@ -8940,32 +8188,32 @@
           <t>0.45</t>
         </is>
       </c>
-      <c r="H160" s="42" t="inlineStr">
+      <c r="H160" s="26" t="inlineStr">
         <is>
           <t>Os concentration (parts per billion).</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="38" t="n">
+      <c r="A161" s="22" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="39" t="inlineStr">
+      <c r="B161" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C161" s="40" t="inlineStr">
+      <c r="C161" s="24" t="inlineStr">
         <is>
           <t>Re_iso</t>
         </is>
       </c>
-      <c r="D161" s="54" t="inlineStr">
+      <c r="D161" s="38" t="inlineStr">
         <is>
           <t>Iso-Os</t>
         </is>
       </c>
-      <c r="E161" s="38" t="inlineStr">
+      <c r="E161" s="22" t="inlineStr">
         <is>
           <t>ppb</t>
         </is>
@@ -8976,60 +8224,60 @@
           <t>0.18</t>
         </is>
       </c>
-      <c r="H161" s="42" t="inlineStr">
+      <c r="H161" s="26" t="inlineStr">
         <is>
           <t>Re concentration.</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="38" t="n">
+      <c r="A162" s="22" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="39" t="inlineStr">
+      <c r="B162" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C162" s="40" t="inlineStr">
+      <c r="C162" s="24" t="inlineStr">
         <is>
           <t>γOs_initial</t>
         </is>
       </c>
-      <c r="D162" s="54" t="inlineStr">
+      <c r="D162" s="38" t="inlineStr">
         <is>
           <t>Iso-Os</t>
         </is>
       </c>
-      <c r="E162" s="38" t="inlineStr"/>
+      <c r="E162" s="22" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
-      <c r="H162" s="42" t="inlineStr">
+      <c r="H162" s="26" t="inlineStr">
         <is>
           <t>Computed by B.I.R.D.S.</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="38" t="n">
+      <c r="A163" s="22" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="39" t="inlineStr">
+      <c r="B163" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C163" s="40" t="inlineStr">
+      <c r="C163" s="24" t="inlineStr">
         <is>
           <t>δ18O</t>
         </is>
       </c>
-      <c r="D163" s="55" t="inlineStr">
+      <c r="D163" s="39" t="inlineStr">
         <is>
           <t>Iso-Stable</t>
         </is>
       </c>
-      <c r="E163" s="38" t="inlineStr">
+      <c r="E163" s="22" t="inlineStr">
         <is>
           <t>‰ VSMOW</t>
         </is>
@@ -9040,32 +8288,32 @@
           <t>+5.8</t>
         </is>
       </c>
-      <c r="H163" s="42" t="inlineStr">
+      <c r="H163" s="26" t="inlineStr">
         <is>
           <t>Oxygen isotope composition relative to VSMOW. Mantle olivine ≈ +5.2 ‰; crustal sediments commonly &gt;+10 ‰.</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="38" t="n">
+      <c r="A164" s="22" t="n">
         <v>163</v>
       </c>
-      <c r="B164" s="39" t="inlineStr">
+      <c r="B164" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C164" s="40" t="inlineStr">
+      <c r="C164" s="24" t="inlineStr">
         <is>
           <t>δ18O_2σ</t>
         </is>
       </c>
-      <c r="D164" s="55" t="inlineStr">
+      <c r="D164" s="39" t="inlineStr">
         <is>
           <t>Iso-Stable</t>
         </is>
       </c>
-      <c r="E164" s="38" t="inlineStr">
+      <c r="E164" s="22" t="inlineStr">
         <is>
           <t>‰</t>
         </is>
@@ -9076,32 +8324,32 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="H164" s="42" t="inlineStr">
+      <c r="H164" s="26" t="inlineStr">
         <is>
           <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="38" t="n">
+      <c r="A165" s="22" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="39" t="inlineStr">
+      <c r="B165" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C165" s="40" t="inlineStr">
+      <c r="C165" s="24" t="inlineStr">
         <is>
           <t>δD</t>
         </is>
       </c>
-      <c r="D165" s="55" t="inlineStr">
+      <c r="D165" s="39" t="inlineStr">
         <is>
           <t>Iso-Stable</t>
         </is>
       </c>
-      <c r="E165" s="38" t="inlineStr">
+      <c r="E165" s="22" t="inlineStr">
         <is>
           <t>‰ VSMOW</t>
         </is>
@@ -9112,32 +8360,32 @@
           <t>-65</t>
         </is>
       </c>
-      <c r="H165" s="42" t="inlineStr">
+      <c r="H165" s="26" t="inlineStr">
         <is>
           <t>Hydrogen isotope composition relative to VSMOW. Useful for hydrous phases (amphibole, biotite, melt inclusions).</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="38" t="n">
+      <c r="A166" s="22" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="39" t="inlineStr">
+      <c r="B166" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C166" s="40" t="inlineStr">
+      <c r="C166" s="24" t="inlineStr">
         <is>
           <t>δD_2σ</t>
         </is>
       </c>
-      <c r="D166" s="55" t="inlineStr">
+      <c r="D166" s="39" t="inlineStr">
         <is>
           <t>Iso-Stable</t>
         </is>
       </c>
-      <c r="E166" s="38" t="inlineStr">
+      <c r="E166" s="22" t="inlineStr">
         <is>
           <t>‰</t>
         </is>
@@ -9148,32 +8396,32 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H166" s="42" t="inlineStr">
+      <c r="H166" s="26" t="inlineStr">
         <is>
           <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="38" t="n">
+      <c r="A167" s="22" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="39" t="inlineStr">
+      <c r="B167" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C167" s="40" t="inlineStr">
+      <c r="C167" s="24" t="inlineStr">
         <is>
           <t>δ13C</t>
         </is>
       </c>
-      <c r="D167" s="55" t="inlineStr">
+      <c r="D167" s="39" t="inlineStr">
         <is>
           <t>Iso-Stable</t>
         </is>
       </c>
-      <c r="E167" s="38" t="inlineStr">
+      <c r="E167" s="22" t="inlineStr">
         <is>
           <t>‰ VPDB</t>
         </is>
@@ -9184,32 +8432,32 @@
           <t>-6.2</t>
         </is>
       </c>
-      <c r="H167" s="42" t="inlineStr">
+      <c r="H167" s="26" t="inlineStr">
         <is>
           <t>Carbon isotope composition relative to VPDB. Mantle CO₂ ≈ -5 ‰; biogenic carbon strongly negative.</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="38" t="n">
+      <c r="A168" s="22" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="39" t="inlineStr">
+      <c r="B168" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C168" s="40" t="inlineStr">
+      <c r="C168" s="24" t="inlineStr">
         <is>
           <t>δ13C_2σ</t>
         </is>
       </c>
-      <c r="D168" s="55" t="inlineStr">
+      <c r="D168" s="39" t="inlineStr">
         <is>
           <t>Iso-Stable</t>
         </is>
       </c>
-      <c r="E168" s="38" t="inlineStr">
+      <c r="E168" s="22" t="inlineStr">
         <is>
           <t>‰</t>
         </is>
@@ -9220,32 +8468,32 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="H168" s="42" t="inlineStr">
+      <c r="H168" s="26" t="inlineStr">
         <is>
           <t>Analytical 2σ uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="38" t="n">
+      <c r="A169" s="22" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="39" t="inlineStr">
+      <c r="B169" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C169" s="40" t="inlineStr">
+      <c r="C169" s="24" t="inlineStr">
         <is>
           <t>δ11B</t>
         </is>
       </c>
-      <c r="D169" s="55" t="inlineStr">
+      <c r="D169" s="39" t="inlineStr">
         <is>
           <t>Iso-Stable</t>
         </is>
       </c>
-      <c r="E169" s="38" t="inlineStr">
+      <c r="E169" s="22" t="inlineStr">
         <is>
           <t>‰</t>
         </is>
@@ -9256,32 +8504,32 @@
           <t>+3.5</t>
         </is>
       </c>
-      <c r="H169" s="42" t="inlineStr">
+      <c r="H169" s="26" t="inlineStr">
         <is>
           <t>Boron isotope composition. Slab fluids / sediments show very contrasted signatures.</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="38" t="n">
+      <c r="A170" s="22" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="39" t="inlineStr">
+      <c r="B170" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C170" s="40" t="inlineStr">
+      <c r="C170" s="24" t="inlineStr">
         <is>
           <t>Iso_Method</t>
         </is>
       </c>
-      <c r="D170" s="56" t="inlineStr">
+      <c r="D170" s="40" t="inlineStr">
         <is>
           <t>Iso-Meta</t>
         </is>
       </c>
-      <c r="E170" s="38" t="inlineStr"/>
+      <c r="E170" s="22" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>TIMS, MC-ICP-MS, Solution MC-ICP-MS, LA-MC-ICP-MS, SIMS, SHRIMP, N-TIMS (Os), Laser fluorination (δ¹⁸O), EA-IRMS (δ¹³C, δD), CRDS, Mixed</t>
@@ -9292,252 +8540,252 @@
           <t>MC-ICP-MS</t>
         </is>
       </c>
-      <c r="H170" s="42" t="inlineStr">
+      <c r="H170" s="26" t="inlineStr">
         <is>
           <t>Mass-spectrometry technique used for the isotope ratio(s).</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="38" t="n">
+      <c r="A171" s="22" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="39" t="inlineStr">
+      <c r="B171" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C171" s="40" t="inlineStr">
+      <c r="C171" s="24" t="inlineStr">
         <is>
           <t>Iso_Laboratory</t>
         </is>
       </c>
-      <c r="D171" s="56" t="inlineStr">
+      <c r="D171" s="40" t="inlineStr">
         <is>
           <t>Iso-Meta</t>
         </is>
       </c>
-      <c r="E171" s="38" t="inlineStr"/>
+      <c r="E171" s="22" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
           <t>MIT Radiogenic Isotope Lab</t>
         </is>
       </c>
-      <c r="H171" s="42" t="inlineStr">
+      <c r="H171" s="26" t="inlineStr">
         <is>
           <t>Lab where the isotope analysis was carried out.</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="38" t="n">
+      <c r="A172" s="22" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="39" t="inlineStr">
+      <c r="B172" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C172" s="40" t="inlineStr">
+      <c r="C172" s="24" t="inlineStr">
         <is>
           <t>Iso_Date</t>
         </is>
       </c>
-      <c r="D172" s="56" t="inlineStr">
+      <c r="D172" s="40" t="inlineStr">
         <is>
           <t>Iso-Meta</t>
         </is>
       </c>
-      <c r="E172" s="38" t="inlineStr"/>
+      <c r="E172" s="22" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
           <t>2024-03</t>
         </is>
       </c>
-      <c r="H172" s="42" t="inlineStr">
+      <c r="H172" s="26" t="inlineStr">
         <is>
           <t>Year or full date of the isotope analysis.</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="38" t="n">
+      <c r="A173" s="22" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="39" t="inlineStr">
+      <c r="B173" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C173" s="40" t="inlineStr">
+      <c r="C173" s="24" t="inlineStr">
         <is>
           <t>Iso_Analyst</t>
         </is>
       </c>
-      <c r="D173" s="56" t="inlineStr">
+      <c r="D173" s="40" t="inlineStr">
         <is>
           <t>Iso-Meta</t>
         </is>
       </c>
-      <c r="E173" s="38" t="inlineStr"/>
+      <c r="E173" s="22" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
           <t>MLG</t>
         </is>
       </c>
-      <c r="H173" s="42" t="inlineStr">
+      <c r="H173" s="26" t="inlineStr">
         <is>
           <t>Analyst initials or name.</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="38" t="n">
+      <c r="A174" s="22" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="39" t="inlineStr">
+      <c r="B174" s="23" t="inlineStr">
         <is>
           <t>Isotopes</t>
         </is>
       </c>
-      <c r="C174" s="40" t="inlineStr">
+      <c r="C174" s="24" t="inlineStr">
         <is>
           <t>Iso_Notes</t>
         </is>
       </c>
-      <c r="D174" s="56" t="inlineStr">
+      <c r="D174" s="40" t="inlineStr">
         <is>
           <t>Iso-Meta</t>
         </is>
       </c>
-      <c r="E174" s="38" t="inlineStr"/>
+      <c r="E174" s="22" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
-      <c r="H174" s="42" t="inlineStr">
+      <c r="H174" s="26" t="inlineStr">
         <is>
           <t>Free-text notes (column chemistry, spike, repeated measurements, blanks).</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="38" t="n">
+      <c r="A175" s="22" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="39" t="inlineStr">
+      <c r="B175" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C175" s="40" t="inlineStr">
+      <c r="C175" s="24" t="inlineStr">
         <is>
           <t>Sample_Name</t>
         </is>
       </c>
-      <c r="D175" s="41" t="inlineStr">
+      <c r="D175" s="25" t="inlineStr">
         <is>
           <t>Petro-ID</t>
         </is>
       </c>
-      <c r="E175" s="38" t="inlineStr"/>
+      <c r="E175" s="22" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
           <t>VOL-2024-018</t>
         </is>
       </c>
-      <c r="H175" s="42" t="inlineStr">
+      <c r="H175" s="26" t="inlineStr">
         <is>
           <t>Must exactly match the Sample_Name in the Data sheet — this is the key B.I.R.D.S uses to join the modal mineralogy back to the bulk composition.</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="38" t="n">
+      <c r="A176" s="22" t="n">
         <v>175</v>
       </c>
-      <c r="B176" s="39" t="inlineStr">
+      <c r="B176" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C176" s="40" t="inlineStr">
+      <c r="C176" s="24" t="inlineStr">
         <is>
           <t>Sample_Label</t>
         </is>
       </c>
-      <c r="D176" s="41" t="inlineStr">
+      <c r="D176" s="25" t="inlineStr">
         <is>
           <t>Petro-ID</t>
         </is>
       </c>
-      <c r="E176" s="38" t="inlineStr"/>
+      <c r="E176" s="22" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
           <t>Mt. Pico flow 18</t>
         </is>
       </c>
-      <c r="H176" s="42" t="inlineStr">
+      <c r="H176" s="26" t="inlineStr">
         <is>
           <t>Optional friendly label used in plots.  Leave blank to inherit the value from the Data sheet — B.I.R.D.S fills this column automatically at import time.</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="38" t="n">
+      <c r="A177" s="22" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="39" t="inlineStr">
+      <c r="B177" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C177" s="40" t="inlineStr">
+      <c r="C177" s="24" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="D177" s="41" t="inlineStr">
+      <c r="D177" s="25" t="inlineStr">
         <is>
           <t>Petro-ID</t>
         </is>
       </c>
-      <c r="E177" s="38" t="inlineStr"/>
+      <c r="E177" s="22" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
           <t>Lower flow</t>
         </is>
       </c>
-      <c r="H177" s="42" t="inlineStr">
+      <c r="H177" s="26" t="inlineStr">
         <is>
           <t>Optional group used for colouring / legend.  Inherited from the Data sheet at import time if left blank.</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="38" t="n">
+      <c r="A178" s="22" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="39" t="inlineStr">
+      <c r="B178" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C178" s="40" t="inlineStr">
+      <c r="C178" s="24" t="inlineStr">
         <is>
           <t>Texture</t>
         </is>
       </c>
-      <c r="D178" s="41" t="inlineStr">
+      <c r="D178" s="25" t="inlineStr">
         <is>
           <t>Petro-ID</t>
         </is>
       </c>
-      <c r="E178" s="38" t="inlineStr"/>
+      <c r="E178" s="22" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>Phaneritic, Aphanitic, Porphyritic, Glassy, Vesicular, Pyroclastic, Cumulate, Cataclastic, Foliated / Gneissic, Mixed</t>
@@ -9548,32 +8796,32 @@
           <t>Porphyritic</t>
         </is>
       </c>
-      <c r="H178" s="42" t="inlineStr">
+      <c r="H178" s="26" t="inlineStr">
         <is>
           <t>Overall rock fabric. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="38" t="n">
+      <c r="A179" s="22" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="39" t="inlineStr">
+      <c r="B179" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C179" s="40" t="inlineStr">
+      <c r="C179" s="24" t="inlineStr">
         <is>
           <t>Q_mode</t>
         </is>
       </c>
-      <c r="D179" s="57" t="inlineStr">
+      <c r="D179" s="41" t="inlineStr">
         <is>
           <t>Petro-QAPF</t>
         </is>
       </c>
-      <c r="E179" s="38" t="inlineStr">
+      <c r="E179" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -9584,32 +8832,32 @@
           <t>28</t>
         </is>
       </c>
-      <c r="H179" s="42" t="inlineStr">
+      <c r="H179" s="26" t="inlineStr">
         <is>
           <t>Modal Quartz (Q apex of the Streckeisen QAPF diagram).</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="38" t="n">
+      <c r="A180" s="22" t="n">
         <v>179</v>
       </c>
-      <c r="B180" s="39" t="inlineStr">
+      <c r="B180" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C180" s="40" t="inlineStr">
+      <c r="C180" s="24" t="inlineStr">
         <is>
           <t>A_mode</t>
         </is>
       </c>
-      <c r="D180" s="57" t="inlineStr">
+      <c r="D180" s="41" t="inlineStr">
         <is>
           <t>Petro-QAPF</t>
         </is>
       </c>
-      <c r="E180" s="38" t="inlineStr">
+      <c r="E180" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -9620,32 +8868,32 @@
           <t>32</t>
         </is>
       </c>
-      <c r="H180" s="42" t="inlineStr">
+      <c r="H180" s="26" t="inlineStr">
         <is>
           <t>Modal Alkali feldspar (K-feldspar + albite component); A apex of QAPF.</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="38" t="n">
+      <c r="A181" s="22" t="n">
         <v>180</v>
       </c>
-      <c r="B181" s="39" t="inlineStr">
+      <c r="B181" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C181" s="40" t="inlineStr">
+      <c r="C181" s="24" t="inlineStr">
         <is>
           <t>P_mode</t>
         </is>
       </c>
-      <c r="D181" s="57" t="inlineStr">
+      <c r="D181" s="41" t="inlineStr">
         <is>
           <t>Petro-QAPF</t>
         </is>
       </c>
-      <c r="E181" s="38" t="inlineStr">
+      <c r="E181" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -9656,32 +8904,32 @@
           <t>35</t>
         </is>
       </c>
-      <c r="H181" s="42" t="inlineStr">
+      <c r="H181" s="26" t="inlineStr">
         <is>
           <t>Modal Plagioclase (calcic / sodic plagioclase); P apex of QAPF.</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="38" t="n">
+      <c r="A182" s="22" t="n">
         <v>181</v>
       </c>
-      <c r="B182" s="39" t="inlineStr">
+      <c r="B182" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C182" s="40" t="inlineStr">
+      <c r="C182" s="24" t="inlineStr">
         <is>
           <t>F_mode</t>
         </is>
       </c>
-      <c r="D182" s="57" t="inlineStr">
+      <c r="D182" s="41" t="inlineStr">
         <is>
           <t>Petro-QAPF</t>
         </is>
       </c>
-      <c r="E182" s="38" t="inlineStr">
+      <c r="E182" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -9692,32 +8940,32 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H182" s="42" t="inlineStr">
+      <c r="H182" s="26" t="inlineStr">
         <is>
           <t>Modal Feldspathoid (nepheline, leucite, sodalite …); F apex of the bottom QAPF triangle. Mutually exclusive with Q (one rock can't have both).</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="38" t="n">
+      <c r="A183" s="22" t="n">
         <v>182</v>
       </c>
-      <c r="B183" s="39" t="inlineStr">
+      <c r="B183" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C183" s="40" t="inlineStr">
+      <c r="C183" s="24" t="inlineStr">
         <is>
           <t>Ol_mode</t>
         </is>
       </c>
-      <c r="D183" s="53" t="inlineStr">
+      <c r="D183" s="37" t="inlineStr">
         <is>
           <t>Petro-Mafic</t>
         </is>
       </c>
-      <c r="E183" s="38" t="inlineStr">
+      <c r="E183" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -9728,32 +8976,32 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H183" s="42" t="inlineStr">
+      <c r="H183" s="26" t="inlineStr">
         <is>
           <t>Modal Olivine. Ol apex of the gabbro Pl-Px-Ol ternary and of the ultramafic Ol-Opx-Cpx ternary.</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="38" t="n">
+      <c r="A184" s="22" t="n">
         <v>183</v>
       </c>
-      <c r="B184" s="39" t="inlineStr">
+      <c r="B184" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C184" s="40" t="inlineStr">
+      <c r="C184" s="24" t="inlineStr">
         <is>
           <t>Opx_mode</t>
         </is>
       </c>
-      <c r="D184" s="53" t="inlineStr">
+      <c r="D184" s="37" t="inlineStr">
         <is>
           <t>Petro-Mafic</t>
         </is>
       </c>
-      <c r="E184" s="38" t="inlineStr">
+      <c r="E184" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -9764,32 +9012,32 @@
           <t>12</t>
         </is>
       </c>
-      <c r="H184" s="42" t="inlineStr">
+      <c r="H184" s="26" t="inlineStr">
         <is>
           <t>Modal Orthopyroxene (enstatite to ferrosilite). Opx apex of the ultramafic ternary.</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="38" t="n">
+      <c r="A185" s="22" t="n">
         <v>184</v>
       </c>
-      <c r="B185" s="39" t="inlineStr">
+      <c r="B185" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C185" s="40" t="inlineStr">
+      <c r="C185" s="24" t="inlineStr">
         <is>
           <t>Cpx_mode</t>
         </is>
       </c>
-      <c r="D185" s="53" t="inlineStr">
+      <c r="D185" s="37" t="inlineStr">
         <is>
           <t>Petro-Mafic</t>
         </is>
       </c>
-      <c r="E185" s="38" t="inlineStr">
+      <c r="E185" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -9800,64 +9048,64 @@
           <t>8</t>
         </is>
       </c>
-      <c r="H185" s="42" t="inlineStr">
+      <c r="H185" s="26" t="inlineStr">
         <is>
           <t>Modal Clinopyroxene (diopside, augite, pigeonite …). Cpx apex of the ultramafic ternary.</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="38" t="n">
+      <c r="A186" s="22" t="n">
         <v>185</v>
       </c>
-      <c r="B186" s="39" t="inlineStr">
+      <c r="B186" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C186" s="40" t="inlineStr">
+      <c r="C186" s="24" t="inlineStr">
         <is>
           <t>Px_mode</t>
         </is>
       </c>
-      <c r="D186" s="53" t="inlineStr">
+      <c r="D186" s="37" t="inlineStr">
         <is>
           <t>Petro-Mafic</t>
         </is>
       </c>
-      <c r="E186" s="38" t="inlineStr">
+      <c r="E186" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
-      <c r="H186" s="42" t="inlineStr">
+      <c r="H186" s="26" t="inlineStr">
         <is>
           <t>Total pyroxene (Opx + Cpx) used by the gabbro Pl-Px-Ol ternary. Leave empty — B.I.R.D.S sums Opx + Cpx automatically if you fill those.</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="38" t="n">
+      <c r="A187" s="22" t="n">
         <v>186</v>
       </c>
-      <c r="B187" s="39" t="inlineStr">
+      <c r="B187" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C187" s="40" t="inlineStr">
+      <c r="C187" s="24" t="inlineStr">
         <is>
           <t>Amph_mode</t>
         </is>
       </c>
-      <c r="D187" s="53" t="inlineStr">
+      <c r="D187" s="37" t="inlineStr">
         <is>
           <t>Petro-Mafic</t>
         </is>
       </c>
-      <c r="E187" s="38" t="inlineStr">
+      <c r="E187" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -9868,32 +9116,32 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H187" s="42" t="inlineStr">
+      <c r="H187" s="26" t="inlineStr">
         <is>
           <t>Modal Amphibole (hornblende, actinolite, kaersutite …). Not used by QAPF but reported for completeness.</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="38" t="n">
+      <c r="A188" s="22" t="n">
         <v>187</v>
       </c>
-      <c r="B188" s="39" t="inlineStr">
+      <c r="B188" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C188" s="40" t="inlineStr">
+      <c r="C188" s="24" t="inlineStr">
         <is>
           <t>Bt_mode</t>
         </is>
       </c>
-      <c r="D188" s="53" t="inlineStr">
+      <c r="D188" s="37" t="inlineStr">
         <is>
           <t>Petro-Mafic</t>
         </is>
       </c>
-      <c r="E188" s="38" t="inlineStr">
+      <c r="E188" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -9904,32 +9152,32 @@
           <t>6</t>
         </is>
       </c>
-      <c r="H188" s="42" t="inlineStr">
+      <c r="H188" s="26" t="inlineStr">
         <is>
           <t>Modal Biotite.</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="38" t="n">
+      <c r="A189" s="22" t="n">
         <v>188</v>
       </c>
-      <c r="B189" s="39" t="inlineStr">
+      <c r="B189" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C189" s="40" t="inlineStr">
+      <c r="C189" s="24" t="inlineStr">
         <is>
           <t>Ms_mode</t>
         </is>
       </c>
-      <c r="D189" s="53" t="inlineStr">
+      <c r="D189" s="37" t="inlineStr">
         <is>
           <t>Petro-Mafic</t>
         </is>
       </c>
-      <c r="E189" s="38" t="inlineStr">
+      <c r="E189" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -9940,32 +9188,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H189" s="42" t="inlineStr">
+      <c r="H189" s="26" t="inlineStr">
         <is>
           <t>Modal Muscovite.</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="38" t="n">
+      <c r="A190" s="22" t="n">
         <v>189</v>
       </c>
-      <c r="B190" s="39" t="inlineStr">
+      <c r="B190" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C190" s="40" t="inlineStr">
+      <c r="C190" s="24" t="inlineStr">
         <is>
           <t>Opaque_mode</t>
         </is>
       </c>
-      <c r="D190" s="54" t="inlineStr">
+      <c r="D190" s="38" t="inlineStr">
         <is>
           <t>Petro-Acc</t>
         </is>
       </c>
-      <c r="E190" s="38" t="inlineStr">
+      <c r="E190" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -9976,32 +9224,32 @@
           <t>1.5</t>
         </is>
       </c>
-      <c r="H190" s="42" t="inlineStr">
+      <c r="H190" s="26" t="inlineStr">
         <is>
           <t>Modal Fe-Ti oxides (magnetite, ilmenite, hematite, chromite).</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="38" t="n">
+      <c r="A191" s="22" t="n">
         <v>190</v>
       </c>
-      <c r="B191" s="39" t="inlineStr">
+      <c r="B191" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C191" s="40" t="inlineStr">
+      <c r="C191" s="24" t="inlineStr">
         <is>
           <t>Apatite_mode</t>
         </is>
       </c>
-      <c r="D191" s="54" t="inlineStr">
+      <c r="D191" s="38" t="inlineStr">
         <is>
           <t>Petro-Acc</t>
         </is>
       </c>
-      <c r="E191" s="38" t="inlineStr">
+      <c r="E191" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10012,32 +9260,32 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="H191" s="42" t="inlineStr">
+      <c r="H191" s="26" t="inlineStr">
         <is>
           <t>Modal Apatite.</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="38" t="n">
+      <c r="A192" s="22" t="n">
         <v>191</v>
       </c>
-      <c r="B192" s="39" t="inlineStr">
+      <c r="B192" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C192" s="40" t="inlineStr">
+      <c r="C192" s="24" t="inlineStr">
         <is>
           <t>Zircon_mode</t>
         </is>
       </c>
-      <c r="D192" s="54" t="inlineStr">
+      <c r="D192" s="38" t="inlineStr">
         <is>
           <t>Petro-Acc</t>
         </is>
       </c>
-      <c r="E192" s="38" t="inlineStr">
+      <c r="E192" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10048,32 +9296,32 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="H192" s="42" t="inlineStr">
+      <c r="H192" s="26" t="inlineStr">
         <is>
           <t>Modal Zircon.</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="38" t="n">
+      <c r="A193" s="22" t="n">
         <v>192</v>
       </c>
-      <c r="B193" s="39" t="inlineStr">
+      <c r="B193" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C193" s="40" t="inlineStr">
+      <c r="C193" s="24" t="inlineStr">
         <is>
           <t>Titanite_mode</t>
         </is>
       </c>
-      <c r="D193" s="54" t="inlineStr">
+      <c r="D193" s="38" t="inlineStr">
         <is>
           <t>Petro-Acc</t>
         </is>
       </c>
-      <c r="E193" s="38" t="inlineStr">
+      <c r="E193" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10084,32 +9332,32 @@
           <t>0.2</t>
         </is>
       </c>
-      <c r="H193" s="42" t="inlineStr">
+      <c r="H193" s="26" t="inlineStr">
         <is>
           <t>Modal Titanite / sphene.</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="38" t="n">
+      <c r="A194" s="22" t="n">
         <v>193</v>
       </c>
-      <c r="B194" s="39" t="inlineStr">
+      <c r="B194" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C194" s="40" t="inlineStr">
+      <c r="C194" s="24" t="inlineStr">
         <is>
           <t>Carbonate_mode</t>
         </is>
       </c>
-      <c r="D194" s="54" t="inlineStr">
+      <c r="D194" s="38" t="inlineStr">
         <is>
           <t>Petro-Acc</t>
         </is>
       </c>
-      <c r="E194" s="38" t="inlineStr">
+      <c r="E194" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10120,32 +9368,32 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H194" s="42" t="inlineStr">
+      <c r="H194" s="26" t="inlineStr">
         <is>
           <t>Modal Calcite, dolomite, ankerite (esp. in alteration / carbonatites).</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="38" t="n">
+      <c r="A195" s="22" t="n">
         <v>194</v>
       </c>
-      <c r="B195" s="39" t="inlineStr">
+      <c r="B195" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C195" s="40" t="inlineStr">
+      <c r="C195" s="24" t="inlineStr">
         <is>
           <t>Other_acc_mode</t>
         </is>
       </c>
-      <c r="D195" s="54" t="inlineStr">
+      <c r="D195" s="38" t="inlineStr">
         <is>
           <t>Petro-Acc</t>
         </is>
       </c>
-      <c r="E195" s="38" t="inlineStr">
+      <c r="E195" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10156,64 +9404,64 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="H195" s="42" t="inlineStr">
+      <c r="H195" s="26" t="inlineStr">
         <is>
           <t>Modal other accessories (epidote, chlorite, sericite, garnet, tourmaline, monazite, …).</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="38" t="n">
+      <c r="A196" s="22" t="n">
         <v>195</v>
       </c>
-      <c r="B196" s="39" t="inlineStr">
+      <c r="B196" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C196" s="40" t="inlineStr">
+      <c r="C196" s="24" t="inlineStr">
         <is>
           <t>Mode_Total</t>
         </is>
       </c>
-      <c r="D196" s="54" t="inlineStr">
+      <c r="D196" s="38" t="inlineStr">
         <is>
           <t>Petro-Acc</t>
         </is>
       </c>
-      <c r="E196" s="38" t="inlineStr">
+      <c r="E196" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
-      <c r="H196" s="42" t="inlineStr">
+      <c r="H196" s="26" t="inlineStr">
         <is>
           <t>Quality-control sum of every modal column above. Should fall between 99 and 101 vol %.</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="38" t="n">
+      <c r="A197" s="22" t="n">
         <v>196</v>
       </c>
-      <c r="B197" s="39" t="inlineStr">
+      <c r="B197" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C197" s="40" t="inlineStr">
+      <c r="C197" s="24" t="inlineStr">
         <is>
           <t>Crystal_pct</t>
         </is>
       </c>
-      <c r="D197" s="55" t="inlineStr">
+      <c r="D197" s="39" t="inlineStr">
         <is>
           <t>Petro-Tuff</t>
         </is>
       </c>
-      <c r="E197" s="38" t="inlineStr">
+      <c r="E197" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10224,32 +9472,32 @@
           <t>30</t>
         </is>
       </c>
-      <c r="H197" s="42" t="inlineStr">
+      <c r="H197" s="26" t="inlineStr">
         <is>
           <t>Crystal fragments — Crystal apex of the IUGS tuff ternary (Schmid 1981).</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="38" t="n">
+      <c r="A198" s="22" t="n">
         <v>197</v>
       </c>
-      <c r="B198" s="39" t="inlineStr">
+      <c r="B198" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C198" s="40" t="inlineStr">
+      <c r="C198" s="24" t="inlineStr">
         <is>
           <t>Vitric_pct</t>
         </is>
       </c>
-      <c r="D198" s="55" t="inlineStr">
+      <c r="D198" s="39" t="inlineStr">
         <is>
           <t>Petro-Tuff</t>
         </is>
       </c>
-      <c r="E198" s="38" t="inlineStr">
+      <c r="E198" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10260,32 +9508,32 @@
           <t>55</t>
         </is>
       </c>
-      <c r="H198" s="42" t="inlineStr">
+      <c r="H198" s="26" t="inlineStr">
         <is>
           <t>Glass shards / pumice fragments — Vitric apex.</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="38" t="n">
+      <c r="A199" s="22" t="n">
         <v>198</v>
       </c>
-      <c r="B199" s="39" t="inlineStr">
+      <c r="B199" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C199" s="40" t="inlineStr">
+      <c r="C199" s="24" t="inlineStr">
         <is>
           <t>Lithic_pct</t>
         </is>
       </c>
-      <c r="D199" s="55" t="inlineStr">
+      <c r="D199" s="39" t="inlineStr">
         <is>
           <t>Petro-Tuff</t>
         </is>
       </c>
-      <c r="E199" s="38" t="inlineStr">
+      <c r="E199" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10296,32 +9544,32 @@
           <t>15</t>
         </is>
       </c>
-      <c r="H199" s="42" t="inlineStr">
+      <c r="H199" s="26" t="inlineStr">
         <is>
           <t>Lithic / rock fragments — Lithic apex.</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="38" t="n">
+      <c r="A200" s="22" t="n">
         <v>199</v>
       </c>
-      <c r="B200" s="39" t="inlineStr">
+      <c r="B200" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C200" s="40" t="inlineStr">
+      <c r="C200" s="24" t="inlineStr">
         <is>
           <t>Pyroclast_size</t>
         </is>
       </c>
-      <c r="D200" s="55" t="inlineStr">
+      <c r="D200" s="39" t="inlineStr">
         <is>
           <t>Petro-Tuff</t>
         </is>
       </c>
-      <c r="E200" s="38" t="inlineStr"/>
+      <c r="E200" s="22" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>Ash (&lt; 2 mm), Lapilli (2-64 mm), Block / Bomb (&gt; 64 mm), Mixed</t>
@@ -10332,32 +9580,32 @@
           <t>Lapilli (2-64 mm)</t>
         </is>
       </c>
-      <c r="H200" s="42" t="inlineStr">
+      <c r="H200" s="26" t="inlineStr">
         <is>
           <t>Granulometric class. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="38" t="n">
+      <c r="A201" s="22" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="39" t="inlineStr">
+      <c r="B201" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C201" s="40" t="inlineStr">
+      <c r="C201" s="24" t="inlineStr">
         <is>
           <t>Blocks_bombs_pct</t>
         </is>
       </c>
-      <c r="D201" s="55" t="inlineStr">
+      <c r="D201" s="39" t="inlineStr">
         <is>
           <t>Petro-Tuff</t>
         </is>
       </c>
-      <c r="E201" s="38" t="inlineStr">
+      <c r="E201" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10368,32 +9616,32 @@
           <t>10</t>
         </is>
       </c>
-      <c r="H201" s="42" t="inlineStr">
+      <c r="H201" s="26" t="inlineStr">
         <is>
           <t>Blocks and bombs, fragments over 64 mm — top apex of Fisher's (1966) fragment-size ternary.</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="38" t="n">
+      <c r="A202" s="22" t="n">
         <v>201</v>
       </c>
-      <c r="B202" s="39" t="inlineStr">
+      <c r="B202" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C202" s="40" t="inlineStr">
+      <c r="C202" s="24" t="inlineStr">
         <is>
           <t>Lapilli_pct</t>
         </is>
       </c>
-      <c r="D202" s="55" t="inlineStr">
+      <c r="D202" s="39" t="inlineStr">
         <is>
           <t>Petro-Tuff</t>
         </is>
       </c>
-      <c r="E202" s="38" t="inlineStr">
+      <c r="E202" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10404,32 +9652,32 @@
           <t>35</t>
         </is>
       </c>
-      <c r="H202" s="42" t="inlineStr">
+      <c r="H202" s="26" t="inlineStr">
         <is>
           <t>Lapilli, fragments of 2-64 mm — left apex.</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="38" t="n">
+      <c r="A203" s="22" t="n">
         <v>202</v>
       </c>
-      <c r="B203" s="39" t="inlineStr">
+      <c r="B203" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C203" s="40" t="inlineStr">
+      <c r="C203" s="24" t="inlineStr">
         <is>
           <t>Ash_pct</t>
         </is>
       </c>
-      <c r="D203" s="55" t="inlineStr">
+      <c r="D203" s="39" t="inlineStr">
         <is>
           <t>Petro-Tuff</t>
         </is>
       </c>
-      <c r="E203" s="38" t="inlineStr">
+      <c r="E203" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10440,32 +9688,32 @@
           <t>55</t>
         </is>
       </c>
-      <c r="H203" s="42" t="inlineStr">
+      <c r="H203" s="26" t="inlineStr">
         <is>
           <t>Ash, fragments under 2 mm — right apex.</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="38" t="n">
+      <c r="A204" s="22" t="n">
         <v>203</v>
       </c>
-      <c r="B204" s="39" t="inlineStr">
+      <c r="B204" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C204" s="40" t="inlineStr">
+      <c r="C204" s="24" t="inlineStr">
         <is>
           <t>Grain_size_mm</t>
         </is>
       </c>
-      <c r="D204" s="45" t="inlineStr">
+      <c r="D204" s="29" t="inlineStr">
         <is>
           <t>Petro-Texture</t>
         </is>
       </c>
-      <c r="E204" s="38" t="inlineStr">
+      <c r="E204" s="22" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
@@ -10476,32 +9724,32 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="H204" s="42" t="inlineStr">
+      <c r="H204" s="26" t="inlineStr">
         <is>
           <t>Average grain size (groundmass for porphyritic rocks).</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="38" t="n">
+      <c r="A205" s="22" t="n">
         <v>204</v>
       </c>
-      <c r="B205" s="39" t="inlineStr">
+      <c r="B205" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C205" s="40" t="inlineStr">
+      <c r="C205" s="24" t="inlineStr">
         <is>
           <t>Phenocryst_pct</t>
         </is>
       </c>
-      <c r="D205" s="45" t="inlineStr">
+      <c r="D205" s="29" t="inlineStr">
         <is>
           <t>Petro-Texture</t>
         </is>
       </c>
-      <c r="E205" s="38" t="inlineStr">
+      <c r="E205" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10512,32 +9760,32 @@
           <t>12</t>
         </is>
       </c>
-      <c r="H205" s="42" t="inlineStr">
+      <c r="H205" s="26" t="inlineStr">
         <is>
           <t>Total phenocryst content (porphyritic rocks).</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="38" t="n">
+      <c r="A206" s="22" t="n">
         <v>205</v>
       </c>
-      <c r="B206" s="39" t="inlineStr">
+      <c r="B206" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C206" s="40" t="inlineStr">
+      <c r="C206" s="24" t="inlineStr">
         <is>
           <t>Vesicle_pct</t>
         </is>
       </c>
-      <c r="D206" s="45" t="inlineStr">
+      <c r="D206" s="29" t="inlineStr">
         <is>
           <t>Petro-Texture</t>
         </is>
       </c>
-      <c r="E206" s="38" t="inlineStr">
+      <c r="E206" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10548,32 +9796,32 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H206" s="42" t="inlineStr">
+      <c r="H206" s="26" t="inlineStr">
         <is>
           <t>Vesicle / vug content.</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="38" t="n">
+      <c r="A207" s="22" t="n">
         <v>206</v>
       </c>
-      <c r="B207" s="39" t="inlineStr">
+      <c r="B207" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C207" s="40" t="inlineStr">
+      <c r="C207" s="24" t="inlineStr">
         <is>
           <t>Alteration_pct</t>
         </is>
       </c>
-      <c r="D207" s="45" t="inlineStr">
+      <c r="D207" s="29" t="inlineStr">
         <is>
           <t>Petro-Texture</t>
         </is>
       </c>
-      <c r="E207" s="38" t="inlineStr">
+      <c r="E207" s="22" t="inlineStr">
         <is>
           <t>vol %</t>
         </is>
@@ -10584,64 +9832,64 @@
           <t>8</t>
         </is>
       </c>
-      <c r="H207" s="42" t="inlineStr">
+      <c r="H207" s="26" t="inlineStr">
         <is>
           <t>Secondary minerals / alteration overprint (sericite, chlorite, clay …).</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="38" t="n">
+      <c r="A208" s="22" t="n">
         <v>207</v>
       </c>
-      <c r="B208" s="39" t="inlineStr">
+      <c r="B208" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C208" s="40" t="inlineStr">
+      <c r="C208" s="24" t="inlineStr">
         <is>
           <t>Texture_notes</t>
         </is>
       </c>
-      <c r="D208" s="45" t="inlineStr">
+      <c r="D208" s="29" t="inlineStr">
         <is>
           <t>Petro-Texture</t>
         </is>
       </c>
-      <c r="E208" s="38" t="inlineStr"/>
+      <c r="E208" s="22" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>Plg zoned; Cpx with sieve texture</t>
         </is>
       </c>
-      <c r="H208" s="42" t="inlineStr">
+      <c r="H208" s="26" t="inlineStr">
         <is>
           <t>Free-text observations (zoning, reaction rims, embayments, cumulate textures, mineral assemblage).</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="38" t="n">
+      <c r="A209" s="22" t="n">
         <v>208</v>
       </c>
-      <c r="B209" s="39" t="inlineStr">
+      <c r="B209" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C209" s="40" t="inlineStr">
+      <c r="C209" s="24" t="inlineStr">
         <is>
           <t>Microscope_method</t>
         </is>
       </c>
-      <c r="D209" s="56" t="inlineStr">
+      <c r="D209" s="40" t="inlineStr">
         <is>
           <t>Petro-Meta</t>
         </is>
       </c>
-      <c r="E209" s="38" t="inlineStr"/>
+      <c r="E209" s="22" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
           <t>Point-count (≥ 300 points), Point-count (100-300 points), Visual estimate, Modal calculation (CIPW), Image analysis (software), SEM-EDS / EBSD, Mixed</t>
@@ -10652,131 +9900,131 @@
           <t>Point-count (≥ 300 points)</t>
         </is>
       </c>
-      <c r="H209" s="42" t="inlineStr">
+      <c r="H209" s="26" t="inlineStr">
         <is>
           <t>How the modal proportions were obtained.</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="38" t="n">
+      <c r="A210" s="22" t="n">
         <v>209</v>
       </c>
-      <c r="B210" s="39" t="inlineStr">
+      <c r="B210" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C210" s="40" t="inlineStr">
+      <c r="C210" s="24" t="inlineStr">
         <is>
           <t>Microscope_lab</t>
         </is>
       </c>
-      <c r="D210" s="56" t="inlineStr">
+      <c r="D210" s="40" t="inlineStr">
         <is>
           <t>Petro-Meta</t>
         </is>
       </c>
-      <c r="E210" s="38" t="inlineStr"/>
+      <c r="E210" s="22" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
           <t>UNAM — Petrology lab</t>
         </is>
       </c>
-      <c r="H210" s="42" t="inlineStr">
+      <c r="H210" s="26" t="inlineStr">
         <is>
           <t>Lab / university where the thin section was studied.</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="38" t="n">
+      <c r="A211" s="22" t="n">
         <v>210</v>
       </c>
-      <c r="B211" s="39" t="inlineStr">
+      <c r="B211" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C211" s="40" t="inlineStr">
+      <c r="C211" s="24" t="inlineStr">
         <is>
           <t>Petrography_date</t>
         </is>
       </c>
-      <c r="D211" s="56" t="inlineStr">
+      <c r="D211" s="40" t="inlineStr">
         <is>
           <t>Petro-Meta</t>
         </is>
       </c>
-      <c r="E211" s="38" t="inlineStr"/>
+      <c r="E211" s="22" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
           <t>2024-04</t>
         </is>
       </c>
-      <c r="H211" s="42" t="inlineStr">
+      <c r="H211" s="26" t="inlineStr">
         <is>
           <t>Year / date of the petrographic analysis (YYYY or YYYY-MM-DD).</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="38" t="n">
+      <c r="A212" s="22" t="n">
         <v>211</v>
       </c>
-      <c r="B212" s="39" t="inlineStr">
+      <c r="B212" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C212" s="40" t="inlineStr">
+      <c r="C212" s="24" t="inlineStr">
         <is>
           <t>Petrographer</t>
         </is>
       </c>
-      <c r="D212" s="56" t="inlineStr">
+      <c r="D212" s="40" t="inlineStr">
         <is>
           <t>Petro-Meta</t>
         </is>
       </c>
-      <c r="E212" s="38" t="inlineStr"/>
+      <c r="E212" s="22" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
           <t>MDC</t>
         </is>
       </c>
-      <c r="H212" s="42" t="inlineStr">
+      <c r="H212" s="26" t="inlineStr">
         <is>
           <t>Analyst initials or name.</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="38" t="n">
+      <c r="A213" s="22" t="n">
         <v>212</v>
       </c>
-      <c r="B213" s="39" t="inlineStr">
+      <c r="B213" s="23" t="inlineStr">
         <is>
           <t>Petrography</t>
         </is>
       </c>
-      <c r="C213" s="40" t="inlineStr">
+      <c r="C213" s="24" t="inlineStr">
         <is>
           <t>Petrography_notes</t>
         </is>
       </c>
-      <c r="D213" s="56" t="inlineStr">
+      <c r="D213" s="40" t="inlineStr">
         <is>
           <t>Petro-Meta</t>
         </is>
       </c>
-      <c r="E213" s="38" t="inlineStr"/>
+      <c r="E213" s="22" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
-      <c r="H213" s="42" t="inlineStr">
+      <c r="H213" s="26" t="inlineStr">
         <is>
           <t>Free-text notes (sample preservation, mounting, staining for K-feldspar, etc.).</t>
         </is>
